--- a/FORMATO.xlsx
+++ b/FORMATO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dairon Alonso\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dairon Alonso\Desktop\App Streamlit-Prediccion\Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3C2ABC-E18A-4741-83E8-665595AB1AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA28E021-3B42-4FA3-8AB2-7B4AAF958B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B5783570-885C-42E9-BB81-08046124F7B7}"/>
+    <workbookView xWindow="22932" yWindow="6240" windowWidth="23256" windowHeight="12456" xr2:uid="{B5783570-885C-42E9-BB81-08046124F7B7}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO" sheetId="1" r:id="rId1"/>
@@ -217,15 +217,6 @@
     <t>AGR 4</t>
   </si>
   <si>
-    <t xml:space="preserve">      REQUIERE ALGÚN TIPO DE TRANSPORTE PROPIO</t>
-  </si>
-  <si>
-    <t>MOTO</t>
-  </si>
-  <si>
-    <t>VEHÍCULO</t>
-  </si>
-  <si>
     <t>AUXILIO</t>
   </si>
   <si>
@@ -408,6 +399,15 @@
   </si>
   <si>
     <t>EL PROFESIONAL SELECCIONADO REQUIERE EXAMENES DE INGRESO ESPECIALIZADOS?</t>
+  </si>
+  <si>
+    <t>AÑOS DE EXPERIENCIA</t>
+  </si>
+  <si>
+    <t>CONDICIÓN DE SALARIO</t>
+  </si>
+  <si>
+    <t>REQUIERE ALGÚN TIPO DE TRANSPORTE PROPIO (Tener en cuenta que el uso de Vehiculo genera un costo adicional por EPPs y Examenes Ocupacionales- Y otras responsabilidades para PGR)</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1146,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="199">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1378,6 +1378,12 @@
     <xf numFmtId="1" fontId="8" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1480,15 +1486,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1713,6 +1716,33 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2059,9 +2089,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="13.5" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="51" customWidth="1"/>
-    <col min="2" max="2" width="3.42578125" style="33" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="33" customWidth="1"/>
     <col min="3" max="3" width="3.5703125" style="33" customWidth="1"/>
-    <col min="4" max="4" width="3.85546875" style="33" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" style="33" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" style="33" customWidth="1"/>
     <col min="6" max="6" width="3.85546875" style="33" customWidth="1"/>
     <col min="7" max="7" width="5.28515625" style="33" customWidth="1"/>
@@ -2072,7 +2102,7 @@
     <col min="12" max="12" width="3.5703125" style="33" customWidth="1"/>
     <col min="13" max="13" width="5.42578125" style="33" customWidth="1"/>
     <col min="14" max="14" width="3.42578125" style="33" customWidth="1"/>
-    <col min="15" max="15" width="25.140625" style="33" customWidth="1"/>
+    <col min="15" max="15" width="30.7109375" style="33" customWidth="1"/>
     <col min="16" max="16" width="6.7109375" style="33" customWidth="1"/>
     <col min="17" max="17" width="5.85546875" style="33" customWidth="1"/>
     <col min="18" max="18" width="9.7109375" style="33" customWidth="1"/>
@@ -2426,109 +2456,109 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="88" t="s">
+      <c r="P1" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="88"/>
-      <c r="R1" s="88"/>
-      <c r="S1" s="88"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="88"/>
-      <c r="V1" s="88"/>
-      <c r="W1" s="88"/>
-      <c r="X1" s="88"/>
-      <c r="Y1" s="88"/>
-      <c r="Z1" s="88"/>
-      <c r="AA1" s="88"/>
-      <c r="AB1" s="88"/>
-      <c r="AC1" s="88"/>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="88"/>
-      <c r="AF1" s="88"/>
-      <c r="AG1" s="88"/>
-      <c r="AH1" s="88"/>
-      <c r="AI1" s="88"/>
-      <c r="AJ1" s="88"/>
+      <c r="Q1" s="90"/>
+      <c r="R1" s="90"/>
+      <c r="S1" s="90"/>
+      <c r="T1" s="90"/>
+      <c r="U1" s="90"/>
+      <c r="V1" s="90"/>
+      <c r="W1" s="90"/>
+      <c r="X1" s="90"/>
+      <c r="Y1" s="90"/>
+      <c r="Z1" s="90"/>
+      <c r="AA1" s="90"/>
+      <c r="AB1" s="90"/>
+      <c r="AC1" s="90"/>
+      <c r="AD1" s="90"/>
+      <c r="AE1" s="90"/>
+      <c r="AF1" s="90"/>
+      <c r="AG1" s="90"/>
+      <c r="AH1" s="90"/>
+      <c r="AI1" s="90"/>
+      <c r="AJ1" s="90"/>
       <c r="AK1" s="6"/>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="87"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
       <c r="N2" s="64"/>
       <c r="O2" s="64"/>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="87"/>
-      <c r="R2" s="87"/>
-      <c r="S2" s="87"/>
-      <c r="T2" s="87"/>
-      <c r="U2" s="87"/>
-      <c r="V2" s="87"/>
-      <c r="W2" s="87"/>
-      <c r="X2" s="87"/>
-      <c r="Y2" s="87"/>
-      <c r="Z2" s="87"/>
-      <c r="AA2" s="87"/>
-      <c r="AB2" s="87"/>
-      <c r="AC2" s="87"/>
-      <c r="AD2" s="87"/>
-      <c r="AE2" s="87"/>
-      <c r="AF2" s="87"/>
-      <c r="AG2" s="87"/>
-      <c r="AH2" s="87"/>
-      <c r="AI2" s="87"/>
-      <c r="AJ2" s="87"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
+      <c r="W2" s="89"/>
+      <c r="X2" s="89"/>
+      <c r="Y2" s="89"/>
+      <c r="Z2" s="89"/>
+      <c r="AA2" s="89"/>
+      <c r="AB2" s="89"/>
+      <c r="AC2" s="89"/>
+      <c r="AD2" s="89"/>
+      <c r="AE2" s="89"/>
+      <c r="AF2" s="89"/>
+      <c r="AG2" s="89"/>
+      <c r="AH2" s="89"/>
+      <c r="AI2" s="89"/>
+      <c r="AJ2" s="89"/>
       <c r="AK2" s="8"/>
     </row>
     <row r="3" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="47"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
+      <c r="J3" s="89"/>
+      <c r="K3" s="89"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
       <c r="N3" s="64"/>
       <c r="O3" s="64"/>
-      <c r="P3" s="87" t="s">
+      <c r="P3" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="87"/>
-      <c r="R3" s="87"/>
-      <c r="S3" s="87"/>
-      <c r="T3" s="87"/>
-      <c r="U3" s="87"/>
-      <c r="V3" s="87"/>
-      <c r="W3" s="87"/>
-      <c r="X3" s="87"/>
-      <c r="Y3" s="87"/>
-      <c r="Z3" s="87"/>
-      <c r="AA3" s="87"/>
-      <c r="AB3" s="87"/>
-      <c r="AC3" s="87"/>
-      <c r="AD3" s="87"/>
-      <c r="AE3" s="87"/>
-      <c r="AF3" s="87"/>
-      <c r="AG3" s="87"/>
-      <c r="AH3" s="87"/>
-      <c r="AI3" s="87"/>
-      <c r="AJ3" s="87"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="W3" s="89"/>
+      <c r="X3" s="89"/>
+      <c r="Y3" s="89"/>
+      <c r="Z3" s="89"/>
+      <c r="AA3" s="89"/>
+      <c r="AB3" s="89"/>
+      <c r="AC3" s="89"/>
+      <c r="AD3" s="89"/>
+      <c r="AE3" s="89"/>
+      <c r="AF3" s="89"/>
+      <c r="AG3" s="89"/>
+      <c r="AH3" s="89"/>
+      <c r="AI3" s="89"/>
+      <c r="AJ3" s="89"/>
       <c r="AK3" s="8"/>
     </row>
     <row r="4" spans="1:37" s="2" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -2547,27 +2577,27 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
-      <c r="P4" s="89"/>
-      <c r="Q4" s="89"/>
-      <c r="R4" s="89"/>
-      <c r="S4" s="89"/>
-      <c r="T4" s="89"/>
-      <c r="U4" s="89"/>
-      <c r="V4" s="89"/>
-      <c r="W4" s="89"/>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="89"/>
-      <c r="Z4" s="89"/>
-      <c r="AA4" s="89"/>
-      <c r="AB4" s="89"/>
-      <c r="AC4" s="89"/>
-      <c r="AD4" s="89"/>
-      <c r="AE4" s="89"/>
-      <c r="AF4" s="89"/>
-      <c r="AG4" s="89"/>
-      <c r="AH4" s="89"/>
-      <c r="AI4" s="89"/>
-      <c r="AJ4" s="89"/>
+      <c r="P4" s="91"/>
+      <c r="Q4" s="91"/>
+      <c r="R4" s="91"/>
+      <c r="S4" s="91"/>
+      <c r="T4" s="91"/>
+      <c r="U4" s="91"/>
+      <c r="V4" s="91"/>
+      <c r="W4" s="91"/>
+      <c r="X4" s="91"/>
+      <c r="Y4" s="91"/>
+      <c r="Z4" s="91"/>
+      <c r="AA4" s="91"/>
+      <c r="AB4" s="91"/>
+      <c r="AC4" s="91"/>
+      <c r="AD4" s="91"/>
+      <c r="AE4" s="91"/>
+      <c r="AF4" s="91"/>
+      <c r="AG4" s="91"/>
+      <c r="AH4" s="91"/>
+      <c r="AI4" s="91"/>
+      <c r="AJ4" s="91"/>
       <c r="AK4" s="10"/>
     </row>
     <row r="5" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2576,75 +2606,75 @@
       <c r="AK5" s="8"/>
     </row>
     <row r="6" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="93"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="93"/>
-      <c r="O6" s="93"/>
-      <c r="P6" s="93"/>
-      <c r="Q6" s="93"/>
-      <c r="R6" s="93"/>
-      <c r="S6" s="93"/>
-      <c r="T6" s="93"/>
-      <c r="U6" s="93"/>
-      <c r="V6" s="93"/>
-      <c r="W6" s="93"/>
-      <c r="X6" s="93"/>
-      <c r="Y6" s="93"/>
-      <c r="Z6" s="93"/>
-      <c r="AA6" s="93"/>
-      <c r="AB6" s="93"/>
-      <c r="AC6" s="93"/>
-      <c r="AD6" s="93"/>
-      <c r="AE6" s="93"/>
-      <c r="AF6" s="93"/>
-      <c r="AG6" s="93"/>
-      <c r="AH6" s="93"/>
-      <c r="AI6" s="93"/>
-      <c r="AJ6" s="93"/>
-      <c r="AK6" s="94"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="95"/>
+      <c r="L6" s="95"/>
+      <c r="M6" s="95"/>
+      <c r="N6" s="95"/>
+      <c r="O6" s="95"/>
+      <c r="P6" s="95"/>
+      <c r="Q6" s="95"/>
+      <c r="R6" s="95"/>
+      <c r="S6" s="95"/>
+      <c r="T6" s="95"/>
+      <c r="U6" s="95"/>
+      <c r="V6" s="95"/>
+      <c r="W6" s="95"/>
+      <c r="X6" s="95"/>
+      <c r="Y6" s="95"/>
+      <c r="Z6" s="95"/>
+      <c r="AA6" s="95"/>
+      <c r="AB6" s="95"/>
+      <c r="AC6" s="95"/>
+      <c r="AD6" s="95"/>
+      <c r="AE6" s="95"/>
+      <c r="AF6" s="95"/>
+      <c r="AG6" s="95"/>
+      <c r="AH6" s="95"/>
+      <c r="AI6" s="95"/>
+      <c r="AJ6" s="95"/>
+      <c r="AK6" s="96"/>
     </row>
     <row r="7" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="47"/>
       <c r="AK7" s="8"/>
     </row>
     <row r="8" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="90" t="s">
+      <c r="A8" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="91"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="91"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="112"/>
-      <c r="L8" s="112"/>
-      <c r="M8" s="112"/>
-      <c r="N8" s="112"/>
-      <c r="O8" s="112"/>
-      <c r="R8" s="91" t="s">
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="114"/>
+      <c r="G8" s="114"/>
+      <c r="H8" s="114"/>
+      <c r="I8" s="114"/>
+      <c r="J8" s="114"/>
+      <c r="K8" s="114"/>
+      <c r="L8" s="114"/>
+      <c r="M8" s="114"/>
+      <c r="N8" s="114"/>
+      <c r="O8" s="114"/>
+      <c r="R8" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="S8" s="91"/>
-      <c r="T8" s="91"/>
-      <c r="U8" s="91"/>
-      <c r="V8" s="91"/>
+      <c r="S8" s="93"/>
+      <c r="T8" s="93"/>
+      <c r="U8" s="93"/>
+      <c r="V8" s="93"/>
       <c r="X8" s="2" t="s">
         <v>5</v>
       </c>
@@ -2676,26 +2706,26 @@
       <c r="L10" s="43"/>
       <c r="M10" s="43"/>
       <c r="N10" s="43"/>
-      <c r="P10" s="111"/>
-      <c r="Q10" s="111"/>
-      <c r="R10" s="111"/>
-      <c r="S10" s="111"/>
-      <c r="T10" s="111"/>
-      <c r="U10" s="111"/>
-      <c r="V10" s="111"/>
-      <c r="W10" s="111"/>
-      <c r="X10" s="111"/>
-      <c r="Y10" s="111"/>
-      <c r="Z10" s="111"/>
-      <c r="AA10" s="111"/>
-      <c r="AB10" s="111"/>
-      <c r="AC10" s="111"/>
-      <c r="AD10" s="111"/>
-      <c r="AE10" s="111"/>
-      <c r="AF10" s="111"/>
-      <c r="AG10" s="111"/>
-      <c r="AH10" s="111"/>
-      <c r="AI10" s="111"/>
+      <c r="P10" s="113"/>
+      <c r="Q10" s="113"/>
+      <c r="R10" s="113"/>
+      <c r="S10" s="113"/>
+      <c r="T10" s="113"/>
+      <c r="U10" s="113"/>
+      <c r="V10" s="113"/>
+      <c r="W10" s="113"/>
+      <c r="X10" s="113"/>
+      <c r="Y10" s="113"/>
+      <c r="Z10" s="113"/>
+      <c r="AA10" s="113"/>
+      <c r="AB10" s="113"/>
+      <c r="AC10" s="113"/>
+      <c r="AD10" s="113"/>
+      <c r="AE10" s="113"/>
+      <c r="AF10" s="113"/>
+      <c r="AG10" s="113"/>
+      <c r="AH10" s="113"/>
+      <c r="AI10" s="113"/>
       <c r="AJ10" s="42"/>
       <c r="AK10" s="8"/>
     </row>
@@ -2722,26 +2752,26 @@
       <c r="N12" s="43"/>
       <c r="O12" s="43"/>
       <c r="P12" s="7"/>
-      <c r="Q12" s="110"/>
-      <c r="R12" s="110"/>
-      <c r="S12" s="110"/>
-      <c r="T12" s="110"/>
-      <c r="U12" s="110"/>
-      <c r="V12" s="110"/>
-      <c r="W12" s="110"/>
-      <c r="X12" s="110"/>
-      <c r="Y12" s="110"/>
-      <c r="Z12" s="110"/>
-      <c r="AA12" s="110"/>
-      <c r="AB12" s="110"/>
-      <c r="AC12" s="110"/>
-      <c r="AD12" s="110"/>
+      <c r="Q12" s="112"/>
+      <c r="R12" s="112"/>
+      <c r="S12" s="112"/>
+      <c r="T12" s="112"/>
+      <c r="U12" s="112"/>
+      <c r="V12" s="112"/>
+      <c r="W12" s="112"/>
+      <c r="X12" s="112"/>
+      <c r="Y12" s="112"/>
+      <c r="Z12" s="112"/>
+      <c r="AA12" s="112"/>
+      <c r="AB12" s="112"/>
+      <c r="AC12" s="112"/>
+      <c r="AD12" s="112"/>
       <c r="AF12" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="AG12" s="110"/>
-      <c r="AH12" s="110"/>
-      <c r="AI12" s="110"/>
+      <c r="AG12" s="112"/>
+      <c r="AH12" s="112"/>
+      <c r="AI12" s="112"/>
       <c r="AJ12" s="42"/>
       <c r="AK12" s="8"/>
     </row>
@@ -2762,29 +2792,29 @@
       <c r="H14" s="43"/>
       <c r="I14" s="43"/>
       <c r="J14" s="43"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="110"/>
-      <c r="P14" s="110"/>
-      <c r="Q14" s="110"/>
-      <c r="R14" s="110"/>
-      <c r="S14" s="110"/>
-      <c r="T14" s="110"/>
-      <c r="U14" s="110"/>
-      <c r="V14" s="110"/>
-      <c r="W14" s="110"/>
-      <c r="X14" s="110"/>
-      <c r="Y14" s="110"/>
-      <c r="Z14" s="110"/>
-      <c r="AA14" s="110"/>
-      <c r="AB14" s="110"/>
-      <c r="AC14" s="110"/>
-      <c r="AD14" s="110"/>
-      <c r="AE14" s="110"/>
-      <c r="AF14" s="110"/>
-      <c r="AG14" s="110"/>
-      <c r="AH14" s="110"/>
-      <c r="AI14" s="110"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="112"/>
+      <c r="R14" s="112"/>
+      <c r="S14" s="112"/>
+      <c r="T14" s="112"/>
+      <c r="U14" s="112"/>
+      <c r="V14" s="112"/>
+      <c r="W14" s="112"/>
+      <c r="X14" s="112"/>
+      <c r="Y14" s="112"/>
+      <c r="Z14" s="112"/>
+      <c r="AA14" s="112"/>
+      <c r="AB14" s="112"/>
+      <c r="AC14" s="112"/>
+      <c r="AD14" s="112"/>
+      <c r="AE14" s="112"/>
+      <c r="AF14" s="112"/>
+      <c r="AG14" s="112"/>
+      <c r="AH14" s="112"/>
+      <c r="AI14" s="112"/>
       <c r="AJ14" s="42"/>
       <c r="AK14" s="8"/>
     </row>
@@ -2796,31 +2826,31 @@
       <c r="A16" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110"/>
-      <c r="J16" s="110"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="110"/>
-      <c r="M16" s="110"/>
-      <c r="N16" s="110"/>
-      <c r="O16" s="110"/>
-      <c r="P16" s="110"/>
-      <c r="Q16" s="110"/>
-      <c r="R16" s="110"/>
-      <c r="S16" s="110"/>
-      <c r="T16" s="110"/>
-      <c r="U16" s="110"/>
-      <c r="V16" s="110"/>
-      <c r="W16" s="110"/>
-      <c r="X16" s="110"/>
-      <c r="Y16" s="110"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="112"/>
+      <c r="J16" s="112"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="112"/>
+      <c r="R16" s="112"/>
+      <c r="S16" s="112"/>
+      <c r="T16" s="112"/>
+      <c r="U16" s="112"/>
+      <c r="V16" s="112"/>
+      <c r="W16" s="112"/>
+      <c r="X16" s="112"/>
+      <c r="Y16" s="112"/>
       <c r="AA16" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="AF16" s="110"/>
-      <c r="AG16" s="110"/>
-      <c r="AH16" s="110"/>
-      <c r="AI16" s="110"/>
+      <c r="AF16" s="112"/>
+      <c r="AG16" s="112"/>
+      <c r="AH16" s="112"/>
+      <c r="AI16" s="112"/>
       <c r="AJ16" s="42"/>
       <c r="AK16" s="8"/>
     </row>
@@ -2836,33 +2866,33 @@
       <c r="C18" s="43"/>
       <c r="D18" s="43"/>
       <c r="E18" s="43"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="110"/>
-      <c r="J18" s="110"/>
-      <c r="K18" s="110"/>
-      <c r="L18" s="110"/>
-      <c r="M18" s="110"/>
-      <c r="N18" s="110"/>
-      <c r="O18" s="110"/>
-      <c r="P18" s="110"/>
-      <c r="Q18" s="110"/>
-      <c r="R18" s="110"/>
+      <c r="G18" s="112"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="112"/>
+      <c r="J18" s="112"/>
+      <c r="K18" s="112"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="112"/>
+      <c r="O18" s="112"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="112"/>
+      <c r="R18" s="112"/>
       <c r="T18" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="X18" s="110"/>
-      <c r="Y18" s="110"/>
-      <c r="Z18" s="110"/>
-      <c r="AA18" s="110"/>
-      <c r="AB18" s="110"/>
-      <c r="AC18" s="110"/>
-      <c r="AD18" s="110"/>
-      <c r="AE18" s="110"/>
-      <c r="AF18" s="110"/>
-      <c r="AG18" s="110"/>
-      <c r="AH18" s="110"/>
-      <c r="AI18" s="110"/>
+      <c r="X18" s="112"/>
+      <c r="Y18" s="112"/>
+      <c r="Z18" s="112"/>
+      <c r="AA18" s="112"/>
+      <c r="AB18" s="112"/>
+      <c r="AC18" s="112"/>
+      <c r="AD18" s="112"/>
+      <c r="AE18" s="112"/>
+      <c r="AF18" s="112"/>
+      <c r="AG18" s="112"/>
+      <c r="AH18" s="112"/>
+      <c r="AI18" s="112"/>
       <c r="AJ18" s="42"/>
       <c r="AK18" s="8"/>
     </row>
@@ -2876,45 +2906,45 @@
       <c r="AK20" s="8"/>
     </row>
     <row r="21" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="115" t="s">
+      <c r="A21" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="116"/>
-      <c r="C21" s="116"/>
-      <c r="D21" s="116"/>
-      <c r="E21" s="116"/>
-      <c r="F21" s="116"/>
-      <c r="G21" s="116"/>
-      <c r="H21" s="116"/>
-      <c r="I21" s="116"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="116"/>
-      <c r="L21" s="116"/>
-      <c r="M21" s="116"/>
-      <c r="N21" s="116"/>
-      <c r="O21" s="116"/>
-      <c r="P21" s="116"/>
-      <c r="Q21" s="116"/>
-      <c r="R21" s="116"/>
-      <c r="S21" s="116"/>
-      <c r="T21" s="116"/>
-      <c r="U21" s="116"/>
-      <c r="V21" s="116"/>
-      <c r="W21" s="116"/>
-      <c r="X21" s="116"/>
-      <c r="Y21" s="116"/>
-      <c r="Z21" s="116"/>
-      <c r="AA21" s="116"/>
-      <c r="AB21" s="116"/>
-      <c r="AC21" s="116"/>
-      <c r="AD21" s="116"/>
-      <c r="AE21" s="116"/>
-      <c r="AF21" s="116"/>
-      <c r="AG21" s="116"/>
-      <c r="AH21" s="116"/>
-      <c r="AI21" s="116"/>
-      <c r="AJ21" s="116"/>
-      <c r="AK21" s="117"/>
+      <c r="B21" s="118"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="118"/>
+      <c r="G21" s="118"/>
+      <c r="H21" s="118"/>
+      <c r="I21" s="118"/>
+      <c r="J21" s="118"/>
+      <c r="K21" s="118"/>
+      <c r="L21" s="118"/>
+      <c r="M21" s="118"/>
+      <c r="N21" s="118"/>
+      <c r="O21" s="118"/>
+      <c r="P21" s="118"/>
+      <c r="Q21" s="118"/>
+      <c r="R21" s="118"/>
+      <c r="S21" s="118"/>
+      <c r="T21" s="118"/>
+      <c r="U21" s="118"/>
+      <c r="V21" s="118"/>
+      <c r="W21" s="118"/>
+      <c r="X21" s="118"/>
+      <c r="Y21" s="118"/>
+      <c r="Z21" s="118"/>
+      <c r="AA21" s="118"/>
+      <c r="AB21" s="118"/>
+      <c r="AC21" s="118"/>
+      <c r="AD21" s="118"/>
+      <c r="AE21" s="118"/>
+      <c r="AF21" s="118"/>
+      <c r="AG21" s="118"/>
+      <c r="AH21" s="118"/>
+      <c r="AI21" s="118"/>
+      <c r="AJ21" s="118"/>
+      <c r="AK21" s="119"/>
     </row>
     <row r="22" spans="1:37" s="2" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="47"/>
@@ -2930,35 +2960,35 @@
       <c r="D23" s="57"/>
       <c r="E23" s="57"/>
       <c r="F23" s="57"/>
-      <c r="G23" s="110"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="110"/>
-      <c r="J23" s="110"/>
-      <c r="K23" s="110"/>
-      <c r="L23" s="110"/>
-      <c r="M23" s="110"/>
-      <c r="N23" s="110"/>
-      <c r="O23" s="110"/>
-      <c r="P23" s="110"/>
-      <c r="Q23" s="110"/>
-      <c r="R23" s="110"/>
-      <c r="S23" s="110"/>
-      <c r="T23" s="110"/>
-      <c r="U23" s="110"/>
-      <c r="V23" s="110"/>
-      <c r="W23" s="110"/>
-      <c r="X23" s="110"/>
-      <c r="Y23" s="110"/>
-      <c r="Z23" s="110"/>
-      <c r="AA23" s="110"/>
-      <c r="AB23" s="110"/>
-      <c r="AC23" s="110"/>
-      <c r="AD23" s="110"/>
-      <c r="AE23" s="110"/>
-      <c r="AF23" s="110"/>
-      <c r="AG23" s="110"/>
-      <c r="AH23" s="110"/>
-      <c r="AI23" s="110"/>
+      <c r="G23" s="112"/>
+      <c r="H23" s="112"/>
+      <c r="I23" s="112"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="112"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="112"/>
+      <c r="R23" s="112"/>
+      <c r="S23" s="112"/>
+      <c r="T23" s="112"/>
+      <c r="U23" s="112"/>
+      <c r="V23" s="112"/>
+      <c r="W23" s="112"/>
+      <c r="X23" s="112"/>
+      <c r="Y23" s="112"/>
+      <c r="Z23" s="112"/>
+      <c r="AA23" s="112"/>
+      <c r="AB23" s="112"/>
+      <c r="AC23" s="112"/>
+      <c r="AD23" s="112"/>
+      <c r="AE23" s="112"/>
+      <c r="AF23" s="112"/>
+      <c r="AG23" s="112"/>
+      <c r="AH23" s="112"/>
+      <c r="AI23" s="112"/>
       <c r="AJ23" s="42"/>
       <c r="AK23" s="8"/>
     </row>
@@ -2968,40 +2998,40 @@
     </row>
     <row r="25" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="46"/>
-      <c r="B25" s="113"/>
-      <c r="C25" s="113"/>
-      <c r="D25" s="113"/>
-      <c r="E25" s="113"/>
-      <c r="F25" s="113"/>
-      <c r="G25" s="113"/>
-      <c r="H25" s="113"/>
-      <c r="I25" s="113"/>
-      <c r="J25" s="113"/>
-      <c r="K25" s="113"/>
-      <c r="L25" s="113"/>
-      <c r="M25" s="113"/>
-      <c r="N25" s="113"/>
-      <c r="O25" s="113"/>
-      <c r="P25" s="113"/>
-      <c r="Q25" s="113"/>
-      <c r="R25" s="113"/>
-      <c r="S25" s="113"/>
-      <c r="T25" s="113"/>
-      <c r="U25" s="113"/>
-      <c r="V25" s="113"/>
-      <c r="W25" s="113"/>
-      <c r="X25" s="113"/>
-      <c r="Y25" s="113"/>
-      <c r="Z25" s="113"/>
-      <c r="AA25" s="113"/>
-      <c r="AB25" s="113"/>
-      <c r="AC25" s="113"/>
-      <c r="AD25" s="113"/>
-      <c r="AE25" s="113"/>
-      <c r="AF25" s="113"/>
-      <c r="AG25" s="113"/>
-      <c r="AH25" s="113"/>
-      <c r="AI25" s="113"/>
+      <c r="B25" s="115"/>
+      <c r="C25" s="115"/>
+      <c r="D25" s="115"/>
+      <c r="E25" s="115"/>
+      <c r="F25" s="115"/>
+      <c r="G25" s="115"/>
+      <c r="H25" s="115"/>
+      <c r="I25" s="115"/>
+      <c r="J25" s="115"/>
+      <c r="K25" s="115"/>
+      <c r="L25" s="115"/>
+      <c r="M25" s="115"/>
+      <c r="N25" s="115"/>
+      <c r="O25" s="115"/>
+      <c r="P25" s="115"/>
+      <c r="Q25" s="115"/>
+      <c r="R25" s="115"/>
+      <c r="S25" s="115"/>
+      <c r="T25" s="115"/>
+      <c r="U25" s="115"/>
+      <c r="V25" s="115"/>
+      <c r="W25" s="115"/>
+      <c r="X25" s="115"/>
+      <c r="Y25" s="115"/>
+      <c r="Z25" s="115"/>
+      <c r="AA25" s="115"/>
+      <c r="AB25" s="115"/>
+      <c r="AC25" s="115"/>
+      <c r="AD25" s="115"/>
+      <c r="AE25" s="115"/>
+      <c r="AF25" s="115"/>
+      <c r="AG25" s="115"/>
+      <c r="AH25" s="115"/>
+      <c r="AI25" s="115"/>
       <c r="AJ25" s="57"/>
       <c r="AK25" s="8"/>
     </row>
@@ -3012,40 +3042,40 @@
     </row>
     <row r="27" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="50"/>
-      <c r="B27" s="114"/>
-      <c r="C27" s="114"/>
-      <c r="D27" s="114"/>
-      <c r="E27" s="114"/>
-      <c r="F27" s="114"/>
-      <c r="G27" s="114"/>
-      <c r="H27" s="114"/>
-      <c r="I27" s="114"/>
-      <c r="J27" s="114"/>
-      <c r="K27" s="114"/>
-      <c r="L27" s="114"/>
-      <c r="M27" s="114"/>
-      <c r="N27" s="114"/>
-      <c r="O27" s="114"/>
-      <c r="P27" s="114"/>
-      <c r="Q27" s="114"/>
-      <c r="R27" s="114"/>
-      <c r="S27" s="114"/>
-      <c r="T27" s="114"/>
-      <c r="U27" s="114"/>
-      <c r="V27" s="114"/>
-      <c r="W27" s="114"/>
-      <c r="X27" s="114"/>
-      <c r="Y27" s="114"/>
-      <c r="Z27" s="114"/>
-      <c r="AA27" s="114"/>
-      <c r="AB27" s="114"/>
-      <c r="AC27" s="114"/>
-      <c r="AD27" s="114"/>
-      <c r="AE27" s="114"/>
-      <c r="AF27" s="114"/>
-      <c r="AG27" s="114"/>
-      <c r="AH27" s="114"/>
-      <c r="AI27" s="114"/>
+      <c r="B27" s="116"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="116"/>
+      <c r="I27" s="116"/>
+      <c r="J27" s="116"/>
+      <c r="K27" s="116"/>
+      <c r="L27" s="116"/>
+      <c r="M27" s="116"/>
+      <c r="N27" s="116"/>
+      <c r="O27" s="116"/>
+      <c r="P27" s="116"/>
+      <c r="Q27" s="116"/>
+      <c r="R27" s="116"/>
+      <c r="S27" s="116"/>
+      <c r="T27" s="116"/>
+      <c r="U27" s="116"/>
+      <c r="V27" s="116"/>
+      <c r="W27" s="116"/>
+      <c r="X27" s="116"/>
+      <c r="Y27" s="116"/>
+      <c r="Z27" s="116"/>
+      <c r="AA27" s="116"/>
+      <c r="AB27" s="116"/>
+      <c r="AC27" s="116"/>
+      <c r="AD27" s="116"/>
+      <c r="AE27" s="116"/>
+      <c r="AF27" s="116"/>
+      <c r="AG27" s="116"/>
+      <c r="AH27" s="116"/>
+      <c r="AI27" s="116"/>
       <c r="AJ27" s="59"/>
       <c r="AK27" s="8"/>
     </row>
@@ -3073,25 +3103,25 @@
       <c r="N29" s="57"/>
       <c r="O29" s="57"/>
       <c r="P29" s="57"/>
-      <c r="Q29" s="110"/>
-      <c r="R29" s="110"/>
-      <c r="S29" s="110"/>
-      <c r="T29" s="110"/>
-      <c r="U29" s="110"/>
-      <c r="V29" s="110"/>
-      <c r="W29" s="110"/>
-      <c r="X29" s="110"/>
-      <c r="Y29" s="110"/>
-      <c r="Z29" s="110"/>
-      <c r="AA29" s="110"/>
-      <c r="AB29" s="110"/>
-      <c r="AC29" s="110"/>
-      <c r="AD29" s="110"/>
-      <c r="AE29" s="110"/>
-      <c r="AF29" s="110"/>
-      <c r="AG29" s="110"/>
-      <c r="AH29" s="110"/>
-      <c r="AI29" s="110"/>
+      <c r="Q29" s="112"/>
+      <c r="R29" s="112"/>
+      <c r="S29" s="112"/>
+      <c r="T29" s="112"/>
+      <c r="U29" s="112"/>
+      <c r="V29" s="112"/>
+      <c r="W29" s="112"/>
+      <c r="X29" s="112"/>
+      <c r="Y29" s="112"/>
+      <c r="Z29" s="112"/>
+      <c r="AA29" s="112"/>
+      <c r="AB29" s="112"/>
+      <c r="AC29" s="112"/>
+      <c r="AD29" s="112"/>
+      <c r="AE29" s="112"/>
+      <c r="AF29" s="112"/>
+      <c r="AG29" s="112"/>
+      <c r="AH29" s="112"/>
+      <c r="AI29" s="112"/>
       <c r="AJ29" s="64"/>
       <c r="AK29" s="8"/>
     </row>
@@ -3102,40 +3132,40 @@
     </row>
     <row r="31" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="47"/>
-      <c r="B31" s="110"/>
-      <c r="C31" s="110"/>
-      <c r="D31" s="110"/>
-      <c r="E31" s="110"/>
-      <c r="F31" s="110"/>
-      <c r="G31" s="110"/>
-      <c r="H31" s="110"/>
-      <c r="I31" s="110"/>
-      <c r="J31" s="110"/>
-      <c r="K31" s="110"/>
-      <c r="L31" s="110"/>
-      <c r="M31" s="110"/>
-      <c r="N31" s="110"/>
-      <c r="O31" s="110"/>
-      <c r="P31" s="110"/>
-      <c r="Q31" s="110"/>
-      <c r="R31" s="110"/>
-      <c r="S31" s="110"/>
-      <c r="T31" s="110"/>
-      <c r="U31" s="110"/>
-      <c r="V31" s="110"/>
-      <c r="W31" s="110"/>
-      <c r="X31" s="110"/>
-      <c r="Y31" s="110"/>
-      <c r="Z31" s="110"/>
-      <c r="AA31" s="110"/>
-      <c r="AB31" s="110"/>
-      <c r="AC31" s="110"/>
-      <c r="AD31" s="110"/>
-      <c r="AE31" s="110"/>
-      <c r="AF31" s="110"/>
-      <c r="AG31" s="110"/>
-      <c r="AH31" s="110"/>
-      <c r="AI31" s="110"/>
+      <c r="B31" s="112"/>
+      <c r="C31" s="112"/>
+      <c r="D31" s="112"/>
+      <c r="E31" s="112"/>
+      <c r="F31" s="112"/>
+      <c r="G31" s="112"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="112"/>
+      <c r="J31" s="112"/>
+      <c r="K31" s="112"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="112"/>
+      <c r="R31" s="112"/>
+      <c r="S31" s="112"/>
+      <c r="T31" s="112"/>
+      <c r="U31" s="112"/>
+      <c r="V31" s="112"/>
+      <c r="W31" s="112"/>
+      <c r="X31" s="112"/>
+      <c r="Y31" s="112"/>
+      <c r="Z31" s="112"/>
+      <c r="AA31" s="112"/>
+      <c r="AB31" s="112"/>
+      <c r="AC31" s="112"/>
+      <c r="AD31" s="112"/>
+      <c r="AE31" s="112"/>
+      <c r="AF31" s="112"/>
+      <c r="AG31" s="112"/>
+      <c r="AH31" s="112"/>
+      <c r="AI31" s="112"/>
       <c r="AJ31" s="65"/>
       <c r="AK31" s="8"/>
     </row>
@@ -3146,40 +3176,44 @@
     </row>
     <row r="33" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="50"/>
-      <c r="B33" s="121"/>
-      <c r="C33" s="121"/>
-      <c r="D33" s="121"/>
-      <c r="E33" s="121"/>
-      <c r="F33" s="121"/>
-      <c r="G33" s="121"/>
-      <c r="H33" s="121"/>
-      <c r="I33" s="121"/>
-      <c r="J33" s="121"/>
-      <c r="K33" s="121"/>
-      <c r="L33" s="121"/>
-      <c r="M33" s="121"/>
-      <c r="N33" s="121"/>
-      <c r="O33" s="121"/>
-      <c r="P33" s="121"/>
-      <c r="Q33" s="121"/>
-      <c r="R33" s="121"/>
-      <c r="S33" s="121"/>
-      <c r="T33" s="121"/>
-      <c r="U33" s="121"/>
-      <c r="V33" s="121"/>
-      <c r="W33" s="121"/>
-      <c r="X33" s="121"/>
-      <c r="Y33" s="121"/>
-      <c r="Z33" s="121"/>
-      <c r="AA33" s="121"/>
-      <c r="AB33" s="121"/>
-      <c r="AC33" s="121"/>
-      <c r="AD33" s="121"/>
-      <c r="AE33" s="121"/>
-      <c r="AF33" s="121"/>
-      <c r="AG33" s="121"/>
-      <c r="AH33" s="121"/>
-      <c r="AI33" s="121"/>
+      <c r="B33" s="207" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="88"/>
+      <c r="G33" s="88"/>
+      <c r="H33" s="88"/>
+      <c r="I33" s="88"/>
+      <c r="J33" s="88"/>
+      <c r="K33" s="88"/>
+      <c r="L33" s="88"/>
+      <c r="M33" s="88"/>
+      <c r="N33" s="87"/>
+      <c r="O33" s="207" t="s">
+        <v>109</v>
+      </c>
+      <c r="P33" s="88"/>
+      <c r="Q33" s="88"/>
+      <c r="R33" s="88"/>
+      <c r="S33" s="88"/>
+      <c r="T33" s="88"/>
+      <c r="U33" s="88"/>
+      <c r="V33" s="88"/>
+      <c r="W33" s="88"/>
+      <c r="X33" s="88"/>
+      <c r="Y33" s="88"/>
+      <c r="Z33" s="88"/>
+      <c r="AA33" s="88"/>
+      <c r="AB33" s="88"/>
+      <c r="AC33" s="88"/>
+      <c r="AD33" s="88"/>
+      <c r="AE33" s="88"/>
+      <c r="AF33" s="88"/>
+      <c r="AG33" s="88"/>
+      <c r="AH33" s="88"/>
+      <c r="AI33" s="87"/>
       <c r="AJ33" s="59"/>
       <c r="AK33" s="8"/>
     </row>
@@ -3189,47 +3223,47 @@
       <c r="AK34" s="8"/>
     </row>
     <row r="35" spans="1:39" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="124" t="s">
+      <c r="A35" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="B35" s="125"/>
-      <c r="C35" s="125"/>
-      <c r="D35" s="126">
+      <c r="B35" s="126"/>
+      <c r="C35" s="126"/>
+      <c r="D35" s="127">
         <v>0</v>
       </c>
-      <c r="E35" s="126"/>
-      <c r="F35" s="126"/>
-      <c r="G35" s="126"/>
-      <c r="H35" s="126"/>
-      <c r="I35" s="126"/>
-      <c r="J35" s="126"/>
-      <c r="K35" s="126"/>
-      <c r="L35" s="126"/>
+      <c r="E35" s="127"/>
+      <c r="F35" s="127"/>
+      <c r="G35" s="127"/>
+      <c r="H35" s="127"/>
+      <c r="I35" s="127"/>
+      <c r="J35" s="127"/>
+      <c r="K35" s="127"/>
+      <c r="L35" s="127"/>
       <c r="M35" s="58"/>
-      <c r="N35" s="127" t="s">
+      <c r="N35" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="O35" s="127"/>
-      <c r="P35" s="127"/>
-      <c r="Q35" s="127"/>
-      <c r="R35" s="127"/>
+      <c r="O35" s="128"/>
+      <c r="P35" s="128"/>
+      <c r="Q35" s="128"/>
+      <c r="R35" s="128"/>
       <c r="S35" s="58"/>
-      <c r="T35" s="118" t="s">
+      <c r="T35" s="120" t="s">
         <v>20</v>
       </c>
-      <c r="U35" s="118"/>
-      <c r="V35" s="118"/>
-      <c r="W35" s="118"/>
-      <c r="X35" s="118"/>
+      <c r="U35" s="120"/>
+      <c r="V35" s="120"/>
+      <c r="W35" s="120"/>
+      <c r="X35" s="120"/>
       <c r="Y35" s="58"/>
       <c r="Z35" s="16"/>
-      <c r="AA35" s="128"/>
-      <c r="AB35" s="118"/>
-      <c r="AC35" s="118"/>
-      <c r="AD35" s="118" t="s">
+      <c r="AA35" s="129"/>
+      <c r="AB35" s="120"/>
+      <c r="AC35" s="120"/>
+      <c r="AD35" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="AE35" s="118"/>
+      <c r="AE35" s="120"/>
       <c r="AF35" s="59"/>
       <c r="AG35" s="14"/>
       <c r="AH35" s="59"/>
@@ -3241,39 +3275,39 @@
       <c r="AK36" s="8"/>
     </row>
     <row r="37" spans="1:39" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="119" t="s">
+      <c r="A37" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="120"/>
-      <c r="C37" s="120"/>
-      <c r="D37" s="120"/>
-      <c r="E37" s="120"/>
-      <c r="F37" s="120"/>
-      <c r="G37" s="120"/>
-      <c r="H37" s="120"/>
-      <c r="I37" s="118" t="s">
+      <c r="B37" s="122"/>
+      <c r="C37" s="122"/>
+      <c r="D37" s="122"/>
+      <c r="E37" s="122"/>
+      <c r="F37" s="122"/>
+      <c r="G37" s="122"/>
+      <c r="H37" s="122"/>
+      <c r="I37" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="J37" s="118"/>
-      <c r="K37" s="118"/>
+      <c r="J37" s="120"/>
+      <c r="K37" s="120"/>
       <c r="L37" s="16"/>
       <c r="M37" s="59"/>
       <c r="N37" s="59"/>
-      <c r="O37" s="118" t="s">
+      <c r="O37" s="120" t="s">
         <v>24</v>
       </c>
-      <c r="P37" s="118"/>
-      <c r="Q37" s="118"/>
+      <c r="P37" s="120"/>
+      <c r="Q37" s="120"/>
       <c r="R37" s="14"/>
       <c r="S37" s="59"/>
-      <c r="T37" s="91" t="s">
+      <c r="T37" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="U37" s="91"/>
-      <c r="V37" s="91"/>
-      <c r="W37" s="91"/>
-      <c r="X37" s="91"/>
-      <c r="Y37" s="91"/>
+      <c r="U37" s="93"/>
+      <c r="V37" s="93"/>
+      <c r="W37" s="93"/>
+      <c r="X37" s="93"/>
+      <c r="Y37" s="93"/>
       <c r="Z37" s="86"/>
       <c r="AK37" s="8"/>
     </row>
@@ -3283,43 +3317,43 @@
       <c r="AK38" s="8"/>
     </row>
     <row r="39" spans="1:39" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="119" t="s">
+      <c r="A39" s="121" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="120"/>
-      <c r="C39" s="120"/>
-      <c r="D39" s="120"/>
-      <c r="E39" s="120"/>
-      <c r="F39" s="120"/>
-      <c r="G39" s="120"/>
-      <c r="H39" s="120"/>
-      <c r="I39" s="120"/>
-      <c r="J39" s="120"/>
-      <c r="K39" s="120"/>
-      <c r="L39" s="120"/>
-      <c r="M39" s="120"/>
-      <c r="N39" s="120"/>
-      <c r="O39" s="122"/>
-      <c r="P39" s="122"/>
-      <c r="Q39" s="122"/>
-      <c r="R39" s="122"/>
-      <c r="S39" s="122"/>
-      <c r="T39" s="122"/>
-      <c r="U39" s="122"/>
-      <c r="V39" s="122"/>
-      <c r="W39" s="122"/>
-      <c r="X39" s="122"/>
-      <c r="Y39" s="122"/>
-      <c r="Z39" s="122"/>
-      <c r="AA39" s="122"/>
-      <c r="AB39" s="122"/>
-      <c r="AC39" s="122"/>
-      <c r="AD39" s="122"/>
-      <c r="AE39" s="122"/>
-      <c r="AF39" s="122"/>
-      <c r="AG39" s="122"/>
-      <c r="AH39" s="122"/>
-      <c r="AI39" s="122"/>
+      <c r="B39" s="122"/>
+      <c r="C39" s="122"/>
+      <c r="D39" s="122"/>
+      <c r="E39" s="122"/>
+      <c r="F39" s="122"/>
+      <c r="G39" s="122"/>
+      <c r="H39" s="122"/>
+      <c r="I39" s="122"/>
+      <c r="J39" s="122"/>
+      <c r="K39" s="122"/>
+      <c r="L39" s="122"/>
+      <c r="M39" s="122"/>
+      <c r="N39" s="122"/>
+      <c r="O39" s="123"/>
+      <c r="P39" s="123"/>
+      <c r="Q39" s="123"/>
+      <c r="R39" s="123"/>
+      <c r="S39" s="123"/>
+      <c r="T39" s="123"/>
+      <c r="U39" s="123"/>
+      <c r="V39" s="123"/>
+      <c r="W39" s="123"/>
+      <c r="X39" s="123"/>
+      <c r="Y39" s="123"/>
+      <c r="Z39" s="123"/>
+      <c r="AA39" s="123"/>
+      <c r="AB39" s="123"/>
+      <c r="AC39" s="123"/>
+      <c r="AD39" s="123"/>
+      <c r="AE39" s="123"/>
+      <c r="AF39" s="123"/>
+      <c r="AG39" s="123"/>
+      <c r="AH39" s="123"/>
+      <c r="AI39" s="123"/>
       <c r="AJ39" s="59"/>
       <c r="AK39" s="8"/>
     </row>
@@ -3329,13 +3363,13 @@
       <c r="AK40" s="8"/>
     </row>
     <row r="41" spans="1:39" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="119" t="s">
+      <c r="A41" s="121" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="120"/>
-      <c r="C41" s="120"/>
-      <c r="D41" s="120"/>
-      <c r="E41" s="120"/>
+      <c r="B41" s="122"/>
+      <c r="C41" s="122"/>
+      <c r="D41" s="122"/>
+      <c r="E41" s="122"/>
       <c r="F41" s="58"/>
       <c r="G41" s="60" t="s">
         <v>28</v>
@@ -3372,13 +3406,13 @@
       </c>
       <c r="Z41" s="14"/>
       <c r="AA41" s="15"/>
-      <c r="AB41" s="118" t="s">
+      <c r="AB41" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="AC41" s="118"/>
-      <c r="AD41" s="118"/>
-      <c r="AE41" s="118"/>
-      <c r="AF41" s="118"/>
+      <c r="AC41" s="120"/>
+      <c r="AD41" s="120"/>
+      <c r="AE41" s="120"/>
+      <c r="AF41" s="120"/>
       <c r="AG41" s="14"/>
       <c r="AH41" s="59"/>
       <c r="AI41" s="59"/>
@@ -3392,43 +3426,43 @@
       <c r="AK42" s="8"/>
     </row>
     <row r="43" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="119" t="s">
+      <c r="A43" s="121" t="s">
         <v>36</v>
       </c>
-      <c r="B43" s="120"/>
-      <c r="C43" s="120"/>
-      <c r="D43" s="120"/>
-      <c r="E43" s="120"/>
-      <c r="F43" s="120"/>
-      <c r="G43" s="121"/>
-      <c r="H43" s="121"/>
-      <c r="I43" s="121"/>
-      <c r="J43" s="121"/>
-      <c r="K43" s="121"/>
-      <c r="L43" s="121"/>
-      <c r="M43" s="121"/>
-      <c r="N43" s="121"/>
-      <c r="O43" s="121"/>
-      <c r="P43" s="121"/>
-      <c r="Q43" s="121"/>
-      <c r="R43" s="121"/>
-      <c r="S43" s="121"/>
-      <c r="T43" s="121"/>
-      <c r="U43" s="121"/>
-      <c r="V43" s="121"/>
-      <c r="W43" s="121"/>
-      <c r="X43" s="121"/>
-      <c r="Y43" s="121"/>
-      <c r="Z43" s="121"/>
-      <c r="AA43" s="121"/>
-      <c r="AB43" s="121"/>
-      <c r="AC43" s="121"/>
-      <c r="AD43" s="121"/>
-      <c r="AE43" s="121"/>
-      <c r="AF43" s="121"/>
-      <c r="AG43" s="121"/>
-      <c r="AH43" s="121"/>
-      <c r="AI43" s="121"/>
+      <c r="B43" s="122"/>
+      <c r="C43" s="122"/>
+      <c r="D43" s="122"/>
+      <c r="E43" s="122"/>
+      <c r="F43" s="122"/>
+      <c r="G43" s="124"/>
+      <c r="H43" s="124"/>
+      <c r="I43" s="124"/>
+      <c r="J43" s="124"/>
+      <c r="K43" s="124"/>
+      <c r="L43" s="124"/>
+      <c r="M43" s="124"/>
+      <c r="N43" s="124"/>
+      <c r="O43" s="124"/>
+      <c r="P43" s="124"/>
+      <c r="Q43" s="124"/>
+      <c r="R43" s="124"/>
+      <c r="S43" s="124"/>
+      <c r="T43" s="124"/>
+      <c r="U43" s="124"/>
+      <c r="V43" s="124"/>
+      <c r="W43" s="124"/>
+      <c r="X43" s="124"/>
+      <c r="Y43" s="124"/>
+      <c r="Z43" s="124"/>
+      <c r="AA43" s="124"/>
+      <c r="AB43" s="124"/>
+      <c r="AC43" s="124"/>
+      <c r="AD43" s="124"/>
+      <c r="AE43" s="124"/>
+      <c r="AF43" s="124"/>
+      <c r="AG43" s="124"/>
+      <c r="AH43" s="124"/>
+      <c r="AI43" s="124"/>
       <c r="AJ43" s="58"/>
       <c r="AK43" s="8"/>
     </row>
@@ -3438,14 +3472,14 @@
       <c r="AK44" s="8"/>
     </row>
     <row r="45" spans="1:39" s="2" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="119" t="s">
+      <c r="A45" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="B45" s="120"/>
-      <c r="C45" s="120"/>
-      <c r="D45" s="120"/>
-      <c r="E45" s="120"/>
-      <c r="F45" s="120"/>
+      <c r="B45" s="122"/>
+      <c r="C45" s="122"/>
+      <c r="D45" s="122"/>
+      <c r="E45" s="122"/>
+      <c r="F45" s="122"/>
       <c r="G45" s="60">
         <v>1</v>
       </c>
@@ -3471,24 +3505,24 @@
       </c>
       <c r="T45" s="16"/>
       <c r="U45" s="58"/>
-      <c r="V45" s="118" t="s">
+      <c r="V45" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="W45" s="118"/>
-      <c r="X45" s="118"/>
-      <c r="Y45" s="118"/>
-      <c r="Z45" s="118"/>
-      <c r="AA45" s="121" t="s">
+      <c r="W45" s="120"/>
+      <c r="X45" s="120"/>
+      <c r="Y45" s="120"/>
+      <c r="Z45" s="120"/>
+      <c r="AA45" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="AB45" s="121"/>
-      <c r="AC45" s="121"/>
-      <c r="AD45" s="121"/>
-      <c r="AE45" s="121"/>
-      <c r="AF45" s="121"/>
-      <c r="AG45" s="121"/>
-      <c r="AH45" s="121"/>
-      <c r="AI45" s="121"/>
+      <c r="AB45" s="124"/>
+      <c r="AC45" s="124"/>
+      <c r="AD45" s="124"/>
+      <c r="AE45" s="124"/>
+      <c r="AF45" s="124"/>
+      <c r="AG45" s="124"/>
+      <c r="AH45" s="124"/>
+      <c r="AI45" s="124"/>
       <c r="AJ45" s="59"/>
       <c r="AK45" s="8"/>
     </row>
@@ -3532,45 +3566,45 @@
       <c r="AK46" s="10"/>
     </row>
     <row r="47" spans="1:39" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="115" t="s">
+      <c r="A47" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="B47" s="116"/>
-      <c r="C47" s="116"/>
-      <c r="D47" s="116"/>
-      <c r="E47" s="116"/>
-      <c r="F47" s="116"/>
-      <c r="G47" s="116"/>
-      <c r="H47" s="116"/>
-      <c r="I47" s="116"/>
-      <c r="J47" s="116"/>
-      <c r="K47" s="116"/>
-      <c r="L47" s="116"/>
-      <c r="M47" s="116"/>
-      <c r="N47" s="116"/>
-      <c r="O47" s="116"/>
-      <c r="P47" s="116"/>
-      <c r="Q47" s="116"/>
-      <c r="R47" s="116"/>
-      <c r="S47" s="116"/>
-      <c r="T47" s="116"/>
-      <c r="U47" s="116"/>
-      <c r="V47" s="116"/>
-      <c r="W47" s="116"/>
-      <c r="X47" s="116"/>
-      <c r="Y47" s="116"/>
-      <c r="Z47" s="116"/>
-      <c r="AA47" s="116"/>
-      <c r="AB47" s="116"/>
-      <c r="AC47" s="116"/>
-      <c r="AD47" s="116"/>
-      <c r="AE47" s="116"/>
-      <c r="AF47" s="116"/>
-      <c r="AG47" s="116"/>
-      <c r="AH47" s="116"/>
-      <c r="AI47" s="116"/>
-      <c r="AJ47" s="116"/>
-      <c r="AK47" s="117"/>
+      <c r="B47" s="118"/>
+      <c r="C47" s="118"/>
+      <c r="D47" s="118"/>
+      <c r="E47" s="118"/>
+      <c r="F47" s="118"/>
+      <c r="G47" s="118"/>
+      <c r="H47" s="118"/>
+      <c r="I47" s="118"/>
+      <c r="J47" s="118"/>
+      <c r="K47" s="118"/>
+      <c r="L47" s="118"/>
+      <c r="M47" s="118"/>
+      <c r="N47" s="118"/>
+      <c r="O47" s="118"/>
+      <c r="P47" s="118"/>
+      <c r="Q47" s="118"/>
+      <c r="R47" s="118"/>
+      <c r="S47" s="118"/>
+      <c r="T47" s="118"/>
+      <c r="U47" s="118"/>
+      <c r="V47" s="118"/>
+      <c r="W47" s="118"/>
+      <c r="X47" s="118"/>
+      <c r="Y47" s="118"/>
+      <c r="Z47" s="118"/>
+      <c r="AA47" s="118"/>
+      <c r="AB47" s="118"/>
+      <c r="AC47" s="118"/>
+      <c r="AD47" s="118"/>
+      <c r="AE47" s="118"/>
+      <c r="AF47" s="118"/>
+      <c r="AG47" s="118"/>
+      <c r="AH47" s="118"/>
+      <c r="AI47" s="118"/>
+      <c r="AJ47" s="118"/>
+      <c r="AK47" s="119"/>
     </row>
     <row r="48" spans="1:39" s="2" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="45"/>
@@ -3612,45 +3646,45 @@
       <c r="AK48" s="6"/>
     </row>
     <row r="49" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="129" t="s">
+      <c r="A49" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="B49" s="118"/>
-      <c r="C49" s="118"/>
-      <c r="D49" s="118"/>
-      <c r="E49" s="118"/>
-      <c r="F49" s="118"/>
-      <c r="G49" s="118"/>
-      <c r="H49" s="121"/>
-      <c r="I49" s="121"/>
-      <c r="J49" s="121"/>
-      <c r="K49" s="121"/>
-      <c r="L49" s="121"/>
-      <c r="M49" s="121"/>
-      <c r="N49" s="121"/>
-      <c r="O49" s="121"/>
-      <c r="P49" s="121"/>
-      <c r="Q49" s="121"/>
-      <c r="R49" s="121"/>
-      <c r="S49" s="121"/>
-      <c r="T49" s="121"/>
+      <c r="B49" s="120"/>
+      <c r="C49" s="120"/>
+      <c r="D49" s="120"/>
+      <c r="E49" s="120"/>
+      <c r="F49" s="120"/>
+      <c r="G49" s="120"/>
+      <c r="H49" s="124"/>
+      <c r="I49" s="124"/>
+      <c r="J49" s="124"/>
+      <c r="K49" s="124"/>
+      <c r="L49" s="124"/>
+      <c r="M49" s="124"/>
+      <c r="N49" s="124"/>
+      <c r="O49" s="124"/>
+      <c r="P49" s="124"/>
+      <c r="Q49" s="124"/>
+      <c r="R49" s="124"/>
+      <c r="S49" s="124"/>
+      <c r="T49" s="124"/>
       <c r="U49" s="58"/>
-      <c r="V49" s="118" t="s">
+      <c r="V49" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="W49" s="118"/>
-      <c r="X49" s="118"/>
-      <c r="Y49" s="118"/>
-      <c r="Z49" s="118"/>
-      <c r="AA49" s="118"/>
-      <c r="AB49" s="118"/>
-      <c r="AC49" s="123"/>
-      <c r="AD49" s="123"/>
-      <c r="AE49" s="123"/>
-      <c r="AF49" s="123"/>
-      <c r="AG49" s="123"/>
-      <c r="AH49" s="123"/>
-      <c r="AI49" s="123"/>
+      <c r="W49" s="120"/>
+      <c r="X49" s="120"/>
+      <c r="Y49" s="120"/>
+      <c r="Z49" s="120"/>
+      <c r="AA49" s="120"/>
+      <c r="AB49" s="120"/>
+      <c r="AC49" s="88"/>
+      <c r="AD49" s="88"/>
+      <c r="AE49" s="88"/>
+      <c r="AF49" s="88"/>
+      <c r="AG49" s="88"/>
+      <c r="AH49" s="88"/>
+      <c r="AI49" s="88"/>
       <c r="AJ49" s="59"/>
       <c r="AK49" s="8"/>
     </row>
@@ -3681,45 +3715,45 @@
       <c r="AK50" s="8"/>
     </row>
     <row r="51" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="129" t="s">
+      <c r="A51" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="B51" s="118"/>
-      <c r="C51" s="118"/>
-      <c r="D51" s="118"/>
-      <c r="E51" s="118"/>
-      <c r="F51" s="118"/>
-      <c r="G51" s="118"/>
-      <c r="H51" s="121"/>
-      <c r="I51" s="121"/>
-      <c r="J51" s="121"/>
-      <c r="K51" s="121"/>
-      <c r="L51" s="121"/>
-      <c r="M51" s="121"/>
-      <c r="N51" s="121"/>
-      <c r="O51" s="121"/>
-      <c r="P51" s="121"/>
-      <c r="Q51" s="121"/>
-      <c r="R51" s="121"/>
-      <c r="S51" s="121"/>
-      <c r="T51" s="121"/>
+      <c r="B51" s="120"/>
+      <c r="C51" s="120"/>
+      <c r="D51" s="120"/>
+      <c r="E51" s="120"/>
+      <c r="F51" s="120"/>
+      <c r="G51" s="120"/>
+      <c r="H51" s="124"/>
+      <c r="I51" s="124"/>
+      <c r="J51" s="124"/>
+      <c r="K51" s="124"/>
+      <c r="L51" s="124"/>
+      <c r="M51" s="124"/>
+      <c r="N51" s="124"/>
+      <c r="O51" s="124"/>
+      <c r="P51" s="124"/>
+      <c r="Q51" s="124"/>
+      <c r="R51" s="124"/>
+      <c r="S51" s="124"/>
+      <c r="T51" s="124"/>
       <c r="U51" s="58"/>
-      <c r="V51" s="118" t="s">
+      <c r="V51" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="W51" s="118"/>
-      <c r="X51" s="118"/>
-      <c r="Y51" s="118"/>
-      <c r="Z51" s="118"/>
-      <c r="AA51" s="118"/>
-      <c r="AB51" s="118"/>
-      <c r="AC51" s="123"/>
-      <c r="AD51" s="123"/>
-      <c r="AE51" s="123"/>
-      <c r="AF51" s="123"/>
-      <c r="AG51" s="123"/>
-      <c r="AH51" s="123"/>
-      <c r="AI51" s="123"/>
+      <c r="W51" s="120"/>
+      <c r="X51" s="120"/>
+      <c r="Y51" s="120"/>
+      <c r="Z51" s="120"/>
+      <c r="AA51" s="120"/>
+      <c r="AB51" s="120"/>
+      <c r="AC51" s="88"/>
+      <c r="AD51" s="88"/>
+      <c r="AE51" s="88"/>
+      <c r="AF51" s="88"/>
+      <c r="AG51" s="88"/>
+      <c r="AH51" s="88"/>
+      <c r="AI51" s="88"/>
       <c r="AJ51" s="58"/>
       <c r="AK51" s="8"/>
     </row>
@@ -3750,45 +3784,45 @@
       <c r="AK52" s="8"/>
     </row>
     <row r="53" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="129" t="s">
+      <c r="A53" s="130" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="118"/>
-      <c r="C53" s="118"/>
-      <c r="D53" s="118"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="118"/>
-      <c r="H53" s="121"/>
-      <c r="I53" s="121"/>
-      <c r="J53" s="121"/>
-      <c r="K53" s="121"/>
-      <c r="L53" s="121"/>
-      <c r="M53" s="121"/>
-      <c r="N53" s="121"/>
-      <c r="O53" s="121"/>
-      <c r="P53" s="121"/>
-      <c r="Q53" s="121"/>
-      <c r="R53" s="121"/>
-      <c r="S53" s="121"/>
-      <c r="T53" s="121"/>
+      <c r="B53" s="120"/>
+      <c r="C53" s="120"/>
+      <c r="D53" s="120"/>
+      <c r="E53" s="120"/>
+      <c r="F53" s="120"/>
+      <c r="G53" s="120"/>
+      <c r="H53" s="124"/>
+      <c r="I53" s="124"/>
+      <c r="J53" s="124"/>
+      <c r="K53" s="124"/>
+      <c r="L53" s="124"/>
+      <c r="M53" s="124"/>
+      <c r="N53" s="124"/>
+      <c r="O53" s="124"/>
+      <c r="P53" s="124"/>
+      <c r="Q53" s="124"/>
+      <c r="R53" s="124"/>
+      <c r="S53" s="124"/>
+      <c r="T53" s="124"/>
       <c r="U53" s="58"/>
-      <c r="V53" s="118" t="s">
+      <c r="V53" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="W53" s="118"/>
-      <c r="X53" s="118"/>
-      <c r="Y53" s="118"/>
-      <c r="Z53" s="118"/>
-      <c r="AA53" s="118"/>
-      <c r="AB53" s="118"/>
-      <c r="AC53" s="123"/>
-      <c r="AD53" s="123"/>
-      <c r="AE53" s="123"/>
-      <c r="AF53" s="123"/>
-      <c r="AG53" s="123"/>
-      <c r="AH53" s="123"/>
-      <c r="AI53" s="123"/>
+      <c r="W53" s="120"/>
+      <c r="X53" s="120"/>
+      <c r="Y53" s="120"/>
+      <c r="Z53" s="120"/>
+      <c r="AA53" s="120"/>
+      <c r="AB53" s="120"/>
+      <c r="AC53" s="88"/>
+      <c r="AD53" s="88"/>
+      <c r="AE53" s="88"/>
+      <c r="AF53" s="88"/>
+      <c r="AG53" s="88"/>
+      <c r="AH53" s="88"/>
+      <c r="AI53" s="88"/>
       <c r="AJ53" s="58"/>
       <c r="AK53" s="8"/>
     </row>
@@ -3819,45 +3853,45 @@
       <c r="AK54" s="8"/>
     </row>
     <row r="55" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="129" t="s">
+      <c r="A55" s="130" t="s">
         <v>45</v>
       </c>
-      <c r="B55" s="118"/>
-      <c r="C55" s="118"/>
-      <c r="D55" s="118"/>
-      <c r="E55" s="118"/>
-      <c r="F55" s="118"/>
-      <c r="G55" s="118"/>
-      <c r="H55" s="121"/>
-      <c r="I55" s="121"/>
-      <c r="J55" s="121"/>
-      <c r="K55" s="121"/>
-      <c r="L55" s="121"/>
-      <c r="M55" s="121"/>
-      <c r="N55" s="121"/>
-      <c r="O55" s="121"/>
-      <c r="P55" s="121"/>
-      <c r="Q55" s="121"/>
-      <c r="R55" s="121"/>
-      <c r="S55" s="121"/>
-      <c r="T55" s="121"/>
+      <c r="B55" s="120"/>
+      <c r="C55" s="120"/>
+      <c r="D55" s="120"/>
+      <c r="E55" s="120"/>
+      <c r="F55" s="120"/>
+      <c r="G55" s="120"/>
+      <c r="H55" s="124"/>
+      <c r="I55" s="124"/>
+      <c r="J55" s="124"/>
+      <c r="K55" s="124"/>
+      <c r="L55" s="124"/>
+      <c r="M55" s="124"/>
+      <c r="N55" s="124"/>
+      <c r="O55" s="124"/>
+      <c r="P55" s="124"/>
+      <c r="Q55" s="124"/>
+      <c r="R55" s="124"/>
+      <c r="S55" s="124"/>
+      <c r="T55" s="124"/>
       <c r="U55" s="58"/>
-      <c r="V55" s="118" t="s">
+      <c r="V55" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="W55" s="118"/>
-      <c r="X55" s="118"/>
-      <c r="Y55" s="118"/>
-      <c r="Z55" s="118"/>
-      <c r="AA55" s="118"/>
-      <c r="AB55" s="118"/>
-      <c r="AC55" s="123"/>
-      <c r="AD55" s="123"/>
-      <c r="AE55" s="123"/>
-      <c r="AF55" s="123"/>
-      <c r="AG55" s="123"/>
-      <c r="AH55" s="123"/>
-      <c r="AI55" s="123"/>
+      <c r="W55" s="120"/>
+      <c r="X55" s="120"/>
+      <c r="Y55" s="120"/>
+      <c r="Z55" s="120"/>
+      <c r="AA55" s="120"/>
+      <c r="AB55" s="120"/>
+      <c r="AC55" s="88"/>
+      <c r="AD55" s="88"/>
+      <c r="AE55" s="88"/>
+      <c r="AF55" s="88"/>
+      <c r="AG55" s="88"/>
+      <c r="AH55" s="88"/>
+      <c r="AI55" s="88"/>
       <c r="AJ55" s="58"/>
       <c r="AK55" s="8"/>
     </row>
@@ -3888,45 +3922,45 @@
       <c r="AK56" s="8"/>
     </row>
     <row r="57" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="129" t="s">
+      <c r="A57" s="130" t="s">
         <v>46</v>
       </c>
-      <c r="B57" s="118"/>
-      <c r="C57" s="118"/>
-      <c r="D57" s="118"/>
-      <c r="E57" s="118"/>
-      <c r="F57" s="118"/>
-      <c r="G57" s="118"/>
-      <c r="H57" s="121"/>
-      <c r="I57" s="121"/>
-      <c r="J57" s="121"/>
-      <c r="K57" s="121"/>
-      <c r="L57" s="121"/>
-      <c r="M57" s="121"/>
-      <c r="N57" s="121"/>
-      <c r="O57" s="121"/>
-      <c r="P57" s="121"/>
-      <c r="Q57" s="121"/>
-      <c r="R57" s="121"/>
-      <c r="S57" s="121"/>
-      <c r="T57" s="121"/>
+      <c r="B57" s="120"/>
+      <c r="C57" s="120"/>
+      <c r="D57" s="120"/>
+      <c r="E57" s="120"/>
+      <c r="F57" s="120"/>
+      <c r="G57" s="120"/>
+      <c r="H57" s="124"/>
+      <c r="I57" s="124"/>
+      <c r="J57" s="124"/>
+      <c r="K57" s="124"/>
+      <c r="L57" s="124"/>
+      <c r="M57" s="124"/>
+      <c r="N57" s="124"/>
+      <c r="O57" s="124"/>
+      <c r="P57" s="124"/>
+      <c r="Q57" s="124"/>
+      <c r="R57" s="124"/>
+      <c r="S57" s="124"/>
+      <c r="T57" s="124"/>
       <c r="U57" s="58"/>
-      <c r="V57" s="118" t="s">
+      <c r="V57" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="W57" s="118"/>
-      <c r="X57" s="118"/>
-      <c r="Y57" s="118"/>
-      <c r="Z57" s="118"/>
-      <c r="AA57" s="118"/>
-      <c r="AB57" s="118"/>
-      <c r="AC57" s="123"/>
-      <c r="AD57" s="123"/>
-      <c r="AE57" s="123"/>
-      <c r="AF57" s="123"/>
-      <c r="AG57" s="123"/>
-      <c r="AH57" s="123"/>
-      <c r="AI57" s="123"/>
+      <c r="W57" s="120"/>
+      <c r="X57" s="120"/>
+      <c r="Y57" s="120"/>
+      <c r="Z57" s="120"/>
+      <c r="AA57" s="120"/>
+      <c r="AB57" s="120"/>
+      <c r="AC57" s="88"/>
+      <c r="AD57" s="88"/>
+      <c r="AE57" s="88"/>
+      <c r="AF57" s="88"/>
+      <c r="AG57" s="88"/>
+      <c r="AH57" s="88"/>
+      <c r="AI57" s="88"/>
       <c r="AJ57" s="58"/>
       <c r="AK57" s="8"/>
     </row>
@@ -3944,49 +3978,45 @@
       <c r="AK58" s="8"/>
     </row>
     <row r="59" spans="1:37" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="119" t="s">
+      <c r="A59" s="200" t="s">
+        <v>110</v>
+      </c>
+      <c r="B59" s="201"/>
+      <c r="C59" s="201"/>
+      <c r="D59" s="201"/>
+      <c r="E59" s="201"/>
+      <c r="F59" s="201"/>
+      <c r="G59" s="201"/>
+      <c r="H59" s="201"/>
+      <c r="I59" s="201"/>
+      <c r="J59" s="201"/>
+      <c r="K59" s="201"/>
+      <c r="L59" s="201"/>
+      <c r="M59" s="201"/>
+      <c r="N59" s="201"/>
+      <c r="O59" s="202"/>
+      <c r="P59" s="203"/>
+      <c r="Q59" s="203"/>
+      <c r="R59" s="204"/>
+      <c r="S59" s="205"/>
+      <c r="T59" s="205"/>
+      <c r="U59" s="205"/>
+      <c r="V59" s="205"/>
+      <c r="W59" s="206"/>
+      <c r="X59" s="58"/>
+      <c r="Y59" s="120" t="s">
         <v>47</v>
       </c>
-      <c r="B59" s="120"/>
-      <c r="C59" s="120"/>
-      <c r="D59" s="120"/>
-      <c r="E59" s="120"/>
-      <c r="F59" s="120"/>
-      <c r="G59" s="120"/>
-      <c r="H59" s="120"/>
-      <c r="I59" s="120"/>
-      <c r="J59" s="120"/>
-      <c r="K59" s="120"/>
-      <c r="L59" s="120"/>
-      <c r="M59" s="120"/>
-      <c r="N59" s="120"/>
-      <c r="O59" s="58"/>
-      <c r="P59" s="118" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q59" s="118"/>
-      <c r="R59" s="14"/>
-      <c r="S59" s="58"/>
-      <c r="T59" s="118" t="s">
-        <v>49</v>
-      </c>
-      <c r="U59" s="118"/>
-      <c r="V59" s="118"/>
-      <c r="W59" s="14"/>
-      <c r="X59" s="58"/>
-      <c r="Y59" s="118" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z59" s="118"/>
-      <c r="AA59" s="118"/>
-      <c r="AB59" s="118"/>
-      <c r="AC59" s="126"/>
-      <c r="AD59" s="126"/>
-      <c r="AE59" s="126"/>
-      <c r="AF59" s="126"/>
-      <c r="AG59" s="126"/>
-      <c r="AH59" s="126"/>
-      <c r="AI59" s="126"/>
+      <c r="Z59" s="120"/>
+      <c r="AA59" s="120"/>
+      <c r="AB59" s="120"/>
+      <c r="AC59" s="127"/>
+      <c r="AD59" s="127"/>
+      <c r="AE59" s="127"/>
+      <c r="AF59" s="127"/>
+      <c r="AG59" s="127"/>
+      <c r="AH59" s="127"/>
+      <c r="AI59" s="127"/>
       <c r="AJ59" s="66"/>
       <c r="AK59" s="8"/>
     </row>
@@ -3996,141 +4026,141 @@
       <c r="AK60" s="8"/>
     </row>
     <row r="61" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="115" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" s="116"/>
-      <c r="C61" s="116"/>
-      <c r="D61" s="116"/>
-      <c r="E61" s="116"/>
-      <c r="F61" s="116"/>
-      <c r="G61" s="116"/>
-      <c r="H61" s="116"/>
-      <c r="I61" s="116"/>
-      <c r="J61" s="116"/>
-      <c r="K61" s="116"/>
-      <c r="L61" s="116"/>
-      <c r="M61" s="116"/>
-      <c r="N61" s="116"/>
-      <c r="O61" s="116"/>
-      <c r="P61" s="116"/>
-      <c r="Q61" s="116"/>
-      <c r="R61" s="116"/>
-      <c r="S61" s="116"/>
-      <c r="T61" s="116"/>
-      <c r="U61" s="116"/>
-      <c r="V61" s="116"/>
-      <c r="W61" s="116"/>
-      <c r="X61" s="116"/>
-      <c r="Y61" s="116"/>
-      <c r="Z61" s="116"/>
-      <c r="AA61" s="116"/>
-      <c r="AB61" s="116"/>
-      <c r="AC61" s="116"/>
-      <c r="AD61" s="116"/>
-      <c r="AE61" s="116"/>
-      <c r="AF61" s="116"/>
-      <c r="AG61" s="116"/>
-      <c r="AH61" s="116"/>
-      <c r="AI61" s="116"/>
-      <c r="AJ61" s="116"/>
-      <c r="AK61" s="117"/>
+      <c r="A61" s="117" t="s">
+        <v>48</v>
+      </c>
+      <c r="B61" s="118"/>
+      <c r="C61" s="118"/>
+      <c r="D61" s="118"/>
+      <c r="E61" s="118"/>
+      <c r="F61" s="118"/>
+      <c r="G61" s="118"/>
+      <c r="H61" s="118"/>
+      <c r="I61" s="118"/>
+      <c r="J61" s="118"/>
+      <c r="K61" s="118"/>
+      <c r="L61" s="118"/>
+      <c r="M61" s="118"/>
+      <c r="N61" s="118"/>
+      <c r="O61" s="118"/>
+      <c r="P61" s="118"/>
+      <c r="Q61" s="118"/>
+      <c r="R61" s="118"/>
+      <c r="S61" s="118"/>
+      <c r="T61" s="118"/>
+      <c r="U61" s="118"/>
+      <c r="V61" s="118"/>
+      <c r="W61" s="118"/>
+      <c r="X61" s="118"/>
+      <c r="Y61" s="118"/>
+      <c r="Z61" s="118"/>
+      <c r="AA61" s="118"/>
+      <c r="AB61" s="118"/>
+      <c r="AC61" s="118"/>
+      <c r="AD61" s="118"/>
+      <c r="AE61" s="118"/>
+      <c r="AF61" s="118"/>
+      <c r="AG61" s="118"/>
+      <c r="AH61" s="118"/>
+      <c r="AI61" s="118"/>
+      <c r="AJ61" s="118"/>
+      <c r="AK61" s="119"/>
     </row>
     <row r="62" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="129" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="118"/>
-      <c r="C62" s="118"/>
-      <c r="D62" s="118"/>
-      <c r="E62" s="118"/>
-      <c r="F62" s="118"/>
-      <c r="G62" s="118"/>
+      <c r="A62" s="130" t="s">
+        <v>49</v>
+      </c>
+      <c r="B62" s="120"/>
+      <c r="C62" s="120"/>
+      <c r="D62" s="120"/>
+      <c r="E62" s="120"/>
+      <c r="F62" s="120"/>
+      <c r="G62" s="120"/>
       <c r="H62" s="58" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I62" s="77"/>
       <c r="J62" s="58"/>
       <c r="K62" s="58" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L62" s="77"/>
       <c r="M62" s="58"/>
-      <c r="N62" s="118" t="s">
-        <v>55</v>
-      </c>
-      <c r="O62" s="118"/>
-      <c r="P62" s="118"/>
-      <c r="Q62" s="130"/>
-      <c r="R62" s="130"/>
-      <c r="S62" s="130"/>
-      <c r="T62" s="130"/>
-      <c r="U62" s="130"/>
-      <c r="V62" s="118" t="s">
-        <v>56</v>
-      </c>
-      <c r="W62" s="118"/>
-      <c r="X62" s="118"/>
-      <c r="Y62" s="118"/>
-      <c r="Z62" s="118"/>
-      <c r="AA62" s="118"/>
-      <c r="AB62" s="118"/>
-      <c r="AC62" s="126"/>
-      <c r="AD62" s="126"/>
-      <c r="AE62" s="126"/>
-      <c r="AF62" s="126"/>
-      <c r="AG62" s="126"/>
-      <c r="AH62" s="126"/>
-      <c r="AI62" s="126"/>
+      <c r="N62" s="120" t="s">
+        <v>52</v>
+      </c>
+      <c r="O62" s="120"/>
+      <c r="P62" s="120"/>
+      <c r="Q62" s="131"/>
+      <c r="R62" s="131"/>
+      <c r="S62" s="131"/>
+      <c r="T62" s="131"/>
+      <c r="U62" s="131"/>
+      <c r="V62" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="W62" s="120"/>
+      <c r="X62" s="120"/>
+      <c r="Y62" s="120"/>
+      <c r="Z62" s="120"/>
+      <c r="AA62" s="120"/>
+      <c r="AB62" s="120"/>
+      <c r="AC62" s="208"/>
+      <c r="AD62" s="208"/>
+      <c r="AE62" s="208"/>
+      <c r="AF62" s="208"/>
+      <c r="AG62" s="208"/>
+      <c r="AH62" s="208"/>
+      <c r="AI62" s="208"/>
       <c r="AJ62" s="66"/>
       <c r="AK62" s="8"/>
     </row>
     <row r="63" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="129" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63" s="118"/>
-      <c r="C63" s="118"/>
-      <c r="D63" s="118"/>
-      <c r="E63" s="118"/>
-      <c r="F63" s="118"/>
-      <c r="G63" s="118"/>
+      <c r="A63" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="B63" s="120"/>
+      <c r="C63" s="120"/>
+      <c r="D63" s="120"/>
+      <c r="E63" s="120"/>
+      <c r="F63" s="120"/>
+      <c r="G63" s="120"/>
       <c r="H63" s="58" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I63" s="14"/>
       <c r="J63" s="58"/>
       <c r="K63" s="58" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L63" s="14"/>
       <c r="M63" s="58"/>
-      <c r="N63" s="118" t="s">
-        <v>55</v>
-      </c>
-      <c r="O63" s="118"/>
-      <c r="P63" s="118"/>
-      <c r="Q63" s="130"/>
-      <c r="R63" s="130"/>
-      <c r="S63" s="130"/>
-      <c r="T63" s="130"/>
-      <c r="U63" s="130"/>
-      <c r="V63" s="118" t="s">
-        <v>56</v>
-      </c>
-      <c r="W63" s="118"/>
-      <c r="X63" s="118"/>
-      <c r="Y63" s="118"/>
-      <c r="Z63" s="118"/>
-      <c r="AA63" s="118"/>
-      <c r="AB63" s="118"/>
-      <c r="AC63" s="131"/>
-      <c r="AD63" s="131"/>
-      <c r="AE63" s="131"/>
-      <c r="AF63" s="131"/>
-      <c r="AG63" s="131"/>
-      <c r="AH63" s="131"/>
-      <c r="AI63" s="131"/>
+      <c r="N63" s="120" t="s">
+        <v>52</v>
+      </c>
+      <c r="O63" s="120"/>
+      <c r="P63" s="120"/>
+      <c r="Q63" s="131"/>
+      <c r="R63" s="131"/>
+      <c r="S63" s="131"/>
+      <c r="T63" s="131"/>
+      <c r="U63" s="131"/>
+      <c r="V63" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="W63" s="120"/>
+      <c r="X63" s="120"/>
+      <c r="Y63" s="120"/>
+      <c r="Z63" s="120"/>
+      <c r="AA63" s="120"/>
+      <c r="AB63" s="120"/>
+      <c r="AC63" s="132"/>
+      <c r="AD63" s="132"/>
+      <c r="AE63" s="132"/>
+      <c r="AF63" s="132"/>
+      <c r="AG63" s="132"/>
+      <c r="AH63" s="132"/>
+      <c r="AI63" s="132"/>
       <c r="AJ63" s="66"/>
       <c r="AK63" s="8"/>
     </row>
@@ -4145,51 +4175,51 @@
       <c r="AK64" s="8"/>
     </row>
     <row r="65" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="129" t="s">
-        <v>58</v>
-      </c>
-      <c r="B65" s="118"/>
-      <c r="C65" s="118"/>
-      <c r="D65" s="118"/>
-      <c r="E65" s="118"/>
-      <c r="F65" s="118"/>
-      <c r="G65" s="118"/>
+      <c r="A65" s="130" t="s">
+        <v>55</v>
+      </c>
+      <c r="B65" s="120"/>
+      <c r="C65" s="120"/>
+      <c r="D65" s="120"/>
+      <c r="E65" s="120"/>
+      <c r="F65" s="120"/>
+      <c r="G65" s="120"/>
       <c r="H65" s="58" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I65" s="14"/>
       <c r="J65" s="58"/>
       <c r="K65" s="58" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L65" s="14"/>
       <c r="M65" s="58"/>
-      <c r="N65" s="118" t="s">
-        <v>55</v>
-      </c>
-      <c r="O65" s="118"/>
-      <c r="P65" s="118"/>
-      <c r="Q65" s="130"/>
-      <c r="R65" s="130"/>
-      <c r="S65" s="130"/>
-      <c r="T65" s="130"/>
-      <c r="U65" s="130"/>
-      <c r="V65" s="118" t="s">
-        <v>56</v>
-      </c>
-      <c r="W65" s="118"/>
-      <c r="X65" s="118"/>
-      <c r="Y65" s="118"/>
-      <c r="Z65" s="118"/>
-      <c r="AA65" s="118"/>
-      <c r="AB65" s="118"/>
-      <c r="AC65" s="126"/>
-      <c r="AD65" s="126"/>
-      <c r="AE65" s="126"/>
-      <c r="AF65" s="126"/>
-      <c r="AG65" s="126"/>
-      <c r="AH65" s="126"/>
-      <c r="AI65" s="126"/>
+      <c r="N65" s="120" t="s">
+        <v>52</v>
+      </c>
+      <c r="O65" s="120"/>
+      <c r="P65" s="120"/>
+      <c r="Q65" s="131"/>
+      <c r="R65" s="131"/>
+      <c r="S65" s="131"/>
+      <c r="T65" s="131"/>
+      <c r="U65" s="131"/>
+      <c r="V65" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="W65" s="120"/>
+      <c r="X65" s="120"/>
+      <c r="Y65" s="120"/>
+      <c r="Z65" s="120"/>
+      <c r="AA65" s="120"/>
+      <c r="AB65" s="120"/>
+      <c r="AC65" s="208"/>
+      <c r="AD65" s="208"/>
+      <c r="AE65" s="208"/>
+      <c r="AF65" s="208"/>
+      <c r="AG65" s="208"/>
+      <c r="AH65" s="208"/>
+      <c r="AI65" s="208"/>
       <c r="AJ65" s="66"/>
       <c r="AK65" s="8"/>
     </row>
@@ -4213,47 +4243,47 @@
       <c r="AK66" s="8"/>
     </row>
     <row r="67" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="129" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="118"/>
-      <c r="C67" s="118"/>
-      <c r="D67" s="118"/>
-      <c r="E67" s="118"/>
-      <c r="F67" s="118"/>
-      <c r="G67" s="118"/>
-      <c r="H67" s="121"/>
-      <c r="I67" s="121"/>
-      <c r="J67" s="121"/>
-      <c r="K67" s="121"/>
-      <c r="L67" s="121"/>
+      <c r="A67" s="130" t="s">
+        <v>56</v>
+      </c>
+      <c r="B67" s="120"/>
+      <c r="C67" s="120"/>
+      <c r="D67" s="120"/>
+      <c r="E67" s="120"/>
+      <c r="F67" s="120"/>
+      <c r="G67" s="120"/>
+      <c r="H67" s="124"/>
+      <c r="I67" s="124"/>
+      <c r="J67" s="124"/>
+      <c r="K67" s="124"/>
+      <c r="L67" s="124"/>
       <c r="M67" s="58"/>
-      <c r="N67" s="118" t="s">
-        <v>55</v>
-      </c>
-      <c r="O67" s="118"/>
-      <c r="P67" s="118"/>
-      <c r="Q67" s="130"/>
-      <c r="R67" s="130"/>
-      <c r="S67" s="130"/>
-      <c r="T67" s="130"/>
-      <c r="U67" s="130"/>
-      <c r="V67" s="118" t="s">
-        <v>56</v>
-      </c>
-      <c r="W67" s="118"/>
-      <c r="X67" s="118"/>
-      <c r="Y67" s="118"/>
-      <c r="Z67" s="118"/>
-      <c r="AA67" s="118"/>
-      <c r="AB67" s="118"/>
-      <c r="AC67" s="126"/>
-      <c r="AD67" s="126"/>
-      <c r="AE67" s="126"/>
-      <c r="AF67" s="126"/>
-      <c r="AG67" s="126"/>
-      <c r="AH67" s="126"/>
-      <c r="AI67" s="126"/>
+      <c r="N67" s="120" t="s">
+        <v>52</v>
+      </c>
+      <c r="O67" s="120"/>
+      <c r="P67" s="120"/>
+      <c r="Q67" s="131"/>
+      <c r="R67" s="131"/>
+      <c r="S67" s="131"/>
+      <c r="T67" s="131"/>
+      <c r="U67" s="131"/>
+      <c r="V67" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="W67" s="120"/>
+      <c r="X67" s="120"/>
+      <c r="Y67" s="120"/>
+      <c r="Z67" s="120"/>
+      <c r="AA67" s="120"/>
+      <c r="AB67" s="120"/>
+      <c r="AC67" s="127"/>
+      <c r="AD67" s="127"/>
+      <c r="AE67" s="127"/>
+      <c r="AF67" s="127"/>
+      <c r="AG67" s="127"/>
+      <c r="AH67" s="127"/>
+      <c r="AI67" s="127"/>
       <c r="AJ67" s="66"/>
       <c r="AK67" s="8"/>
     </row>
@@ -4297,45 +4327,45 @@
       <c r="AK68" s="10"/>
     </row>
     <row r="69" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="92" t="s">
-        <v>60</v>
-      </c>
-      <c r="B69" s="93"/>
-      <c r="C69" s="93"/>
-      <c r="D69" s="93"/>
-      <c r="E69" s="93"/>
-      <c r="F69" s="93"/>
-      <c r="G69" s="93"/>
-      <c r="H69" s="93"/>
-      <c r="I69" s="93"/>
-      <c r="J69" s="93"/>
-      <c r="K69" s="93"/>
-      <c r="L69" s="93"/>
-      <c r="M69" s="93"/>
-      <c r="N69" s="93"/>
-      <c r="O69" s="93"/>
-      <c r="P69" s="93"/>
-      <c r="Q69" s="93"/>
-      <c r="R69" s="93"/>
-      <c r="S69" s="93"/>
-      <c r="T69" s="93"/>
-      <c r="U69" s="93"/>
-      <c r="V69" s="93"/>
-      <c r="W69" s="93"/>
-      <c r="X69" s="93"/>
-      <c r="Y69" s="93"/>
-      <c r="Z69" s="93"/>
-      <c r="AA69" s="93"/>
-      <c r="AB69" s="93"/>
-      <c r="AC69" s="93"/>
-      <c r="AD69" s="93"/>
-      <c r="AE69" s="93"/>
-      <c r="AF69" s="93"/>
-      <c r="AG69" s="93"/>
-      <c r="AH69" s="93"/>
-      <c r="AI69" s="93"/>
-      <c r="AJ69" s="93"/>
-      <c r="AK69" s="94"/>
+      <c r="A69" s="94" t="s">
+        <v>57</v>
+      </c>
+      <c r="B69" s="95"/>
+      <c r="C69" s="95"/>
+      <c r="D69" s="95"/>
+      <c r="E69" s="95"/>
+      <c r="F69" s="95"/>
+      <c r="G69" s="95"/>
+      <c r="H69" s="95"/>
+      <c r="I69" s="95"/>
+      <c r="J69" s="95"/>
+      <c r="K69" s="95"/>
+      <c r="L69" s="95"/>
+      <c r="M69" s="95"/>
+      <c r="N69" s="95"/>
+      <c r="O69" s="95"/>
+      <c r="P69" s="95"/>
+      <c r="Q69" s="95"/>
+      <c r="R69" s="95"/>
+      <c r="S69" s="95"/>
+      <c r="T69" s="95"/>
+      <c r="U69" s="95"/>
+      <c r="V69" s="95"/>
+      <c r="W69" s="95"/>
+      <c r="X69" s="95"/>
+      <c r="Y69" s="95"/>
+      <c r="Z69" s="95"/>
+      <c r="AA69" s="95"/>
+      <c r="AB69" s="95"/>
+      <c r="AC69" s="95"/>
+      <c r="AD69" s="95"/>
+      <c r="AE69" s="95"/>
+      <c r="AF69" s="95"/>
+      <c r="AG69" s="95"/>
+      <c r="AH69" s="95"/>
+      <c r="AI69" s="95"/>
+      <c r="AJ69" s="95"/>
+      <c r="AK69" s="96"/>
     </row>
     <row r="70" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="47"/>
@@ -4343,94 +4373,94 @@
       <c r="AK70" s="10"/>
     </row>
     <row r="71" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="132" t="s">
+      <c r="A71" s="133" t="s">
+        <v>58</v>
+      </c>
+      <c r="B71" s="134"/>
+      <c r="C71" s="134"/>
+      <c r="D71" s="134"/>
+      <c r="E71" s="134"/>
+      <c r="F71" s="134"/>
+      <c r="G71" s="134"/>
+      <c r="H71" s="134"/>
+      <c r="I71" s="134"/>
+      <c r="J71" s="134"/>
+      <c r="K71" s="134"/>
+      <c r="L71" s="134"/>
+      <c r="M71" s="134"/>
+      <c r="N71" s="134"/>
+      <c r="O71" s="134"/>
+      <c r="P71" s="134"/>
+      <c r="Q71" s="134"/>
+      <c r="R71" s="135"/>
+      <c r="S71" s="133" t="s">
+        <v>59</v>
+      </c>
+      <c r="T71" s="134"/>
+      <c r="U71" s="134"/>
+      <c r="V71" s="134"/>
+      <c r="W71" s="134"/>
+      <c r="X71" s="134"/>
+      <c r="Y71" s="134"/>
+      <c r="Z71" s="134"/>
+      <c r="AA71" s="134"/>
+      <c r="AB71" s="134"/>
+      <c r="AC71" s="134"/>
+      <c r="AD71" s="134"/>
+      <c r="AE71" s="134"/>
+      <c r="AF71" s="136"/>
+      <c r="AG71" s="136"/>
+      <c r="AH71" s="136"/>
+      <c r="AI71" s="136"/>
+      <c r="AJ71" s="137"/>
+      <c r="AK71" s="6"/>
+    </row>
+    <row r="72" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="138" t="s">
+        <v>60</v>
+      </c>
+      <c r="B72" s="139"/>
+      <c r="C72" s="139"/>
+      <c r="D72" s="139"/>
+      <c r="E72" s="139"/>
+      <c r="F72" s="139"/>
+      <c r="G72" s="139"/>
+      <c r="H72" s="139"/>
+      <c r="I72" s="139"/>
+      <c r="J72" s="139"/>
+      <c r="K72" s="139"/>
+      <c r="L72" s="139"/>
+      <c r="M72" s="139"/>
+      <c r="N72" s="139" t="s">
         <v>61</v>
       </c>
-      <c r="B71" s="133"/>
-      <c r="C71" s="133"/>
-      <c r="D71" s="133"/>
-      <c r="E71" s="133"/>
-      <c r="F71" s="133"/>
-      <c r="G71" s="133"/>
-      <c r="H71" s="133"/>
-      <c r="I71" s="133"/>
-      <c r="J71" s="133"/>
-      <c r="K71" s="133"/>
-      <c r="L71" s="133"/>
-      <c r="M71" s="133"/>
-      <c r="N71" s="133"/>
-      <c r="O71" s="133"/>
-      <c r="P71" s="133"/>
-      <c r="Q71" s="133"/>
-      <c r="R71" s="134"/>
-      <c r="S71" s="132" t="s">
-        <v>62</v>
-      </c>
-      <c r="T71" s="133"/>
-      <c r="U71" s="133"/>
-      <c r="V71" s="133"/>
-      <c r="W71" s="133"/>
-      <c r="X71" s="133"/>
-      <c r="Y71" s="133"/>
-      <c r="Z71" s="133"/>
-      <c r="AA71" s="133"/>
-      <c r="AB71" s="133"/>
-      <c r="AC71" s="133"/>
-      <c r="AD71" s="133"/>
-      <c r="AE71" s="133"/>
-      <c r="AF71" s="135"/>
-      <c r="AG71" s="135"/>
-      <c r="AH71" s="135"/>
-      <c r="AI71" s="135"/>
-      <c r="AJ71" s="136"/>
-      <c r="AK71" s="6"/>
-    </row>
-    <row r="72" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="137" t="s">
-        <v>63</v>
-      </c>
-      <c r="B72" s="138"/>
-      <c r="C72" s="138"/>
-      <c r="D72" s="138"/>
-      <c r="E72" s="138"/>
-      <c r="F72" s="138"/>
-      <c r="G72" s="138"/>
-      <c r="H72" s="138"/>
-      <c r="I72" s="138"/>
-      <c r="J72" s="138"/>
-      <c r="K72" s="138"/>
-      <c r="L72" s="138"/>
-      <c r="M72" s="138"/>
-      <c r="N72" s="138" t="s">
-        <v>64</v>
-      </c>
-      <c r="O72" s="138"/>
-      <c r="P72" s="138"/>
-      <c r="Q72" s="138"/>
-      <c r="R72" s="139"/>
-      <c r="S72" s="137" t="s">
-        <v>63</v>
-      </c>
-      <c r="T72" s="138"/>
-      <c r="U72" s="138"/>
-      <c r="V72" s="138"/>
-      <c r="W72" s="138"/>
-      <c r="X72" s="138"/>
-      <c r="Y72" s="138"/>
-      <c r="Z72" s="138"/>
-      <c r="AA72" s="138"/>
-      <c r="AB72" s="138"/>
-      <c r="AC72" s="138"/>
-      <c r="AD72" s="138"/>
-      <c r="AE72" s="138"/>
-      <c r="AF72" s="98" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG72" s="99"/>
-      <c r="AH72" s="99"/>
-      <c r="AI72" s="99"/>
-      <c r="AJ72" s="99"/>
-      <c r="AK72" s="100"/>
+      <c r="O72" s="139"/>
+      <c r="P72" s="139"/>
+      <c r="Q72" s="139"/>
+      <c r="R72" s="140"/>
+      <c r="S72" s="138" t="s">
+        <v>60</v>
+      </c>
+      <c r="T72" s="139"/>
+      <c r="U72" s="139"/>
+      <c r="V72" s="139"/>
+      <c r="W72" s="139"/>
+      <c r="X72" s="139"/>
+      <c r="Y72" s="139"/>
+      <c r="Z72" s="139"/>
+      <c r="AA72" s="139"/>
+      <c r="AB72" s="139"/>
+      <c r="AC72" s="139"/>
+      <c r="AD72" s="139"/>
+      <c r="AE72" s="139"/>
+      <c r="AF72" s="100" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG72" s="101"/>
+      <c r="AH72" s="101"/>
+      <c r="AI72" s="101"/>
+      <c r="AJ72" s="101"/>
+      <c r="AK72" s="102"/>
     </row>
     <row r="73" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="47"/>
@@ -4463,52 +4493,52 @@
       <c r="AK73" s="8"/>
     </row>
     <row r="74" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="140" t="s">
-        <v>65</v>
-      </c>
-      <c r="B74" s="141"/>
-      <c r="C74" s="141"/>
-      <c r="D74" s="141"/>
-      <c r="E74" s="141"/>
-      <c r="F74" s="141"/>
-      <c r="G74" s="141"/>
-      <c r="H74" s="141"/>
-      <c r="I74" s="141"/>
-      <c r="J74" s="141"/>
-      <c r="K74" s="141"/>
-      <c r="L74" s="141"/>
-      <c r="M74" s="142"/>
+      <c r="A74" s="141" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="142"/>
+      <c r="C74" s="142"/>
+      <c r="D74" s="142"/>
+      <c r="E74" s="142"/>
+      <c r="F74" s="142"/>
+      <c r="G74" s="142"/>
+      <c r="H74" s="142"/>
+      <c r="I74" s="142"/>
+      <c r="J74" s="142"/>
+      <c r="K74" s="142"/>
+      <c r="L74" s="142"/>
+      <c r="M74" s="143"/>
       <c r="N74" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O74" s="14"/>
       <c r="P74" s="58"/>
       <c r="Q74" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R74" s="79"/>
-      <c r="S74" s="146" t="s">
-        <v>67</v>
-      </c>
-      <c r="T74" s="127"/>
-      <c r="U74" s="127"/>
-      <c r="V74" s="127"/>
-      <c r="W74" s="127"/>
-      <c r="X74" s="127"/>
-      <c r="Y74" s="127"/>
-      <c r="Z74" s="127"/>
-      <c r="AA74" s="127"/>
-      <c r="AB74" s="127"/>
-      <c r="AC74" s="127"/>
-      <c r="AD74" s="127"/>
-      <c r="AE74" s="147"/>
+      <c r="S74" s="147" t="s">
+        <v>64</v>
+      </c>
+      <c r="T74" s="128"/>
+      <c r="U74" s="128"/>
+      <c r="V74" s="128"/>
+      <c r="W74" s="128"/>
+      <c r="X74" s="128"/>
+      <c r="Y74" s="128"/>
+      <c r="Z74" s="128"/>
+      <c r="AA74" s="128"/>
+      <c r="AB74" s="128"/>
+      <c r="AC74" s="128"/>
+      <c r="AD74" s="128"/>
+      <c r="AE74" s="148"/>
       <c r="AF74" s="37" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG74" s="14"/>
       <c r="AH74" s="58"/>
       <c r="AI74" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ74" s="14"/>
       <c r="AK74" s="8"/>
@@ -4553,52 +4583,52 @@
       <c r="AK75" s="8"/>
     </row>
     <row r="76" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="140" t="s">
-        <v>68</v>
-      </c>
-      <c r="B76" s="141"/>
-      <c r="C76" s="141"/>
-      <c r="D76" s="141"/>
-      <c r="E76" s="141"/>
-      <c r="F76" s="141"/>
-      <c r="G76" s="141"/>
-      <c r="H76" s="141"/>
-      <c r="I76" s="141"/>
-      <c r="J76" s="141"/>
-      <c r="K76" s="141"/>
-      <c r="L76" s="141"/>
-      <c r="M76" s="142"/>
+      <c r="A76" s="141" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76" s="142"/>
+      <c r="C76" s="142"/>
+      <c r="D76" s="142"/>
+      <c r="E76" s="142"/>
+      <c r="F76" s="142"/>
+      <c r="G76" s="142"/>
+      <c r="H76" s="142"/>
+      <c r="I76" s="142"/>
+      <c r="J76" s="142"/>
+      <c r="K76" s="142"/>
+      <c r="L76" s="142"/>
+      <c r="M76" s="143"/>
       <c r="N76" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O76" s="14"/>
       <c r="P76" s="58"/>
       <c r="Q76" s="60" t="s">
+        <v>63</v>
+      </c>
+      <c r="R76" s="79"/>
+      <c r="S76" s="147" t="s">
         <v>66</v>
       </c>
-      <c r="R76" s="79"/>
-      <c r="S76" s="146" t="s">
-        <v>69</v>
-      </c>
-      <c r="T76" s="127"/>
-      <c r="U76" s="127"/>
-      <c r="V76" s="127"/>
-      <c r="W76" s="127"/>
-      <c r="X76" s="127"/>
-      <c r="Y76" s="127"/>
-      <c r="Z76" s="127"/>
-      <c r="AA76" s="127"/>
-      <c r="AB76" s="127"/>
-      <c r="AC76" s="127"/>
-      <c r="AD76" s="127"/>
-      <c r="AE76" s="147"/>
+      <c r="T76" s="128"/>
+      <c r="U76" s="128"/>
+      <c r="V76" s="128"/>
+      <c r="W76" s="128"/>
+      <c r="X76" s="128"/>
+      <c r="Y76" s="128"/>
+      <c r="Z76" s="128"/>
+      <c r="AA76" s="128"/>
+      <c r="AB76" s="128"/>
+      <c r="AC76" s="128"/>
+      <c r="AD76" s="128"/>
+      <c r="AE76" s="148"/>
       <c r="AF76" s="37" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG76" s="14"/>
       <c r="AH76" s="58"/>
       <c r="AI76" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ76" s="14"/>
       <c r="AK76" s="8"/>
@@ -4643,52 +4673,52 @@
       <c r="AK77" s="8"/>
     </row>
     <row r="78" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="140" t="s">
-        <v>70</v>
-      </c>
-      <c r="B78" s="141"/>
-      <c r="C78" s="141"/>
-      <c r="D78" s="141"/>
-      <c r="E78" s="141"/>
-      <c r="F78" s="141"/>
-      <c r="G78" s="141"/>
-      <c r="H78" s="141"/>
-      <c r="I78" s="141"/>
-      <c r="J78" s="141"/>
-      <c r="K78" s="141"/>
-      <c r="L78" s="141"/>
-      <c r="M78" s="142"/>
+      <c r="A78" s="141" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" s="142"/>
+      <c r="C78" s="142"/>
+      <c r="D78" s="142"/>
+      <c r="E78" s="142"/>
+      <c r="F78" s="142"/>
+      <c r="G78" s="142"/>
+      <c r="H78" s="142"/>
+      <c r="I78" s="142"/>
+      <c r="J78" s="142"/>
+      <c r="K78" s="142"/>
+      <c r="L78" s="142"/>
+      <c r="M78" s="143"/>
       <c r="N78" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O78" s="14"/>
       <c r="P78" s="58"/>
       <c r="Q78" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R78" s="79"/>
-      <c r="S78" s="146" t="s">
-        <v>71</v>
-      </c>
-      <c r="T78" s="127"/>
-      <c r="U78" s="127"/>
-      <c r="V78" s="127"/>
-      <c r="W78" s="127"/>
-      <c r="X78" s="127"/>
-      <c r="Y78" s="127"/>
-      <c r="Z78" s="127"/>
-      <c r="AA78" s="127"/>
-      <c r="AB78" s="127"/>
-      <c r="AC78" s="127"/>
-      <c r="AD78" s="127"/>
-      <c r="AE78" s="147"/>
+      <c r="S78" s="147" t="s">
+        <v>68</v>
+      </c>
+      <c r="T78" s="128"/>
+      <c r="U78" s="128"/>
+      <c r="V78" s="128"/>
+      <c r="W78" s="128"/>
+      <c r="X78" s="128"/>
+      <c r="Y78" s="128"/>
+      <c r="Z78" s="128"/>
+      <c r="AA78" s="128"/>
+      <c r="AB78" s="128"/>
+      <c r="AC78" s="128"/>
+      <c r="AD78" s="128"/>
+      <c r="AE78" s="148"/>
       <c r="AF78" s="37" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG78" s="14"/>
       <c r="AH78" s="58"/>
       <c r="AI78" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ78" s="14"/>
       <c r="AK78" s="8"/>
@@ -4733,52 +4763,52 @@
       <c r="AK79" s="8"/>
     </row>
     <row r="80" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="140" t="s">
-        <v>72</v>
-      </c>
-      <c r="B80" s="141"/>
-      <c r="C80" s="141"/>
-      <c r="D80" s="141"/>
-      <c r="E80" s="141"/>
-      <c r="F80" s="141"/>
-      <c r="G80" s="141"/>
-      <c r="H80" s="141"/>
-      <c r="I80" s="141"/>
-      <c r="J80" s="141"/>
-      <c r="K80" s="141"/>
-      <c r="L80" s="141"/>
-      <c r="M80" s="142"/>
+      <c r="A80" s="141" t="s">
+        <v>69</v>
+      </c>
+      <c r="B80" s="142"/>
+      <c r="C80" s="142"/>
+      <c r="D80" s="142"/>
+      <c r="E80" s="142"/>
+      <c r="F80" s="142"/>
+      <c r="G80" s="142"/>
+      <c r="H80" s="142"/>
+      <c r="I80" s="142"/>
+      <c r="J80" s="142"/>
+      <c r="K80" s="142"/>
+      <c r="L80" s="142"/>
+      <c r="M80" s="143"/>
       <c r="N80" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O80" s="14"/>
       <c r="P80" s="58"/>
       <c r="Q80" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R80" s="79"/>
-      <c r="S80" s="143" t="s">
-        <v>73</v>
-      </c>
-      <c r="T80" s="144"/>
-      <c r="U80" s="144"/>
-      <c r="V80" s="144"/>
-      <c r="W80" s="144"/>
-      <c r="X80" s="144"/>
-      <c r="Y80" s="144"/>
-      <c r="Z80" s="144"/>
-      <c r="AA80" s="144"/>
-      <c r="AB80" s="144"/>
-      <c r="AC80" s="144"/>
-      <c r="AD80" s="144"/>
-      <c r="AE80" s="145"/>
+      <c r="S80" s="144" t="s">
+        <v>70</v>
+      </c>
+      <c r="T80" s="145"/>
+      <c r="U80" s="145"/>
+      <c r="V80" s="145"/>
+      <c r="W80" s="145"/>
+      <c r="X80" s="145"/>
+      <c r="Y80" s="145"/>
+      <c r="Z80" s="145"/>
+      <c r="AA80" s="145"/>
+      <c r="AB80" s="145"/>
+      <c r="AC80" s="145"/>
+      <c r="AD80" s="145"/>
+      <c r="AE80" s="146"/>
       <c r="AF80" s="67" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG80" s="14"/>
       <c r="AH80" s="52"/>
       <c r="AI80" s="39" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ80" s="14"/>
       <c r="AK80" s="68"/>
@@ -4818,51 +4848,51 @@
       <c r="AK81" s="8"/>
     </row>
     <row r="82" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="140" t="s">
-        <v>74</v>
-      </c>
-      <c r="B82" s="141"/>
-      <c r="C82" s="141"/>
-      <c r="D82" s="141"/>
-      <c r="E82" s="141"/>
-      <c r="F82" s="141"/>
-      <c r="G82" s="141"/>
-      <c r="H82" s="141"/>
-      <c r="I82" s="141"/>
-      <c r="J82" s="141"/>
-      <c r="K82" s="141"/>
-      <c r="L82" s="141"/>
-      <c r="M82" s="142"/>
+      <c r="A82" s="141" t="s">
+        <v>71</v>
+      </c>
+      <c r="B82" s="142"/>
+      <c r="C82" s="142"/>
+      <c r="D82" s="142"/>
+      <c r="E82" s="142"/>
+      <c r="F82" s="142"/>
+      <c r="G82" s="142"/>
+      <c r="H82" s="142"/>
+      <c r="I82" s="142"/>
+      <c r="J82" s="142"/>
+      <c r="K82" s="142"/>
+      <c r="L82" s="142"/>
+      <c r="M82" s="143"/>
       <c r="N82" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O82" s="14"/>
       <c r="P82" s="58"/>
       <c r="Q82" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R82" s="79"/>
-      <c r="S82" s="95" t="s">
-        <v>75</v>
-      </c>
-      <c r="T82" s="96"/>
-      <c r="U82" s="96"/>
-      <c r="V82" s="96"/>
-      <c r="W82" s="96"/>
-      <c r="X82" s="96"/>
-      <c r="Y82" s="96"/>
-      <c r="Z82" s="96"/>
-      <c r="AA82" s="96"/>
-      <c r="AB82" s="96"/>
-      <c r="AC82" s="96"/>
-      <c r="AD82" s="96"/>
-      <c r="AE82" s="96"/>
-      <c r="AF82" s="96"/>
-      <c r="AG82" s="96"/>
-      <c r="AH82" s="96"/>
-      <c r="AI82" s="96"/>
-      <c r="AJ82" s="96"/>
-      <c r="AK82" s="97"/>
+      <c r="S82" s="97" t="s">
+        <v>72</v>
+      </c>
+      <c r="T82" s="98"/>
+      <c r="U82" s="98"/>
+      <c r="V82" s="98"/>
+      <c r="W82" s="98"/>
+      <c r="X82" s="98"/>
+      <c r="Y82" s="98"/>
+      <c r="Z82" s="98"/>
+      <c r="AA82" s="98"/>
+      <c r="AB82" s="98"/>
+      <c r="AC82" s="98"/>
+      <c r="AD82" s="98"/>
+      <c r="AE82" s="98"/>
+      <c r="AF82" s="98"/>
+      <c r="AG82" s="98"/>
+      <c r="AH82" s="98"/>
+      <c r="AI82" s="98"/>
+      <c r="AJ82" s="98"/>
+      <c r="AK82" s="99"/>
     </row>
     <row r="83" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="74"/>
@@ -4899,49 +4929,49 @@
       <c r="AK83" s="8"/>
     </row>
     <row r="84" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="140" t="s">
-        <v>58</v>
-      </c>
-      <c r="B84" s="141"/>
-      <c r="C84" s="141"/>
-      <c r="D84" s="141"/>
-      <c r="E84" s="141"/>
-      <c r="F84" s="141"/>
-      <c r="G84" s="141"/>
-      <c r="H84" s="141"/>
-      <c r="I84" s="141"/>
-      <c r="J84" s="141"/>
-      <c r="K84" s="141"/>
-      <c r="L84" s="141"/>
-      <c r="M84" s="142"/>
+      <c r="A84" s="141" t="s">
+        <v>55</v>
+      </c>
+      <c r="B84" s="142"/>
+      <c r="C84" s="142"/>
+      <c r="D84" s="142"/>
+      <c r="E84" s="142"/>
+      <c r="F84" s="142"/>
+      <c r="G84" s="142"/>
+      <c r="H84" s="142"/>
+      <c r="I84" s="142"/>
+      <c r="J84" s="142"/>
+      <c r="K84" s="142"/>
+      <c r="L84" s="142"/>
+      <c r="M84" s="143"/>
       <c r="N84" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O84" s="14"/>
       <c r="P84" s="58"/>
       <c r="Q84" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R84" s="79"/>
-      <c r="S84" s="101"/>
-      <c r="T84" s="102"/>
-      <c r="U84" s="102"/>
-      <c r="V84" s="102"/>
-      <c r="W84" s="102"/>
-      <c r="X84" s="102"/>
-      <c r="Y84" s="102"/>
-      <c r="Z84" s="102"/>
-      <c r="AA84" s="102"/>
-      <c r="AB84" s="102"/>
-      <c r="AC84" s="102"/>
-      <c r="AD84" s="102"/>
-      <c r="AE84" s="102"/>
-      <c r="AF84" s="102"/>
-      <c r="AG84" s="102"/>
-      <c r="AH84" s="102"/>
-      <c r="AI84" s="102"/>
-      <c r="AJ84" s="102"/>
-      <c r="AK84" s="103"/>
+      <c r="S84" s="103"/>
+      <c r="T84" s="104"/>
+      <c r="U84" s="104"/>
+      <c r="V84" s="104"/>
+      <c r="W84" s="104"/>
+      <c r="X84" s="104"/>
+      <c r="Y84" s="104"/>
+      <c r="Z84" s="104"/>
+      <c r="AA84" s="104"/>
+      <c r="AB84" s="104"/>
+      <c r="AC84" s="104"/>
+      <c r="AD84" s="104"/>
+      <c r="AE84" s="104"/>
+      <c r="AF84" s="104"/>
+      <c r="AG84" s="104"/>
+      <c r="AH84" s="104"/>
+      <c r="AI84" s="104"/>
+      <c r="AJ84" s="104"/>
+      <c r="AK84" s="105"/>
     </row>
     <row r="85" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="74"/>
@@ -4962,70 +4992,70 @@
       <c r="P85" s="42"/>
       <c r="Q85" s="42"/>
       <c r="R85" s="42"/>
-      <c r="S85" s="104"/>
-      <c r="T85" s="105"/>
-      <c r="U85" s="105"/>
-      <c r="V85" s="105"/>
-      <c r="W85" s="105"/>
-      <c r="X85" s="105"/>
-      <c r="Y85" s="105"/>
-      <c r="Z85" s="105"/>
-      <c r="AA85" s="105"/>
-      <c r="AB85" s="105"/>
-      <c r="AC85" s="105"/>
-      <c r="AD85" s="105"/>
-      <c r="AE85" s="105"/>
-      <c r="AF85" s="105"/>
-      <c r="AG85" s="105"/>
-      <c r="AH85" s="105"/>
-      <c r="AI85" s="105"/>
-      <c r="AJ85" s="105"/>
-      <c r="AK85" s="106"/>
+      <c r="S85" s="106"/>
+      <c r="T85" s="107"/>
+      <c r="U85" s="107"/>
+      <c r="V85" s="107"/>
+      <c r="W85" s="107"/>
+      <c r="X85" s="107"/>
+      <c r="Y85" s="107"/>
+      <c r="Z85" s="107"/>
+      <c r="AA85" s="107"/>
+      <c r="AB85" s="107"/>
+      <c r="AC85" s="107"/>
+      <c r="AD85" s="107"/>
+      <c r="AE85" s="107"/>
+      <c r="AF85" s="107"/>
+      <c r="AG85" s="107"/>
+      <c r="AH85" s="107"/>
+      <c r="AI85" s="107"/>
+      <c r="AJ85" s="107"/>
+      <c r="AK85" s="108"/>
     </row>
     <row r="86" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="140" t="s">
-        <v>76</v>
-      </c>
-      <c r="B86" s="141"/>
-      <c r="C86" s="141"/>
-      <c r="D86" s="141"/>
-      <c r="E86" s="141"/>
-      <c r="F86" s="141"/>
-      <c r="G86" s="141"/>
-      <c r="H86" s="141"/>
-      <c r="I86" s="141"/>
-      <c r="J86" s="141"/>
-      <c r="K86" s="141"/>
-      <c r="L86" s="141"/>
-      <c r="M86" s="142"/>
+      <c r="A86" s="141" t="s">
+        <v>73</v>
+      </c>
+      <c r="B86" s="142"/>
+      <c r="C86" s="142"/>
+      <c r="D86" s="142"/>
+      <c r="E86" s="142"/>
+      <c r="F86" s="142"/>
+      <c r="G86" s="142"/>
+      <c r="H86" s="142"/>
+      <c r="I86" s="142"/>
+      <c r="J86" s="142"/>
+      <c r="K86" s="142"/>
+      <c r="L86" s="142"/>
+      <c r="M86" s="143"/>
       <c r="N86" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O86" s="14"/>
       <c r="P86" s="58"/>
       <c r="Q86" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R86" s="79"/>
-      <c r="S86" s="104"/>
-      <c r="T86" s="105"/>
-      <c r="U86" s="105"/>
-      <c r="V86" s="105"/>
-      <c r="W86" s="105"/>
-      <c r="X86" s="105"/>
-      <c r="Y86" s="105"/>
-      <c r="Z86" s="105"/>
-      <c r="AA86" s="105"/>
-      <c r="AB86" s="105"/>
-      <c r="AC86" s="105"/>
-      <c r="AD86" s="105"/>
-      <c r="AE86" s="105"/>
-      <c r="AF86" s="105"/>
-      <c r="AG86" s="105"/>
-      <c r="AH86" s="105"/>
-      <c r="AI86" s="105"/>
-      <c r="AJ86" s="105"/>
-      <c r="AK86" s="106"/>
+      <c r="S86" s="106"/>
+      <c r="T86" s="107"/>
+      <c r="U86" s="107"/>
+      <c r="V86" s="107"/>
+      <c r="W86" s="107"/>
+      <c r="X86" s="107"/>
+      <c r="Y86" s="107"/>
+      <c r="Z86" s="107"/>
+      <c r="AA86" s="107"/>
+      <c r="AB86" s="107"/>
+      <c r="AC86" s="107"/>
+      <c r="AD86" s="107"/>
+      <c r="AE86" s="107"/>
+      <c r="AF86" s="107"/>
+      <c r="AG86" s="107"/>
+      <c r="AH86" s="107"/>
+      <c r="AI86" s="107"/>
+      <c r="AJ86" s="107"/>
+      <c r="AK86" s="108"/>
     </row>
     <row r="87" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="74"/>
@@ -5046,70 +5076,70 @@
       <c r="P87" s="42"/>
       <c r="Q87" s="42"/>
       <c r="R87" s="42"/>
-      <c r="S87" s="104"/>
-      <c r="T87" s="105"/>
-      <c r="U87" s="105"/>
-      <c r="V87" s="105"/>
-      <c r="W87" s="105"/>
-      <c r="X87" s="105"/>
-      <c r="Y87" s="105"/>
-      <c r="Z87" s="105"/>
-      <c r="AA87" s="105"/>
-      <c r="AB87" s="105"/>
-      <c r="AC87" s="105"/>
-      <c r="AD87" s="105"/>
-      <c r="AE87" s="105"/>
-      <c r="AF87" s="105"/>
-      <c r="AG87" s="105"/>
-      <c r="AH87" s="105"/>
-      <c r="AI87" s="105"/>
-      <c r="AJ87" s="105"/>
-      <c r="AK87" s="106"/>
+      <c r="S87" s="106"/>
+      <c r="T87" s="107"/>
+      <c r="U87" s="107"/>
+      <c r="V87" s="107"/>
+      <c r="W87" s="107"/>
+      <c r="X87" s="107"/>
+      <c r="Y87" s="107"/>
+      <c r="Z87" s="107"/>
+      <c r="AA87" s="107"/>
+      <c r="AB87" s="107"/>
+      <c r="AC87" s="107"/>
+      <c r="AD87" s="107"/>
+      <c r="AE87" s="107"/>
+      <c r="AF87" s="107"/>
+      <c r="AG87" s="107"/>
+      <c r="AH87" s="107"/>
+      <c r="AI87" s="107"/>
+      <c r="AJ87" s="107"/>
+      <c r="AK87" s="108"/>
     </row>
     <row r="88" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="140" t="s">
-        <v>77</v>
-      </c>
-      <c r="B88" s="141"/>
-      <c r="C88" s="141"/>
-      <c r="D88" s="141"/>
-      <c r="E88" s="141"/>
-      <c r="F88" s="141"/>
-      <c r="G88" s="141"/>
-      <c r="H88" s="141"/>
-      <c r="I88" s="141"/>
-      <c r="J88" s="141"/>
-      <c r="K88" s="141"/>
-      <c r="L88" s="141"/>
-      <c r="M88" s="142"/>
+      <c r="A88" s="141" t="s">
+        <v>74</v>
+      </c>
+      <c r="B88" s="142"/>
+      <c r="C88" s="142"/>
+      <c r="D88" s="142"/>
+      <c r="E88" s="142"/>
+      <c r="F88" s="142"/>
+      <c r="G88" s="142"/>
+      <c r="H88" s="142"/>
+      <c r="I88" s="142"/>
+      <c r="J88" s="142"/>
+      <c r="K88" s="142"/>
+      <c r="L88" s="142"/>
+      <c r="M88" s="143"/>
       <c r="N88" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O88" s="14"/>
       <c r="P88" s="58"/>
       <c r="Q88" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R88" s="79"/>
-      <c r="S88" s="104"/>
-      <c r="T88" s="105"/>
-      <c r="U88" s="105"/>
-      <c r="V88" s="105"/>
-      <c r="W88" s="105"/>
-      <c r="X88" s="105"/>
-      <c r="Y88" s="105"/>
-      <c r="Z88" s="105"/>
-      <c r="AA88" s="105"/>
-      <c r="AB88" s="105"/>
-      <c r="AC88" s="105"/>
-      <c r="AD88" s="105"/>
-      <c r="AE88" s="105"/>
-      <c r="AF88" s="105"/>
-      <c r="AG88" s="105"/>
-      <c r="AH88" s="105"/>
-      <c r="AI88" s="105"/>
-      <c r="AJ88" s="105"/>
-      <c r="AK88" s="106"/>
+      <c r="S88" s="106"/>
+      <c r="T88" s="107"/>
+      <c r="U88" s="107"/>
+      <c r="V88" s="107"/>
+      <c r="W88" s="107"/>
+      <c r="X88" s="107"/>
+      <c r="Y88" s="107"/>
+      <c r="Z88" s="107"/>
+      <c r="AA88" s="107"/>
+      <c r="AB88" s="107"/>
+      <c r="AC88" s="107"/>
+      <c r="AD88" s="107"/>
+      <c r="AE88" s="107"/>
+      <c r="AF88" s="107"/>
+      <c r="AG88" s="107"/>
+      <c r="AH88" s="107"/>
+      <c r="AI88" s="107"/>
+      <c r="AJ88" s="107"/>
+      <c r="AK88" s="108"/>
     </row>
     <row r="89" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="74"/>
@@ -5130,70 +5160,70 @@
       <c r="P89" s="42"/>
       <c r="Q89" s="42"/>
       <c r="R89" s="42"/>
-      <c r="S89" s="104"/>
-      <c r="T89" s="105"/>
-      <c r="U89" s="105"/>
-      <c r="V89" s="105"/>
-      <c r="W89" s="105"/>
-      <c r="X89" s="105"/>
-      <c r="Y89" s="105"/>
-      <c r="Z89" s="105"/>
-      <c r="AA89" s="105"/>
-      <c r="AB89" s="105"/>
-      <c r="AC89" s="105"/>
-      <c r="AD89" s="105"/>
-      <c r="AE89" s="105"/>
-      <c r="AF89" s="105"/>
-      <c r="AG89" s="105"/>
-      <c r="AH89" s="105"/>
-      <c r="AI89" s="105"/>
-      <c r="AJ89" s="105"/>
-      <c r="AK89" s="106"/>
+      <c r="S89" s="106"/>
+      <c r="T89" s="107"/>
+      <c r="U89" s="107"/>
+      <c r="V89" s="107"/>
+      <c r="W89" s="107"/>
+      <c r="X89" s="107"/>
+      <c r="Y89" s="107"/>
+      <c r="Z89" s="107"/>
+      <c r="AA89" s="107"/>
+      <c r="AB89" s="107"/>
+      <c r="AC89" s="107"/>
+      <c r="AD89" s="107"/>
+      <c r="AE89" s="107"/>
+      <c r="AF89" s="107"/>
+      <c r="AG89" s="107"/>
+      <c r="AH89" s="107"/>
+      <c r="AI89" s="107"/>
+      <c r="AJ89" s="107"/>
+      <c r="AK89" s="108"/>
     </row>
     <row r="90" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="140" t="s">
-        <v>78</v>
-      </c>
-      <c r="B90" s="141"/>
-      <c r="C90" s="141"/>
-      <c r="D90" s="141"/>
-      <c r="E90" s="141"/>
-      <c r="F90" s="141"/>
-      <c r="G90" s="141"/>
-      <c r="H90" s="141"/>
-      <c r="I90" s="141"/>
-      <c r="J90" s="141"/>
-      <c r="K90" s="141"/>
-      <c r="L90" s="141"/>
-      <c r="M90" s="142"/>
+      <c r="A90" s="141" t="s">
+        <v>75</v>
+      </c>
+      <c r="B90" s="142"/>
+      <c r="C90" s="142"/>
+      <c r="D90" s="142"/>
+      <c r="E90" s="142"/>
+      <c r="F90" s="142"/>
+      <c r="G90" s="142"/>
+      <c r="H90" s="142"/>
+      <c r="I90" s="142"/>
+      <c r="J90" s="142"/>
+      <c r="K90" s="142"/>
+      <c r="L90" s="142"/>
+      <c r="M90" s="143"/>
       <c r="N90" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O90" s="14"/>
       <c r="P90" s="58"/>
       <c r="Q90" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R90" s="79"/>
-      <c r="S90" s="104"/>
-      <c r="T90" s="105"/>
-      <c r="U90" s="105"/>
-      <c r="V90" s="105"/>
-      <c r="W90" s="105"/>
-      <c r="X90" s="105"/>
-      <c r="Y90" s="105"/>
-      <c r="Z90" s="105"/>
-      <c r="AA90" s="105"/>
-      <c r="AB90" s="105"/>
-      <c r="AC90" s="105"/>
-      <c r="AD90" s="105"/>
-      <c r="AE90" s="105"/>
-      <c r="AF90" s="105"/>
-      <c r="AG90" s="105"/>
-      <c r="AH90" s="105"/>
-      <c r="AI90" s="105"/>
-      <c r="AJ90" s="105"/>
-      <c r="AK90" s="106"/>
+      <c r="S90" s="106"/>
+      <c r="T90" s="107"/>
+      <c r="U90" s="107"/>
+      <c r="V90" s="107"/>
+      <c r="W90" s="107"/>
+      <c r="X90" s="107"/>
+      <c r="Y90" s="107"/>
+      <c r="Z90" s="107"/>
+      <c r="AA90" s="107"/>
+      <c r="AB90" s="107"/>
+      <c r="AC90" s="107"/>
+      <c r="AD90" s="107"/>
+      <c r="AE90" s="107"/>
+      <c r="AF90" s="107"/>
+      <c r="AG90" s="107"/>
+      <c r="AH90" s="107"/>
+      <c r="AI90" s="107"/>
+      <c r="AJ90" s="107"/>
+      <c r="AK90" s="108"/>
     </row>
     <row r="91" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="74"/>
@@ -5214,70 +5244,70 @@
       <c r="P91" s="42"/>
       <c r="Q91" s="42"/>
       <c r="R91" s="42"/>
-      <c r="S91" s="104"/>
-      <c r="T91" s="105"/>
-      <c r="U91" s="105"/>
-      <c r="V91" s="105"/>
-      <c r="W91" s="105"/>
-      <c r="X91" s="105"/>
-      <c r="Y91" s="105"/>
-      <c r="Z91" s="105"/>
-      <c r="AA91" s="105"/>
-      <c r="AB91" s="105"/>
-      <c r="AC91" s="105"/>
-      <c r="AD91" s="105"/>
-      <c r="AE91" s="105"/>
-      <c r="AF91" s="105"/>
-      <c r="AG91" s="105"/>
-      <c r="AH91" s="105"/>
-      <c r="AI91" s="105"/>
-      <c r="AJ91" s="105"/>
-      <c r="AK91" s="106"/>
+      <c r="S91" s="106"/>
+      <c r="T91" s="107"/>
+      <c r="U91" s="107"/>
+      <c r="V91" s="107"/>
+      <c r="W91" s="107"/>
+      <c r="X91" s="107"/>
+      <c r="Y91" s="107"/>
+      <c r="Z91" s="107"/>
+      <c r="AA91" s="107"/>
+      <c r="AB91" s="107"/>
+      <c r="AC91" s="107"/>
+      <c r="AD91" s="107"/>
+      <c r="AE91" s="107"/>
+      <c r="AF91" s="107"/>
+      <c r="AG91" s="107"/>
+      <c r="AH91" s="107"/>
+      <c r="AI91" s="107"/>
+      <c r="AJ91" s="107"/>
+      <c r="AK91" s="108"/>
     </row>
     <row r="92" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="154" t="s">
-        <v>79</v>
-      </c>
-      <c r="B92" s="155"/>
-      <c r="C92" s="155"/>
-      <c r="D92" s="155"/>
-      <c r="E92" s="155"/>
-      <c r="F92" s="155"/>
-      <c r="G92" s="155"/>
-      <c r="H92" s="155"/>
-      <c r="I92" s="155"/>
-      <c r="J92" s="155"/>
-      <c r="K92" s="155"/>
-      <c r="L92" s="155"/>
-      <c r="M92" s="175"/>
+      <c r="A92" s="155" t="s">
+        <v>76</v>
+      </c>
+      <c r="B92" s="156"/>
+      <c r="C92" s="156"/>
+      <c r="D92" s="156"/>
+      <c r="E92" s="156"/>
+      <c r="F92" s="156"/>
+      <c r="G92" s="156"/>
+      <c r="H92" s="156"/>
+      <c r="I92" s="156"/>
+      <c r="J92" s="156"/>
+      <c r="K92" s="156"/>
+      <c r="L92" s="156"/>
+      <c r="M92" s="176"/>
       <c r="N92" s="27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O92" s="78"/>
       <c r="P92" s="32"/>
       <c r="Q92" s="27" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R92" s="80"/>
-      <c r="S92" s="107"/>
-      <c r="T92" s="108"/>
-      <c r="U92" s="108"/>
-      <c r="V92" s="108"/>
-      <c r="W92" s="108"/>
-      <c r="X92" s="108"/>
-      <c r="Y92" s="108"/>
-      <c r="Z92" s="108"/>
-      <c r="AA92" s="108"/>
-      <c r="AB92" s="108"/>
-      <c r="AC92" s="108"/>
-      <c r="AD92" s="108"/>
-      <c r="AE92" s="108"/>
-      <c r="AF92" s="108"/>
-      <c r="AG92" s="108"/>
-      <c r="AH92" s="108"/>
-      <c r="AI92" s="108"/>
-      <c r="AJ92" s="108"/>
-      <c r="AK92" s="109"/>
+      <c r="S92" s="109"/>
+      <c r="T92" s="110"/>
+      <c r="U92" s="110"/>
+      <c r="V92" s="110"/>
+      <c r="W92" s="110"/>
+      <c r="X92" s="110"/>
+      <c r="Y92" s="110"/>
+      <c r="Z92" s="110"/>
+      <c r="AA92" s="110"/>
+      <c r="AB92" s="110"/>
+      <c r="AC92" s="110"/>
+      <c r="AD92" s="110"/>
+      <c r="AE92" s="110"/>
+      <c r="AF92" s="110"/>
+      <c r="AG92" s="110"/>
+      <c r="AH92" s="110"/>
+      <c r="AI92" s="110"/>
+      <c r="AJ92" s="110"/>
+      <c r="AK92" s="111"/>
     </row>
     <row r="93" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="47"/>
@@ -5286,45 +5316,45 @@
       <c r="AK93" s="8"/>
     </row>
     <row r="94" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="92" t="s">
-        <v>80</v>
-      </c>
-      <c r="B94" s="93"/>
-      <c r="C94" s="93"/>
-      <c r="D94" s="93"/>
-      <c r="E94" s="93"/>
-      <c r="F94" s="93"/>
-      <c r="G94" s="93"/>
-      <c r="H94" s="93"/>
-      <c r="I94" s="93"/>
-      <c r="J94" s="93"/>
-      <c r="K94" s="93"/>
-      <c r="L94" s="93"/>
-      <c r="M94" s="93"/>
-      <c r="N94" s="93"/>
-      <c r="O94" s="93"/>
-      <c r="P94" s="93"/>
-      <c r="Q94" s="93"/>
-      <c r="R94" s="93"/>
-      <c r="S94" s="93"/>
-      <c r="T94" s="93"/>
-      <c r="U94" s="93"/>
-      <c r="V94" s="93"/>
-      <c r="W94" s="93"/>
-      <c r="X94" s="93"/>
-      <c r="Y94" s="93"/>
-      <c r="Z94" s="93"/>
-      <c r="AA94" s="93"/>
-      <c r="AB94" s="93"/>
-      <c r="AC94" s="93"/>
-      <c r="AD94" s="93"/>
-      <c r="AE94" s="93"/>
-      <c r="AF94" s="93"/>
-      <c r="AG94" s="93"/>
-      <c r="AH94" s="93"/>
-      <c r="AI94" s="93"/>
-      <c r="AJ94" s="93"/>
-      <c r="AK94" s="94"/>
+      <c r="A94" s="94" t="s">
+        <v>77</v>
+      </c>
+      <c r="B94" s="95"/>
+      <c r="C94" s="95"/>
+      <c r="D94" s="95"/>
+      <c r="E94" s="95"/>
+      <c r="F94" s="95"/>
+      <c r="G94" s="95"/>
+      <c r="H94" s="95"/>
+      <c r="I94" s="95"/>
+      <c r="J94" s="95"/>
+      <c r="K94" s="95"/>
+      <c r="L94" s="95"/>
+      <c r="M94" s="95"/>
+      <c r="N94" s="95"/>
+      <c r="O94" s="95"/>
+      <c r="P94" s="95"/>
+      <c r="Q94" s="95"/>
+      <c r="R94" s="95"/>
+      <c r="S94" s="95"/>
+      <c r="T94" s="95"/>
+      <c r="U94" s="95"/>
+      <c r="V94" s="95"/>
+      <c r="W94" s="95"/>
+      <c r="X94" s="95"/>
+      <c r="Y94" s="95"/>
+      <c r="Z94" s="95"/>
+      <c r="AA94" s="95"/>
+      <c r="AB94" s="95"/>
+      <c r="AC94" s="95"/>
+      <c r="AD94" s="95"/>
+      <c r="AE94" s="95"/>
+      <c r="AF94" s="95"/>
+      <c r="AG94" s="95"/>
+      <c r="AH94" s="95"/>
+      <c r="AI94" s="95"/>
+      <c r="AJ94" s="95"/>
+      <c r="AK94" s="96"/>
     </row>
     <row r="95" spans="1:37" s="2" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="47"/>
@@ -5332,142 +5362,142 @@
       <c r="AK95" s="8"/>
     </row>
     <row r="96" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="92" t="s">
+      <c r="A96" s="94" t="s">
+        <v>78</v>
+      </c>
+      <c r="B96" s="95"/>
+      <c r="C96" s="95"/>
+      <c r="D96" s="95"/>
+      <c r="E96" s="95"/>
+      <c r="F96" s="95"/>
+      <c r="G96" s="95"/>
+      <c r="H96" s="95"/>
+      <c r="I96" s="95"/>
+      <c r="J96" s="95"/>
+      <c r="K96" s="95"/>
+      <c r="L96" s="95"/>
+      <c r="M96" s="95"/>
+      <c r="N96" s="95"/>
+      <c r="O96" s="95"/>
+      <c r="P96" s="95"/>
+      <c r="Q96" s="95"/>
+      <c r="R96" s="96"/>
+      <c r="S96" s="94" t="s">
+        <v>79</v>
+      </c>
+      <c r="T96" s="95"/>
+      <c r="U96" s="95"/>
+      <c r="V96" s="95"/>
+      <c r="W96" s="95"/>
+      <c r="X96" s="95"/>
+      <c r="Y96" s="95"/>
+      <c r="Z96" s="95"/>
+      <c r="AA96" s="95"/>
+      <c r="AB96" s="95"/>
+      <c r="AC96" s="95"/>
+      <c r="AD96" s="95"/>
+      <c r="AE96" s="95"/>
+      <c r="AF96" s="95"/>
+      <c r="AG96" s="95"/>
+      <c r="AH96" s="95"/>
+      <c r="AI96" s="95"/>
+      <c r="AJ96" s="95"/>
+      <c r="AK96" s="96"/>
+    </row>
+    <row r="97" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="149" t="s">
+        <v>80</v>
+      </c>
+      <c r="B97" s="150"/>
+      <c r="C97" s="150"/>
+      <c r="D97" s="150"/>
+      <c r="E97" s="150"/>
+      <c r="F97" s="150"/>
+      <c r="G97" s="150"/>
+      <c r="H97" s="150"/>
+      <c r="I97" s="150"/>
+      <c r="J97" s="150"/>
+      <c r="K97" s="150"/>
+      <c r="L97" s="150"/>
+      <c r="M97" s="151"/>
+      <c r="N97" s="152" t="s">
+        <v>61</v>
+      </c>
+      <c r="O97" s="153"/>
+      <c r="P97" s="153"/>
+      <c r="Q97" s="153"/>
+      <c r="R97" s="154"/>
+      <c r="S97" s="177" t="s">
+        <v>80</v>
+      </c>
+      <c r="T97" s="153"/>
+      <c r="U97" s="153"/>
+      <c r="V97" s="153"/>
+      <c r="W97" s="153"/>
+      <c r="X97" s="153"/>
+      <c r="Y97" s="153"/>
+      <c r="Z97" s="153"/>
+      <c r="AA97" s="153"/>
+      <c r="AB97" s="153"/>
+      <c r="AC97" s="153"/>
+      <c r="AD97" s="153"/>
+      <c r="AE97" s="178"/>
+      <c r="AF97" s="172" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG97" s="173"/>
+      <c r="AH97" s="173"/>
+      <c r="AI97" s="173"/>
+      <c r="AJ97" s="173"/>
+      <c r="AK97" s="174"/>
+    </row>
+    <row r="98" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="141" t="s">
         <v>81</v>
       </c>
-      <c r="B96" s="93"/>
-      <c r="C96" s="93"/>
-      <c r="D96" s="93"/>
-      <c r="E96" s="93"/>
-      <c r="F96" s="93"/>
-      <c r="G96" s="93"/>
-      <c r="H96" s="93"/>
-      <c r="I96" s="93"/>
-      <c r="J96" s="93"/>
-      <c r="K96" s="93"/>
-      <c r="L96" s="93"/>
-      <c r="M96" s="93"/>
-      <c r="N96" s="93"/>
-      <c r="O96" s="93"/>
-      <c r="P96" s="93"/>
-      <c r="Q96" s="93"/>
-      <c r="R96" s="94"/>
-      <c r="S96" s="92" t="s">
-        <v>82</v>
-      </c>
-      <c r="T96" s="93"/>
-      <c r="U96" s="93"/>
-      <c r="V96" s="93"/>
-      <c r="W96" s="93"/>
-      <c r="X96" s="93"/>
-      <c r="Y96" s="93"/>
-      <c r="Z96" s="93"/>
-      <c r="AA96" s="93"/>
-      <c r="AB96" s="93"/>
-      <c r="AC96" s="93"/>
-      <c r="AD96" s="93"/>
-      <c r="AE96" s="93"/>
-      <c r="AF96" s="93"/>
-      <c r="AG96" s="93"/>
-      <c r="AH96" s="93"/>
-      <c r="AI96" s="93"/>
-      <c r="AJ96" s="93"/>
-      <c r="AK96" s="94"/>
-    </row>
-    <row r="97" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="148" t="s">
-        <v>83</v>
-      </c>
-      <c r="B97" s="149"/>
-      <c r="C97" s="149"/>
-      <c r="D97" s="149"/>
-      <c r="E97" s="149"/>
-      <c r="F97" s="149"/>
-      <c r="G97" s="149"/>
-      <c r="H97" s="149"/>
-      <c r="I97" s="149"/>
-      <c r="J97" s="149"/>
-      <c r="K97" s="149"/>
-      <c r="L97" s="149"/>
-      <c r="M97" s="150"/>
-      <c r="N97" s="151" t="s">
-        <v>64</v>
-      </c>
-      <c r="O97" s="152"/>
-      <c r="P97" s="152"/>
-      <c r="Q97" s="152"/>
-      <c r="R97" s="153"/>
-      <c r="S97" s="176" t="s">
-        <v>83</v>
-      </c>
-      <c r="T97" s="152"/>
-      <c r="U97" s="152"/>
-      <c r="V97" s="152"/>
-      <c r="W97" s="152"/>
-      <c r="X97" s="152"/>
-      <c r="Y97" s="152"/>
-      <c r="Z97" s="152"/>
-      <c r="AA97" s="152"/>
-      <c r="AB97" s="152"/>
-      <c r="AC97" s="152"/>
-      <c r="AD97" s="152"/>
-      <c r="AE97" s="177"/>
-      <c r="AF97" s="171" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG97" s="172"/>
-      <c r="AH97" s="172"/>
-      <c r="AI97" s="172"/>
-      <c r="AJ97" s="172"/>
-      <c r="AK97" s="173"/>
-    </row>
-    <row r="98" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="140" t="s">
-        <v>84</v>
-      </c>
-      <c r="B98" s="141"/>
-      <c r="C98" s="141"/>
-      <c r="D98" s="141"/>
-      <c r="E98" s="141"/>
-      <c r="F98" s="141"/>
-      <c r="G98" s="141"/>
-      <c r="H98" s="141"/>
-      <c r="I98" s="141"/>
-      <c r="J98" s="141"/>
-      <c r="K98" s="141"/>
-      <c r="L98" s="141"/>
-      <c r="M98" s="141"/>
+      <c r="B98" s="142"/>
+      <c r="C98" s="142"/>
+      <c r="D98" s="142"/>
+      <c r="E98" s="142"/>
+      <c r="F98" s="142"/>
+      <c r="G98" s="142"/>
+      <c r="H98" s="142"/>
+      <c r="I98" s="142"/>
+      <c r="J98" s="142"/>
+      <c r="K98" s="142"/>
+      <c r="L98" s="142"/>
+      <c r="M98" s="142"/>
       <c r="N98" s="28" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O98" s="81"/>
       <c r="P98" s="21"/>
       <c r="Q98" s="30" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R98" s="82"/>
-      <c r="S98" s="194" t="s">
-        <v>85</v>
-      </c>
-      <c r="T98" s="195"/>
-      <c r="U98" s="195"/>
-      <c r="V98" s="195"/>
-      <c r="W98" s="195"/>
-      <c r="X98" s="195"/>
-      <c r="Y98" s="195"/>
-      <c r="Z98" s="195"/>
-      <c r="AA98" s="195"/>
-      <c r="AB98" s="195"/>
-      <c r="AC98" s="195"/>
-      <c r="AD98" s="195"/>
-      <c r="AE98" s="196"/>
+      <c r="S98" s="195" t="s">
+        <v>82</v>
+      </c>
+      <c r="T98" s="196"/>
+      <c r="U98" s="196"/>
+      <c r="V98" s="196"/>
+      <c r="W98" s="196"/>
+      <c r="X98" s="196"/>
+      <c r="Y98" s="196"/>
+      <c r="Z98" s="196"/>
+      <c r="AA98" s="196"/>
+      <c r="AB98" s="196"/>
+      <c r="AC98" s="196"/>
+      <c r="AD98" s="196"/>
+      <c r="AE98" s="197"/>
       <c r="AF98" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG98" s="77"/>
       <c r="AH98" s="55"/>
       <c r="AI98" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ98" s="77"/>
       <c r="AK98" s="8"/>
@@ -5507,52 +5537,52 @@
       <c r="AK99" s="8"/>
     </row>
     <row r="100" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="140" t="s">
-        <v>86</v>
-      </c>
-      <c r="B100" s="141"/>
-      <c r="C100" s="141"/>
-      <c r="D100" s="141"/>
-      <c r="E100" s="141"/>
-      <c r="F100" s="141"/>
-      <c r="G100" s="141"/>
-      <c r="H100" s="141"/>
-      <c r="I100" s="141"/>
-      <c r="J100" s="141"/>
-      <c r="K100" s="141"/>
-      <c r="L100" s="141"/>
-      <c r="M100" s="141"/>
+      <c r="A100" s="141" t="s">
+        <v>83</v>
+      </c>
+      <c r="B100" s="142"/>
+      <c r="C100" s="142"/>
+      <c r="D100" s="142"/>
+      <c r="E100" s="142"/>
+      <c r="F100" s="142"/>
+      <c r="G100" s="142"/>
+      <c r="H100" s="142"/>
+      <c r="I100" s="142"/>
+      <c r="J100" s="142"/>
+      <c r="K100" s="142"/>
+      <c r="L100" s="142"/>
+      <c r="M100" s="142"/>
       <c r="N100" s="38" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O100" s="14"/>
       <c r="P100" s="55"/>
       <c r="Q100" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R100" s="83"/>
-      <c r="S100" s="146" t="s">
-        <v>87</v>
-      </c>
-      <c r="T100" s="127"/>
-      <c r="U100" s="127"/>
-      <c r="V100" s="127"/>
-      <c r="W100" s="127"/>
-      <c r="X100" s="127"/>
-      <c r="Y100" s="127"/>
-      <c r="Z100" s="127"/>
-      <c r="AA100" s="127"/>
-      <c r="AB100" s="127"/>
-      <c r="AC100" s="127"/>
-      <c r="AD100" s="127"/>
-      <c r="AE100" s="174"/>
+      <c r="S100" s="147" t="s">
+        <v>84</v>
+      </c>
+      <c r="T100" s="128"/>
+      <c r="U100" s="128"/>
+      <c r="V100" s="128"/>
+      <c r="W100" s="128"/>
+      <c r="X100" s="128"/>
+      <c r="Y100" s="128"/>
+      <c r="Z100" s="128"/>
+      <c r="AA100" s="128"/>
+      <c r="AB100" s="128"/>
+      <c r="AC100" s="128"/>
+      <c r="AD100" s="128"/>
+      <c r="AE100" s="175"/>
       <c r="AF100" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG100" s="14"/>
       <c r="AH100" s="55"/>
       <c r="AI100" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ100" s="14"/>
       <c r="AK100" s="8"/>
@@ -5574,8 +5604,8 @@
       <c r="N101" s="24"/>
       <c r="Q101" s="42"/>
       <c r="R101" s="8"/>
-      <c r="S101" s="197"/>
-      <c r="T101" s="198"/>
+      <c r="S101" s="198"/>
+      <c r="T101" s="199"/>
       <c r="U101" s="72"/>
       <c r="V101" s="72"/>
       <c r="W101" s="72"/>
@@ -5592,52 +5622,52 @@
       <c r="AK101" s="8"/>
     </row>
     <row r="102" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="140" t="s">
-        <v>88</v>
-      </c>
-      <c r="B102" s="141"/>
-      <c r="C102" s="141"/>
-      <c r="D102" s="141"/>
-      <c r="E102" s="141"/>
-      <c r="F102" s="141"/>
-      <c r="G102" s="141"/>
-      <c r="H102" s="141"/>
-      <c r="I102" s="141"/>
-      <c r="J102" s="141"/>
-      <c r="K102" s="141"/>
-      <c r="L102" s="141"/>
-      <c r="M102" s="141"/>
+      <c r="A102" s="141" t="s">
+        <v>85</v>
+      </c>
+      <c r="B102" s="142"/>
+      <c r="C102" s="142"/>
+      <c r="D102" s="142"/>
+      <c r="E102" s="142"/>
+      <c r="F102" s="142"/>
+      <c r="G102" s="142"/>
+      <c r="H102" s="142"/>
+      <c r="I102" s="142"/>
+      <c r="J102" s="142"/>
+      <c r="K102" s="142"/>
+      <c r="L102" s="142"/>
+      <c r="M102" s="142"/>
       <c r="N102" s="38" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O102" s="14"/>
       <c r="P102" s="55"/>
       <c r="Q102" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R102" s="83"/>
-      <c r="S102" s="146" t="s">
-        <v>89</v>
-      </c>
-      <c r="T102" s="127"/>
-      <c r="U102" s="127"/>
-      <c r="V102" s="127"/>
-      <c r="W102" s="127"/>
-      <c r="X102" s="127"/>
-      <c r="Y102" s="127"/>
-      <c r="Z102" s="127"/>
-      <c r="AA102" s="127"/>
-      <c r="AB102" s="127"/>
-      <c r="AC102" s="127"/>
-      <c r="AD102" s="127"/>
-      <c r="AE102" s="174"/>
+      <c r="S102" s="147" t="s">
+        <v>86</v>
+      </c>
+      <c r="T102" s="128"/>
+      <c r="U102" s="128"/>
+      <c r="V102" s="128"/>
+      <c r="W102" s="128"/>
+      <c r="X102" s="128"/>
+      <c r="Y102" s="128"/>
+      <c r="Z102" s="128"/>
+      <c r="AA102" s="128"/>
+      <c r="AB102" s="128"/>
+      <c r="AC102" s="128"/>
+      <c r="AD102" s="128"/>
+      <c r="AE102" s="175"/>
       <c r="AF102" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG102" s="14"/>
       <c r="AH102" s="55"/>
       <c r="AI102" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ102" s="14"/>
       <c r="AK102" s="8"/>
@@ -5677,52 +5707,52 @@
       <c r="AK103" s="8"/>
     </row>
     <row r="104" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="140" t="s">
-        <v>90</v>
-      </c>
-      <c r="B104" s="141"/>
-      <c r="C104" s="141"/>
-      <c r="D104" s="141"/>
-      <c r="E104" s="141"/>
-      <c r="F104" s="141"/>
-      <c r="G104" s="141"/>
-      <c r="H104" s="141"/>
-      <c r="I104" s="141"/>
-      <c r="J104" s="141"/>
-      <c r="K104" s="141"/>
-      <c r="L104" s="141"/>
-      <c r="M104" s="141"/>
+      <c r="A104" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="B104" s="142"/>
+      <c r="C104" s="142"/>
+      <c r="D104" s="142"/>
+      <c r="E104" s="142"/>
+      <c r="F104" s="142"/>
+      <c r="G104" s="142"/>
+      <c r="H104" s="142"/>
+      <c r="I104" s="142"/>
+      <c r="J104" s="142"/>
+      <c r="K104" s="142"/>
+      <c r="L104" s="142"/>
+      <c r="M104" s="142"/>
       <c r="N104" s="38" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O104" s="14"/>
       <c r="P104" s="55"/>
       <c r="Q104" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R104" s="83"/>
-      <c r="S104" s="146" t="s">
-        <v>91</v>
-      </c>
-      <c r="T104" s="127"/>
-      <c r="U104" s="127"/>
-      <c r="V104" s="127"/>
-      <c r="W104" s="127"/>
-      <c r="X104" s="127"/>
-      <c r="Y104" s="127"/>
-      <c r="Z104" s="127"/>
-      <c r="AA104" s="127"/>
-      <c r="AB104" s="127"/>
-      <c r="AC104" s="127"/>
-      <c r="AD104" s="127"/>
-      <c r="AE104" s="174"/>
+      <c r="S104" s="147" t="s">
+        <v>88</v>
+      </c>
+      <c r="T104" s="128"/>
+      <c r="U104" s="128"/>
+      <c r="V104" s="128"/>
+      <c r="W104" s="128"/>
+      <c r="X104" s="128"/>
+      <c r="Y104" s="128"/>
+      <c r="Z104" s="128"/>
+      <c r="AA104" s="128"/>
+      <c r="AB104" s="128"/>
+      <c r="AC104" s="128"/>
+      <c r="AD104" s="128"/>
+      <c r="AE104" s="175"/>
       <c r="AF104" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG104" s="14"/>
       <c r="AH104" s="55"/>
       <c r="AI104" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ104" s="14"/>
       <c r="AK104" s="8"/>
@@ -5762,52 +5792,52 @@
       <c r="AK105" s="8"/>
     </row>
     <row r="106" spans="1:37" s="2" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="140" t="s">
-        <v>92</v>
-      </c>
-      <c r="B106" s="141"/>
-      <c r="C106" s="141"/>
-      <c r="D106" s="141"/>
-      <c r="E106" s="141"/>
-      <c r="F106" s="141"/>
-      <c r="G106" s="141"/>
-      <c r="H106" s="141"/>
-      <c r="I106" s="141"/>
-      <c r="J106" s="141"/>
-      <c r="K106" s="141"/>
-      <c r="L106" s="141"/>
-      <c r="M106" s="141"/>
+      <c r="A106" s="141" t="s">
+        <v>89</v>
+      </c>
+      <c r="B106" s="142"/>
+      <c r="C106" s="142"/>
+      <c r="D106" s="142"/>
+      <c r="E106" s="142"/>
+      <c r="F106" s="142"/>
+      <c r="G106" s="142"/>
+      <c r="H106" s="142"/>
+      <c r="I106" s="142"/>
+      <c r="J106" s="142"/>
+      <c r="K106" s="142"/>
+      <c r="L106" s="142"/>
+      <c r="M106" s="142"/>
       <c r="N106" s="38" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O106" s="14"/>
       <c r="P106" s="58"/>
       <c r="Q106" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R106" s="83"/>
-      <c r="S106" s="146" t="s">
-        <v>93</v>
-      </c>
-      <c r="T106" s="127"/>
-      <c r="U106" s="127"/>
-      <c r="V106" s="127"/>
-      <c r="W106" s="127"/>
-      <c r="X106" s="127"/>
-      <c r="Y106" s="127"/>
-      <c r="Z106" s="127"/>
-      <c r="AA106" s="127"/>
-      <c r="AB106" s="127"/>
-      <c r="AC106" s="127"/>
-      <c r="AD106" s="127"/>
-      <c r="AE106" s="174"/>
+      <c r="S106" s="147" t="s">
+        <v>90</v>
+      </c>
+      <c r="T106" s="128"/>
+      <c r="U106" s="128"/>
+      <c r="V106" s="128"/>
+      <c r="W106" s="128"/>
+      <c r="X106" s="128"/>
+      <c r="Y106" s="128"/>
+      <c r="Z106" s="128"/>
+      <c r="AA106" s="128"/>
+      <c r="AB106" s="128"/>
+      <c r="AC106" s="128"/>
+      <c r="AD106" s="128"/>
+      <c r="AE106" s="175"/>
       <c r="AF106" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG106" s="14"/>
       <c r="AH106" s="55"/>
       <c r="AI106" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ106" s="14"/>
       <c r="AK106" s="8"/>
@@ -5849,52 +5879,52 @@
       <c r="AK107" s="8"/>
     </row>
     <row r="108" spans="1:37" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="140" t="s">
-        <v>94</v>
-      </c>
-      <c r="B108" s="141"/>
-      <c r="C108" s="141"/>
-      <c r="D108" s="141"/>
-      <c r="E108" s="141"/>
-      <c r="F108" s="141"/>
-      <c r="G108" s="141"/>
-      <c r="H108" s="141"/>
-      <c r="I108" s="141"/>
-      <c r="J108" s="141"/>
-      <c r="K108" s="141"/>
-      <c r="L108" s="141"/>
-      <c r="M108" s="141"/>
+      <c r="A108" s="141" t="s">
+        <v>91</v>
+      </c>
+      <c r="B108" s="142"/>
+      <c r="C108" s="142"/>
+      <c r="D108" s="142"/>
+      <c r="E108" s="142"/>
+      <c r="F108" s="142"/>
+      <c r="G108" s="142"/>
+      <c r="H108" s="142"/>
+      <c r="I108" s="142"/>
+      <c r="J108" s="142"/>
+      <c r="K108" s="142"/>
+      <c r="L108" s="142"/>
+      <c r="M108" s="142"/>
       <c r="N108" s="38" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O108" s="14"/>
       <c r="P108" s="58"/>
       <c r="Q108" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R108" s="83"/>
-      <c r="S108" s="146" t="s">
-        <v>95</v>
-      </c>
-      <c r="T108" s="127"/>
-      <c r="U108" s="127"/>
-      <c r="V108" s="127"/>
-      <c r="W108" s="127"/>
-      <c r="X108" s="127"/>
-      <c r="Y108" s="127"/>
-      <c r="Z108" s="127"/>
-      <c r="AA108" s="127"/>
-      <c r="AB108" s="127"/>
-      <c r="AC108" s="127"/>
-      <c r="AD108" s="127"/>
-      <c r="AE108" s="174"/>
+      <c r="S108" s="147" t="s">
+        <v>92</v>
+      </c>
+      <c r="T108" s="128"/>
+      <c r="U108" s="128"/>
+      <c r="V108" s="128"/>
+      <c r="W108" s="128"/>
+      <c r="X108" s="128"/>
+      <c r="Y108" s="128"/>
+      <c r="Z108" s="128"/>
+      <c r="AA108" s="128"/>
+      <c r="AB108" s="128"/>
+      <c r="AC108" s="128"/>
+      <c r="AD108" s="128"/>
+      <c r="AE108" s="175"/>
       <c r="AF108" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG108" s="14"/>
       <c r="AH108" s="55"/>
       <c r="AI108" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ108" s="14"/>
       <c r="AK108" s="8"/>
@@ -5936,236 +5966,236 @@
       <c r="AK109" s="8"/>
     </row>
     <row r="110" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="140" t="s">
-        <v>96</v>
-      </c>
-      <c r="B110" s="141"/>
-      <c r="C110" s="141"/>
-      <c r="D110" s="141"/>
-      <c r="E110" s="141"/>
-      <c r="F110" s="141"/>
-      <c r="G110" s="141"/>
-      <c r="H110" s="141"/>
-      <c r="I110" s="141"/>
-      <c r="J110" s="141"/>
-      <c r="K110" s="141"/>
-      <c r="L110" s="141"/>
-      <c r="M110" s="141"/>
-      <c r="N110" s="156" t="s">
-        <v>53</v>
-      </c>
-      <c r="O110" s="158"/>
+      <c r="A110" s="141" t="s">
+        <v>93</v>
+      </c>
+      <c r="B110" s="142"/>
+      <c r="C110" s="142"/>
+      <c r="D110" s="142"/>
+      <c r="E110" s="142"/>
+      <c r="F110" s="142"/>
+      <c r="G110" s="142"/>
+      <c r="H110" s="142"/>
+      <c r="I110" s="142"/>
+      <c r="J110" s="142"/>
+      <c r="K110" s="142"/>
+      <c r="L110" s="142"/>
+      <c r="M110" s="142"/>
+      <c r="N110" s="157" t="s">
+        <v>50</v>
+      </c>
+      <c r="O110" s="159"/>
       <c r="P110" s="58"/>
-      <c r="Q110" s="160" t="s">
-        <v>66</v>
-      </c>
-      <c r="R110" s="162"/>
-      <c r="S110" s="164" t="s">
-        <v>97</v>
-      </c>
-      <c r="T110" s="165"/>
-      <c r="U110" s="165"/>
-      <c r="V110" s="165"/>
-      <c r="W110" s="165"/>
-      <c r="X110" s="165"/>
-      <c r="Y110" s="165"/>
-      <c r="Z110" s="165"/>
-      <c r="AA110" s="165"/>
-      <c r="AB110" s="165"/>
-      <c r="AC110" s="165"/>
-      <c r="AD110" s="165"/>
-      <c r="AE110" s="166"/>
+      <c r="Q110" s="161" t="s">
+        <v>63</v>
+      </c>
+      <c r="R110" s="163"/>
+      <c r="S110" s="165" t="s">
+        <v>94</v>
+      </c>
+      <c r="T110" s="166"/>
+      <c r="U110" s="166"/>
+      <c r="V110" s="166"/>
+      <c r="W110" s="166"/>
+      <c r="X110" s="166"/>
+      <c r="Y110" s="166"/>
+      <c r="Z110" s="166"/>
+      <c r="AA110" s="166"/>
+      <c r="AB110" s="166"/>
+      <c r="AC110" s="166"/>
+      <c r="AD110" s="166"/>
+      <c r="AE110" s="167"/>
       <c r="AF110" s="60" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG110" s="14"/>
       <c r="AH110" s="55"/>
       <c r="AI110" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ110" s="14"/>
       <c r="AK110" s="8"/>
     </row>
     <row r="111" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="154"/>
-      <c r="B111" s="155"/>
-      <c r="C111" s="155"/>
-      <c r="D111" s="155"/>
-      <c r="E111" s="155"/>
-      <c r="F111" s="155"/>
-      <c r="G111" s="155"/>
-      <c r="H111" s="155"/>
-      <c r="I111" s="155"/>
-      <c r="J111" s="155"/>
-      <c r="K111" s="155"/>
-      <c r="L111" s="155"/>
-      <c r="M111" s="155"/>
-      <c r="N111" s="157"/>
-      <c r="O111" s="159"/>
+      <c r="A111" s="155"/>
+      <c r="B111" s="156"/>
+      <c r="C111" s="156"/>
+      <c r="D111" s="156"/>
+      <c r="E111" s="156"/>
+      <c r="F111" s="156"/>
+      <c r="G111" s="156"/>
+      <c r="H111" s="156"/>
+      <c r="I111" s="156"/>
+      <c r="J111" s="156"/>
+      <c r="K111" s="156"/>
+      <c r="L111" s="156"/>
+      <c r="M111" s="156"/>
+      <c r="N111" s="158"/>
+      <c r="O111" s="160"/>
       <c r="P111" s="27"/>
-      <c r="Q111" s="161"/>
-      <c r="R111" s="163"/>
-      <c r="S111" s="167" t="s">
+      <c r="Q111" s="162"/>
+      <c r="R111" s="164"/>
+      <c r="S111" s="168" t="s">
+        <v>95</v>
+      </c>
+      <c r="T111" s="169"/>
+      <c r="U111" s="170"/>
+      <c r="V111" s="170"/>
+      <c r="W111" s="170"/>
+      <c r="X111" s="170"/>
+      <c r="Y111" s="170"/>
+      <c r="Z111" s="170"/>
+      <c r="AA111" s="170"/>
+      <c r="AB111" s="170"/>
+      <c r="AC111" s="170"/>
+      <c r="AD111" s="170"/>
+      <c r="AE111" s="170"/>
+      <c r="AF111" s="170"/>
+      <c r="AG111" s="170"/>
+      <c r="AH111" s="170"/>
+      <c r="AI111" s="170"/>
+      <c r="AJ111" s="170"/>
+      <c r="AK111" s="171"/>
+    </row>
+    <row r="112" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="94" t="s">
+        <v>96</v>
+      </c>
+      <c r="B112" s="95"/>
+      <c r="C112" s="95"/>
+      <c r="D112" s="95"/>
+      <c r="E112" s="95"/>
+      <c r="F112" s="95"/>
+      <c r="G112" s="95"/>
+      <c r="H112" s="95"/>
+      <c r="I112" s="95"/>
+      <c r="J112" s="95"/>
+      <c r="K112" s="95"/>
+      <c r="L112" s="95"/>
+      <c r="M112" s="95"/>
+      <c r="N112" s="95"/>
+      <c r="O112" s="95"/>
+      <c r="P112" s="95"/>
+      <c r="Q112" s="95"/>
+      <c r="R112" s="95"/>
+      <c r="S112" s="94" t="s">
+        <v>97</v>
+      </c>
+      <c r="T112" s="95"/>
+      <c r="U112" s="95"/>
+      <c r="V112" s="95"/>
+      <c r="W112" s="95"/>
+      <c r="X112" s="95"/>
+      <c r="Y112" s="95"/>
+      <c r="Z112" s="95"/>
+      <c r="AA112" s="95"/>
+      <c r="AB112" s="95"/>
+      <c r="AC112" s="95"/>
+      <c r="AD112" s="95"/>
+      <c r="AE112" s="95"/>
+      <c r="AF112" s="95"/>
+      <c r="AG112" s="95"/>
+      <c r="AH112" s="95"/>
+      <c r="AI112" s="95"/>
+      <c r="AJ112" s="95"/>
+      <c r="AK112" s="96"/>
+    </row>
+    <row r="113" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="149" t="s">
+        <v>80</v>
+      </c>
+      <c r="B113" s="150"/>
+      <c r="C113" s="150"/>
+      <c r="D113" s="150"/>
+      <c r="E113" s="150"/>
+      <c r="F113" s="150"/>
+      <c r="G113" s="150"/>
+      <c r="H113" s="150"/>
+      <c r="I113" s="150"/>
+      <c r="J113" s="150"/>
+      <c r="K113" s="150"/>
+      <c r="L113" s="150"/>
+      <c r="M113" s="151"/>
+      <c r="N113" s="152" t="s">
+        <v>61</v>
+      </c>
+      <c r="O113" s="153"/>
+      <c r="P113" s="153"/>
+      <c r="Q113" s="153"/>
+      <c r="R113" s="154"/>
+      <c r="S113" s="149" t="s">
         <v>98</v>
       </c>
-      <c r="T111" s="168"/>
-      <c r="U111" s="169"/>
-      <c r="V111" s="169"/>
-      <c r="W111" s="169"/>
-      <c r="X111" s="169"/>
-      <c r="Y111" s="169"/>
-      <c r="Z111" s="169"/>
-      <c r="AA111" s="169"/>
-      <c r="AB111" s="169"/>
-      <c r="AC111" s="169"/>
-      <c r="AD111" s="169"/>
-      <c r="AE111" s="169"/>
-      <c r="AF111" s="169"/>
-      <c r="AG111" s="169"/>
-      <c r="AH111" s="169"/>
-      <c r="AI111" s="169"/>
-      <c r="AJ111" s="169"/>
-      <c r="AK111" s="170"/>
-    </row>
-    <row r="112" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="92" t="s">
+      <c r="T113" s="150"/>
+      <c r="U113" s="150"/>
+      <c r="V113" s="150"/>
+      <c r="W113" s="150"/>
+      <c r="X113" s="150"/>
+      <c r="Y113" s="150"/>
+      <c r="Z113" s="150"/>
+      <c r="AA113" s="150"/>
+      <c r="AB113" s="150"/>
+      <c r="AC113" s="150"/>
+      <c r="AD113" s="150"/>
+      <c r="AE113" s="151"/>
+      <c r="AF113" s="172" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG113" s="173"/>
+      <c r="AH113" s="173"/>
+      <c r="AI113" s="173"/>
+      <c r="AJ113" s="173"/>
+      <c r="AK113" s="174"/>
+    </row>
+    <row r="114" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="193" t="s">
         <v>99</v>
       </c>
-      <c r="B112" s="93"/>
-      <c r="C112" s="93"/>
-      <c r="D112" s="93"/>
-      <c r="E112" s="93"/>
-      <c r="F112" s="93"/>
-      <c r="G112" s="93"/>
-      <c r="H112" s="93"/>
-      <c r="I112" s="93"/>
-      <c r="J112" s="93"/>
-      <c r="K112" s="93"/>
-      <c r="L112" s="93"/>
-      <c r="M112" s="93"/>
-      <c r="N112" s="93"/>
-      <c r="O112" s="93"/>
-      <c r="P112" s="93"/>
-      <c r="Q112" s="93"/>
-      <c r="R112" s="93"/>
-      <c r="S112" s="92" t="s">
+      <c r="B114" s="194" t="s">
         <v>100</v>
       </c>
-      <c r="T112" s="93"/>
-      <c r="U112" s="93"/>
-      <c r="V112" s="93"/>
-      <c r="W112" s="93"/>
-      <c r="X112" s="93"/>
-      <c r="Y112" s="93"/>
-      <c r="Z112" s="93"/>
-      <c r="AA112" s="93"/>
-      <c r="AB112" s="93"/>
-      <c r="AC112" s="93"/>
-      <c r="AD112" s="93"/>
-      <c r="AE112" s="93"/>
-      <c r="AF112" s="93"/>
-      <c r="AG112" s="93"/>
-      <c r="AH112" s="93"/>
-      <c r="AI112" s="93"/>
-      <c r="AJ112" s="93"/>
-      <c r="AK112" s="94"/>
-    </row>
-    <row r="113" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="148" t="s">
-        <v>83</v>
-      </c>
-      <c r="B113" s="149"/>
-      <c r="C113" s="149"/>
-      <c r="D113" s="149"/>
-      <c r="E113" s="149"/>
-      <c r="F113" s="149"/>
-      <c r="G113" s="149"/>
-      <c r="H113" s="149"/>
-      <c r="I113" s="149"/>
-      <c r="J113" s="149"/>
-      <c r="K113" s="149"/>
-      <c r="L113" s="149"/>
-      <c r="M113" s="150"/>
-      <c r="N113" s="151" t="s">
-        <v>64</v>
-      </c>
-      <c r="O113" s="152"/>
-      <c r="P113" s="152"/>
-      <c r="Q113" s="152"/>
-      <c r="R113" s="153"/>
-      <c r="S113" s="148" t="s">
-        <v>101</v>
-      </c>
-      <c r="T113" s="149"/>
-      <c r="U113" s="149"/>
-      <c r="V113" s="149"/>
-      <c r="W113" s="149"/>
-      <c r="X113" s="149"/>
-      <c r="Y113" s="149"/>
-      <c r="Z113" s="149"/>
-      <c r="AA113" s="149"/>
-      <c r="AB113" s="149"/>
-      <c r="AC113" s="149"/>
-      <c r="AD113" s="149"/>
-      <c r="AE113" s="150"/>
-      <c r="AF113" s="171" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG113" s="172"/>
-      <c r="AH113" s="172"/>
-      <c r="AI113" s="172"/>
-      <c r="AJ113" s="172"/>
-      <c r="AK113" s="173"/>
-    </row>
-    <row r="114" spans="1:37" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.25">
-      <c r="A114" s="192" t="s">
-        <v>102</v>
-      </c>
-      <c r="B114" s="193" t="s">
-        <v>103</v>
-      </c>
-      <c r="C114" s="193"/>
-      <c r="D114" s="193"/>
-      <c r="E114" s="193"/>
-      <c r="F114" s="193"/>
-      <c r="G114" s="193"/>
-      <c r="H114" s="193"/>
-      <c r="I114" s="193"/>
-      <c r="J114" s="193"/>
-      <c r="K114" s="193"/>
-      <c r="L114" s="193"/>
-      <c r="M114" s="193"/>
+      <c r="C114" s="194"/>
+      <c r="D114" s="194"/>
+      <c r="E114" s="194"/>
+      <c r="F114" s="194"/>
+      <c r="G114" s="194"/>
+      <c r="H114" s="194"/>
+      <c r="I114" s="194"/>
+      <c r="J114" s="194"/>
+      <c r="K114" s="194"/>
+      <c r="L114" s="194"/>
+      <c r="M114" s="194"/>
       <c r="N114" s="28" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O114" s="81"/>
       <c r="P114" s="29"/>
       <c r="Q114" s="30" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R114" s="82"/>
-      <c r="S114" s="192" t="s">
-        <v>104</v>
-      </c>
-      <c r="T114" s="193"/>
-      <c r="U114" s="193"/>
-      <c r="V114" s="193"/>
-      <c r="W114" s="193"/>
-      <c r="X114" s="193"/>
-      <c r="Y114" s="193"/>
-      <c r="Z114" s="193"/>
-      <c r="AA114" s="193"/>
-      <c r="AB114" s="193"/>
-      <c r="AC114" s="193"/>
-      <c r="AD114" s="193"/>
-      <c r="AE114" s="193"/>
+      <c r="S114" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="T114" s="194"/>
+      <c r="U114" s="194"/>
+      <c r="V114" s="194"/>
+      <c r="W114" s="194"/>
+      <c r="X114" s="194"/>
+      <c r="Y114" s="194"/>
+      <c r="Z114" s="194"/>
+      <c r="AA114" s="194"/>
+      <c r="AB114" s="194"/>
+      <c r="AC114" s="194"/>
+      <c r="AD114" s="194"/>
+      <c r="AE114" s="194"/>
       <c r="AF114" s="38" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG114" s="77"/>
       <c r="AH114" s="58"/>
       <c r="AI114" s="60" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ114" s="77"/>
       <c r="AK114" s="8"/>
@@ -6206,171 +6236,171 @@
       <c r="AK115" s="8"/>
     </row>
     <row r="116" spans="1:37" s="2" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="154" t="s">
-        <v>105</v>
-      </c>
-      <c r="B116" s="155" t="s">
-        <v>103</v>
-      </c>
-      <c r="C116" s="155"/>
-      <c r="D116" s="155"/>
-      <c r="E116" s="155"/>
-      <c r="F116" s="155"/>
-      <c r="G116" s="155"/>
-      <c r="H116" s="155"/>
-      <c r="I116" s="155"/>
-      <c r="J116" s="155"/>
-      <c r="K116" s="155"/>
-      <c r="L116" s="155"/>
-      <c r="M116" s="155"/>
+      <c r="A116" s="155" t="s">
+        <v>102</v>
+      </c>
+      <c r="B116" s="156" t="s">
+        <v>100</v>
+      </c>
+      <c r="C116" s="156"/>
+      <c r="D116" s="156"/>
+      <c r="E116" s="156"/>
+      <c r="F116" s="156"/>
+      <c r="G116" s="156"/>
+      <c r="H116" s="156"/>
+      <c r="I116" s="156"/>
+      <c r="J116" s="156"/>
+      <c r="K116" s="156"/>
+      <c r="L116" s="156"/>
+      <c r="M116" s="156"/>
       <c r="N116" s="31" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O116" s="78"/>
       <c r="P116" s="32"/>
       <c r="Q116" s="27" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R116" s="84"/>
-      <c r="S116" s="154" t="s">
-        <v>106</v>
-      </c>
-      <c r="T116" s="155"/>
-      <c r="U116" s="155"/>
-      <c r="V116" s="155"/>
-      <c r="W116" s="155"/>
-      <c r="X116" s="155"/>
-      <c r="Y116" s="155"/>
-      <c r="Z116" s="155"/>
-      <c r="AA116" s="155"/>
-      <c r="AB116" s="155"/>
-      <c r="AC116" s="155"/>
-      <c r="AD116" s="155"/>
-      <c r="AE116" s="155"/>
+      <c r="S116" s="155" t="s">
+        <v>103</v>
+      </c>
+      <c r="T116" s="156"/>
+      <c r="U116" s="156"/>
+      <c r="V116" s="156"/>
+      <c r="W116" s="156"/>
+      <c r="X116" s="156"/>
+      <c r="Y116" s="156"/>
+      <c r="Z116" s="156"/>
+      <c r="AA116" s="156"/>
+      <c r="AB116" s="156"/>
+      <c r="AC116" s="156"/>
+      <c r="AD116" s="156"/>
+      <c r="AE116" s="156"/>
       <c r="AF116" s="31" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG116" s="78"/>
       <c r="AH116" s="32"/>
       <c r="AI116" s="27" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ116" s="78"/>
       <c r="AK116" s="10"/>
     </row>
     <row r="117" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="92" t="s">
+      <c r="A117" s="94" t="s">
+        <v>104</v>
+      </c>
+      <c r="B117" s="95"/>
+      <c r="C117" s="95"/>
+      <c r="D117" s="95"/>
+      <c r="E117" s="95"/>
+      <c r="F117" s="95"/>
+      <c r="G117" s="95"/>
+      <c r="H117" s="95"/>
+      <c r="I117" s="95"/>
+      <c r="J117" s="95"/>
+      <c r="K117" s="95"/>
+      <c r="L117" s="95"/>
+      <c r="M117" s="95"/>
+      <c r="N117" s="95"/>
+      <c r="O117" s="95"/>
+      <c r="P117" s="95"/>
+      <c r="Q117" s="95"/>
+      <c r="R117" s="95"/>
+      <c r="S117" s="95"/>
+      <c r="T117" s="95"/>
+      <c r="U117" s="95"/>
+      <c r="V117" s="95"/>
+      <c r="W117" s="95"/>
+      <c r="X117" s="95"/>
+      <c r="Y117" s="95"/>
+      <c r="Z117" s="95"/>
+      <c r="AA117" s="95"/>
+      <c r="AB117" s="95"/>
+      <c r="AC117" s="95"/>
+      <c r="AD117" s="95"/>
+      <c r="AE117" s="95"/>
+      <c r="AF117" s="95"/>
+      <c r="AG117" s="95"/>
+      <c r="AH117" s="95"/>
+      <c r="AI117" s="95"/>
+      <c r="AJ117" s="95"/>
+      <c r="AK117" s="96"/>
+    </row>
+    <row r="118" spans="1:37" s="2" customFormat="1" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="179" t="s">
         <v>107</v>
       </c>
-      <c r="B117" s="93"/>
-      <c r="C117" s="93"/>
-      <c r="D117" s="93"/>
-      <c r="E117" s="93"/>
-      <c r="F117" s="93"/>
-      <c r="G117" s="93"/>
-      <c r="H117" s="93"/>
-      <c r="I117" s="93"/>
-      <c r="J117" s="93"/>
-      <c r="K117" s="93"/>
-      <c r="L117" s="93"/>
-      <c r="M117" s="93"/>
-      <c r="N117" s="93"/>
-      <c r="O117" s="93"/>
-      <c r="P117" s="93"/>
-      <c r="Q117" s="93"/>
-      <c r="R117" s="93"/>
-      <c r="S117" s="93"/>
-      <c r="T117" s="93"/>
-      <c r="U117" s="93"/>
-      <c r="V117" s="93"/>
-      <c r="W117" s="93"/>
-      <c r="X117" s="93"/>
-      <c r="Y117" s="93"/>
-      <c r="Z117" s="93"/>
-      <c r="AA117" s="93"/>
-      <c r="AB117" s="93"/>
-      <c r="AC117" s="93"/>
-      <c r="AD117" s="93"/>
-      <c r="AE117" s="93"/>
-      <c r="AF117" s="93"/>
-      <c r="AG117" s="93"/>
-      <c r="AH117" s="93"/>
-      <c r="AI117" s="93"/>
-      <c r="AJ117" s="93"/>
-      <c r="AK117" s="94"/>
-    </row>
-    <row r="118" spans="1:37" s="2" customFormat="1" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="178" t="s">
-        <v>110</v>
-      </c>
-      <c r="B118" s="179"/>
-      <c r="C118" s="179"/>
-      <c r="D118" s="179"/>
-      <c r="E118" s="179"/>
-      <c r="F118" s="179"/>
-      <c r="G118" s="179"/>
-      <c r="H118" s="179"/>
-      <c r="I118" s="179"/>
-      <c r="J118" s="179"/>
-      <c r="K118" s="179"/>
-      <c r="L118" s="179"/>
-      <c r="M118" s="179"/>
-      <c r="N118" s="179"/>
-      <c r="O118" s="179"/>
-      <c r="P118" s="179"/>
-      <c r="Q118" s="179"/>
-      <c r="R118" s="179"/>
-      <c r="S118" s="179"/>
-      <c r="T118" s="179"/>
-      <c r="U118" s="179"/>
-      <c r="V118" s="179"/>
-      <c r="W118" s="179"/>
-      <c r="X118" s="179"/>
-      <c r="Y118" s="179"/>
-      <c r="Z118" s="179"/>
-      <c r="AA118" s="179"/>
-      <c r="AB118" s="179"/>
-      <c r="AC118" s="179"/>
-      <c r="AD118" s="179"/>
-      <c r="AE118" s="179"/>
+      <c r="B118" s="180"/>
+      <c r="C118" s="180"/>
+      <c r="D118" s="180"/>
+      <c r="E118" s="180"/>
+      <c r="F118" s="180"/>
+      <c r="G118" s="180"/>
+      <c r="H118" s="180"/>
+      <c r="I118" s="180"/>
+      <c r="J118" s="180"/>
+      <c r="K118" s="180"/>
+      <c r="L118" s="180"/>
+      <c r="M118" s="180"/>
+      <c r="N118" s="180"/>
+      <c r="O118" s="180"/>
+      <c r="P118" s="180"/>
+      <c r="Q118" s="180"/>
+      <c r="R118" s="180"/>
+      <c r="S118" s="180"/>
+      <c r="T118" s="180"/>
+      <c r="U118" s="180"/>
+      <c r="V118" s="180"/>
+      <c r="W118" s="180"/>
+      <c r="X118" s="180"/>
+      <c r="Y118" s="180"/>
+      <c r="Z118" s="180"/>
+      <c r="AA118" s="180"/>
+      <c r="AB118" s="180"/>
+      <c r="AC118" s="180"/>
+      <c r="AD118" s="180"/>
+      <c r="AE118" s="180"/>
       <c r="AF118" s="31" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AG118" s="78"/>
       <c r="AH118" s="32"/>
       <c r="AI118" s="27" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="AJ118" s="78"/>
       <c r="AK118" s="8"/>
     </row>
-    <row r="119" spans="1:37" s="182" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="180" t="s">
-        <v>108</v>
-      </c>
-      <c r="B119" s="181"/>
-      <c r="C119" s="181"/>
-      <c r="D119" s="181"/>
-      <c r="E119" s="181"/>
-      <c r="F119" s="181"/>
-      <c r="G119" s="181"/>
-      <c r="H119" s="181"/>
-      <c r="I119" s="181"/>
-      <c r="J119" s="181"/>
-      <c r="K119" s="181"/>
-      <c r="L119" s="181"/>
-      <c r="M119" s="181"/>
-      <c r="N119" s="181"/>
-      <c r="O119" s="181"/>
-      <c r="P119" s="181"/>
-      <c r="Q119" s="181"/>
-      <c r="R119" s="181"/>
-      <c r="S119" s="181"/>
-      <c r="T119" s="181"/>
-      <c r="U119" s="181"/>
-      <c r="V119" s="181"/>
-      <c r="W119" s="181"/>
-      <c r="X119" s="181"/>
+    <row r="119" spans="1:37" s="183" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="181" t="s">
+        <v>105</v>
+      </c>
+      <c r="B119" s="182"/>
+      <c r="C119" s="182"/>
+      <c r="D119" s="182"/>
+      <c r="E119" s="182"/>
+      <c r="F119" s="182"/>
+      <c r="G119" s="182"/>
+      <c r="H119" s="182"/>
+      <c r="I119" s="182"/>
+      <c r="J119" s="182"/>
+      <c r="K119" s="182"/>
+      <c r="L119" s="182"/>
+      <c r="M119" s="182"/>
+      <c r="N119" s="182"/>
+      <c r="O119" s="182"/>
+      <c r="P119" s="182"/>
+      <c r="Q119" s="182"/>
+      <c r="R119" s="182"/>
+      <c r="S119" s="182"/>
+      <c r="T119" s="182"/>
+      <c r="U119" s="182"/>
+      <c r="V119" s="182"/>
+      <c r="W119" s="182"/>
+      <c r="X119" s="182"/>
     </row>
     <row r="120" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="47"/>
@@ -6408,282 +6438,284 @@
       <c r="AK120" s="8"/>
     </row>
     <row r="121" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="92" t="s">
-        <v>109</v>
-      </c>
-      <c r="B121" s="93"/>
-      <c r="C121" s="93"/>
-      <c r="D121" s="93"/>
-      <c r="E121" s="93"/>
-      <c r="F121" s="93"/>
-      <c r="G121" s="93"/>
-      <c r="H121" s="93"/>
-      <c r="I121" s="93"/>
-      <c r="J121" s="93"/>
-      <c r="K121" s="93"/>
-      <c r="L121" s="93"/>
-      <c r="M121" s="93"/>
-      <c r="N121" s="93"/>
-      <c r="O121" s="93"/>
-      <c r="P121" s="93"/>
-      <c r="Q121" s="93"/>
-      <c r="R121" s="93"/>
-      <c r="S121" s="93"/>
-      <c r="T121" s="93"/>
-      <c r="U121" s="93"/>
-      <c r="V121" s="93"/>
-      <c r="W121" s="93"/>
-      <c r="X121" s="93"/>
-      <c r="Y121" s="93"/>
-      <c r="Z121" s="93"/>
-      <c r="AA121" s="93"/>
-      <c r="AB121" s="93"/>
-      <c r="AC121" s="93"/>
-      <c r="AD121" s="93"/>
-      <c r="AE121" s="93"/>
-      <c r="AF121" s="93"/>
-      <c r="AG121" s="93"/>
-      <c r="AH121" s="93"/>
-      <c r="AI121" s="93"/>
-      <c r="AJ121" s="93"/>
-      <c r="AK121" s="94"/>
+      <c r="A121" s="94" t="s">
+        <v>106</v>
+      </c>
+      <c r="B121" s="95"/>
+      <c r="C121" s="95"/>
+      <c r="D121" s="95"/>
+      <c r="E121" s="95"/>
+      <c r="F121" s="95"/>
+      <c r="G121" s="95"/>
+      <c r="H121" s="95"/>
+      <c r="I121" s="95"/>
+      <c r="J121" s="95"/>
+      <c r="K121" s="95"/>
+      <c r="L121" s="95"/>
+      <c r="M121" s="95"/>
+      <c r="N121" s="95"/>
+      <c r="O121" s="95"/>
+      <c r="P121" s="95"/>
+      <c r="Q121" s="95"/>
+      <c r="R121" s="95"/>
+      <c r="S121" s="95"/>
+      <c r="T121" s="95"/>
+      <c r="U121" s="95"/>
+      <c r="V121" s="95"/>
+      <c r="W121" s="95"/>
+      <c r="X121" s="95"/>
+      <c r="Y121" s="95"/>
+      <c r="Z121" s="95"/>
+      <c r="AA121" s="95"/>
+      <c r="AB121" s="95"/>
+      <c r="AC121" s="95"/>
+      <c r="AD121" s="95"/>
+      <c r="AE121" s="95"/>
+      <c r="AF121" s="95"/>
+      <c r="AG121" s="95"/>
+      <c r="AH121" s="95"/>
+      <c r="AI121" s="95"/>
+      <c r="AJ121" s="95"/>
+      <c r="AK121" s="96"/>
     </row>
     <row r="122" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="183"/>
-      <c r="B122" s="184"/>
-      <c r="C122" s="184"/>
-      <c r="D122" s="184"/>
-      <c r="E122" s="184"/>
-      <c r="F122" s="184"/>
-      <c r="G122" s="184"/>
-      <c r="H122" s="184"/>
-      <c r="I122" s="184"/>
-      <c r="J122" s="184"/>
-      <c r="K122" s="184"/>
-      <c r="L122" s="184"/>
-      <c r="M122" s="184"/>
-      <c r="N122" s="184"/>
-      <c r="O122" s="184"/>
-      <c r="P122" s="184"/>
-      <c r="Q122" s="184"/>
-      <c r="R122" s="184"/>
-      <c r="S122" s="184"/>
-      <c r="T122" s="184"/>
-      <c r="U122" s="184"/>
-      <c r="V122" s="184"/>
-      <c r="W122" s="184"/>
-      <c r="X122" s="184"/>
-      <c r="Y122" s="184"/>
-      <c r="Z122" s="184"/>
-      <c r="AA122" s="184"/>
-      <c r="AB122" s="184"/>
-      <c r="AC122" s="184"/>
-      <c r="AD122" s="184"/>
-      <c r="AE122" s="184"/>
-      <c r="AF122" s="184"/>
-      <c r="AG122" s="184"/>
-      <c r="AH122" s="184"/>
-      <c r="AI122" s="184"/>
-      <c r="AJ122" s="184"/>
-      <c r="AK122" s="185"/>
+      <c r="A122" s="184"/>
+      <c r="B122" s="185"/>
+      <c r="C122" s="185"/>
+      <c r="D122" s="185"/>
+      <c r="E122" s="185"/>
+      <c r="F122" s="185"/>
+      <c r="G122" s="185"/>
+      <c r="H122" s="185"/>
+      <c r="I122" s="185"/>
+      <c r="J122" s="185"/>
+      <c r="K122" s="185"/>
+      <c r="L122" s="185"/>
+      <c r="M122" s="185"/>
+      <c r="N122" s="185"/>
+      <c r="O122" s="185"/>
+      <c r="P122" s="185"/>
+      <c r="Q122" s="185"/>
+      <c r="R122" s="185"/>
+      <c r="S122" s="185"/>
+      <c r="T122" s="185"/>
+      <c r="U122" s="185"/>
+      <c r="V122" s="185"/>
+      <c r="W122" s="185"/>
+      <c r="X122" s="185"/>
+      <c r="Y122" s="185"/>
+      <c r="Z122" s="185"/>
+      <c r="AA122" s="185"/>
+      <c r="AB122" s="185"/>
+      <c r="AC122" s="185"/>
+      <c r="AD122" s="185"/>
+      <c r="AE122" s="185"/>
+      <c r="AF122" s="185"/>
+      <c r="AG122" s="185"/>
+      <c r="AH122" s="185"/>
+      <c r="AI122" s="185"/>
+      <c r="AJ122" s="185"/>
+      <c r="AK122" s="186"/>
     </row>
     <row r="123" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="186"/>
-      <c r="B123" s="187"/>
-      <c r="C123" s="187"/>
-      <c r="D123" s="187"/>
-      <c r="E123" s="187"/>
-      <c r="F123" s="187"/>
-      <c r="G123" s="187"/>
-      <c r="H123" s="187"/>
-      <c r="I123" s="187"/>
-      <c r="J123" s="187"/>
-      <c r="K123" s="187"/>
-      <c r="L123" s="187"/>
-      <c r="M123" s="187"/>
-      <c r="N123" s="187"/>
-      <c r="O123" s="187"/>
-      <c r="P123" s="187"/>
-      <c r="Q123" s="187"/>
-      <c r="R123" s="187"/>
-      <c r="S123" s="187"/>
-      <c r="T123" s="187"/>
-      <c r="U123" s="187"/>
-      <c r="V123" s="187"/>
-      <c r="W123" s="187"/>
-      <c r="X123" s="187"/>
-      <c r="Y123" s="187"/>
-      <c r="Z123" s="187"/>
-      <c r="AA123" s="187"/>
-      <c r="AB123" s="187"/>
-      <c r="AC123" s="187"/>
-      <c r="AD123" s="187"/>
-      <c r="AE123" s="187"/>
-      <c r="AF123" s="187"/>
-      <c r="AG123" s="187"/>
-      <c r="AH123" s="187"/>
-      <c r="AI123" s="187"/>
-      <c r="AJ123" s="187"/>
-      <c r="AK123" s="188"/>
+      <c r="A123" s="187"/>
+      <c r="B123" s="188"/>
+      <c r="C123" s="188"/>
+      <c r="D123" s="188"/>
+      <c r="E123" s="188"/>
+      <c r="F123" s="188"/>
+      <c r="G123" s="188"/>
+      <c r="H123" s="188"/>
+      <c r="I123" s="188"/>
+      <c r="J123" s="188"/>
+      <c r="K123" s="188"/>
+      <c r="L123" s="188"/>
+      <c r="M123" s="188"/>
+      <c r="N123" s="188"/>
+      <c r="O123" s="188"/>
+      <c r="P123" s="188"/>
+      <c r="Q123" s="188"/>
+      <c r="R123" s="188"/>
+      <c r="S123" s="188"/>
+      <c r="T123" s="188"/>
+      <c r="U123" s="188"/>
+      <c r="V123" s="188"/>
+      <c r="W123" s="188"/>
+      <c r="X123" s="188"/>
+      <c r="Y123" s="188"/>
+      <c r="Z123" s="188"/>
+      <c r="AA123" s="188"/>
+      <c r="AB123" s="188"/>
+      <c r="AC123" s="188"/>
+      <c r="AD123" s="188"/>
+      <c r="AE123" s="188"/>
+      <c r="AF123" s="188"/>
+      <c r="AG123" s="188"/>
+      <c r="AH123" s="188"/>
+      <c r="AI123" s="188"/>
+      <c r="AJ123" s="188"/>
+      <c r="AK123" s="189"/>
     </row>
     <row r="124" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="186"/>
-      <c r="B124" s="187"/>
-      <c r="C124" s="187"/>
-      <c r="D124" s="187"/>
-      <c r="E124" s="187"/>
-      <c r="F124" s="187"/>
-      <c r="G124" s="187"/>
-      <c r="H124" s="187"/>
-      <c r="I124" s="187"/>
-      <c r="J124" s="187"/>
-      <c r="K124" s="187"/>
-      <c r="L124" s="187"/>
-      <c r="M124" s="187"/>
-      <c r="N124" s="187"/>
-      <c r="O124" s="187"/>
-      <c r="P124" s="187"/>
-      <c r="Q124" s="187"/>
-      <c r="R124" s="187"/>
-      <c r="S124" s="187"/>
-      <c r="T124" s="187"/>
-      <c r="U124" s="187"/>
-      <c r="V124" s="187"/>
-      <c r="W124" s="187"/>
-      <c r="X124" s="187"/>
-      <c r="Y124" s="187"/>
-      <c r="Z124" s="187"/>
-      <c r="AA124" s="187"/>
-      <c r="AB124" s="187"/>
-      <c r="AC124" s="187"/>
-      <c r="AD124" s="187"/>
-      <c r="AE124" s="187"/>
-      <c r="AF124" s="187"/>
-      <c r="AG124" s="187"/>
-      <c r="AH124" s="187"/>
-      <c r="AI124" s="187"/>
-      <c r="AJ124" s="187"/>
-      <c r="AK124" s="188"/>
+      <c r="A124" s="187"/>
+      <c r="B124" s="188"/>
+      <c r="C124" s="188"/>
+      <c r="D124" s="188"/>
+      <c r="E124" s="188"/>
+      <c r="F124" s="188"/>
+      <c r="G124" s="188"/>
+      <c r="H124" s="188"/>
+      <c r="I124" s="188"/>
+      <c r="J124" s="188"/>
+      <c r="K124" s="188"/>
+      <c r="L124" s="188"/>
+      <c r="M124" s="188"/>
+      <c r="N124" s="188"/>
+      <c r="O124" s="188"/>
+      <c r="P124" s="188"/>
+      <c r="Q124" s="188"/>
+      <c r="R124" s="188"/>
+      <c r="S124" s="188"/>
+      <c r="T124" s="188"/>
+      <c r="U124" s="188"/>
+      <c r="V124" s="188"/>
+      <c r="W124" s="188"/>
+      <c r="X124" s="188"/>
+      <c r="Y124" s="188"/>
+      <c r="Z124" s="188"/>
+      <c r="AA124" s="188"/>
+      <c r="AB124" s="188"/>
+      <c r="AC124" s="188"/>
+      <c r="AD124" s="188"/>
+      <c r="AE124" s="188"/>
+      <c r="AF124" s="188"/>
+      <c r="AG124" s="188"/>
+      <c r="AH124" s="188"/>
+      <c r="AI124" s="188"/>
+      <c r="AJ124" s="188"/>
+      <c r="AK124" s="189"/>
     </row>
     <row r="125" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="186"/>
-      <c r="B125" s="187"/>
-      <c r="C125" s="187"/>
-      <c r="D125" s="187"/>
-      <c r="E125" s="187"/>
-      <c r="F125" s="187"/>
-      <c r="G125" s="187"/>
-      <c r="H125" s="187"/>
-      <c r="I125" s="187"/>
-      <c r="J125" s="187"/>
-      <c r="K125" s="187"/>
-      <c r="L125" s="187"/>
-      <c r="M125" s="187"/>
-      <c r="N125" s="187"/>
-      <c r="O125" s="187"/>
-      <c r="P125" s="187"/>
-      <c r="Q125" s="187"/>
-      <c r="R125" s="187"/>
-      <c r="S125" s="187"/>
-      <c r="T125" s="187"/>
-      <c r="U125" s="187"/>
-      <c r="V125" s="187"/>
-      <c r="W125" s="187"/>
-      <c r="X125" s="187"/>
-      <c r="Y125" s="187"/>
-      <c r="Z125" s="187"/>
-      <c r="AA125" s="187"/>
-      <c r="AB125" s="187"/>
-      <c r="AC125" s="187"/>
-      <c r="AD125" s="187"/>
-      <c r="AE125" s="187"/>
-      <c r="AF125" s="187"/>
-      <c r="AG125" s="187"/>
-      <c r="AH125" s="187"/>
-      <c r="AI125" s="187"/>
-      <c r="AJ125" s="187"/>
-      <c r="AK125" s="188"/>
+      <c r="A125" s="187"/>
+      <c r="B125" s="188"/>
+      <c r="C125" s="188"/>
+      <c r="D125" s="188"/>
+      <c r="E125" s="188"/>
+      <c r="F125" s="188"/>
+      <c r="G125" s="188"/>
+      <c r="H125" s="188"/>
+      <c r="I125" s="188"/>
+      <c r="J125" s="188"/>
+      <c r="K125" s="188"/>
+      <c r="L125" s="188"/>
+      <c r="M125" s="188"/>
+      <c r="N125" s="188"/>
+      <c r="O125" s="188"/>
+      <c r="P125" s="188"/>
+      <c r="Q125" s="188"/>
+      <c r="R125" s="188"/>
+      <c r="S125" s="188"/>
+      <c r="T125" s="188"/>
+      <c r="U125" s="188"/>
+      <c r="V125" s="188"/>
+      <c r="W125" s="188"/>
+      <c r="X125" s="188"/>
+      <c r="Y125" s="188"/>
+      <c r="Z125" s="188"/>
+      <c r="AA125" s="188"/>
+      <c r="AB125" s="188"/>
+      <c r="AC125" s="188"/>
+      <c r="AD125" s="188"/>
+      <c r="AE125" s="188"/>
+      <c r="AF125" s="188"/>
+      <c r="AG125" s="188"/>
+      <c r="AH125" s="188"/>
+      <c r="AI125" s="188"/>
+      <c r="AJ125" s="188"/>
+      <c r="AK125" s="189"/>
     </row>
     <row r="126" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="186"/>
-      <c r="B126" s="187"/>
-      <c r="C126" s="187"/>
-      <c r="D126" s="187"/>
-      <c r="E126" s="187"/>
-      <c r="F126" s="187"/>
-      <c r="G126" s="187"/>
-      <c r="H126" s="187"/>
-      <c r="I126" s="187"/>
-      <c r="J126" s="187"/>
-      <c r="K126" s="187"/>
-      <c r="L126" s="187"/>
-      <c r="M126" s="187"/>
-      <c r="N126" s="187"/>
-      <c r="O126" s="187"/>
-      <c r="P126" s="187"/>
-      <c r="Q126" s="187"/>
-      <c r="R126" s="187"/>
-      <c r="S126" s="187"/>
-      <c r="T126" s="187"/>
-      <c r="U126" s="187"/>
-      <c r="V126" s="187"/>
-      <c r="W126" s="187"/>
-      <c r="X126" s="187"/>
-      <c r="Y126" s="187"/>
-      <c r="Z126" s="187"/>
-      <c r="AA126" s="187"/>
-      <c r="AB126" s="187"/>
-      <c r="AC126" s="187"/>
-      <c r="AD126" s="187"/>
-      <c r="AE126" s="187"/>
-      <c r="AF126" s="187"/>
-      <c r="AG126" s="187"/>
-      <c r="AH126" s="187"/>
-      <c r="AI126" s="187"/>
-      <c r="AJ126" s="187"/>
-      <c r="AK126" s="188"/>
+      <c r="A126" s="187"/>
+      <c r="B126" s="188"/>
+      <c r="C126" s="188"/>
+      <c r="D126" s="188"/>
+      <c r="E126" s="188"/>
+      <c r="F126" s="188"/>
+      <c r="G126" s="188"/>
+      <c r="H126" s="188"/>
+      <c r="I126" s="188"/>
+      <c r="J126" s="188"/>
+      <c r="K126" s="188"/>
+      <c r="L126" s="188"/>
+      <c r="M126" s="188"/>
+      <c r="N126" s="188"/>
+      <c r="O126" s="188"/>
+      <c r="P126" s="188"/>
+      <c r="Q126" s="188"/>
+      <c r="R126" s="188"/>
+      <c r="S126" s="188"/>
+      <c r="T126" s="188"/>
+      <c r="U126" s="188"/>
+      <c r="V126" s="188"/>
+      <c r="W126" s="188"/>
+      <c r="X126" s="188"/>
+      <c r="Y126" s="188"/>
+      <c r="Z126" s="188"/>
+      <c r="AA126" s="188"/>
+      <c r="AB126" s="188"/>
+      <c r="AC126" s="188"/>
+      <c r="AD126" s="188"/>
+      <c r="AE126" s="188"/>
+      <c r="AF126" s="188"/>
+      <c r="AG126" s="188"/>
+      <c r="AH126" s="188"/>
+      <c r="AI126" s="188"/>
+      <c r="AJ126" s="188"/>
+      <c r="AK126" s="189"/>
     </row>
     <row r="127" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="189"/>
-      <c r="B127" s="190"/>
-      <c r="C127" s="190"/>
-      <c r="D127" s="190"/>
-      <c r="E127" s="190"/>
-      <c r="F127" s="190"/>
-      <c r="G127" s="190"/>
-      <c r="H127" s="190"/>
-      <c r="I127" s="190"/>
-      <c r="J127" s="190"/>
-      <c r="K127" s="190"/>
-      <c r="L127" s="190"/>
-      <c r="M127" s="190"/>
-      <c r="N127" s="190"/>
-      <c r="O127" s="190"/>
-      <c r="P127" s="190"/>
-      <c r="Q127" s="190"/>
-      <c r="R127" s="190"/>
-      <c r="S127" s="190"/>
-      <c r="T127" s="190"/>
-      <c r="U127" s="190"/>
-      <c r="V127" s="190"/>
-      <c r="W127" s="190"/>
-      <c r="X127" s="190"/>
-      <c r="Y127" s="190"/>
-      <c r="Z127" s="190"/>
-      <c r="AA127" s="190"/>
-      <c r="AB127" s="190"/>
-      <c r="AC127" s="190"/>
-      <c r="AD127" s="190"/>
-      <c r="AE127" s="190"/>
-      <c r="AF127" s="190"/>
-      <c r="AG127" s="190"/>
-      <c r="AH127" s="190"/>
-      <c r="AI127" s="190"/>
-      <c r="AJ127" s="190"/>
-      <c r="AK127" s="191"/>
+      <c r="A127" s="190"/>
+      <c r="B127" s="191"/>
+      <c r="C127" s="191"/>
+      <c r="D127" s="191"/>
+      <c r="E127" s="191"/>
+      <c r="F127" s="191"/>
+      <c r="G127" s="191"/>
+      <c r="H127" s="191"/>
+      <c r="I127" s="191"/>
+      <c r="J127" s="191"/>
+      <c r="K127" s="191"/>
+      <c r="L127" s="191"/>
+      <c r="M127" s="191"/>
+      <c r="N127" s="191"/>
+      <c r="O127" s="191"/>
+      <c r="P127" s="191"/>
+      <c r="Q127" s="191"/>
+      <c r="R127" s="191"/>
+      <c r="S127" s="191"/>
+      <c r="T127" s="191"/>
+      <c r="U127" s="191"/>
+      <c r="V127" s="191"/>
+      <c r="W127" s="191"/>
+      <c r="X127" s="191"/>
+      <c r="Y127" s="191"/>
+      <c r="Z127" s="191"/>
+      <c r="AA127" s="191"/>
+      <c r="AB127" s="191"/>
+      <c r="AC127" s="191"/>
+      <c r="AD127" s="191"/>
+      <c r="AE127" s="191"/>
+      <c r="AF127" s="191"/>
+      <c r="AG127" s="191"/>
+      <c r="AH127" s="191"/>
+      <c r="AI127" s="191"/>
+      <c r="AJ127" s="191"/>
+      <c r="AK127" s="192"/>
     </row>
   </sheetData>
-  <mergeCells count="156">
+  <mergeCells count="157">
+    <mergeCell ref="E33:M33"/>
+    <mergeCell ref="R59:W59"/>
     <mergeCell ref="A117:AK117"/>
     <mergeCell ref="A118:AE118"/>
     <mergeCell ref="A119:X119"/>
@@ -6779,7 +6811,7 @@
     <mergeCell ref="V57:AB57"/>
     <mergeCell ref="A59:N59"/>
     <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="T59:V59"/>
+    <mergeCell ref="A53:G53"/>
     <mergeCell ref="H53:T53"/>
     <mergeCell ref="V53:AB53"/>
     <mergeCell ref="Y59:AB59"/>
@@ -6792,38 +6824,6 @@
     <mergeCell ref="A51:G51"/>
     <mergeCell ref="H51:T51"/>
     <mergeCell ref="V51:AB51"/>
-    <mergeCell ref="B31:AI31"/>
-    <mergeCell ref="B33:AI33"/>
-    <mergeCell ref="O39:AI39"/>
-    <mergeCell ref="G43:AI43"/>
-    <mergeCell ref="AA45:AI45"/>
-    <mergeCell ref="AC49:AI49"/>
-    <mergeCell ref="AC51:AI51"/>
-    <mergeCell ref="AC53:AI53"/>
-    <mergeCell ref="AC55:AI55"/>
-    <mergeCell ref="A47:AK47"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:L35"/>
-    <mergeCell ref="N35:R35"/>
-    <mergeCell ref="T35:X35"/>
-    <mergeCell ref="AA35:AC35"/>
-    <mergeCell ref="AD35:AE35"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="AB41:AF41"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="V45:Z45"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="A53:G53"/>
-    <mergeCell ref="B2:M3"/>
-    <mergeCell ref="P1:AJ2"/>
-    <mergeCell ref="P3:AJ4"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="A6:AK6"/>
-    <mergeCell ref="S82:AK82"/>
-    <mergeCell ref="AF72:AK72"/>
     <mergeCell ref="S84:AK92"/>
     <mergeCell ref="AF16:AI16"/>
     <mergeCell ref="M14:AI14"/>
@@ -6840,6 +6840,37 @@
     <mergeCell ref="O37:Q37"/>
     <mergeCell ref="T37:Y37"/>
     <mergeCell ref="A39:N39"/>
+    <mergeCell ref="B31:AI31"/>
+    <mergeCell ref="O39:AI39"/>
+    <mergeCell ref="G43:AI43"/>
+    <mergeCell ref="AA45:AI45"/>
+    <mergeCell ref="AC49:AI49"/>
+    <mergeCell ref="AC51:AI51"/>
+    <mergeCell ref="AC53:AI53"/>
+    <mergeCell ref="AC55:AI55"/>
+    <mergeCell ref="P33:AH33"/>
+    <mergeCell ref="B2:M3"/>
+    <mergeCell ref="P1:AJ2"/>
+    <mergeCell ref="P3:AJ4"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="A6:AK6"/>
+    <mergeCell ref="S82:AK82"/>
+    <mergeCell ref="AF72:AK72"/>
+    <mergeCell ref="A47:AK47"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:L35"/>
+    <mergeCell ref="N35:R35"/>
+    <mergeCell ref="T35:X35"/>
+    <mergeCell ref="AA35:AC35"/>
+    <mergeCell ref="AD35:AE35"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="AB41:AF41"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="V45:Z45"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="I37:K37"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/FORMATO.xlsx
+++ b/FORMATO.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dairon Alonso\Desktop\App Streamlit-Prediccion\Streamlit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dairon Alonso\Desktop\Aplicativos Streamlit\Bolivar ARL\Formulario\Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA28E021-3B42-4FA3-8AB2-7B4AAF958B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01ACF0F-A443-4283-B4BF-A78559664850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="6240" windowWidth="23256" windowHeight="12456" xr2:uid="{B5783570-885C-42E9-BB81-08046124F7B7}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="110">
   <si>
     <t>SOLICITUD DE OUTSOURCING DE SERVICIOS ESPECIALIZADOS DE GESTIÓN</t>
   </si>
@@ -399,9 +399,6 @@
   </si>
   <si>
     <t>EL PROFESIONAL SELECCIONADO REQUIERE EXAMENES DE INGRESO ESPECIALIZADOS?</t>
-  </si>
-  <si>
-    <t>AÑOS DE EXPERIENCIA</t>
   </si>
   <si>
     <t>CONDICIÓN DE SALARIO</t>
@@ -1146,7 +1143,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1381,9 +1378,333 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="8" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1396,353 +1717,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="8" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2456,109 +2441,109 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="90" t="s">
+      <c r="P1" s="198" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="90"/>
-      <c r="R1" s="90"/>
-      <c r="S1" s="90"/>
-      <c r="T1" s="90"/>
-      <c r="U1" s="90"/>
-      <c r="V1" s="90"/>
-      <c r="W1" s="90"/>
-      <c r="X1" s="90"/>
-      <c r="Y1" s="90"/>
-      <c r="Z1" s="90"/>
-      <c r="AA1" s="90"/>
-      <c r="AB1" s="90"/>
-      <c r="AC1" s="90"/>
-      <c r="AD1" s="90"/>
-      <c r="AE1" s="90"/>
-      <c r="AF1" s="90"/>
-      <c r="AG1" s="90"/>
-      <c r="AH1" s="90"/>
-      <c r="AI1" s="90"/>
-      <c r="AJ1" s="90"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
+      <c r="V1" s="198"/>
+      <c r="W1" s="198"/>
+      <c r="X1" s="198"/>
+      <c r="Y1" s="198"/>
+      <c r="Z1" s="198"/>
+      <c r="AA1" s="198"/>
+      <c r="AB1" s="198"/>
+      <c r="AC1" s="198"/>
+      <c r="AD1" s="198"/>
+      <c r="AE1" s="198"/>
+      <c r="AF1" s="198"/>
+      <c r="AG1" s="198"/>
+      <c r="AH1" s="198"/>
+      <c r="AI1" s="198"/>
+      <c r="AJ1" s="198"/>
       <c r="AK1" s="6"/>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
+      <c r="B2" s="197"/>
+      <c r="C2" s="197"/>
+      <c r="D2" s="197"/>
+      <c r="E2" s="197"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="197"/>
+      <c r="H2" s="197"/>
+      <c r="I2" s="197"/>
+      <c r="J2" s="197"/>
+      <c r="K2" s="197"/>
+      <c r="L2" s="197"/>
+      <c r="M2" s="197"/>
       <c r="N2" s="64"/>
       <c r="O2" s="64"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
-      <c r="R2" s="89"/>
-      <c r="S2" s="89"/>
-      <c r="T2" s="89"/>
-      <c r="U2" s="89"/>
-      <c r="V2" s="89"/>
-      <c r="W2" s="89"/>
-      <c r="X2" s="89"/>
-      <c r="Y2" s="89"/>
-      <c r="Z2" s="89"/>
-      <c r="AA2" s="89"/>
-      <c r="AB2" s="89"/>
-      <c r="AC2" s="89"/>
-      <c r="AD2" s="89"/>
-      <c r="AE2" s="89"/>
-      <c r="AF2" s="89"/>
-      <c r="AG2" s="89"/>
-      <c r="AH2" s="89"/>
-      <c r="AI2" s="89"/>
-      <c r="AJ2" s="89"/>
+      <c r="P2" s="197"/>
+      <c r="Q2" s="197"/>
+      <c r="R2" s="197"/>
+      <c r="S2" s="197"/>
+      <c r="T2" s="197"/>
+      <c r="U2" s="197"/>
+      <c r="V2" s="197"/>
+      <c r="W2" s="197"/>
+      <c r="X2" s="197"/>
+      <c r="Y2" s="197"/>
+      <c r="Z2" s="197"/>
+      <c r="AA2" s="197"/>
+      <c r="AB2" s="197"/>
+      <c r="AC2" s="197"/>
+      <c r="AD2" s="197"/>
+      <c r="AE2" s="197"/>
+      <c r="AF2" s="197"/>
+      <c r="AG2" s="197"/>
+      <c r="AH2" s="197"/>
+      <c r="AI2" s="197"/>
+      <c r="AJ2" s="197"/>
       <c r="AK2" s="8"/>
     </row>
     <row r="3" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="47"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="89"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
+      <c r="B3" s="197"/>
+      <c r="C3" s="197"/>
+      <c r="D3" s="197"/>
+      <c r="E3" s="197"/>
+      <c r="F3" s="197"/>
+      <c r="G3" s="197"/>
+      <c r="H3" s="197"/>
+      <c r="I3" s="197"/>
+      <c r="J3" s="197"/>
+      <c r="K3" s="197"/>
+      <c r="L3" s="197"/>
+      <c r="M3" s="197"/>
       <c r="N3" s="64"/>
       <c r="O3" s="64"/>
-      <c r="P3" s="89" t="s">
+      <c r="P3" s="197" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="89"/>
-      <c r="R3" s="89"/>
-      <c r="S3" s="89"/>
-      <c r="T3" s="89"/>
-      <c r="U3" s="89"/>
-      <c r="V3" s="89"/>
-      <c r="W3" s="89"/>
-      <c r="X3" s="89"/>
-      <c r="Y3" s="89"/>
-      <c r="Z3" s="89"/>
-      <c r="AA3" s="89"/>
-      <c r="AB3" s="89"/>
-      <c r="AC3" s="89"/>
-      <c r="AD3" s="89"/>
-      <c r="AE3" s="89"/>
-      <c r="AF3" s="89"/>
-      <c r="AG3" s="89"/>
-      <c r="AH3" s="89"/>
-      <c r="AI3" s="89"/>
-      <c r="AJ3" s="89"/>
+      <c r="Q3" s="197"/>
+      <c r="R3" s="197"/>
+      <c r="S3" s="197"/>
+      <c r="T3" s="197"/>
+      <c r="U3" s="197"/>
+      <c r="V3" s="197"/>
+      <c r="W3" s="197"/>
+      <c r="X3" s="197"/>
+      <c r="Y3" s="197"/>
+      <c r="Z3" s="197"/>
+      <c r="AA3" s="197"/>
+      <c r="AB3" s="197"/>
+      <c r="AC3" s="197"/>
+      <c r="AD3" s="197"/>
+      <c r="AE3" s="197"/>
+      <c r="AF3" s="197"/>
+      <c r="AG3" s="197"/>
+      <c r="AH3" s="197"/>
+      <c r="AI3" s="197"/>
+      <c r="AJ3" s="197"/>
       <c r="AK3" s="8"/>
     </row>
     <row r="4" spans="1:37" s="2" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -2577,27 +2562,27 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
-      <c r="P4" s="91"/>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="91"/>
-      <c r="S4" s="91"/>
-      <c r="T4" s="91"/>
-      <c r="U4" s="91"/>
-      <c r="V4" s="91"/>
-      <c r="W4" s="91"/>
-      <c r="X4" s="91"/>
-      <c r="Y4" s="91"/>
-      <c r="Z4" s="91"/>
-      <c r="AA4" s="91"/>
-      <c r="AB4" s="91"/>
-      <c r="AC4" s="91"/>
-      <c r="AD4" s="91"/>
-      <c r="AE4" s="91"/>
-      <c r="AF4" s="91"/>
-      <c r="AG4" s="91"/>
-      <c r="AH4" s="91"/>
-      <c r="AI4" s="91"/>
-      <c r="AJ4" s="91"/>
+      <c r="P4" s="199"/>
+      <c r="Q4" s="199"/>
+      <c r="R4" s="199"/>
+      <c r="S4" s="199"/>
+      <c r="T4" s="199"/>
+      <c r="U4" s="199"/>
+      <c r="V4" s="199"/>
+      <c r="W4" s="199"/>
+      <c r="X4" s="199"/>
+      <c r="Y4" s="199"/>
+      <c r="Z4" s="199"/>
+      <c r="AA4" s="199"/>
+      <c r="AB4" s="199"/>
+      <c r="AC4" s="199"/>
+      <c r="AD4" s="199"/>
+      <c r="AE4" s="199"/>
+      <c r="AF4" s="199"/>
+      <c r="AG4" s="199"/>
+      <c r="AH4" s="199"/>
+      <c r="AI4" s="199"/>
+      <c r="AJ4" s="199"/>
       <c r="AK4" s="10"/>
     </row>
     <row r="5" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2606,75 +2591,75 @@
       <c r="AK5" s="8"/>
     </row>
     <row r="6" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="95"/>
-      <c r="K6" s="95"/>
-      <c r="L6" s="95"/>
-      <c r="M6" s="95"/>
-      <c r="N6" s="95"/>
-      <c r="O6" s="95"/>
-      <c r="P6" s="95"/>
-      <c r="Q6" s="95"/>
-      <c r="R6" s="95"/>
-      <c r="S6" s="95"/>
-      <c r="T6" s="95"/>
-      <c r="U6" s="95"/>
-      <c r="V6" s="95"/>
-      <c r="W6" s="95"/>
-      <c r="X6" s="95"/>
-      <c r="Y6" s="95"/>
-      <c r="Z6" s="95"/>
-      <c r="AA6" s="95"/>
-      <c r="AB6" s="95"/>
-      <c r="AC6" s="95"/>
-      <c r="AD6" s="95"/>
-      <c r="AE6" s="95"/>
-      <c r="AF6" s="95"/>
-      <c r="AG6" s="95"/>
-      <c r="AH6" s="95"/>
-      <c r="AI6" s="95"/>
-      <c r="AJ6" s="95"/>
-      <c r="AK6" s="96"/>
+      <c r="B6" s="93"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="93"/>
+      <c r="N6" s="93"/>
+      <c r="O6" s="93"/>
+      <c r="P6" s="93"/>
+      <c r="Q6" s="93"/>
+      <c r="R6" s="93"/>
+      <c r="S6" s="93"/>
+      <c r="T6" s="93"/>
+      <c r="U6" s="93"/>
+      <c r="V6" s="93"/>
+      <c r="W6" s="93"/>
+      <c r="X6" s="93"/>
+      <c r="Y6" s="93"/>
+      <c r="Z6" s="93"/>
+      <c r="AA6" s="93"/>
+      <c r="AB6" s="93"/>
+      <c r="AC6" s="93"/>
+      <c r="AD6" s="93"/>
+      <c r="AE6" s="93"/>
+      <c r="AF6" s="93"/>
+      <c r="AG6" s="93"/>
+      <c r="AH6" s="93"/>
+      <c r="AI6" s="93"/>
+      <c r="AJ6" s="93"/>
+      <c r="AK6" s="94"/>
     </row>
     <row r="7" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="47"/>
       <c r="AK7" s="8"/>
     </row>
     <row r="8" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="92" t="s">
+      <c r="A8" s="200" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="93"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="93"/>
-      <c r="F8" s="114"/>
-      <c r="G8" s="114"/>
-      <c r="H8" s="114"/>
-      <c r="I8" s="114"/>
-      <c r="J8" s="114"/>
-      <c r="K8" s="114"/>
-      <c r="L8" s="114"/>
-      <c r="M8" s="114"/>
-      <c r="N8" s="114"/>
-      <c r="O8" s="114"/>
-      <c r="R8" s="93" t="s">
+      <c r="B8" s="195"/>
+      <c r="C8" s="195"/>
+      <c r="D8" s="195"/>
+      <c r="E8" s="195"/>
+      <c r="F8" s="192"/>
+      <c r="G8" s="192"/>
+      <c r="H8" s="192"/>
+      <c r="I8" s="192"/>
+      <c r="J8" s="192"/>
+      <c r="K8" s="192"/>
+      <c r="L8" s="192"/>
+      <c r="M8" s="192"/>
+      <c r="N8" s="192"/>
+      <c r="O8" s="192"/>
+      <c r="R8" s="195" t="s">
         <v>4</v>
       </c>
-      <c r="S8" s="93"/>
-      <c r="T8" s="93"/>
-      <c r="U8" s="93"/>
-      <c r="V8" s="93"/>
+      <c r="S8" s="195"/>
+      <c r="T8" s="195"/>
+      <c r="U8" s="195"/>
+      <c r="V8" s="195"/>
       <c r="X8" s="2" t="s">
         <v>5</v>
       </c>
@@ -2706,26 +2691,26 @@
       <c r="L10" s="43"/>
       <c r="M10" s="43"/>
       <c r="N10" s="43"/>
-      <c r="P10" s="113"/>
-      <c r="Q10" s="113"/>
-      <c r="R10" s="113"/>
-      <c r="S10" s="113"/>
-      <c r="T10" s="113"/>
-      <c r="U10" s="113"/>
-      <c r="V10" s="113"/>
-      <c r="W10" s="113"/>
-      <c r="X10" s="113"/>
-      <c r="Y10" s="113"/>
-      <c r="Z10" s="113"/>
-      <c r="AA10" s="113"/>
-      <c r="AB10" s="113"/>
-      <c r="AC10" s="113"/>
-      <c r="AD10" s="113"/>
-      <c r="AE10" s="113"/>
-      <c r="AF10" s="113"/>
-      <c r="AG10" s="113"/>
-      <c r="AH10" s="113"/>
-      <c r="AI10" s="113"/>
+      <c r="P10" s="191"/>
+      <c r="Q10" s="191"/>
+      <c r="R10" s="191"/>
+      <c r="S10" s="191"/>
+      <c r="T10" s="191"/>
+      <c r="U10" s="191"/>
+      <c r="V10" s="191"/>
+      <c r="W10" s="191"/>
+      <c r="X10" s="191"/>
+      <c r="Y10" s="191"/>
+      <c r="Z10" s="191"/>
+      <c r="AA10" s="191"/>
+      <c r="AB10" s="191"/>
+      <c r="AC10" s="191"/>
+      <c r="AD10" s="191"/>
+      <c r="AE10" s="191"/>
+      <c r="AF10" s="191"/>
+      <c r="AG10" s="191"/>
+      <c r="AH10" s="191"/>
+      <c r="AI10" s="191"/>
       <c r="AJ10" s="42"/>
       <c r="AK10" s="8"/>
     </row>
@@ -2752,26 +2737,26 @@
       <c r="N12" s="43"/>
       <c r="O12" s="43"/>
       <c r="P12" s="7"/>
-      <c r="Q12" s="112"/>
-      <c r="R12" s="112"/>
-      <c r="S12" s="112"/>
-      <c r="T12" s="112"/>
-      <c r="U12" s="112"/>
-      <c r="V12" s="112"/>
-      <c r="W12" s="112"/>
-      <c r="X12" s="112"/>
-      <c r="Y12" s="112"/>
-      <c r="Z12" s="112"/>
-      <c r="AA12" s="112"/>
-      <c r="AB12" s="112"/>
-      <c r="AC12" s="112"/>
-      <c r="AD12" s="112"/>
+      <c r="Q12" s="104"/>
+      <c r="R12" s="104"/>
+      <c r="S12" s="104"/>
+      <c r="T12" s="104"/>
+      <c r="U12" s="104"/>
+      <c r="V12" s="104"/>
+      <c r="W12" s="104"/>
+      <c r="X12" s="104"/>
+      <c r="Y12" s="104"/>
+      <c r="Z12" s="104"/>
+      <c r="AA12" s="104"/>
+      <c r="AB12" s="104"/>
+      <c r="AC12" s="104"/>
+      <c r="AD12" s="104"/>
       <c r="AF12" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="AG12" s="112"/>
-      <c r="AH12" s="112"/>
-      <c r="AI12" s="112"/>
+      <c r="AG12" s="104"/>
+      <c r="AH12" s="104"/>
+      <c r="AI12" s="104"/>
       <c r="AJ12" s="42"/>
       <c r="AK12" s="8"/>
     </row>
@@ -2792,29 +2777,29 @@
       <c r="H14" s="43"/>
       <c r="I14" s="43"/>
       <c r="J14" s="43"/>
-      <c r="M14" s="112"/>
-      <c r="N14" s="112"/>
-      <c r="O14" s="112"/>
-      <c r="P14" s="112"/>
-      <c r="Q14" s="112"/>
-      <c r="R14" s="112"/>
-      <c r="S14" s="112"/>
-      <c r="T14" s="112"/>
-      <c r="U14" s="112"/>
-      <c r="V14" s="112"/>
-      <c r="W14" s="112"/>
-      <c r="X14" s="112"/>
-      <c r="Y14" s="112"/>
-      <c r="Z14" s="112"/>
-      <c r="AA14" s="112"/>
-      <c r="AB14" s="112"/>
-      <c r="AC14" s="112"/>
-      <c r="AD14" s="112"/>
-      <c r="AE14" s="112"/>
-      <c r="AF14" s="112"/>
-      <c r="AG14" s="112"/>
-      <c r="AH14" s="112"/>
-      <c r="AI14" s="112"/>
+      <c r="M14" s="104"/>
+      <c r="N14" s="104"/>
+      <c r="O14" s="104"/>
+      <c r="P14" s="104"/>
+      <c r="Q14" s="104"/>
+      <c r="R14" s="104"/>
+      <c r="S14" s="104"/>
+      <c r="T14" s="104"/>
+      <c r="U14" s="104"/>
+      <c r="V14" s="104"/>
+      <c r="W14" s="104"/>
+      <c r="X14" s="104"/>
+      <c r="Y14" s="104"/>
+      <c r="Z14" s="104"/>
+      <c r="AA14" s="104"/>
+      <c r="AB14" s="104"/>
+      <c r="AC14" s="104"/>
+      <c r="AD14" s="104"/>
+      <c r="AE14" s="104"/>
+      <c r="AF14" s="104"/>
+      <c r="AG14" s="104"/>
+      <c r="AH14" s="104"/>
+      <c r="AI14" s="104"/>
       <c r="AJ14" s="42"/>
       <c r="AK14" s="8"/>
     </row>
@@ -2826,31 +2811,31 @@
       <c r="A16" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="112"/>
-      <c r="I16" s="112"/>
-      <c r="J16" s="112"/>
-      <c r="K16" s="112"/>
-      <c r="L16" s="112"/>
-      <c r="M16" s="112"/>
-      <c r="N16" s="112"/>
-      <c r="O16" s="112"/>
-      <c r="P16" s="112"/>
-      <c r="Q16" s="112"/>
-      <c r="R16" s="112"/>
-      <c r="S16" s="112"/>
-      <c r="T16" s="112"/>
-      <c r="U16" s="112"/>
-      <c r="V16" s="112"/>
-      <c r="W16" s="112"/>
-      <c r="X16" s="112"/>
-      <c r="Y16" s="112"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="104"/>
+      <c r="J16" s="104"/>
+      <c r="K16" s="104"/>
+      <c r="L16" s="104"/>
+      <c r="M16" s="104"/>
+      <c r="N16" s="104"/>
+      <c r="O16" s="104"/>
+      <c r="P16" s="104"/>
+      <c r="Q16" s="104"/>
+      <c r="R16" s="104"/>
+      <c r="S16" s="104"/>
+      <c r="T16" s="104"/>
+      <c r="U16" s="104"/>
+      <c r="V16" s="104"/>
+      <c r="W16" s="104"/>
+      <c r="X16" s="104"/>
+      <c r="Y16" s="104"/>
       <c r="AA16" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="AF16" s="112"/>
-      <c r="AG16" s="112"/>
-      <c r="AH16" s="112"/>
-      <c r="AI16" s="112"/>
+      <c r="AF16" s="104"/>
+      <c r="AG16" s="104"/>
+      <c r="AH16" s="104"/>
+      <c r="AI16" s="104"/>
       <c r="AJ16" s="42"/>
       <c r="AK16" s="8"/>
     </row>
@@ -2866,33 +2851,33 @@
       <c r="C18" s="43"/>
       <c r="D18" s="43"/>
       <c r="E18" s="43"/>
-      <c r="G18" s="112"/>
-      <c r="H18" s="112"/>
-      <c r="I18" s="112"/>
-      <c r="J18" s="112"/>
-      <c r="K18" s="112"/>
-      <c r="L18" s="112"/>
-      <c r="M18" s="112"/>
-      <c r="N18" s="112"/>
-      <c r="O18" s="112"/>
-      <c r="P18" s="112"/>
-      <c r="Q18" s="112"/>
-      <c r="R18" s="112"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="104"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="104"/>
+      <c r="N18" s="104"/>
+      <c r="O18" s="104"/>
+      <c r="P18" s="104"/>
+      <c r="Q18" s="104"/>
+      <c r="R18" s="104"/>
       <c r="T18" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="X18" s="112"/>
-      <c r="Y18" s="112"/>
-      <c r="Z18" s="112"/>
-      <c r="AA18" s="112"/>
-      <c r="AB18" s="112"/>
-      <c r="AC18" s="112"/>
-      <c r="AD18" s="112"/>
-      <c r="AE18" s="112"/>
-      <c r="AF18" s="112"/>
-      <c r="AG18" s="112"/>
-      <c r="AH18" s="112"/>
-      <c r="AI18" s="112"/>
+      <c r="X18" s="104"/>
+      <c r="Y18" s="104"/>
+      <c r="Z18" s="104"/>
+      <c r="AA18" s="104"/>
+      <c r="AB18" s="104"/>
+      <c r="AC18" s="104"/>
+      <c r="AD18" s="104"/>
+      <c r="AE18" s="104"/>
+      <c r="AF18" s="104"/>
+      <c r="AG18" s="104"/>
+      <c r="AH18" s="104"/>
+      <c r="AI18" s="104"/>
       <c r="AJ18" s="42"/>
       <c r="AK18" s="8"/>
     </row>
@@ -2906,45 +2891,45 @@
       <c r="AK20" s="8"/>
     </row>
     <row r="21" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="117" t="s">
+      <c r="A21" s="185" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="118"/>
-      <c r="C21" s="118"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="118"/>
-      <c r="F21" s="118"/>
-      <c r="G21" s="118"/>
-      <c r="H21" s="118"/>
-      <c r="I21" s="118"/>
-      <c r="J21" s="118"/>
-      <c r="K21" s="118"/>
-      <c r="L21" s="118"/>
-      <c r="M21" s="118"/>
-      <c r="N21" s="118"/>
-      <c r="O21" s="118"/>
-      <c r="P21" s="118"/>
-      <c r="Q21" s="118"/>
-      <c r="R21" s="118"/>
-      <c r="S21" s="118"/>
-      <c r="T21" s="118"/>
-      <c r="U21" s="118"/>
-      <c r="V21" s="118"/>
-      <c r="W21" s="118"/>
-      <c r="X21" s="118"/>
-      <c r="Y21" s="118"/>
-      <c r="Z21" s="118"/>
-      <c r="AA21" s="118"/>
-      <c r="AB21" s="118"/>
-      <c r="AC21" s="118"/>
-      <c r="AD21" s="118"/>
-      <c r="AE21" s="118"/>
-      <c r="AF21" s="118"/>
-      <c r="AG21" s="118"/>
-      <c r="AH21" s="118"/>
-      <c r="AI21" s="118"/>
-      <c r="AJ21" s="118"/>
-      <c r="AK21" s="119"/>
+      <c r="B21" s="186"/>
+      <c r="C21" s="186"/>
+      <c r="D21" s="186"/>
+      <c r="E21" s="186"/>
+      <c r="F21" s="186"/>
+      <c r="G21" s="186"/>
+      <c r="H21" s="186"/>
+      <c r="I21" s="186"/>
+      <c r="J21" s="186"/>
+      <c r="K21" s="186"/>
+      <c r="L21" s="186"/>
+      <c r="M21" s="186"/>
+      <c r="N21" s="186"/>
+      <c r="O21" s="186"/>
+      <c r="P21" s="186"/>
+      <c r="Q21" s="186"/>
+      <c r="R21" s="186"/>
+      <c r="S21" s="186"/>
+      <c r="T21" s="186"/>
+      <c r="U21" s="186"/>
+      <c r="V21" s="186"/>
+      <c r="W21" s="186"/>
+      <c r="X21" s="186"/>
+      <c r="Y21" s="186"/>
+      <c r="Z21" s="186"/>
+      <c r="AA21" s="186"/>
+      <c r="AB21" s="186"/>
+      <c r="AC21" s="186"/>
+      <c r="AD21" s="186"/>
+      <c r="AE21" s="186"/>
+      <c r="AF21" s="186"/>
+      <c r="AG21" s="186"/>
+      <c r="AH21" s="186"/>
+      <c r="AI21" s="186"/>
+      <c r="AJ21" s="186"/>
+      <c r="AK21" s="187"/>
     </row>
     <row r="22" spans="1:37" s="2" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="47"/>
@@ -2960,35 +2945,35 @@
       <c r="D23" s="57"/>
       <c r="E23" s="57"/>
       <c r="F23" s="57"/>
-      <c r="G23" s="112"/>
-      <c r="H23" s="112"/>
-      <c r="I23" s="112"/>
-      <c r="J23" s="112"/>
-      <c r="K23" s="112"/>
-      <c r="L23" s="112"/>
-      <c r="M23" s="112"/>
-      <c r="N23" s="112"/>
-      <c r="O23" s="112"/>
-      <c r="P23" s="112"/>
-      <c r="Q23" s="112"/>
-      <c r="R23" s="112"/>
-      <c r="S23" s="112"/>
-      <c r="T23" s="112"/>
-      <c r="U23" s="112"/>
-      <c r="V23" s="112"/>
-      <c r="W23" s="112"/>
-      <c r="X23" s="112"/>
-      <c r="Y23" s="112"/>
-      <c r="Z23" s="112"/>
-      <c r="AA23" s="112"/>
-      <c r="AB23" s="112"/>
-      <c r="AC23" s="112"/>
-      <c r="AD23" s="112"/>
-      <c r="AE23" s="112"/>
-      <c r="AF23" s="112"/>
-      <c r="AG23" s="112"/>
-      <c r="AH23" s="112"/>
-      <c r="AI23" s="112"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="104"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="104"/>
+      <c r="N23" s="104"/>
+      <c r="O23" s="104"/>
+      <c r="P23" s="104"/>
+      <c r="Q23" s="104"/>
+      <c r="R23" s="104"/>
+      <c r="S23" s="104"/>
+      <c r="T23" s="104"/>
+      <c r="U23" s="104"/>
+      <c r="V23" s="104"/>
+      <c r="W23" s="104"/>
+      <c r="X23" s="104"/>
+      <c r="Y23" s="104"/>
+      <c r="Z23" s="104"/>
+      <c r="AA23" s="104"/>
+      <c r="AB23" s="104"/>
+      <c r="AC23" s="104"/>
+      <c r="AD23" s="104"/>
+      <c r="AE23" s="104"/>
+      <c r="AF23" s="104"/>
+      <c r="AG23" s="104"/>
+      <c r="AH23" s="104"/>
+      <c r="AI23" s="104"/>
       <c r="AJ23" s="42"/>
       <c r="AK23" s="8"/>
     </row>
@@ -2998,40 +2983,40 @@
     </row>
     <row r="25" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="46"/>
-      <c r="B25" s="115"/>
-      <c r="C25" s="115"/>
-      <c r="D25" s="115"/>
-      <c r="E25" s="115"/>
-      <c r="F25" s="115"/>
-      <c r="G25" s="115"/>
-      <c r="H25" s="115"/>
-      <c r="I25" s="115"/>
-      <c r="J25" s="115"/>
-      <c r="K25" s="115"/>
-      <c r="L25" s="115"/>
-      <c r="M25" s="115"/>
-      <c r="N25" s="115"/>
-      <c r="O25" s="115"/>
-      <c r="P25" s="115"/>
-      <c r="Q25" s="115"/>
-      <c r="R25" s="115"/>
-      <c r="S25" s="115"/>
-      <c r="T25" s="115"/>
-      <c r="U25" s="115"/>
-      <c r="V25" s="115"/>
-      <c r="W25" s="115"/>
-      <c r="X25" s="115"/>
-      <c r="Y25" s="115"/>
-      <c r="Z25" s="115"/>
-      <c r="AA25" s="115"/>
-      <c r="AB25" s="115"/>
-      <c r="AC25" s="115"/>
-      <c r="AD25" s="115"/>
-      <c r="AE25" s="115"/>
-      <c r="AF25" s="115"/>
-      <c r="AG25" s="115"/>
-      <c r="AH25" s="115"/>
-      <c r="AI25" s="115"/>
+      <c r="B25" s="193"/>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193"/>
+      <c r="G25" s="193"/>
+      <c r="H25" s="193"/>
+      <c r="I25" s="193"/>
+      <c r="J25" s="193"/>
+      <c r="K25" s="193"/>
+      <c r="L25" s="193"/>
+      <c r="M25" s="193"/>
+      <c r="N25" s="193"/>
+      <c r="O25" s="193"/>
+      <c r="P25" s="193"/>
+      <c r="Q25" s="193"/>
+      <c r="R25" s="193"/>
+      <c r="S25" s="193"/>
+      <c r="T25" s="193"/>
+      <c r="U25" s="193"/>
+      <c r="V25" s="193"/>
+      <c r="W25" s="193"/>
+      <c r="X25" s="193"/>
+      <c r="Y25" s="193"/>
+      <c r="Z25" s="193"/>
+      <c r="AA25" s="193"/>
+      <c r="AB25" s="193"/>
+      <c r="AC25" s="193"/>
+      <c r="AD25" s="193"/>
+      <c r="AE25" s="193"/>
+      <c r="AF25" s="193"/>
+      <c r="AG25" s="193"/>
+      <c r="AH25" s="193"/>
+      <c r="AI25" s="193"/>
       <c r="AJ25" s="57"/>
       <c r="AK25" s="8"/>
     </row>
@@ -3042,40 +3027,40 @@
     </row>
     <row r="27" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="50"/>
-      <c r="B27" s="116"/>
-      <c r="C27" s="116"/>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="116"/>
-      <c r="I27" s="116"/>
-      <c r="J27" s="116"/>
-      <c r="K27" s="116"/>
-      <c r="L27" s="116"/>
-      <c r="M27" s="116"/>
-      <c r="N27" s="116"/>
-      <c r="O27" s="116"/>
-      <c r="P27" s="116"/>
-      <c r="Q27" s="116"/>
-      <c r="R27" s="116"/>
-      <c r="S27" s="116"/>
-      <c r="T27" s="116"/>
-      <c r="U27" s="116"/>
-      <c r="V27" s="116"/>
-      <c r="W27" s="116"/>
-      <c r="X27" s="116"/>
-      <c r="Y27" s="116"/>
-      <c r="Z27" s="116"/>
-      <c r="AA27" s="116"/>
-      <c r="AB27" s="116"/>
-      <c r="AC27" s="116"/>
-      <c r="AD27" s="116"/>
-      <c r="AE27" s="116"/>
-      <c r="AF27" s="116"/>
-      <c r="AG27" s="116"/>
-      <c r="AH27" s="116"/>
-      <c r="AI27" s="116"/>
+      <c r="B27" s="194"/>
+      <c r="C27" s="194"/>
+      <c r="D27" s="194"/>
+      <c r="E27" s="194"/>
+      <c r="F27" s="194"/>
+      <c r="G27" s="194"/>
+      <c r="H27" s="194"/>
+      <c r="I27" s="194"/>
+      <c r="J27" s="194"/>
+      <c r="K27" s="194"/>
+      <c r="L27" s="194"/>
+      <c r="M27" s="194"/>
+      <c r="N27" s="194"/>
+      <c r="O27" s="194"/>
+      <c r="P27" s="194"/>
+      <c r="Q27" s="194"/>
+      <c r="R27" s="194"/>
+      <c r="S27" s="194"/>
+      <c r="T27" s="194"/>
+      <c r="U27" s="194"/>
+      <c r="V27" s="194"/>
+      <c r="W27" s="194"/>
+      <c r="X27" s="194"/>
+      <c r="Y27" s="194"/>
+      <c r="Z27" s="194"/>
+      <c r="AA27" s="194"/>
+      <c r="AB27" s="194"/>
+      <c r="AC27" s="194"/>
+      <c r="AD27" s="194"/>
+      <c r="AE27" s="194"/>
+      <c r="AF27" s="194"/>
+      <c r="AG27" s="194"/>
+      <c r="AH27" s="194"/>
+      <c r="AI27" s="194"/>
       <c r="AJ27" s="59"/>
       <c r="AK27" s="8"/>
     </row>
@@ -3085,7 +3070,7 @@
       <c r="AK28" s="8"/>
     </row>
     <row r="29" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="46" t="s">
+      <c r="A29" s="204" t="s">
         <v>17</v>
       </c>
       <c r="B29" s="57"/>
@@ -3103,25 +3088,25 @@
       <c r="N29" s="57"/>
       <c r="O29" s="57"/>
       <c r="P29" s="57"/>
-      <c r="Q29" s="112"/>
-      <c r="R29" s="112"/>
-      <c r="S29" s="112"/>
-      <c r="T29" s="112"/>
-      <c r="U29" s="112"/>
-      <c r="V29" s="112"/>
-      <c r="W29" s="112"/>
-      <c r="X29" s="112"/>
-      <c r="Y29" s="112"/>
-      <c r="Z29" s="112"/>
-      <c r="AA29" s="112"/>
-      <c r="AB29" s="112"/>
-      <c r="AC29" s="112"/>
-      <c r="AD29" s="112"/>
-      <c r="AE29" s="112"/>
-      <c r="AF29" s="112"/>
-      <c r="AG29" s="112"/>
-      <c r="AH29" s="112"/>
-      <c r="AI29" s="112"/>
+      <c r="Q29" s="104"/>
+      <c r="R29" s="104"/>
+      <c r="S29" s="104"/>
+      <c r="T29" s="104"/>
+      <c r="U29" s="104"/>
+      <c r="V29" s="104"/>
+      <c r="W29" s="104"/>
+      <c r="X29" s="104"/>
+      <c r="Y29" s="104"/>
+      <c r="Z29" s="104"/>
+      <c r="AA29" s="104"/>
+      <c r="AB29" s="104"/>
+      <c r="AC29" s="104"/>
+      <c r="AD29" s="104"/>
+      <c r="AE29" s="104"/>
+      <c r="AF29" s="104"/>
+      <c r="AG29" s="104"/>
+      <c r="AH29" s="104"/>
+      <c r="AI29" s="104"/>
       <c r="AJ29" s="64"/>
       <c r="AK29" s="8"/>
     </row>
@@ -3132,40 +3117,40 @@
     </row>
     <row r="31" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="47"/>
-      <c r="B31" s="112"/>
-      <c r="C31" s="112"/>
-      <c r="D31" s="112"/>
-      <c r="E31" s="112"/>
-      <c r="F31" s="112"/>
-      <c r="G31" s="112"/>
-      <c r="H31" s="112"/>
-      <c r="I31" s="112"/>
-      <c r="J31" s="112"/>
-      <c r="K31" s="112"/>
-      <c r="L31" s="112"/>
-      <c r="M31" s="112"/>
-      <c r="N31" s="112"/>
-      <c r="O31" s="112"/>
-      <c r="P31" s="112"/>
-      <c r="Q31" s="112"/>
-      <c r="R31" s="112"/>
-      <c r="S31" s="112"/>
-      <c r="T31" s="112"/>
-      <c r="U31" s="112"/>
-      <c r="V31" s="112"/>
-      <c r="W31" s="112"/>
-      <c r="X31" s="112"/>
-      <c r="Y31" s="112"/>
-      <c r="Z31" s="112"/>
-      <c r="AA31" s="112"/>
-      <c r="AB31" s="112"/>
-      <c r="AC31" s="112"/>
-      <c r="AD31" s="112"/>
-      <c r="AE31" s="112"/>
-      <c r="AF31" s="112"/>
-      <c r="AG31" s="112"/>
-      <c r="AH31" s="112"/>
-      <c r="AI31" s="112"/>
+      <c r="B31" s="104"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="104"/>
+      <c r="N31" s="104"/>
+      <c r="O31" s="104"/>
+      <c r="P31" s="104"/>
+      <c r="Q31" s="104"/>
+      <c r="R31" s="104"/>
+      <c r="S31" s="104"/>
+      <c r="T31" s="104"/>
+      <c r="U31" s="104"/>
+      <c r="V31" s="104"/>
+      <c r="W31" s="104"/>
+      <c r="X31" s="104"/>
+      <c r="Y31" s="104"/>
+      <c r="Z31" s="104"/>
+      <c r="AA31" s="104"/>
+      <c r="AB31" s="104"/>
+      <c r="AC31" s="104"/>
+      <c r="AD31" s="104"/>
+      <c r="AE31" s="104"/>
+      <c r="AF31" s="104"/>
+      <c r="AG31" s="104"/>
+      <c r="AH31" s="104"/>
+      <c r="AI31" s="104"/>
       <c r="AJ31" s="65"/>
       <c r="AK31" s="8"/>
     </row>
@@ -3176,43 +3161,41 @@
     </row>
     <row r="33" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="50"/>
-      <c r="B33" s="207" t="s">
-        <v>108</v>
-      </c>
+      <c r="B33" s="88"/>
       <c r="C33" s="87"/>
       <c r="D33" s="87"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="88"/>
-      <c r="H33" s="88"/>
-      <c r="I33" s="88"/>
-      <c r="J33" s="88"/>
-      <c r="K33" s="88"/>
-      <c r="L33" s="88"/>
-      <c r="M33" s="88"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="132"/>
+      <c r="H33" s="132"/>
+      <c r="I33" s="132"/>
+      <c r="J33" s="132"/>
+      <c r="K33" s="132"/>
+      <c r="L33" s="132"/>
+      <c r="M33" s="132"/>
       <c r="N33" s="87"/>
-      <c r="O33" s="207" t="s">
-        <v>109</v>
-      </c>
-      <c r="P33" s="88"/>
-      <c r="Q33" s="88"/>
-      <c r="R33" s="88"/>
-      <c r="S33" s="88"/>
-      <c r="T33" s="88"/>
-      <c r="U33" s="88"/>
-      <c r="V33" s="88"/>
-      <c r="W33" s="88"/>
-      <c r="X33" s="88"/>
-      <c r="Y33" s="88"/>
-      <c r="Z33" s="88"/>
-      <c r="AA33" s="88"/>
-      <c r="AB33" s="88"/>
-      <c r="AC33" s="88"/>
-      <c r="AD33" s="88"/>
-      <c r="AE33" s="88"/>
-      <c r="AF33" s="88"/>
-      <c r="AG33" s="88"/>
-      <c r="AH33" s="88"/>
+      <c r="O33" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="P33" s="132"/>
+      <c r="Q33" s="132"/>
+      <c r="R33" s="132"/>
+      <c r="S33" s="132"/>
+      <c r="T33" s="132"/>
+      <c r="U33" s="132"/>
+      <c r="V33" s="132"/>
+      <c r="W33" s="132"/>
+      <c r="X33" s="132"/>
+      <c r="Y33" s="132"/>
+      <c r="Z33" s="132"/>
+      <c r="AA33" s="132"/>
+      <c r="AB33" s="132"/>
+      <c r="AC33" s="132"/>
+      <c r="AD33" s="132"/>
+      <c r="AE33" s="132"/>
+      <c r="AF33" s="132"/>
+      <c r="AG33" s="132"/>
+      <c r="AH33" s="132"/>
       <c r="AI33" s="87"/>
       <c r="AJ33" s="59"/>
       <c r="AK33" s="8"/>
@@ -3223,47 +3206,47 @@
       <c r="AK34" s="8"/>
     </row>
     <row r="35" spans="1:39" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="125" t="s">
+      <c r="A35" s="201" t="s">
         <v>18</v>
       </c>
-      <c r="B35" s="126"/>
-      <c r="C35" s="126"/>
-      <c r="D35" s="127">
+      <c r="B35" s="202"/>
+      <c r="C35" s="202"/>
+      <c r="D35" s="180">
         <v>0</v>
       </c>
-      <c r="E35" s="127"/>
-      <c r="F35" s="127"/>
-      <c r="G35" s="127"/>
-      <c r="H35" s="127"/>
-      <c r="I35" s="127"/>
-      <c r="J35" s="127"/>
-      <c r="K35" s="127"/>
-      <c r="L35" s="127"/>
+      <c r="E35" s="180"/>
+      <c r="F35" s="180"/>
+      <c r="G35" s="180"/>
+      <c r="H35" s="180"/>
+      <c r="I35" s="180"/>
+      <c r="J35" s="180"/>
+      <c r="K35" s="180"/>
+      <c r="L35" s="180"/>
       <c r="M35" s="58"/>
-      <c r="N35" s="128" t="s">
+      <c r="N35" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="O35" s="128"/>
-      <c r="P35" s="128"/>
-      <c r="Q35" s="128"/>
-      <c r="R35" s="128"/>
+      <c r="O35" s="141"/>
+      <c r="P35" s="141"/>
+      <c r="Q35" s="141"/>
+      <c r="R35" s="141"/>
       <c r="S35" s="58"/>
-      <c r="T35" s="120" t="s">
+      <c r="T35" s="177" t="s">
         <v>20</v>
       </c>
-      <c r="U35" s="120"/>
-      <c r="V35" s="120"/>
-      <c r="W35" s="120"/>
-      <c r="X35" s="120"/>
+      <c r="U35" s="177"/>
+      <c r="V35" s="177"/>
+      <c r="W35" s="177"/>
+      <c r="X35" s="177"/>
       <c r="Y35" s="58"/>
       <c r="Z35" s="16"/>
-      <c r="AA35" s="129"/>
-      <c r="AB35" s="120"/>
-      <c r="AC35" s="120"/>
-      <c r="AD35" s="120" t="s">
+      <c r="AA35" s="203"/>
+      <c r="AB35" s="177"/>
+      <c r="AC35" s="177"/>
+      <c r="AD35" s="177" t="s">
         <v>21</v>
       </c>
-      <c r="AE35" s="120"/>
+      <c r="AE35" s="177"/>
       <c r="AF35" s="59"/>
       <c r="AG35" s="14"/>
       <c r="AH35" s="59"/>
@@ -3275,39 +3258,39 @@
       <c r="AK36" s="8"/>
     </row>
     <row r="37" spans="1:39" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="121" t="s">
+      <c r="A37" s="189" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="122"/>
-      <c r="C37" s="122"/>
-      <c r="D37" s="122"/>
-      <c r="E37" s="122"/>
-      <c r="F37" s="122"/>
-      <c r="G37" s="122"/>
-      <c r="H37" s="122"/>
-      <c r="I37" s="120" t="s">
+      <c r="B37" s="190"/>
+      <c r="C37" s="190"/>
+      <c r="D37" s="190"/>
+      <c r="E37" s="190"/>
+      <c r="F37" s="190"/>
+      <c r="G37" s="190"/>
+      <c r="H37" s="190"/>
+      <c r="I37" s="177" t="s">
         <v>23</v>
       </c>
-      <c r="J37" s="120"/>
-      <c r="K37" s="120"/>
+      <c r="J37" s="177"/>
+      <c r="K37" s="177"/>
       <c r="L37" s="16"/>
       <c r="M37" s="59"/>
       <c r="N37" s="59"/>
-      <c r="O37" s="120" t="s">
+      <c r="O37" s="177" t="s">
         <v>24</v>
       </c>
-      <c r="P37" s="120"/>
-      <c r="Q37" s="120"/>
+      <c r="P37" s="177"/>
+      <c r="Q37" s="177"/>
       <c r="R37" s="14"/>
       <c r="S37" s="59"/>
-      <c r="T37" s="93" t="s">
+      <c r="T37" s="195" t="s">
         <v>25</v>
       </c>
-      <c r="U37" s="93"/>
-      <c r="V37" s="93"/>
-      <c r="W37" s="93"/>
-      <c r="X37" s="93"/>
-      <c r="Y37" s="93"/>
+      <c r="U37" s="195"/>
+      <c r="V37" s="195"/>
+      <c r="W37" s="195"/>
+      <c r="X37" s="195"/>
+      <c r="Y37" s="195"/>
       <c r="Z37" s="86"/>
       <c r="AK37" s="8"/>
     </row>
@@ -3317,43 +3300,43 @@
       <c r="AK38" s="8"/>
     </row>
     <row r="39" spans="1:39" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="121" t="s">
+      <c r="A39" s="189" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="122"/>
-      <c r="C39" s="122"/>
-      <c r="D39" s="122"/>
-      <c r="E39" s="122"/>
-      <c r="F39" s="122"/>
-      <c r="G39" s="122"/>
-      <c r="H39" s="122"/>
-      <c r="I39" s="122"/>
-      <c r="J39" s="122"/>
-      <c r="K39" s="122"/>
-      <c r="L39" s="122"/>
-      <c r="M39" s="122"/>
-      <c r="N39" s="122"/>
-      <c r="O39" s="123"/>
-      <c r="P39" s="123"/>
-      <c r="Q39" s="123"/>
-      <c r="R39" s="123"/>
-      <c r="S39" s="123"/>
-      <c r="T39" s="123"/>
-      <c r="U39" s="123"/>
-      <c r="V39" s="123"/>
-      <c r="W39" s="123"/>
-      <c r="X39" s="123"/>
-      <c r="Y39" s="123"/>
-      <c r="Z39" s="123"/>
-      <c r="AA39" s="123"/>
-      <c r="AB39" s="123"/>
-      <c r="AC39" s="123"/>
-      <c r="AD39" s="123"/>
-      <c r="AE39" s="123"/>
-      <c r="AF39" s="123"/>
-      <c r="AG39" s="123"/>
-      <c r="AH39" s="123"/>
-      <c r="AI39" s="123"/>
+      <c r="B39" s="190"/>
+      <c r="C39" s="190"/>
+      <c r="D39" s="190"/>
+      <c r="E39" s="190"/>
+      <c r="F39" s="190"/>
+      <c r="G39" s="190"/>
+      <c r="H39" s="190"/>
+      <c r="I39" s="190"/>
+      <c r="J39" s="190"/>
+      <c r="K39" s="190"/>
+      <c r="L39" s="190"/>
+      <c r="M39" s="190"/>
+      <c r="N39" s="190"/>
+      <c r="O39" s="196"/>
+      <c r="P39" s="196"/>
+      <c r="Q39" s="196"/>
+      <c r="R39" s="196"/>
+      <c r="S39" s="196"/>
+      <c r="T39" s="196"/>
+      <c r="U39" s="196"/>
+      <c r="V39" s="196"/>
+      <c r="W39" s="196"/>
+      <c r="X39" s="196"/>
+      <c r="Y39" s="196"/>
+      <c r="Z39" s="196"/>
+      <c r="AA39" s="196"/>
+      <c r="AB39" s="196"/>
+      <c r="AC39" s="196"/>
+      <c r="AD39" s="196"/>
+      <c r="AE39" s="196"/>
+      <c r="AF39" s="196"/>
+      <c r="AG39" s="196"/>
+      <c r="AH39" s="196"/>
+      <c r="AI39" s="196"/>
       <c r="AJ39" s="59"/>
       <c r="AK39" s="8"/>
     </row>
@@ -3363,13 +3346,13 @@
       <c r="AK40" s="8"/>
     </row>
     <row r="41" spans="1:39" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="121" t="s">
+      <c r="A41" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="122"/>
-      <c r="C41" s="122"/>
-      <c r="D41" s="122"/>
-      <c r="E41" s="122"/>
+      <c r="B41" s="190"/>
+      <c r="C41" s="190"/>
+      <c r="D41" s="190"/>
+      <c r="E41" s="190"/>
       <c r="F41" s="58"/>
       <c r="G41" s="60" t="s">
         <v>28</v>
@@ -3406,13 +3389,13 @@
       </c>
       <c r="Z41" s="14"/>
       <c r="AA41" s="15"/>
-      <c r="AB41" s="120" t="s">
+      <c r="AB41" s="177" t="s">
         <v>35</v>
       </c>
-      <c r="AC41" s="120"/>
-      <c r="AD41" s="120"/>
-      <c r="AE41" s="120"/>
-      <c r="AF41" s="120"/>
+      <c r="AC41" s="177"/>
+      <c r="AD41" s="177"/>
+      <c r="AE41" s="177"/>
+      <c r="AF41" s="177"/>
       <c r="AG41" s="14"/>
       <c r="AH41" s="59"/>
       <c r="AI41" s="59"/>
@@ -3426,43 +3409,43 @@
       <c r="AK42" s="8"/>
     </row>
     <row r="43" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="121" t="s">
+      <c r="A43" s="189" t="s">
         <v>36</v>
       </c>
-      <c r="B43" s="122"/>
-      <c r="C43" s="122"/>
-      <c r="D43" s="122"/>
-      <c r="E43" s="122"/>
-      <c r="F43" s="122"/>
-      <c r="G43" s="124"/>
-      <c r="H43" s="124"/>
-      <c r="I43" s="124"/>
-      <c r="J43" s="124"/>
-      <c r="K43" s="124"/>
-      <c r="L43" s="124"/>
-      <c r="M43" s="124"/>
-      <c r="N43" s="124"/>
-      <c r="O43" s="124"/>
-      <c r="P43" s="124"/>
-      <c r="Q43" s="124"/>
-      <c r="R43" s="124"/>
-      <c r="S43" s="124"/>
-      <c r="T43" s="124"/>
-      <c r="U43" s="124"/>
-      <c r="V43" s="124"/>
-      <c r="W43" s="124"/>
-      <c r="X43" s="124"/>
-      <c r="Y43" s="124"/>
-      <c r="Z43" s="124"/>
-      <c r="AA43" s="124"/>
-      <c r="AB43" s="124"/>
-      <c r="AC43" s="124"/>
-      <c r="AD43" s="124"/>
-      <c r="AE43" s="124"/>
-      <c r="AF43" s="124"/>
-      <c r="AG43" s="124"/>
-      <c r="AH43" s="124"/>
-      <c r="AI43" s="124"/>
+      <c r="B43" s="190"/>
+      <c r="C43" s="190"/>
+      <c r="D43" s="190"/>
+      <c r="E43" s="190"/>
+      <c r="F43" s="190"/>
+      <c r="G43" s="179"/>
+      <c r="H43" s="179"/>
+      <c r="I43" s="179"/>
+      <c r="J43" s="179"/>
+      <c r="K43" s="179"/>
+      <c r="L43" s="179"/>
+      <c r="M43" s="179"/>
+      <c r="N43" s="179"/>
+      <c r="O43" s="179"/>
+      <c r="P43" s="179"/>
+      <c r="Q43" s="179"/>
+      <c r="R43" s="179"/>
+      <c r="S43" s="179"/>
+      <c r="T43" s="179"/>
+      <c r="U43" s="179"/>
+      <c r="V43" s="179"/>
+      <c r="W43" s="179"/>
+      <c r="X43" s="179"/>
+      <c r="Y43" s="179"/>
+      <c r="Z43" s="179"/>
+      <c r="AA43" s="179"/>
+      <c r="AB43" s="179"/>
+      <c r="AC43" s="179"/>
+      <c r="AD43" s="179"/>
+      <c r="AE43" s="179"/>
+      <c r="AF43" s="179"/>
+      <c r="AG43" s="179"/>
+      <c r="AH43" s="179"/>
+      <c r="AI43" s="179"/>
       <c r="AJ43" s="58"/>
       <c r="AK43" s="8"/>
     </row>
@@ -3472,14 +3455,14 @@
       <c r="AK44" s="8"/>
     </row>
     <row r="45" spans="1:39" s="2" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="121" t="s">
+      <c r="A45" s="189" t="s">
         <v>37</v>
       </c>
-      <c r="B45" s="122"/>
-      <c r="C45" s="122"/>
-      <c r="D45" s="122"/>
-      <c r="E45" s="122"/>
-      <c r="F45" s="122"/>
+      <c r="B45" s="190"/>
+      <c r="C45" s="190"/>
+      <c r="D45" s="190"/>
+      <c r="E45" s="190"/>
+      <c r="F45" s="190"/>
       <c r="G45" s="60">
         <v>1</v>
       </c>
@@ -3505,24 +3488,24 @@
       </c>
       <c r="T45" s="16"/>
       <c r="U45" s="58"/>
-      <c r="V45" s="120" t="s">
+      <c r="V45" s="177" t="s">
         <v>38</v>
       </c>
-      <c r="W45" s="120"/>
-      <c r="X45" s="120"/>
-      <c r="Y45" s="120"/>
-      <c r="Z45" s="120"/>
-      <c r="AA45" s="124" t="s">
+      <c r="W45" s="177"/>
+      <c r="X45" s="177"/>
+      <c r="Y45" s="177"/>
+      <c r="Z45" s="177"/>
+      <c r="AA45" s="179" t="s">
         <v>39</v>
       </c>
-      <c r="AB45" s="124"/>
-      <c r="AC45" s="124"/>
-      <c r="AD45" s="124"/>
-      <c r="AE45" s="124"/>
-      <c r="AF45" s="124"/>
-      <c r="AG45" s="124"/>
-      <c r="AH45" s="124"/>
-      <c r="AI45" s="124"/>
+      <c r="AB45" s="179"/>
+      <c r="AC45" s="179"/>
+      <c r="AD45" s="179"/>
+      <c r="AE45" s="179"/>
+      <c r="AF45" s="179"/>
+      <c r="AG45" s="179"/>
+      <c r="AH45" s="179"/>
+      <c r="AI45" s="179"/>
       <c r="AJ45" s="59"/>
       <c r="AK45" s="8"/>
     </row>
@@ -3566,45 +3549,45 @@
       <c r="AK46" s="10"/>
     </row>
     <row r="47" spans="1:39" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="117" t="s">
+      <c r="A47" s="185" t="s">
         <v>40</v>
       </c>
-      <c r="B47" s="118"/>
-      <c r="C47" s="118"/>
-      <c r="D47" s="118"/>
-      <c r="E47" s="118"/>
-      <c r="F47" s="118"/>
-      <c r="G47" s="118"/>
-      <c r="H47" s="118"/>
-      <c r="I47" s="118"/>
-      <c r="J47" s="118"/>
-      <c r="K47" s="118"/>
-      <c r="L47" s="118"/>
-      <c r="M47" s="118"/>
-      <c r="N47" s="118"/>
-      <c r="O47" s="118"/>
-      <c r="P47" s="118"/>
-      <c r="Q47" s="118"/>
-      <c r="R47" s="118"/>
-      <c r="S47" s="118"/>
-      <c r="T47" s="118"/>
-      <c r="U47" s="118"/>
-      <c r="V47" s="118"/>
-      <c r="W47" s="118"/>
-      <c r="X47" s="118"/>
-      <c r="Y47" s="118"/>
-      <c r="Z47" s="118"/>
-      <c r="AA47" s="118"/>
-      <c r="AB47" s="118"/>
-      <c r="AC47" s="118"/>
-      <c r="AD47" s="118"/>
-      <c r="AE47" s="118"/>
-      <c r="AF47" s="118"/>
-      <c r="AG47" s="118"/>
-      <c r="AH47" s="118"/>
-      <c r="AI47" s="118"/>
-      <c r="AJ47" s="118"/>
-      <c r="AK47" s="119"/>
+      <c r="B47" s="186"/>
+      <c r="C47" s="186"/>
+      <c r="D47" s="186"/>
+      <c r="E47" s="186"/>
+      <c r="F47" s="186"/>
+      <c r="G47" s="186"/>
+      <c r="H47" s="186"/>
+      <c r="I47" s="186"/>
+      <c r="J47" s="186"/>
+      <c r="K47" s="186"/>
+      <c r="L47" s="186"/>
+      <c r="M47" s="186"/>
+      <c r="N47" s="186"/>
+      <c r="O47" s="186"/>
+      <c r="P47" s="186"/>
+      <c r="Q47" s="186"/>
+      <c r="R47" s="186"/>
+      <c r="S47" s="186"/>
+      <c r="T47" s="186"/>
+      <c r="U47" s="186"/>
+      <c r="V47" s="186"/>
+      <c r="W47" s="186"/>
+      <c r="X47" s="186"/>
+      <c r="Y47" s="186"/>
+      <c r="Z47" s="186"/>
+      <c r="AA47" s="186"/>
+      <c r="AB47" s="186"/>
+      <c r="AC47" s="186"/>
+      <c r="AD47" s="186"/>
+      <c r="AE47" s="186"/>
+      <c r="AF47" s="186"/>
+      <c r="AG47" s="186"/>
+      <c r="AH47" s="186"/>
+      <c r="AI47" s="186"/>
+      <c r="AJ47" s="186"/>
+      <c r="AK47" s="187"/>
     </row>
     <row r="48" spans="1:39" s="2" customFormat="1" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="45"/>
@@ -3646,45 +3629,45 @@
       <c r="AK48" s="6"/>
     </row>
     <row r="49" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="130" t="s">
+      <c r="A49" s="176" t="s">
         <v>41</v>
       </c>
-      <c r="B49" s="120"/>
-      <c r="C49" s="120"/>
-      <c r="D49" s="120"/>
-      <c r="E49" s="120"/>
-      <c r="F49" s="120"/>
-      <c r="G49" s="120"/>
-      <c r="H49" s="124"/>
-      <c r="I49" s="124"/>
-      <c r="J49" s="124"/>
-      <c r="K49" s="124"/>
-      <c r="L49" s="124"/>
-      <c r="M49" s="124"/>
-      <c r="N49" s="124"/>
-      <c r="O49" s="124"/>
-      <c r="P49" s="124"/>
-      <c r="Q49" s="124"/>
-      <c r="R49" s="124"/>
-      <c r="S49" s="124"/>
-      <c r="T49" s="124"/>
+      <c r="B49" s="177"/>
+      <c r="C49" s="177"/>
+      <c r="D49" s="177"/>
+      <c r="E49" s="177"/>
+      <c r="F49" s="177"/>
+      <c r="G49" s="177"/>
+      <c r="H49" s="179"/>
+      <c r="I49" s="179"/>
+      <c r="J49" s="179"/>
+      <c r="K49" s="179"/>
+      <c r="L49" s="179"/>
+      <c r="M49" s="179"/>
+      <c r="N49" s="179"/>
+      <c r="O49" s="179"/>
+      <c r="P49" s="179"/>
+      <c r="Q49" s="179"/>
+      <c r="R49" s="179"/>
+      <c r="S49" s="179"/>
+      <c r="T49" s="179"/>
       <c r="U49" s="58"/>
-      <c r="V49" s="120" t="s">
+      <c r="V49" s="177" t="s">
         <v>42</v>
       </c>
-      <c r="W49" s="120"/>
-      <c r="X49" s="120"/>
-      <c r="Y49" s="120"/>
-      <c r="Z49" s="120"/>
-      <c r="AA49" s="120"/>
-      <c r="AB49" s="120"/>
-      <c r="AC49" s="88"/>
-      <c r="AD49" s="88"/>
-      <c r="AE49" s="88"/>
-      <c r="AF49" s="88"/>
-      <c r="AG49" s="88"/>
-      <c r="AH49" s="88"/>
-      <c r="AI49" s="88"/>
+      <c r="W49" s="177"/>
+      <c r="X49" s="177"/>
+      <c r="Y49" s="177"/>
+      <c r="Z49" s="177"/>
+      <c r="AA49" s="177"/>
+      <c r="AB49" s="177"/>
+      <c r="AC49" s="132"/>
+      <c r="AD49" s="132"/>
+      <c r="AE49" s="132"/>
+      <c r="AF49" s="132"/>
+      <c r="AG49" s="132"/>
+      <c r="AH49" s="132"/>
+      <c r="AI49" s="132"/>
       <c r="AJ49" s="59"/>
       <c r="AK49" s="8"/>
     </row>
@@ -3715,45 +3698,45 @@
       <c r="AK50" s="8"/>
     </row>
     <row r="51" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="130" t="s">
+      <c r="A51" s="176" t="s">
         <v>43</v>
       </c>
-      <c r="B51" s="120"/>
-      <c r="C51" s="120"/>
-      <c r="D51" s="120"/>
-      <c r="E51" s="120"/>
-      <c r="F51" s="120"/>
-      <c r="G51" s="120"/>
-      <c r="H51" s="124"/>
-      <c r="I51" s="124"/>
-      <c r="J51" s="124"/>
-      <c r="K51" s="124"/>
-      <c r="L51" s="124"/>
-      <c r="M51" s="124"/>
-      <c r="N51" s="124"/>
-      <c r="O51" s="124"/>
-      <c r="P51" s="124"/>
-      <c r="Q51" s="124"/>
-      <c r="R51" s="124"/>
-      <c r="S51" s="124"/>
-      <c r="T51" s="124"/>
+      <c r="B51" s="177"/>
+      <c r="C51" s="177"/>
+      <c r="D51" s="177"/>
+      <c r="E51" s="177"/>
+      <c r="F51" s="177"/>
+      <c r="G51" s="177"/>
+      <c r="H51" s="179"/>
+      <c r="I51" s="179"/>
+      <c r="J51" s="179"/>
+      <c r="K51" s="179"/>
+      <c r="L51" s="179"/>
+      <c r="M51" s="179"/>
+      <c r="N51" s="179"/>
+      <c r="O51" s="179"/>
+      <c r="P51" s="179"/>
+      <c r="Q51" s="179"/>
+      <c r="R51" s="179"/>
+      <c r="S51" s="179"/>
+      <c r="T51" s="179"/>
       <c r="U51" s="58"/>
-      <c r="V51" s="120" t="s">
+      <c r="V51" s="177" t="s">
         <v>42</v>
       </c>
-      <c r="W51" s="120"/>
-      <c r="X51" s="120"/>
-      <c r="Y51" s="120"/>
-      <c r="Z51" s="120"/>
-      <c r="AA51" s="120"/>
-      <c r="AB51" s="120"/>
-      <c r="AC51" s="88"/>
-      <c r="AD51" s="88"/>
-      <c r="AE51" s="88"/>
-      <c r="AF51" s="88"/>
-      <c r="AG51" s="88"/>
-      <c r="AH51" s="88"/>
-      <c r="AI51" s="88"/>
+      <c r="W51" s="177"/>
+      <c r="X51" s="177"/>
+      <c r="Y51" s="177"/>
+      <c r="Z51" s="177"/>
+      <c r="AA51" s="177"/>
+      <c r="AB51" s="177"/>
+      <c r="AC51" s="132"/>
+      <c r="AD51" s="132"/>
+      <c r="AE51" s="132"/>
+      <c r="AF51" s="132"/>
+      <c r="AG51" s="132"/>
+      <c r="AH51" s="132"/>
+      <c r="AI51" s="132"/>
       <c r="AJ51" s="58"/>
       <c r="AK51" s="8"/>
     </row>
@@ -3784,45 +3767,45 @@
       <c r="AK52" s="8"/>
     </row>
     <row r="53" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="130" t="s">
+      <c r="A53" s="176" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="120"/>
-      <c r="C53" s="120"/>
-      <c r="D53" s="120"/>
-      <c r="E53" s="120"/>
-      <c r="F53" s="120"/>
-      <c r="G53" s="120"/>
-      <c r="H53" s="124"/>
-      <c r="I53" s="124"/>
-      <c r="J53" s="124"/>
-      <c r="K53" s="124"/>
-      <c r="L53" s="124"/>
-      <c r="M53" s="124"/>
-      <c r="N53" s="124"/>
-      <c r="O53" s="124"/>
-      <c r="P53" s="124"/>
-      <c r="Q53" s="124"/>
-      <c r="R53" s="124"/>
-      <c r="S53" s="124"/>
-      <c r="T53" s="124"/>
+      <c r="B53" s="177"/>
+      <c r="C53" s="177"/>
+      <c r="D53" s="177"/>
+      <c r="E53" s="177"/>
+      <c r="F53" s="177"/>
+      <c r="G53" s="177"/>
+      <c r="H53" s="179"/>
+      <c r="I53" s="179"/>
+      <c r="J53" s="179"/>
+      <c r="K53" s="179"/>
+      <c r="L53" s="179"/>
+      <c r="M53" s="179"/>
+      <c r="N53" s="179"/>
+      <c r="O53" s="179"/>
+      <c r="P53" s="179"/>
+      <c r="Q53" s="179"/>
+      <c r="R53" s="179"/>
+      <c r="S53" s="179"/>
+      <c r="T53" s="179"/>
       <c r="U53" s="58"/>
-      <c r="V53" s="120" t="s">
+      <c r="V53" s="177" t="s">
         <v>42</v>
       </c>
-      <c r="W53" s="120"/>
-      <c r="X53" s="120"/>
-      <c r="Y53" s="120"/>
-      <c r="Z53" s="120"/>
-      <c r="AA53" s="120"/>
-      <c r="AB53" s="120"/>
-      <c r="AC53" s="88"/>
-      <c r="AD53" s="88"/>
-      <c r="AE53" s="88"/>
-      <c r="AF53" s="88"/>
-      <c r="AG53" s="88"/>
-      <c r="AH53" s="88"/>
-      <c r="AI53" s="88"/>
+      <c r="W53" s="177"/>
+      <c r="X53" s="177"/>
+      <c r="Y53" s="177"/>
+      <c r="Z53" s="177"/>
+      <c r="AA53" s="177"/>
+      <c r="AB53" s="177"/>
+      <c r="AC53" s="132"/>
+      <c r="AD53" s="132"/>
+      <c r="AE53" s="132"/>
+      <c r="AF53" s="132"/>
+      <c r="AG53" s="132"/>
+      <c r="AH53" s="132"/>
+      <c r="AI53" s="132"/>
       <c r="AJ53" s="58"/>
       <c r="AK53" s="8"/>
     </row>
@@ -3853,45 +3836,45 @@
       <c r="AK54" s="8"/>
     </row>
     <row r="55" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="130" t="s">
+      <c r="A55" s="176" t="s">
         <v>45</v>
       </c>
-      <c r="B55" s="120"/>
-      <c r="C55" s="120"/>
-      <c r="D55" s="120"/>
-      <c r="E55" s="120"/>
-      <c r="F55" s="120"/>
-      <c r="G55" s="120"/>
-      <c r="H55" s="124"/>
-      <c r="I55" s="124"/>
-      <c r="J55" s="124"/>
-      <c r="K55" s="124"/>
-      <c r="L55" s="124"/>
-      <c r="M55" s="124"/>
-      <c r="N55" s="124"/>
-      <c r="O55" s="124"/>
-      <c r="P55" s="124"/>
-      <c r="Q55" s="124"/>
-      <c r="R55" s="124"/>
-      <c r="S55" s="124"/>
-      <c r="T55" s="124"/>
+      <c r="B55" s="177"/>
+      <c r="C55" s="177"/>
+      <c r="D55" s="177"/>
+      <c r="E55" s="177"/>
+      <c r="F55" s="177"/>
+      <c r="G55" s="177"/>
+      <c r="H55" s="179"/>
+      <c r="I55" s="179"/>
+      <c r="J55" s="179"/>
+      <c r="K55" s="179"/>
+      <c r="L55" s="179"/>
+      <c r="M55" s="179"/>
+      <c r="N55" s="179"/>
+      <c r="O55" s="179"/>
+      <c r="P55" s="179"/>
+      <c r="Q55" s="179"/>
+      <c r="R55" s="179"/>
+      <c r="S55" s="179"/>
+      <c r="T55" s="179"/>
       <c r="U55" s="58"/>
-      <c r="V55" s="120" t="s">
+      <c r="V55" s="177" t="s">
         <v>42</v>
       </c>
-      <c r="W55" s="120"/>
-      <c r="X55" s="120"/>
-      <c r="Y55" s="120"/>
-      <c r="Z55" s="120"/>
-      <c r="AA55" s="120"/>
-      <c r="AB55" s="120"/>
-      <c r="AC55" s="88"/>
-      <c r="AD55" s="88"/>
-      <c r="AE55" s="88"/>
-      <c r="AF55" s="88"/>
-      <c r="AG55" s="88"/>
-      <c r="AH55" s="88"/>
-      <c r="AI55" s="88"/>
+      <c r="W55" s="177"/>
+      <c r="X55" s="177"/>
+      <c r="Y55" s="177"/>
+      <c r="Z55" s="177"/>
+      <c r="AA55" s="177"/>
+      <c r="AB55" s="177"/>
+      <c r="AC55" s="132"/>
+      <c r="AD55" s="132"/>
+      <c r="AE55" s="132"/>
+      <c r="AF55" s="132"/>
+      <c r="AG55" s="132"/>
+      <c r="AH55" s="132"/>
+      <c r="AI55" s="132"/>
       <c r="AJ55" s="58"/>
       <c r="AK55" s="8"/>
     </row>
@@ -3922,45 +3905,45 @@
       <c r="AK56" s="8"/>
     </row>
     <row r="57" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="130" t="s">
+      <c r="A57" s="176" t="s">
         <v>46</v>
       </c>
-      <c r="B57" s="120"/>
-      <c r="C57" s="120"/>
-      <c r="D57" s="120"/>
-      <c r="E57" s="120"/>
-      <c r="F57" s="120"/>
-      <c r="G57" s="120"/>
-      <c r="H57" s="124"/>
-      <c r="I57" s="124"/>
-      <c r="J57" s="124"/>
-      <c r="K57" s="124"/>
-      <c r="L57" s="124"/>
-      <c r="M57" s="124"/>
-      <c r="N57" s="124"/>
-      <c r="O57" s="124"/>
-      <c r="P57" s="124"/>
-      <c r="Q57" s="124"/>
-      <c r="R57" s="124"/>
-      <c r="S57" s="124"/>
-      <c r="T57" s="124"/>
+      <c r="B57" s="177"/>
+      <c r="C57" s="177"/>
+      <c r="D57" s="177"/>
+      <c r="E57" s="177"/>
+      <c r="F57" s="177"/>
+      <c r="G57" s="177"/>
+      <c r="H57" s="179"/>
+      <c r="I57" s="179"/>
+      <c r="J57" s="179"/>
+      <c r="K57" s="179"/>
+      <c r="L57" s="179"/>
+      <c r="M57" s="179"/>
+      <c r="N57" s="179"/>
+      <c r="O57" s="179"/>
+      <c r="P57" s="179"/>
+      <c r="Q57" s="179"/>
+      <c r="R57" s="179"/>
+      <c r="S57" s="179"/>
+      <c r="T57" s="179"/>
       <c r="U57" s="58"/>
-      <c r="V57" s="120" t="s">
+      <c r="V57" s="177" t="s">
         <v>42</v>
       </c>
-      <c r="W57" s="120"/>
-      <c r="X57" s="120"/>
-      <c r="Y57" s="120"/>
-      <c r="Z57" s="120"/>
-      <c r="AA57" s="120"/>
-      <c r="AB57" s="120"/>
-      <c r="AC57" s="88"/>
-      <c r="AD57" s="88"/>
-      <c r="AE57" s="88"/>
-      <c r="AF57" s="88"/>
-      <c r="AG57" s="88"/>
-      <c r="AH57" s="88"/>
-      <c r="AI57" s="88"/>
+      <c r="W57" s="177"/>
+      <c r="X57" s="177"/>
+      <c r="Y57" s="177"/>
+      <c r="Z57" s="177"/>
+      <c r="AA57" s="177"/>
+      <c r="AB57" s="177"/>
+      <c r="AC57" s="132"/>
+      <c r="AD57" s="132"/>
+      <c r="AE57" s="132"/>
+      <c r="AF57" s="132"/>
+      <c r="AG57" s="132"/>
+      <c r="AH57" s="132"/>
+      <c r="AI57" s="132"/>
       <c r="AJ57" s="58"/>
       <c r="AK57" s="8"/>
     </row>
@@ -3978,45 +3961,45 @@
       <c r="AK58" s="8"/>
     </row>
     <row r="59" spans="1:37" s="2" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="200" t="s">
-        <v>110</v>
-      </c>
-      <c r="B59" s="201"/>
-      <c r="C59" s="201"/>
-      <c r="D59" s="201"/>
-      <c r="E59" s="201"/>
-      <c r="F59" s="201"/>
-      <c r="G59" s="201"/>
-      <c r="H59" s="201"/>
-      <c r="I59" s="201"/>
-      <c r="J59" s="201"/>
-      <c r="K59" s="201"/>
-      <c r="L59" s="201"/>
-      <c r="M59" s="201"/>
-      <c r="N59" s="201"/>
-      <c r="O59" s="202"/>
-      <c r="P59" s="203"/>
-      <c r="Q59" s="203"/>
-      <c r="R59" s="204"/>
-      <c r="S59" s="205"/>
-      <c r="T59" s="205"/>
-      <c r="U59" s="205"/>
-      <c r="V59" s="205"/>
-      <c r="W59" s="206"/>
+      <c r="A59" s="189" t="s">
+        <v>109</v>
+      </c>
+      <c r="B59" s="190"/>
+      <c r="C59" s="190"/>
+      <c r="D59" s="190"/>
+      <c r="E59" s="190"/>
+      <c r="F59" s="190"/>
+      <c r="G59" s="190"/>
+      <c r="H59" s="190"/>
+      <c r="I59" s="190"/>
+      <c r="J59" s="190"/>
+      <c r="K59" s="190"/>
+      <c r="L59" s="190"/>
+      <c r="M59" s="190"/>
+      <c r="N59" s="190"/>
+      <c r="O59" s="58"/>
+      <c r="P59" s="177"/>
+      <c r="Q59" s="177"/>
+      <c r="R59" s="133"/>
+      <c r="S59" s="134"/>
+      <c r="T59" s="134"/>
+      <c r="U59" s="134"/>
+      <c r="V59" s="134"/>
+      <c r="W59" s="135"/>
       <c r="X59" s="58"/>
-      <c r="Y59" s="120" t="s">
+      <c r="Y59" s="177" t="s">
         <v>47</v>
       </c>
-      <c r="Z59" s="120"/>
-      <c r="AA59" s="120"/>
-      <c r="AB59" s="120"/>
-      <c r="AC59" s="127"/>
-      <c r="AD59" s="127"/>
-      <c r="AE59" s="127"/>
-      <c r="AF59" s="127"/>
-      <c r="AG59" s="127"/>
-      <c r="AH59" s="127"/>
-      <c r="AI59" s="127"/>
+      <c r="Z59" s="177"/>
+      <c r="AA59" s="177"/>
+      <c r="AB59" s="177"/>
+      <c r="AC59" s="180"/>
+      <c r="AD59" s="180"/>
+      <c r="AE59" s="180"/>
+      <c r="AF59" s="180"/>
+      <c r="AG59" s="180"/>
+      <c r="AH59" s="180"/>
+      <c r="AI59" s="180"/>
       <c r="AJ59" s="66"/>
       <c r="AK59" s="8"/>
     </row>
@@ -4026,56 +4009,56 @@
       <c r="AK60" s="8"/>
     </row>
     <row r="61" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="117" t="s">
+      <c r="A61" s="185" t="s">
         <v>48</v>
       </c>
-      <c r="B61" s="118"/>
-      <c r="C61" s="118"/>
-      <c r="D61" s="118"/>
-      <c r="E61" s="118"/>
-      <c r="F61" s="118"/>
-      <c r="G61" s="118"/>
-      <c r="H61" s="118"/>
-      <c r="I61" s="118"/>
-      <c r="J61" s="118"/>
-      <c r="K61" s="118"/>
-      <c r="L61" s="118"/>
-      <c r="M61" s="118"/>
-      <c r="N61" s="118"/>
-      <c r="O61" s="118"/>
-      <c r="P61" s="118"/>
-      <c r="Q61" s="118"/>
-      <c r="R61" s="118"/>
-      <c r="S61" s="118"/>
-      <c r="T61" s="118"/>
-      <c r="U61" s="118"/>
-      <c r="V61" s="118"/>
-      <c r="W61" s="118"/>
-      <c r="X61" s="118"/>
-      <c r="Y61" s="118"/>
-      <c r="Z61" s="118"/>
-      <c r="AA61" s="118"/>
-      <c r="AB61" s="118"/>
-      <c r="AC61" s="118"/>
-      <c r="AD61" s="118"/>
-      <c r="AE61" s="118"/>
-      <c r="AF61" s="118"/>
-      <c r="AG61" s="118"/>
-      <c r="AH61" s="118"/>
-      <c r="AI61" s="118"/>
-      <c r="AJ61" s="118"/>
-      <c r="AK61" s="119"/>
+      <c r="B61" s="186"/>
+      <c r="C61" s="186"/>
+      <c r="D61" s="186"/>
+      <c r="E61" s="186"/>
+      <c r="F61" s="186"/>
+      <c r="G61" s="186"/>
+      <c r="H61" s="186"/>
+      <c r="I61" s="186"/>
+      <c r="J61" s="186"/>
+      <c r="K61" s="186"/>
+      <c r="L61" s="186"/>
+      <c r="M61" s="186"/>
+      <c r="N61" s="186"/>
+      <c r="O61" s="186"/>
+      <c r="P61" s="186"/>
+      <c r="Q61" s="186"/>
+      <c r="R61" s="186"/>
+      <c r="S61" s="186"/>
+      <c r="T61" s="186"/>
+      <c r="U61" s="186"/>
+      <c r="V61" s="186"/>
+      <c r="W61" s="186"/>
+      <c r="X61" s="186"/>
+      <c r="Y61" s="186"/>
+      <c r="Z61" s="186"/>
+      <c r="AA61" s="186"/>
+      <c r="AB61" s="186"/>
+      <c r="AC61" s="186"/>
+      <c r="AD61" s="186"/>
+      <c r="AE61" s="186"/>
+      <c r="AF61" s="186"/>
+      <c r="AG61" s="186"/>
+      <c r="AH61" s="186"/>
+      <c r="AI61" s="186"/>
+      <c r="AJ61" s="186"/>
+      <c r="AK61" s="187"/>
     </row>
     <row r="62" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="130" t="s">
+      <c r="A62" s="176" t="s">
         <v>49</v>
       </c>
-      <c r="B62" s="120"/>
-      <c r="C62" s="120"/>
-      <c r="D62" s="120"/>
-      <c r="E62" s="120"/>
-      <c r="F62" s="120"/>
-      <c r="G62" s="120"/>
+      <c r="B62" s="177"/>
+      <c r="C62" s="177"/>
+      <c r="D62" s="177"/>
+      <c r="E62" s="177"/>
+      <c r="F62" s="177"/>
+      <c r="G62" s="177"/>
       <c r="H62" s="58" t="s">
         <v>50</v>
       </c>
@@ -4086,45 +4069,45 @@
       </c>
       <c r="L62" s="77"/>
       <c r="M62" s="58"/>
-      <c r="N62" s="120" t="s">
+      <c r="N62" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="O62" s="120"/>
-      <c r="P62" s="120"/>
-      <c r="Q62" s="131"/>
-      <c r="R62" s="131"/>
-      <c r="S62" s="131"/>
-      <c r="T62" s="131"/>
-      <c r="U62" s="131"/>
-      <c r="V62" s="120" t="s">
+      <c r="O62" s="177"/>
+      <c r="P62" s="177"/>
+      <c r="Q62" s="178"/>
+      <c r="R62" s="178"/>
+      <c r="S62" s="178"/>
+      <c r="T62" s="178"/>
+      <c r="U62" s="178"/>
+      <c r="V62" s="177" t="s">
         <v>53</v>
       </c>
-      <c r="W62" s="120"/>
-      <c r="X62" s="120"/>
-      <c r="Y62" s="120"/>
-      <c r="Z62" s="120"/>
-      <c r="AA62" s="120"/>
-      <c r="AB62" s="120"/>
-      <c r="AC62" s="208"/>
-      <c r="AD62" s="208"/>
-      <c r="AE62" s="208"/>
-      <c r="AF62" s="208"/>
-      <c r="AG62" s="208"/>
-      <c r="AH62" s="208"/>
-      <c r="AI62" s="208"/>
+      <c r="W62" s="177"/>
+      <c r="X62" s="177"/>
+      <c r="Y62" s="177"/>
+      <c r="Z62" s="177"/>
+      <c r="AA62" s="177"/>
+      <c r="AB62" s="177"/>
+      <c r="AC62" s="184"/>
+      <c r="AD62" s="184"/>
+      <c r="AE62" s="184"/>
+      <c r="AF62" s="184"/>
+      <c r="AG62" s="184"/>
+      <c r="AH62" s="184"/>
+      <c r="AI62" s="184"/>
       <c r="AJ62" s="66"/>
       <c r="AK62" s="8"/>
     </row>
     <row r="63" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="130" t="s">
+      <c r="A63" s="176" t="s">
         <v>54</v>
       </c>
-      <c r="B63" s="120"/>
-      <c r="C63" s="120"/>
-      <c r="D63" s="120"/>
-      <c r="E63" s="120"/>
-      <c r="F63" s="120"/>
-      <c r="G63" s="120"/>
+      <c r="B63" s="177"/>
+      <c r="C63" s="177"/>
+      <c r="D63" s="177"/>
+      <c r="E63" s="177"/>
+      <c r="F63" s="177"/>
+      <c r="G63" s="177"/>
       <c r="H63" s="58" t="s">
         <v>50</v>
       </c>
@@ -4135,32 +4118,32 @@
       </c>
       <c r="L63" s="14"/>
       <c r="M63" s="58"/>
-      <c r="N63" s="120" t="s">
+      <c r="N63" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="O63" s="120"/>
-      <c r="P63" s="120"/>
-      <c r="Q63" s="131"/>
-      <c r="R63" s="131"/>
-      <c r="S63" s="131"/>
-      <c r="T63" s="131"/>
-      <c r="U63" s="131"/>
-      <c r="V63" s="120" t="s">
+      <c r="O63" s="177"/>
+      <c r="P63" s="177"/>
+      <c r="Q63" s="178"/>
+      <c r="R63" s="178"/>
+      <c r="S63" s="178"/>
+      <c r="T63" s="178"/>
+      <c r="U63" s="178"/>
+      <c r="V63" s="177" t="s">
         <v>53</v>
       </c>
-      <c r="W63" s="120"/>
-      <c r="X63" s="120"/>
-      <c r="Y63" s="120"/>
-      <c r="Z63" s="120"/>
-      <c r="AA63" s="120"/>
-      <c r="AB63" s="120"/>
-      <c r="AC63" s="132"/>
-      <c r="AD63" s="132"/>
-      <c r="AE63" s="132"/>
-      <c r="AF63" s="132"/>
-      <c r="AG63" s="132"/>
-      <c r="AH63" s="132"/>
-      <c r="AI63" s="132"/>
+      <c r="W63" s="177"/>
+      <c r="X63" s="177"/>
+      <c r="Y63" s="177"/>
+      <c r="Z63" s="177"/>
+      <c r="AA63" s="177"/>
+      <c r="AB63" s="177"/>
+      <c r="AC63" s="188"/>
+      <c r="AD63" s="188"/>
+      <c r="AE63" s="188"/>
+      <c r="AF63" s="188"/>
+      <c r="AG63" s="188"/>
+      <c r="AH63" s="188"/>
+      <c r="AI63" s="188"/>
       <c r="AJ63" s="66"/>
       <c r="AK63" s="8"/>
     </row>
@@ -4175,15 +4158,15 @@
       <c r="AK64" s="8"/>
     </row>
     <row r="65" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="130" t="s">
+      <c r="A65" s="176" t="s">
         <v>55</v>
       </c>
-      <c r="B65" s="120"/>
-      <c r="C65" s="120"/>
-      <c r="D65" s="120"/>
-      <c r="E65" s="120"/>
-      <c r="F65" s="120"/>
-      <c r="G65" s="120"/>
+      <c r="B65" s="177"/>
+      <c r="C65" s="177"/>
+      <c r="D65" s="177"/>
+      <c r="E65" s="177"/>
+      <c r="F65" s="177"/>
+      <c r="G65" s="177"/>
       <c r="H65" s="58" t="s">
         <v>50</v>
       </c>
@@ -4194,32 +4177,32 @@
       </c>
       <c r="L65" s="14"/>
       <c r="M65" s="58"/>
-      <c r="N65" s="120" t="s">
+      <c r="N65" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="O65" s="120"/>
-      <c r="P65" s="120"/>
-      <c r="Q65" s="131"/>
-      <c r="R65" s="131"/>
-      <c r="S65" s="131"/>
-      <c r="T65" s="131"/>
-      <c r="U65" s="131"/>
-      <c r="V65" s="120" t="s">
+      <c r="O65" s="177"/>
+      <c r="P65" s="177"/>
+      <c r="Q65" s="178"/>
+      <c r="R65" s="178"/>
+      <c r="S65" s="178"/>
+      <c r="T65" s="178"/>
+      <c r="U65" s="178"/>
+      <c r="V65" s="177" t="s">
         <v>53</v>
       </c>
-      <c r="W65" s="120"/>
-      <c r="X65" s="120"/>
-      <c r="Y65" s="120"/>
-      <c r="Z65" s="120"/>
-      <c r="AA65" s="120"/>
-      <c r="AB65" s="120"/>
-      <c r="AC65" s="208"/>
-      <c r="AD65" s="208"/>
-      <c r="AE65" s="208"/>
-      <c r="AF65" s="208"/>
-      <c r="AG65" s="208"/>
-      <c r="AH65" s="208"/>
-      <c r="AI65" s="208"/>
+      <c r="W65" s="177"/>
+      <c r="X65" s="177"/>
+      <c r="Y65" s="177"/>
+      <c r="Z65" s="177"/>
+      <c r="AA65" s="177"/>
+      <c r="AB65" s="177"/>
+      <c r="AC65" s="184"/>
+      <c r="AD65" s="184"/>
+      <c r="AE65" s="184"/>
+      <c r="AF65" s="184"/>
+      <c r="AG65" s="184"/>
+      <c r="AH65" s="184"/>
+      <c r="AI65" s="184"/>
       <c r="AJ65" s="66"/>
       <c r="AK65" s="8"/>
     </row>
@@ -4243,47 +4226,47 @@
       <c r="AK66" s="8"/>
     </row>
     <row r="67" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="130" t="s">
+      <c r="A67" s="176" t="s">
         <v>56</v>
       </c>
-      <c r="B67" s="120"/>
-      <c r="C67" s="120"/>
-      <c r="D67" s="120"/>
-      <c r="E67" s="120"/>
-      <c r="F67" s="120"/>
-      <c r="G67" s="120"/>
-      <c r="H67" s="124"/>
-      <c r="I67" s="124"/>
-      <c r="J67" s="124"/>
-      <c r="K67" s="124"/>
-      <c r="L67" s="124"/>
+      <c r="B67" s="177"/>
+      <c r="C67" s="177"/>
+      <c r="D67" s="177"/>
+      <c r="E67" s="177"/>
+      <c r="F67" s="177"/>
+      <c r="G67" s="177"/>
+      <c r="H67" s="179"/>
+      <c r="I67" s="179"/>
+      <c r="J67" s="179"/>
+      <c r="K67" s="179"/>
+      <c r="L67" s="179"/>
       <c r="M67" s="58"/>
-      <c r="N67" s="120" t="s">
+      <c r="N67" s="177" t="s">
         <v>52</v>
       </c>
-      <c r="O67" s="120"/>
-      <c r="P67" s="120"/>
-      <c r="Q67" s="131"/>
-      <c r="R67" s="131"/>
-      <c r="S67" s="131"/>
-      <c r="T67" s="131"/>
-      <c r="U67" s="131"/>
-      <c r="V67" s="120" t="s">
+      <c r="O67" s="177"/>
+      <c r="P67" s="177"/>
+      <c r="Q67" s="178"/>
+      <c r="R67" s="178"/>
+      <c r="S67" s="178"/>
+      <c r="T67" s="178"/>
+      <c r="U67" s="178"/>
+      <c r="V67" s="177" t="s">
         <v>53</v>
       </c>
-      <c r="W67" s="120"/>
-      <c r="X67" s="120"/>
-      <c r="Y67" s="120"/>
-      <c r="Z67" s="120"/>
-      <c r="AA67" s="120"/>
-      <c r="AB67" s="120"/>
-      <c r="AC67" s="127"/>
-      <c r="AD67" s="127"/>
-      <c r="AE67" s="127"/>
-      <c r="AF67" s="127"/>
-      <c r="AG67" s="127"/>
-      <c r="AH67" s="127"/>
-      <c r="AI67" s="127"/>
+      <c r="W67" s="177"/>
+      <c r="X67" s="177"/>
+      <c r="Y67" s="177"/>
+      <c r="Z67" s="177"/>
+      <c r="AA67" s="177"/>
+      <c r="AB67" s="177"/>
+      <c r="AC67" s="180"/>
+      <c r="AD67" s="180"/>
+      <c r="AE67" s="180"/>
+      <c r="AF67" s="180"/>
+      <c r="AG67" s="180"/>
+      <c r="AH67" s="180"/>
+      <c r="AI67" s="180"/>
       <c r="AJ67" s="66"/>
       <c r="AK67" s="8"/>
     </row>
@@ -4327,45 +4310,45 @@
       <c r="AK68" s="10"/>
     </row>
     <row r="69" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="94" t="s">
+      <c r="A69" s="92" t="s">
         <v>57</v>
       </c>
-      <c r="B69" s="95"/>
-      <c r="C69" s="95"/>
-      <c r="D69" s="95"/>
-      <c r="E69" s="95"/>
-      <c r="F69" s="95"/>
-      <c r="G69" s="95"/>
-      <c r="H69" s="95"/>
-      <c r="I69" s="95"/>
-      <c r="J69" s="95"/>
-      <c r="K69" s="95"/>
-      <c r="L69" s="95"/>
-      <c r="M69" s="95"/>
-      <c r="N69" s="95"/>
-      <c r="O69" s="95"/>
-      <c r="P69" s="95"/>
-      <c r="Q69" s="95"/>
-      <c r="R69" s="95"/>
-      <c r="S69" s="95"/>
-      <c r="T69" s="95"/>
-      <c r="U69" s="95"/>
-      <c r="V69" s="95"/>
-      <c r="W69" s="95"/>
-      <c r="X69" s="95"/>
-      <c r="Y69" s="95"/>
-      <c r="Z69" s="95"/>
-      <c r="AA69" s="95"/>
-      <c r="AB69" s="95"/>
-      <c r="AC69" s="95"/>
-      <c r="AD69" s="95"/>
-      <c r="AE69" s="95"/>
-      <c r="AF69" s="95"/>
-      <c r="AG69" s="95"/>
-      <c r="AH69" s="95"/>
-      <c r="AI69" s="95"/>
-      <c r="AJ69" s="95"/>
-      <c r="AK69" s="96"/>
+      <c r="B69" s="93"/>
+      <c r="C69" s="93"/>
+      <c r="D69" s="93"/>
+      <c r="E69" s="93"/>
+      <c r="F69" s="93"/>
+      <c r="G69" s="93"/>
+      <c r="H69" s="93"/>
+      <c r="I69" s="93"/>
+      <c r="J69" s="93"/>
+      <c r="K69" s="93"/>
+      <c r="L69" s="93"/>
+      <c r="M69" s="93"/>
+      <c r="N69" s="93"/>
+      <c r="O69" s="93"/>
+      <c r="P69" s="93"/>
+      <c r="Q69" s="93"/>
+      <c r="R69" s="93"/>
+      <c r="S69" s="93"/>
+      <c r="T69" s="93"/>
+      <c r="U69" s="93"/>
+      <c r="V69" s="93"/>
+      <c r="W69" s="93"/>
+      <c r="X69" s="93"/>
+      <c r="Y69" s="93"/>
+      <c r="Z69" s="93"/>
+      <c r="AA69" s="93"/>
+      <c r="AB69" s="93"/>
+      <c r="AC69" s="93"/>
+      <c r="AD69" s="93"/>
+      <c r="AE69" s="93"/>
+      <c r="AF69" s="93"/>
+      <c r="AG69" s="93"/>
+      <c r="AH69" s="93"/>
+      <c r="AI69" s="93"/>
+      <c r="AJ69" s="93"/>
+      <c r="AK69" s="94"/>
     </row>
     <row r="70" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="47"/>
@@ -4373,94 +4356,94 @@
       <c r="AK70" s="10"/>
     </row>
     <row r="71" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="133" t="s">
+      <c r="A71" s="168" t="s">
         <v>58</v>
       </c>
-      <c r="B71" s="134"/>
-      <c r="C71" s="134"/>
-      <c r="D71" s="134"/>
-      <c r="E71" s="134"/>
-      <c r="F71" s="134"/>
-      <c r="G71" s="134"/>
-      <c r="H71" s="134"/>
-      <c r="I71" s="134"/>
-      <c r="J71" s="134"/>
-      <c r="K71" s="134"/>
-      <c r="L71" s="134"/>
-      <c r="M71" s="134"/>
-      <c r="N71" s="134"/>
-      <c r="O71" s="134"/>
-      <c r="P71" s="134"/>
-      <c r="Q71" s="134"/>
-      <c r="R71" s="135"/>
-      <c r="S71" s="133" t="s">
+      <c r="B71" s="169"/>
+      <c r="C71" s="169"/>
+      <c r="D71" s="169"/>
+      <c r="E71" s="169"/>
+      <c r="F71" s="169"/>
+      <c r="G71" s="169"/>
+      <c r="H71" s="169"/>
+      <c r="I71" s="169"/>
+      <c r="J71" s="169"/>
+      <c r="K71" s="169"/>
+      <c r="L71" s="169"/>
+      <c r="M71" s="169"/>
+      <c r="N71" s="169"/>
+      <c r="O71" s="169"/>
+      <c r="P71" s="169"/>
+      <c r="Q71" s="169"/>
+      <c r="R71" s="170"/>
+      <c r="S71" s="168" t="s">
         <v>59</v>
       </c>
-      <c r="T71" s="134"/>
-      <c r="U71" s="134"/>
-      <c r="V71" s="134"/>
-      <c r="W71" s="134"/>
-      <c r="X71" s="134"/>
-      <c r="Y71" s="134"/>
-      <c r="Z71" s="134"/>
-      <c r="AA71" s="134"/>
-      <c r="AB71" s="134"/>
-      <c r="AC71" s="134"/>
-      <c r="AD71" s="134"/>
-      <c r="AE71" s="134"/>
-      <c r="AF71" s="136"/>
-      <c r="AG71" s="136"/>
-      <c r="AH71" s="136"/>
-      <c r="AI71" s="136"/>
-      <c r="AJ71" s="137"/>
+      <c r="T71" s="169"/>
+      <c r="U71" s="169"/>
+      <c r="V71" s="169"/>
+      <c r="W71" s="169"/>
+      <c r="X71" s="169"/>
+      <c r="Y71" s="169"/>
+      <c r="Z71" s="169"/>
+      <c r="AA71" s="169"/>
+      <c r="AB71" s="169"/>
+      <c r="AC71" s="169"/>
+      <c r="AD71" s="169"/>
+      <c r="AE71" s="169"/>
+      <c r="AF71" s="171"/>
+      <c r="AG71" s="171"/>
+      <c r="AH71" s="171"/>
+      <c r="AI71" s="171"/>
+      <c r="AJ71" s="172"/>
       <c r="AK71" s="6"/>
     </row>
     <row r="72" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="138" t="s">
+      <c r="A72" s="173" t="s">
         <v>60</v>
       </c>
-      <c r="B72" s="139"/>
-      <c r="C72" s="139"/>
-      <c r="D72" s="139"/>
-      <c r="E72" s="139"/>
-      <c r="F72" s="139"/>
-      <c r="G72" s="139"/>
-      <c r="H72" s="139"/>
-      <c r="I72" s="139"/>
-      <c r="J72" s="139"/>
-      <c r="K72" s="139"/>
-      <c r="L72" s="139"/>
-      <c r="M72" s="139"/>
-      <c r="N72" s="139" t="s">
+      <c r="B72" s="174"/>
+      <c r="C72" s="174"/>
+      <c r="D72" s="174"/>
+      <c r="E72" s="174"/>
+      <c r="F72" s="174"/>
+      <c r="G72" s="174"/>
+      <c r="H72" s="174"/>
+      <c r="I72" s="174"/>
+      <c r="J72" s="174"/>
+      <c r="K72" s="174"/>
+      <c r="L72" s="174"/>
+      <c r="M72" s="174"/>
+      <c r="N72" s="174" t="s">
         <v>61</v>
       </c>
-      <c r="O72" s="139"/>
-      <c r="P72" s="139"/>
-      <c r="Q72" s="139"/>
-      <c r="R72" s="140"/>
-      <c r="S72" s="138" t="s">
+      <c r="O72" s="174"/>
+      <c r="P72" s="174"/>
+      <c r="Q72" s="174"/>
+      <c r="R72" s="175"/>
+      <c r="S72" s="173" t="s">
         <v>60</v>
       </c>
-      <c r="T72" s="139"/>
-      <c r="U72" s="139"/>
-      <c r="V72" s="139"/>
-      <c r="W72" s="139"/>
-      <c r="X72" s="139"/>
-      <c r="Y72" s="139"/>
-      <c r="Z72" s="139"/>
-      <c r="AA72" s="139"/>
-      <c r="AB72" s="139"/>
-      <c r="AC72" s="139"/>
-      <c r="AD72" s="139"/>
-      <c r="AE72" s="139"/>
-      <c r="AF72" s="100" t="s">
+      <c r="T72" s="174"/>
+      <c r="U72" s="174"/>
+      <c r="V72" s="174"/>
+      <c r="W72" s="174"/>
+      <c r="X72" s="174"/>
+      <c r="Y72" s="174"/>
+      <c r="Z72" s="174"/>
+      <c r="AA72" s="174"/>
+      <c r="AB72" s="174"/>
+      <c r="AC72" s="174"/>
+      <c r="AD72" s="174"/>
+      <c r="AE72" s="174"/>
+      <c r="AF72" s="181" t="s">
         <v>61</v>
       </c>
-      <c r="AG72" s="101"/>
-      <c r="AH72" s="101"/>
-      <c r="AI72" s="101"/>
-      <c r="AJ72" s="101"/>
-      <c r="AK72" s="102"/>
+      <c r="AG72" s="182"/>
+      <c r="AH72" s="182"/>
+      <c r="AI72" s="182"/>
+      <c r="AJ72" s="182"/>
+      <c r="AK72" s="183"/>
     </row>
     <row r="73" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="47"/>
@@ -4493,21 +4476,21 @@
       <c r="AK73" s="8"/>
     </row>
     <row r="74" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="141" t="s">
+      <c r="A74" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="B74" s="142"/>
-      <c r="C74" s="142"/>
-      <c r="D74" s="142"/>
-      <c r="E74" s="142"/>
-      <c r="F74" s="142"/>
-      <c r="G74" s="142"/>
-      <c r="H74" s="142"/>
-      <c r="I74" s="142"/>
-      <c r="J74" s="142"/>
-      <c r="K74" s="142"/>
-      <c r="L74" s="142"/>
-      <c r="M74" s="143"/>
+      <c r="B74" s="106"/>
+      <c r="C74" s="106"/>
+      <c r="D74" s="106"/>
+      <c r="E74" s="106"/>
+      <c r="F74" s="106"/>
+      <c r="G74" s="106"/>
+      <c r="H74" s="106"/>
+      <c r="I74" s="106"/>
+      <c r="J74" s="106"/>
+      <c r="K74" s="106"/>
+      <c r="L74" s="106"/>
+      <c r="M74" s="107"/>
       <c r="N74" s="60" t="s">
         <v>50</v>
       </c>
@@ -4517,21 +4500,21 @@
         <v>63</v>
       </c>
       <c r="R74" s="79"/>
-      <c r="S74" s="147" t="s">
+      <c r="S74" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="T74" s="128"/>
-      <c r="U74" s="128"/>
-      <c r="V74" s="128"/>
-      <c r="W74" s="128"/>
-      <c r="X74" s="128"/>
-      <c r="Y74" s="128"/>
-      <c r="Z74" s="128"/>
-      <c r="AA74" s="128"/>
-      <c r="AB74" s="128"/>
-      <c r="AC74" s="128"/>
-      <c r="AD74" s="128"/>
-      <c r="AE74" s="148"/>
+      <c r="T74" s="141"/>
+      <c r="U74" s="141"/>
+      <c r="V74" s="141"/>
+      <c r="W74" s="141"/>
+      <c r="X74" s="141"/>
+      <c r="Y74" s="141"/>
+      <c r="Z74" s="141"/>
+      <c r="AA74" s="141"/>
+      <c r="AB74" s="141"/>
+      <c r="AC74" s="141"/>
+      <c r="AD74" s="141"/>
+      <c r="AE74" s="150"/>
       <c r="AF74" s="37" t="s">
         <v>50</v>
       </c>
@@ -4583,21 +4566,21 @@
       <c r="AK75" s="8"/>
     </row>
     <row r="76" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="141" t="s">
+      <c r="A76" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="B76" s="142"/>
-      <c r="C76" s="142"/>
-      <c r="D76" s="142"/>
-      <c r="E76" s="142"/>
-      <c r="F76" s="142"/>
-      <c r="G76" s="142"/>
-      <c r="H76" s="142"/>
-      <c r="I76" s="142"/>
-      <c r="J76" s="142"/>
-      <c r="K76" s="142"/>
-      <c r="L76" s="142"/>
-      <c r="M76" s="143"/>
+      <c r="B76" s="106"/>
+      <c r="C76" s="106"/>
+      <c r="D76" s="106"/>
+      <c r="E76" s="106"/>
+      <c r="F76" s="106"/>
+      <c r="G76" s="106"/>
+      <c r="H76" s="106"/>
+      <c r="I76" s="106"/>
+      <c r="J76" s="106"/>
+      <c r="K76" s="106"/>
+      <c r="L76" s="106"/>
+      <c r="M76" s="107"/>
       <c r="N76" s="60" t="s">
         <v>50</v>
       </c>
@@ -4607,21 +4590,21 @@
         <v>63</v>
       </c>
       <c r="R76" s="79"/>
-      <c r="S76" s="147" t="s">
+      <c r="S76" s="140" t="s">
         <v>66</v>
       </c>
-      <c r="T76" s="128"/>
-      <c r="U76" s="128"/>
-      <c r="V76" s="128"/>
-      <c r="W76" s="128"/>
-      <c r="X76" s="128"/>
-      <c r="Y76" s="128"/>
-      <c r="Z76" s="128"/>
-      <c r="AA76" s="128"/>
-      <c r="AB76" s="128"/>
-      <c r="AC76" s="128"/>
-      <c r="AD76" s="128"/>
-      <c r="AE76" s="148"/>
+      <c r="T76" s="141"/>
+      <c r="U76" s="141"/>
+      <c r="V76" s="141"/>
+      <c r="W76" s="141"/>
+      <c r="X76" s="141"/>
+      <c r="Y76" s="141"/>
+      <c r="Z76" s="141"/>
+      <c r="AA76" s="141"/>
+      <c r="AB76" s="141"/>
+      <c r="AC76" s="141"/>
+      <c r="AD76" s="141"/>
+      <c r="AE76" s="150"/>
       <c r="AF76" s="37" t="s">
         <v>50</v>
       </c>
@@ -4673,21 +4656,21 @@
       <c r="AK77" s="8"/>
     </row>
     <row r="78" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="141" t="s">
+      <c r="A78" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="B78" s="142"/>
-      <c r="C78" s="142"/>
-      <c r="D78" s="142"/>
-      <c r="E78" s="142"/>
-      <c r="F78" s="142"/>
-      <c r="G78" s="142"/>
-      <c r="H78" s="142"/>
-      <c r="I78" s="142"/>
-      <c r="J78" s="142"/>
-      <c r="K78" s="142"/>
-      <c r="L78" s="142"/>
-      <c r="M78" s="143"/>
+      <c r="B78" s="106"/>
+      <c r="C78" s="106"/>
+      <c r="D78" s="106"/>
+      <c r="E78" s="106"/>
+      <c r="F78" s="106"/>
+      <c r="G78" s="106"/>
+      <c r="H78" s="106"/>
+      <c r="I78" s="106"/>
+      <c r="J78" s="106"/>
+      <c r="K78" s="106"/>
+      <c r="L78" s="106"/>
+      <c r="M78" s="107"/>
       <c r="N78" s="60" t="s">
         <v>50</v>
       </c>
@@ -4697,21 +4680,21 @@
         <v>63</v>
       </c>
       <c r="R78" s="79"/>
-      <c r="S78" s="147" t="s">
+      <c r="S78" s="140" t="s">
         <v>68</v>
       </c>
-      <c r="T78" s="128"/>
-      <c r="U78" s="128"/>
-      <c r="V78" s="128"/>
-      <c r="W78" s="128"/>
-      <c r="X78" s="128"/>
-      <c r="Y78" s="128"/>
-      <c r="Z78" s="128"/>
-      <c r="AA78" s="128"/>
-      <c r="AB78" s="128"/>
-      <c r="AC78" s="128"/>
-      <c r="AD78" s="128"/>
-      <c r="AE78" s="148"/>
+      <c r="T78" s="141"/>
+      <c r="U78" s="141"/>
+      <c r="V78" s="141"/>
+      <c r="W78" s="141"/>
+      <c r="X78" s="141"/>
+      <c r="Y78" s="141"/>
+      <c r="Z78" s="141"/>
+      <c r="AA78" s="141"/>
+      <c r="AB78" s="141"/>
+      <c r="AC78" s="141"/>
+      <c r="AD78" s="141"/>
+      <c r="AE78" s="150"/>
       <c r="AF78" s="37" t="s">
         <v>50</v>
       </c>
@@ -4763,21 +4746,21 @@
       <c r="AK79" s="8"/>
     </row>
     <row r="80" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="141" t="s">
+      <c r="A80" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="B80" s="142"/>
-      <c r="C80" s="142"/>
-      <c r="D80" s="142"/>
-      <c r="E80" s="142"/>
-      <c r="F80" s="142"/>
-      <c r="G80" s="142"/>
-      <c r="H80" s="142"/>
-      <c r="I80" s="142"/>
-      <c r="J80" s="142"/>
-      <c r="K80" s="142"/>
-      <c r="L80" s="142"/>
-      <c r="M80" s="143"/>
+      <c r="B80" s="106"/>
+      <c r="C80" s="106"/>
+      <c r="D80" s="106"/>
+      <c r="E80" s="106"/>
+      <c r="F80" s="106"/>
+      <c r="G80" s="106"/>
+      <c r="H80" s="106"/>
+      <c r="I80" s="106"/>
+      <c r="J80" s="106"/>
+      <c r="K80" s="106"/>
+      <c r="L80" s="106"/>
+      <c r="M80" s="107"/>
       <c r="N80" s="60" t="s">
         <v>50</v>
       </c>
@@ -4787,21 +4770,21 @@
         <v>63</v>
       </c>
       <c r="R80" s="79"/>
-      <c r="S80" s="144" t="s">
+      <c r="S80" s="147" t="s">
         <v>70</v>
       </c>
-      <c r="T80" s="145"/>
-      <c r="U80" s="145"/>
-      <c r="V80" s="145"/>
-      <c r="W80" s="145"/>
-      <c r="X80" s="145"/>
-      <c r="Y80" s="145"/>
-      <c r="Z80" s="145"/>
-      <c r="AA80" s="145"/>
-      <c r="AB80" s="145"/>
-      <c r="AC80" s="145"/>
-      <c r="AD80" s="145"/>
-      <c r="AE80" s="146"/>
+      <c r="T80" s="148"/>
+      <c r="U80" s="148"/>
+      <c r="V80" s="148"/>
+      <c r="W80" s="148"/>
+      <c r="X80" s="148"/>
+      <c r="Y80" s="148"/>
+      <c r="Z80" s="148"/>
+      <c r="AA80" s="148"/>
+      <c r="AB80" s="148"/>
+      <c r="AC80" s="148"/>
+      <c r="AD80" s="148"/>
+      <c r="AE80" s="149"/>
       <c r="AF80" s="67" t="s">
         <v>50</v>
       </c>
@@ -4848,21 +4831,21 @@
       <c r="AK81" s="8"/>
     </row>
     <row r="82" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="141" t="s">
+      <c r="A82" s="105" t="s">
         <v>71</v>
       </c>
-      <c r="B82" s="142"/>
-      <c r="C82" s="142"/>
-      <c r="D82" s="142"/>
-      <c r="E82" s="142"/>
-      <c r="F82" s="142"/>
-      <c r="G82" s="142"/>
-      <c r="H82" s="142"/>
-      <c r="I82" s="142"/>
-      <c r="J82" s="142"/>
-      <c r="K82" s="142"/>
-      <c r="L82" s="142"/>
-      <c r="M82" s="143"/>
+      <c r="B82" s="106"/>
+      <c r="C82" s="106"/>
+      <c r="D82" s="106"/>
+      <c r="E82" s="106"/>
+      <c r="F82" s="106"/>
+      <c r="G82" s="106"/>
+      <c r="H82" s="106"/>
+      <c r="I82" s="106"/>
+      <c r="J82" s="106"/>
+      <c r="K82" s="106"/>
+      <c r="L82" s="106"/>
+      <c r="M82" s="107"/>
       <c r="N82" s="60" t="s">
         <v>50</v>
       </c>
@@ -4872,27 +4855,27 @@
         <v>63</v>
       </c>
       <c r="R82" s="79"/>
-      <c r="S82" s="97" t="s">
+      <c r="S82" s="159" t="s">
         <v>72</v>
       </c>
-      <c r="T82" s="98"/>
-      <c r="U82" s="98"/>
-      <c r="V82" s="98"/>
-      <c r="W82" s="98"/>
-      <c r="X82" s="98"/>
-      <c r="Y82" s="98"/>
-      <c r="Z82" s="98"/>
-      <c r="AA82" s="98"/>
-      <c r="AB82" s="98"/>
-      <c r="AC82" s="98"/>
-      <c r="AD82" s="98"/>
-      <c r="AE82" s="98"/>
-      <c r="AF82" s="98"/>
-      <c r="AG82" s="98"/>
-      <c r="AH82" s="98"/>
-      <c r="AI82" s="98"/>
-      <c r="AJ82" s="98"/>
-      <c r="AK82" s="99"/>
+      <c r="T82" s="160"/>
+      <c r="U82" s="160"/>
+      <c r="V82" s="160"/>
+      <c r="W82" s="160"/>
+      <c r="X82" s="160"/>
+      <c r="Y82" s="160"/>
+      <c r="Z82" s="160"/>
+      <c r="AA82" s="160"/>
+      <c r="AB82" s="160"/>
+      <c r="AC82" s="160"/>
+      <c r="AD82" s="160"/>
+      <c r="AE82" s="160"/>
+      <c r="AF82" s="160"/>
+      <c r="AG82" s="160"/>
+      <c r="AH82" s="160"/>
+      <c r="AI82" s="160"/>
+      <c r="AJ82" s="160"/>
+      <c r="AK82" s="161"/>
     </row>
     <row r="83" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="74"/>
@@ -4929,21 +4912,21 @@
       <c r="AK83" s="8"/>
     </row>
     <row r="84" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="141" t="s">
+      <c r="A84" s="105" t="s">
         <v>55</v>
       </c>
-      <c r="B84" s="142"/>
-      <c r="C84" s="142"/>
-      <c r="D84" s="142"/>
-      <c r="E84" s="142"/>
-      <c r="F84" s="142"/>
-      <c r="G84" s="142"/>
-      <c r="H84" s="142"/>
-      <c r="I84" s="142"/>
-      <c r="J84" s="142"/>
-      <c r="K84" s="142"/>
-      <c r="L84" s="142"/>
-      <c r="M84" s="143"/>
+      <c r="B84" s="106"/>
+      <c r="C84" s="106"/>
+      <c r="D84" s="106"/>
+      <c r="E84" s="106"/>
+      <c r="F84" s="106"/>
+      <c r="G84" s="106"/>
+      <c r="H84" s="106"/>
+      <c r="I84" s="106"/>
+      <c r="J84" s="106"/>
+      <c r="K84" s="106"/>
+      <c r="L84" s="106"/>
+      <c r="M84" s="107"/>
       <c r="N84" s="60" t="s">
         <v>50</v>
       </c>
@@ -4953,25 +4936,25 @@
         <v>63</v>
       </c>
       <c r="R84" s="79"/>
-      <c r="S84" s="103"/>
-      <c r="T84" s="104"/>
-      <c r="U84" s="104"/>
-      <c r="V84" s="104"/>
-      <c r="W84" s="104"/>
-      <c r="X84" s="104"/>
-      <c r="Y84" s="104"/>
-      <c r="Z84" s="104"/>
-      <c r="AA84" s="104"/>
-      <c r="AB84" s="104"/>
-      <c r="AC84" s="104"/>
-      <c r="AD84" s="104"/>
-      <c r="AE84" s="104"/>
-      <c r="AF84" s="104"/>
-      <c r="AG84" s="104"/>
-      <c r="AH84" s="104"/>
-      <c r="AI84" s="104"/>
-      <c r="AJ84" s="104"/>
-      <c r="AK84" s="105"/>
+      <c r="S84" s="151"/>
+      <c r="T84" s="152"/>
+      <c r="U84" s="152"/>
+      <c r="V84" s="152"/>
+      <c r="W84" s="152"/>
+      <c r="X84" s="152"/>
+      <c r="Y84" s="152"/>
+      <c r="Z84" s="152"/>
+      <c r="AA84" s="152"/>
+      <c r="AB84" s="152"/>
+      <c r="AC84" s="152"/>
+      <c r="AD84" s="152"/>
+      <c r="AE84" s="152"/>
+      <c r="AF84" s="152"/>
+      <c r="AG84" s="152"/>
+      <c r="AH84" s="152"/>
+      <c r="AI84" s="152"/>
+      <c r="AJ84" s="152"/>
+      <c r="AK84" s="153"/>
     </row>
     <row r="85" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="74"/>
@@ -4992,42 +4975,42 @@
       <c r="P85" s="42"/>
       <c r="Q85" s="42"/>
       <c r="R85" s="42"/>
-      <c r="S85" s="106"/>
-      <c r="T85" s="107"/>
-      <c r="U85" s="107"/>
-      <c r="V85" s="107"/>
-      <c r="W85" s="107"/>
-      <c r="X85" s="107"/>
-      <c r="Y85" s="107"/>
-      <c r="Z85" s="107"/>
-      <c r="AA85" s="107"/>
-      <c r="AB85" s="107"/>
-      <c r="AC85" s="107"/>
-      <c r="AD85" s="107"/>
-      <c r="AE85" s="107"/>
-      <c r="AF85" s="107"/>
-      <c r="AG85" s="107"/>
-      <c r="AH85" s="107"/>
-      <c r="AI85" s="107"/>
-      <c r="AJ85" s="107"/>
-      <c r="AK85" s="108"/>
+      <c r="S85" s="154"/>
+      <c r="T85" s="134"/>
+      <c r="U85" s="134"/>
+      <c r="V85" s="134"/>
+      <c r="W85" s="134"/>
+      <c r="X85" s="134"/>
+      <c r="Y85" s="134"/>
+      <c r="Z85" s="134"/>
+      <c r="AA85" s="134"/>
+      <c r="AB85" s="134"/>
+      <c r="AC85" s="134"/>
+      <c r="AD85" s="134"/>
+      <c r="AE85" s="134"/>
+      <c r="AF85" s="134"/>
+      <c r="AG85" s="134"/>
+      <c r="AH85" s="134"/>
+      <c r="AI85" s="134"/>
+      <c r="AJ85" s="134"/>
+      <c r="AK85" s="155"/>
     </row>
     <row r="86" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="141" t="s">
+      <c r="A86" s="105" t="s">
         <v>73</v>
       </c>
-      <c r="B86" s="142"/>
-      <c r="C86" s="142"/>
-      <c r="D86" s="142"/>
-      <c r="E86" s="142"/>
-      <c r="F86" s="142"/>
-      <c r="G86" s="142"/>
-      <c r="H86" s="142"/>
-      <c r="I86" s="142"/>
-      <c r="J86" s="142"/>
-      <c r="K86" s="142"/>
-      <c r="L86" s="142"/>
-      <c r="M86" s="143"/>
+      <c r="B86" s="106"/>
+      <c r="C86" s="106"/>
+      <c r="D86" s="106"/>
+      <c r="E86" s="106"/>
+      <c r="F86" s="106"/>
+      <c r="G86" s="106"/>
+      <c r="H86" s="106"/>
+      <c r="I86" s="106"/>
+      <c r="J86" s="106"/>
+      <c r="K86" s="106"/>
+      <c r="L86" s="106"/>
+      <c r="M86" s="107"/>
       <c r="N86" s="60" t="s">
         <v>50</v>
       </c>
@@ -5037,25 +5020,25 @@
         <v>63</v>
       </c>
       <c r="R86" s="79"/>
-      <c r="S86" s="106"/>
-      <c r="T86" s="107"/>
-      <c r="U86" s="107"/>
-      <c r="V86" s="107"/>
-      <c r="W86" s="107"/>
-      <c r="X86" s="107"/>
-      <c r="Y86" s="107"/>
-      <c r="Z86" s="107"/>
-      <c r="AA86" s="107"/>
-      <c r="AB86" s="107"/>
-      <c r="AC86" s="107"/>
-      <c r="AD86" s="107"/>
-      <c r="AE86" s="107"/>
-      <c r="AF86" s="107"/>
-      <c r="AG86" s="107"/>
-      <c r="AH86" s="107"/>
-      <c r="AI86" s="107"/>
-      <c r="AJ86" s="107"/>
-      <c r="AK86" s="108"/>
+      <c r="S86" s="154"/>
+      <c r="T86" s="134"/>
+      <c r="U86" s="134"/>
+      <c r="V86" s="134"/>
+      <c r="W86" s="134"/>
+      <c r="X86" s="134"/>
+      <c r="Y86" s="134"/>
+      <c r="Z86" s="134"/>
+      <c r="AA86" s="134"/>
+      <c r="AB86" s="134"/>
+      <c r="AC86" s="134"/>
+      <c r="AD86" s="134"/>
+      <c r="AE86" s="134"/>
+      <c r="AF86" s="134"/>
+      <c r="AG86" s="134"/>
+      <c r="AH86" s="134"/>
+      <c r="AI86" s="134"/>
+      <c r="AJ86" s="134"/>
+      <c r="AK86" s="155"/>
     </row>
     <row r="87" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="74"/>
@@ -5076,42 +5059,42 @@
       <c r="P87" s="42"/>
       <c r="Q87" s="42"/>
       <c r="R87" s="42"/>
-      <c r="S87" s="106"/>
-      <c r="T87" s="107"/>
-      <c r="U87" s="107"/>
-      <c r="V87" s="107"/>
-      <c r="W87" s="107"/>
-      <c r="X87" s="107"/>
-      <c r="Y87" s="107"/>
-      <c r="Z87" s="107"/>
-      <c r="AA87" s="107"/>
-      <c r="AB87" s="107"/>
-      <c r="AC87" s="107"/>
-      <c r="AD87" s="107"/>
-      <c r="AE87" s="107"/>
-      <c r="AF87" s="107"/>
-      <c r="AG87" s="107"/>
-      <c r="AH87" s="107"/>
-      <c r="AI87" s="107"/>
-      <c r="AJ87" s="107"/>
-      <c r="AK87" s="108"/>
+      <c r="S87" s="154"/>
+      <c r="T87" s="134"/>
+      <c r="U87" s="134"/>
+      <c r="V87" s="134"/>
+      <c r="W87" s="134"/>
+      <c r="X87" s="134"/>
+      <c r="Y87" s="134"/>
+      <c r="Z87" s="134"/>
+      <c r="AA87" s="134"/>
+      <c r="AB87" s="134"/>
+      <c r="AC87" s="134"/>
+      <c r="AD87" s="134"/>
+      <c r="AE87" s="134"/>
+      <c r="AF87" s="134"/>
+      <c r="AG87" s="134"/>
+      <c r="AH87" s="134"/>
+      <c r="AI87" s="134"/>
+      <c r="AJ87" s="134"/>
+      <c r="AK87" s="155"/>
     </row>
     <row r="88" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="141" t="s">
+      <c r="A88" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="B88" s="142"/>
-      <c r="C88" s="142"/>
-      <c r="D88" s="142"/>
-      <c r="E88" s="142"/>
-      <c r="F88" s="142"/>
-      <c r="G88" s="142"/>
-      <c r="H88" s="142"/>
-      <c r="I88" s="142"/>
-      <c r="J88" s="142"/>
-      <c r="K88" s="142"/>
-      <c r="L88" s="142"/>
-      <c r="M88" s="143"/>
+      <c r="B88" s="106"/>
+      <c r="C88" s="106"/>
+      <c r="D88" s="106"/>
+      <c r="E88" s="106"/>
+      <c r="F88" s="106"/>
+      <c r="G88" s="106"/>
+      <c r="H88" s="106"/>
+      <c r="I88" s="106"/>
+      <c r="J88" s="106"/>
+      <c r="K88" s="106"/>
+      <c r="L88" s="106"/>
+      <c r="M88" s="107"/>
       <c r="N88" s="60" t="s">
         <v>50</v>
       </c>
@@ -5121,25 +5104,25 @@
         <v>63</v>
       </c>
       <c r="R88" s="79"/>
-      <c r="S88" s="106"/>
-      <c r="T88" s="107"/>
-      <c r="U88" s="107"/>
-      <c r="V88" s="107"/>
-      <c r="W88" s="107"/>
-      <c r="X88" s="107"/>
-      <c r="Y88" s="107"/>
-      <c r="Z88" s="107"/>
-      <c r="AA88" s="107"/>
-      <c r="AB88" s="107"/>
-      <c r="AC88" s="107"/>
-      <c r="AD88" s="107"/>
-      <c r="AE88" s="107"/>
-      <c r="AF88" s="107"/>
-      <c r="AG88" s="107"/>
-      <c r="AH88" s="107"/>
-      <c r="AI88" s="107"/>
-      <c r="AJ88" s="107"/>
-      <c r="AK88" s="108"/>
+      <c r="S88" s="154"/>
+      <c r="T88" s="134"/>
+      <c r="U88" s="134"/>
+      <c r="V88" s="134"/>
+      <c r="W88" s="134"/>
+      <c r="X88" s="134"/>
+      <c r="Y88" s="134"/>
+      <c r="Z88" s="134"/>
+      <c r="AA88" s="134"/>
+      <c r="AB88" s="134"/>
+      <c r="AC88" s="134"/>
+      <c r="AD88" s="134"/>
+      <c r="AE88" s="134"/>
+      <c r="AF88" s="134"/>
+      <c r="AG88" s="134"/>
+      <c r="AH88" s="134"/>
+      <c r="AI88" s="134"/>
+      <c r="AJ88" s="134"/>
+      <c r="AK88" s="155"/>
     </row>
     <row r="89" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="74"/>
@@ -5160,42 +5143,42 @@
       <c r="P89" s="42"/>
       <c r="Q89" s="42"/>
       <c r="R89" s="42"/>
-      <c r="S89" s="106"/>
-      <c r="T89" s="107"/>
-      <c r="U89" s="107"/>
-      <c r="V89" s="107"/>
-      <c r="W89" s="107"/>
-      <c r="X89" s="107"/>
-      <c r="Y89" s="107"/>
-      <c r="Z89" s="107"/>
-      <c r="AA89" s="107"/>
-      <c r="AB89" s="107"/>
-      <c r="AC89" s="107"/>
-      <c r="AD89" s="107"/>
-      <c r="AE89" s="107"/>
-      <c r="AF89" s="107"/>
-      <c r="AG89" s="107"/>
-      <c r="AH89" s="107"/>
-      <c r="AI89" s="107"/>
-      <c r="AJ89" s="107"/>
-      <c r="AK89" s="108"/>
+      <c r="S89" s="154"/>
+      <c r="T89" s="134"/>
+      <c r="U89" s="134"/>
+      <c r="V89" s="134"/>
+      <c r="W89" s="134"/>
+      <c r="X89" s="134"/>
+      <c r="Y89" s="134"/>
+      <c r="Z89" s="134"/>
+      <c r="AA89" s="134"/>
+      <c r="AB89" s="134"/>
+      <c r="AC89" s="134"/>
+      <c r="AD89" s="134"/>
+      <c r="AE89" s="134"/>
+      <c r="AF89" s="134"/>
+      <c r="AG89" s="134"/>
+      <c r="AH89" s="134"/>
+      <c r="AI89" s="134"/>
+      <c r="AJ89" s="134"/>
+      <c r="AK89" s="155"/>
     </row>
     <row r="90" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="141" t="s">
+      <c r="A90" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="B90" s="142"/>
-      <c r="C90" s="142"/>
-      <c r="D90" s="142"/>
-      <c r="E90" s="142"/>
-      <c r="F90" s="142"/>
-      <c r="G90" s="142"/>
-      <c r="H90" s="142"/>
-      <c r="I90" s="142"/>
-      <c r="J90" s="142"/>
-      <c r="K90" s="142"/>
-      <c r="L90" s="142"/>
-      <c r="M90" s="143"/>
+      <c r="B90" s="106"/>
+      <c r="C90" s="106"/>
+      <c r="D90" s="106"/>
+      <c r="E90" s="106"/>
+      <c r="F90" s="106"/>
+      <c r="G90" s="106"/>
+      <c r="H90" s="106"/>
+      <c r="I90" s="106"/>
+      <c r="J90" s="106"/>
+      <c r="K90" s="106"/>
+      <c r="L90" s="106"/>
+      <c r="M90" s="107"/>
       <c r="N90" s="60" t="s">
         <v>50</v>
       </c>
@@ -5205,25 +5188,25 @@
         <v>63</v>
       </c>
       <c r="R90" s="79"/>
-      <c r="S90" s="106"/>
-      <c r="T90" s="107"/>
-      <c r="U90" s="107"/>
-      <c r="V90" s="107"/>
-      <c r="W90" s="107"/>
-      <c r="X90" s="107"/>
-      <c r="Y90" s="107"/>
-      <c r="Z90" s="107"/>
-      <c r="AA90" s="107"/>
-      <c r="AB90" s="107"/>
-      <c r="AC90" s="107"/>
-      <c r="AD90" s="107"/>
-      <c r="AE90" s="107"/>
-      <c r="AF90" s="107"/>
-      <c r="AG90" s="107"/>
-      <c r="AH90" s="107"/>
-      <c r="AI90" s="107"/>
-      <c r="AJ90" s="107"/>
-      <c r="AK90" s="108"/>
+      <c r="S90" s="154"/>
+      <c r="T90" s="134"/>
+      <c r="U90" s="134"/>
+      <c r="V90" s="134"/>
+      <c r="W90" s="134"/>
+      <c r="X90" s="134"/>
+      <c r="Y90" s="134"/>
+      <c r="Z90" s="134"/>
+      <c r="AA90" s="134"/>
+      <c r="AB90" s="134"/>
+      <c r="AC90" s="134"/>
+      <c r="AD90" s="134"/>
+      <c r="AE90" s="134"/>
+      <c r="AF90" s="134"/>
+      <c r="AG90" s="134"/>
+      <c r="AH90" s="134"/>
+      <c r="AI90" s="134"/>
+      <c r="AJ90" s="134"/>
+      <c r="AK90" s="155"/>
     </row>
     <row r="91" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="74"/>
@@ -5244,42 +5227,42 @@
       <c r="P91" s="42"/>
       <c r="Q91" s="42"/>
       <c r="R91" s="42"/>
-      <c r="S91" s="106"/>
-      <c r="T91" s="107"/>
-      <c r="U91" s="107"/>
-      <c r="V91" s="107"/>
-      <c r="W91" s="107"/>
-      <c r="X91" s="107"/>
-      <c r="Y91" s="107"/>
-      <c r="Z91" s="107"/>
-      <c r="AA91" s="107"/>
-      <c r="AB91" s="107"/>
-      <c r="AC91" s="107"/>
-      <c r="AD91" s="107"/>
-      <c r="AE91" s="107"/>
-      <c r="AF91" s="107"/>
-      <c r="AG91" s="107"/>
-      <c r="AH91" s="107"/>
-      <c r="AI91" s="107"/>
-      <c r="AJ91" s="107"/>
-      <c r="AK91" s="108"/>
+      <c r="S91" s="154"/>
+      <c r="T91" s="134"/>
+      <c r="U91" s="134"/>
+      <c r="V91" s="134"/>
+      <c r="W91" s="134"/>
+      <c r="X91" s="134"/>
+      <c r="Y91" s="134"/>
+      <c r="Z91" s="134"/>
+      <c r="AA91" s="134"/>
+      <c r="AB91" s="134"/>
+      <c r="AC91" s="134"/>
+      <c r="AD91" s="134"/>
+      <c r="AE91" s="134"/>
+      <c r="AF91" s="134"/>
+      <c r="AG91" s="134"/>
+      <c r="AH91" s="134"/>
+      <c r="AI91" s="134"/>
+      <c r="AJ91" s="134"/>
+      <c r="AK91" s="155"/>
     </row>
     <row r="92" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="155" t="s">
+      <c r="A92" s="117" t="s">
         <v>76</v>
       </c>
-      <c r="B92" s="156"/>
-      <c r="C92" s="156"/>
-      <c r="D92" s="156"/>
-      <c r="E92" s="156"/>
-      <c r="F92" s="156"/>
-      <c r="G92" s="156"/>
-      <c r="H92" s="156"/>
-      <c r="I92" s="156"/>
-      <c r="J92" s="156"/>
-      <c r="K92" s="156"/>
-      <c r="L92" s="156"/>
-      <c r="M92" s="176"/>
+      <c r="B92" s="118"/>
+      <c r="C92" s="118"/>
+      <c r="D92" s="118"/>
+      <c r="E92" s="118"/>
+      <c r="F92" s="118"/>
+      <c r="G92" s="118"/>
+      <c r="H92" s="118"/>
+      <c r="I92" s="118"/>
+      <c r="J92" s="118"/>
+      <c r="K92" s="118"/>
+      <c r="L92" s="118"/>
+      <c r="M92" s="167"/>
       <c r="N92" s="27" t="s">
         <v>50</v>
       </c>
@@ -5289,25 +5272,25 @@
         <v>63</v>
       </c>
       <c r="R92" s="80"/>
-      <c r="S92" s="109"/>
-      <c r="T92" s="110"/>
-      <c r="U92" s="110"/>
-      <c r="V92" s="110"/>
-      <c r="W92" s="110"/>
-      <c r="X92" s="110"/>
-      <c r="Y92" s="110"/>
-      <c r="Z92" s="110"/>
-      <c r="AA92" s="110"/>
-      <c r="AB92" s="110"/>
-      <c r="AC92" s="110"/>
-      <c r="AD92" s="110"/>
-      <c r="AE92" s="110"/>
-      <c r="AF92" s="110"/>
-      <c r="AG92" s="110"/>
-      <c r="AH92" s="110"/>
-      <c r="AI92" s="110"/>
-      <c r="AJ92" s="110"/>
-      <c r="AK92" s="111"/>
+      <c r="S92" s="156"/>
+      <c r="T92" s="157"/>
+      <c r="U92" s="157"/>
+      <c r="V92" s="157"/>
+      <c r="W92" s="157"/>
+      <c r="X92" s="157"/>
+      <c r="Y92" s="157"/>
+      <c r="Z92" s="157"/>
+      <c r="AA92" s="157"/>
+      <c r="AB92" s="157"/>
+      <c r="AC92" s="157"/>
+      <c r="AD92" s="157"/>
+      <c r="AE92" s="157"/>
+      <c r="AF92" s="157"/>
+      <c r="AG92" s="157"/>
+      <c r="AH92" s="157"/>
+      <c r="AI92" s="157"/>
+      <c r="AJ92" s="157"/>
+      <c r="AK92" s="158"/>
     </row>
     <row r="93" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="47"/>
@@ -5316,45 +5299,45 @@
       <c r="AK93" s="8"/>
     </row>
     <row r="94" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="94" t="s">
+      <c r="A94" s="92" t="s">
         <v>77</v>
       </c>
-      <c r="B94" s="95"/>
-      <c r="C94" s="95"/>
-      <c r="D94" s="95"/>
-      <c r="E94" s="95"/>
-      <c r="F94" s="95"/>
-      <c r="G94" s="95"/>
-      <c r="H94" s="95"/>
-      <c r="I94" s="95"/>
-      <c r="J94" s="95"/>
-      <c r="K94" s="95"/>
-      <c r="L94" s="95"/>
-      <c r="M94" s="95"/>
-      <c r="N94" s="95"/>
-      <c r="O94" s="95"/>
-      <c r="P94" s="95"/>
-      <c r="Q94" s="95"/>
-      <c r="R94" s="95"/>
-      <c r="S94" s="95"/>
-      <c r="T94" s="95"/>
-      <c r="U94" s="95"/>
-      <c r="V94" s="95"/>
-      <c r="W94" s="95"/>
-      <c r="X94" s="95"/>
-      <c r="Y94" s="95"/>
-      <c r="Z94" s="95"/>
-      <c r="AA94" s="95"/>
-      <c r="AB94" s="95"/>
-      <c r="AC94" s="95"/>
-      <c r="AD94" s="95"/>
-      <c r="AE94" s="95"/>
-      <c r="AF94" s="95"/>
-      <c r="AG94" s="95"/>
-      <c r="AH94" s="95"/>
-      <c r="AI94" s="95"/>
-      <c r="AJ94" s="95"/>
-      <c r="AK94" s="96"/>
+      <c r="B94" s="93"/>
+      <c r="C94" s="93"/>
+      <c r="D94" s="93"/>
+      <c r="E94" s="93"/>
+      <c r="F94" s="93"/>
+      <c r="G94" s="93"/>
+      <c r="H94" s="93"/>
+      <c r="I94" s="93"/>
+      <c r="J94" s="93"/>
+      <c r="K94" s="93"/>
+      <c r="L94" s="93"/>
+      <c r="M94" s="93"/>
+      <c r="N94" s="93"/>
+      <c r="O94" s="93"/>
+      <c r="P94" s="93"/>
+      <c r="Q94" s="93"/>
+      <c r="R94" s="93"/>
+      <c r="S94" s="93"/>
+      <c r="T94" s="93"/>
+      <c r="U94" s="93"/>
+      <c r="V94" s="93"/>
+      <c r="W94" s="93"/>
+      <c r="X94" s="93"/>
+      <c r="Y94" s="93"/>
+      <c r="Z94" s="93"/>
+      <c r="AA94" s="93"/>
+      <c r="AB94" s="93"/>
+      <c r="AC94" s="93"/>
+      <c r="AD94" s="93"/>
+      <c r="AE94" s="93"/>
+      <c r="AF94" s="93"/>
+      <c r="AG94" s="93"/>
+      <c r="AH94" s="93"/>
+      <c r="AI94" s="93"/>
+      <c r="AJ94" s="93"/>
+      <c r="AK94" s="94"/>
     </row>
     <row r="95" spans="1:37" s="2" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="47"/>
@@ -5362,111 +5345,111 @@
       <c r="AK95" s="8"/>
     </row>
     <row r="96" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="94" t="s">
+      <c r="A96" s="92" t="s">
         <v>78</v>
       </c>
-      <c r="B96" s="95"/>
-      <c r="C96" s="95"/>
-      <c r="D96" s="95"/>
-      <c r="E96" s="95"/>
-      <c r="F96" s="95"/>
-      <c r="G96" s="95"/>
-      <c r="H96" s="95"/>
-      <c r="I96" s="95"/>
-      <c r="J96" s="95"/>
-      <c r="K96" s="95"/>
-      <c r="L96" s="95"/>
-      <c r="M96" s="95"/>
-      <c r="N96" s="95"/>
-      <c r="O96" s="95"/>
-      <c r="P96" s="95"/>
-      <c r="Q96" s="95"/>
-      <c r="R96" s="96"/>
-      <c r="S96" s="94" t="s">
+      <c r="B96" s="93"/>
+      <c r="C96" s="93"/>
+      <c r="D96" s="93"/>
+      <c r="E96" s="93"/>
+      <c r="F96" s="93"/>
+      <c r="G96" s="93"/>
+      <c r="H96" s="93"/>
+      <c r="I96" s="93"/>
+      <c r="J96" s="93"/>
+      <c r="K96" s="93"/>
+      <c r="L96" s="93"/>
+      <c r="M96" s="93"/>
+      <c r="N96" s="93"/>
+      <c r="O96" s="93"/>
+      <c r="P96" s="93"/>
+      <c r="Q96" s="93"/>
+      <c r="R96" s="94"/>
+      <c r="S96" s="92" t="s">
         <v>79</v>
       </c>
-      <c r="T96" s="95"/>
-      <c r="U96" s="95"/>
-      <c r="V96" s="95"/>
-      <c r="W96" s="95"/>
-      <c r="X96" s="95"/>
-      <c r="Y96" s="95"/>
-      <c r="Z96" s="95"/>
-      <c r="AA96" s="95"/>
-      <c r="AB96" s="95"/>
-      <c r="AC96" s="95"/>
-      <c r="AD96" s="95"/>
-      <c r="AE96" s="95"/>
-      <c r="AF96" s="95"/>
-      <c r="AG96" s="95"/>
-      <c r="AH96" s="95"/>
-      <c r="AI96" s="95"/>
-      <c r="AJ96" s="95"/>
-      <c r="AK96" s="96"/>
+      <c r="T96" s="93"/>
+      <c r="U96" s="93"/>
+      <c r="V96" s="93"/>
+      <c r="W96" s="93"/>
+      <c r="X96" s="93"/>
+      <c r="Y96" s="93"/>
+      <c r="Z96" s="93"/>
+      <c r="AA96" s="93"/>
+      <c r="AB96" s="93"/>
+      <c r="AC96" s="93"/>
+      <c r="AD96" s="93"/>
+      <c r="AE96" s="93"/>
+      <c r="AF96" s="93"/>
+      <c r="AG96" s="93"/>
+      <c r="AH96" s="93"/>
+      <c r="AI96" s="93"/>
+      <c r="AJ96" s="93"/>
+      <c r="AK96" s="94"/>
     </row>
     <row r="97" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="149" t="s">
+      <c r="A97" s="111" t="s">
         <v>80</v>
       </c>
-      <c r="B97" s="150"/>
-      <c r="C97" s="150"/>
-      <c r="D97" s="150"/>
-      <c r="E97" s="150"/>
-      <c r="F97" s="150"/>
-      <c r="G97" s="150"/>
-      <c r="H97" s="150"/>
-      <c r="I97" s="150"/>
-      <c r="J97" s="150"/>
-      <c r="K97" s="150"/>
-      <c r="L97" s="150"/>
-      <c r="M97" s="151"/>
-      <c r="N97" s="152" t="s">
+      <c r="B97" s="112"/>
+      <c r="C97" s="112"/>
+      <c r="D97" s="112"/>
+      <c r="E97" s="112"/>
+      <c r="F97" s="112"/>
+      <c r="G97" s="112"/>
+      <c r="H97" s="112"/>
+      <c r="I97" s="112"/>
+      <c r="J97" s="112"/>
+      <c r="K97" s="112"/>
+      <c r="L97" s="112"/>
+      <c r="M97" s="113"/>
+      <c r="N97" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="O97" s="153"/>
-      <c r="P97" s="153"/>
-      <c r="Q97" s="153"/>
-      <c r="R97" s="154"/>
-      <c r="S97" s="177" t="s">
+      <c r="O97" s="115"/>
+      <c r="P97" s="115"/>
+      <c r="Q97" s="115"/>
+      <c r="R97" s="116"/>
+      <c r="S97" s="130" t="s">
         <v>80</v>
       </c>
-      <c r="T97" s="153"/>
-      <c r="U97" s="153"/>
-      <c r="V97" s="153"/>
-      <c r="W97" s="153"/>
-      <c r="X97" s="153"/>
-      <c r="Y97" s="153"/>
-      <c r="Z97" s="153"/>
-      <c r="AA97" s="153"/>
-      <c r="AB97" s="153"/>
-      <c r="AC97" s="153"/>
-      <c r="AD97" s="153"/>
-      <c r="AE97" s="178"/>
-      <c r="AF97" s="172" t="s">
+      <c r="T97" s="115"/>
+      <c r="U97" s="115"/>
+      <c r="V97" s="115"/>
+      <c r="W97" s="115"/>
+      <c r="X97" s="115"/>
+      <c r="Y97" s="115"/>
+      <c r="Z97" s="115"/>
+      <c r="AA97" s="115"/>
+      <c r="AB97" s="115"/>
+      <c r="AC97" s="115"/>
+      <c r="AD97" s="115"/>
+      <c r="AE97" s="131"/>
+      <c r="AF97" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="AG97" s="173"/>
-      <c r="AH97" s="173"/>
-      <c r="AI97" s="173"/>
-      <c r="AJ97" s="173"/>
-      <c r="AK97" s="174"/>
+      <c r="AG97" s="109"/>
+      <c r="AH97" s="109"/>
+      <c r="AI97" s="109"/>
+      <c r="AJ97" s="109"/>
+      <c r="AK97" s="110"/>
     </row>
     <row r="98" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="141" t="s">
+      <c r="A98" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="B98" s="142"/>
-      <c r="C98" s="142"/>
-      <c r="D98" s="142"/>
-      <c r="E98" s="142"/>
-      <c r="F98" s="142"/>
-      <c r="G98" s="142"/>
-      <c r="H98" s="142"/>
-      <c r="I98" s="142"/>
-      <c r="J98" s="142"/>
-      <c r="K98" s="142"/>
-      <c r="L98" s="142"/>
-      <c r="M98" s="142"/>
+      <c r="B98" s="106"/>
+      <c r="C98" s="106"/>
+      <c r="D98" s="106"/>
+      <c r="E98" s="106"/>
+      <c r="F98" s="106"/>
+      <c r="G98" s="106"/>
+      <c r="H98" s="106"/>
+      <c r="I98" s="106"/>
+      <c r="J98" s="106"/>
+      <c r="K98" s="106"/>
+      <c r="L98" s="106"/>
+      <c r="M98" s="106"/>
       <c r="N98" s="28" t="s">
         <v>50</v>
       </c>
@@ -5476,21 +5459,21 @@
         <v>63</v>
       </c>
       <c r="R98" s="82"/>
-      <c r="S98" s="195" t="s">
+      <c r="S98" s="162" t="s">
         <v>82</v>
       </c>
-      <c r="T98" s="196"/>
-      <c r="U98" s="196"/>
-      <c r="V98" s="196"/>
-      <c r="W98" s="196"/>
-      <c r="X98" s="196"/>
-      <c r="Y98" s="196"/>
-      <c r="Z98" s="196"/>
-      <c r="AA98" s="196"/>
-      <c r="AB98" s="196"/>
-      <c r="AC98" s="196"/>
-      <c r="AD98" s="196"/>
-      <c r="AE98" s="197"/>
+      <c r="T98" s="163"/>
+      <c r="U98" s="163"/>
+      <c r="V98" s="163"/>
+      <c r="W98" s="163"/>
+      <c r="X98" s="163"/>
+      <c r="Y98" s="163"/>
+      <c r="Z98" s="163"/>
+      <c r="AA98" s="163"/>
+      <c r="AB98" s="163"/>
+      <c r="AC98" s="163"/>
+      <c r="AD98" s="163"/>
+      <c r="AE98" s="164"/>
       <c r="AF98" s="60" t="s">
         <v>50</v>
       </c>
@@ -5537,21 +5520,21 @@
       <c r="AK99" s="8"/>
     </row>
     <row r="100" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="141" t="s">
+      <c r="A100" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="B100" s="142"/>
-      <c r="C100" s="142"/>
-      <c r="D100" s="142"/>
-      <c r="E100" s="142"/>
-      <c r="F100" s="142"/>
-      <c r="G100" s="142"/>
-      <c r="H100" s="142"/>
-      <c r="I100" s="142"/>
-      <c r="J100" s="142"/>
-      <c r="K100" s="142"/>
-      <c r="L100" s="142"/>
-      <c r="M100" s="142"/>
+      <c r="B100" s="106"/>
+      <c r="C100" s="106"/>
+      <c r="D100" s="106"/>
+      <c r="E100" s="106"/>
+      <c r="F100" s="106"/>
+      <c r="G100" s="106"/>
+      <c r="H100" s="106"/>
+      <c r="I100" s="106"/>
+      <c r="J100" s="106"/>
+      <c r="K100" s="106"/>
+      <c r="L100" s="106"/>
+      <c r="M100" s="106"/>
       <c r="N100" s="38" t="s">
         <v>50</v>
       </c>
@@ -5561,21 +5544,21 @@
         <v>63</v>
       </c>
       <c r="R100" s="83"/>
-      <c r="S100" s="147" t="s">
+      <c r="S100" s="140" t="s">
         <v>84</v>
       </c>
-      <c r="T100" s="128"/>
-      <c r="U100" s="128"/>
-      <c r="V100" s="128"/>
-      <c r="W100" s="128"/>
-      <c r="X100" s="128"/>
-      <c r="Y100" s="128"/>
-      <c r="Z100" s="128"/>
-      <c r="AA100" s="128"/>
-      <c r="AB100" s="128"/>
-      <c r="AC100" s="128"/>
-      <c r="AD100" s="128"/>
-      <c r="AE100" s="175"/>
+      <c r="T100" s="141"/>
+      <c r="U100" s="141"/>
+      <c r="V100" s="141"/>
+      <c r="W100" s="141"/>
+      <c r="X100" s="141"/>
+      <c r="Y100" s="141"/>
+      <c r="Z100" s="141"/>
+      <c r="AA100" s="141"/>
+      <c r="AB100" s="141"/>
+      <c r="AC100" s="141"/>
+      <c r="AD100" s="141"/>
+      <c r="AE100" s="142"/>
       <c r="AF100" s="60" t="s">
         <v>50</v>
       </c>
@@ -5604,8 +5587,8 @@
       <c r="N101" s="24"/>
       <c r="Q101" s="42"/>
       <c r="R101" s="8"/>
-      <c r="S101" s="198"/>
-      <c r="T101" s="199"/>
+      <c r="S101" s="165"/>
+      <c r="T101" s="166"/>
       <c r="U101" s="72"/>
       <c r="V101" s="72"/>
       <c r="W101" s="72"/>
@@ -5622,21 +5605,21 @@
       <c r="AK101" s="8"/>
     </row>
     <row r="102" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="141" t="s">
+      <c r="A102" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="B102" s="142"/>
-      <c r="C102" s="142"/>
-      <c r="D102" s="142"/>
-      <c r="E102" s="142"/>
-      <c r="F102" s="142"/>
-      <c r="G102" s="142"/>
-      <c r="H102" s="142"/>
-      <c r="I102" s="142"/>
-      <c r="J102" s="142"/>
-      <c r="K102" s="142"/>
-      <c r="L102" s="142"/>
-      <c r="M102" s="142"/>
+      <c r="B102" s="106"/>
+      <c r="C102" s="106"/>
+      <c r="D102" s="106"/>
+      <c r="E102" s="106"/>
+      <c r="F102" s="106"/>
+      <c r="G102" s="106"/>
+      <c r="H102" s="106"/>
+      <c r="I102" s="106"/>
+      <c r="J102" s="106"/>
+      <c r="K102" s="106"/>
+      <c r="L102" s="106"/>
+      <c r="M102" s="106"/>
       <c r="N102" s="38" t="s">
         <v>50</v>
       </c>
@@ -5646,21 +5629,21 @@
         <v>63</v>
       </c>
       <c r="R102" s="83"/>
-      <c r="S102" s="147" t="s">
+      <c r="S102" s="140" t="s">
         <v>86</v>
       </c>
-      <c r="T102" s="128"/>
-      <c r="U102" s="128"/>
-      <c r="V102" s="128"/>
-      <c r="W102" s="128"/>
-      <c r="X102" s="128"/>
-      <c r="Y102" s="128"/>
-      <c r="Z102" s="128"/>
-      <c r="AA102" s="128"/>
-      <c r="AB102" s="128"/>
-      <c r="AC102" s="128"/>
-      <c r="AD102" s="128"/>
-      <c r="AE102" s="175"/>
+      <c r="T102" s="141"/>
+      <c r="U102" s="141"/>
+      <c r="V102" s="141"/>
+      <c r="W102" s="141"/>
+      <c r="X102" s="141"/>
+      <c r="Y102" s="141"/>
+      <c r="Z102" s="141"/>
+      <c r="AA102" s="141"/>
+      <c r="AB102" s="141"/>
+      <c r="AC102" s="141"/>
+      <c r="AD102" s="141"/>
+      <c r="AE102" s="142"/>
       <c r="AF102" s="60" t="s">
         <v>50</v>
       </c>
@@ -5707,21 +5690,21 @@
       <c r="AK103" s="8"/>
     </row>
     <row r="104" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="141" t="s">
+      <c r="A104" s="105" t="s">
         <v>87</v>
       </c>
-      <c r="B104" s="142"/>
-      <c r="C104" s="142"/>
-      <c r="D104" s="142"/>
-      <c r="E104" s="142"/>
-      <c r="F104" s="142"/>
-      <c r="G104" s="142"/>
-      <c r="H104" s="142"/>
-      <c r="I104" s="142"/>
-      <c r="J104" s="142"/>
-      <c r="K104" s="142"/>
-      <c r="L104" s="142"/>
-      <c r="M104" s="142"/>
+      <c r="B104" s="106"/>
+      <c r="C104" s="106"/>
+      <c r="D104" s="106"/>
+      <c r="E104" s="106"/>
+      <c r="F104" s="106"/>
+      <c r="G104" s="106"/>
+      <c r="H104" s="106"/>
+      <c r="I104" s="106"/>
+      <c r="J104" s="106"/>
+      <c r="K104" s="106"/>
+      <c r="L104" s="106"/>
+      <c r="M104" s="106"/>
       <c r="N104" s="38" t="s">
         <v>50</v>
       </c>
@@ -5731,21 +5714,21 @@
         <v>63</v>
       </c>
       <c r="R104" s="83"/>
-      <c r="S104" s="147" t="s">
+      <c r="S104" s="140" t="s">
         <v>88</v>
       </c>
-      <c r="T104" s="128"/>
-      <c r="U104" s="128"/>
-      <c r="V104" s="128"/>
-      <c r="W104" s="128"/>
-      <c r="X104" s="128"/>
-      <c r="Y104" s="128"/>
-      <c r="Z104" s="128"/>
-      <c r="AA104" s="128"/>
-      <c r="AB104" s="128"/>
-      <c r="AC104" s="128"/>
-      <c r="AD104" s="128"/>
-      <c r="AE104" s="175"/>
+      <c r="T104" s="141"/>
+      <c r="U104" s="141"/>
+      <c r="V104" s="141"/>
+      <c r="W104" s="141"/>
+      <c r="X104" s="141"/>
+      <c r="Y104" s="141"/>
+      <c r="Z104" s="141"/>
+      <c r="AA104" s="141"/>
+      <c r="AB104" s="141"/>
+      <c r="AC104" s="141"/>
+      <c r="AD104" s="141"/>
+      <c r="AE104" s="142"/>
       <c r="AF104" s="60" t="s">
         <v>50</v>
       </c>
@@ -5792,21 +5775,21 @@
       <c r="AK105" s="8"/>
     </row>
     <row r="106" spans="1:37" s="2" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="141" t="s">
+      <c r="A106" s="105" t="s">
         <v>89</v>
       </c>
-      <c r="B106" s="142"/>
-      <c r="C106" s="142"/>
-      <c r="D106" s="142"/>
-      <c r="E106" s="142"/>
-      <c r="F106" s="142"/>
-      <c r="G106" s="142"/>
-      <c r="H106" s="142"/>
-      <c r="I106" s="142"/>
-      <c r="J106" s="142"/>
-      <c r="K106" s="142"/>
-      <c r="L106" s="142"/>
-      <c r="M106" s="142"/>
+      <c r="B106" s="106"/>
+      <c r="C106" s="106"/>
+      <c r="D106" s="106"/>
+      <c r="E106" s="106"/>
+      <c r="F106" s="106"/>
+      <c r="G106" s="106"/>
+      <c r="H106" s="106"/>
+      <c r="I106" s="106"/>
+      <c r="J106" s="106"/>
+      <c r="K106" s="106"/>
+      <c r="L106" s="106"/>
+      <c r="M106" s="106"/>
       <c r="N106" s="38" t="s">
         <v>50</v>
       </c>
@@ -5816,21 +5799,21 @@
         <v>63</v>
       </c>
       <c r="R106" s="83"/>
-      <c r="S106" s="147" t="s">
+      <c r="S106" s="140" t="s">
         <v>90</v>
       </c>
-      <c r="T106" s="128"/>
-      <c r="U106" s="128"/>
-      <c r="V106" s="128"/>
-      <c r="W106" s="128"/>
-      <c r="X106" s="128"/>
-      <c r="Y106" s="128"/>
-      <c r="Z106" s="128"/>
-      <c r="AA106" s="128"/>
-      <c r="AB106" s="128"/>
-      <c r="AC106" s="128"/>
-      <c r="AD106" s="128"/>
-      <c r="AE106" s="175"/>
+      <c r="T106" s="141"/>
+      <c r="U106" s="141"/>
+      <c r="V106" s="141"/>
+      <c r="W106" s="141"/>
+      <c r="X106" s="141"/>
+      <c r="Y106" s="141"/>
+      <c r="Z106" s="141"/>
+      <c r="AA106" s="141"/>
+      <c r="AB106" s="141"/>
+      <c r="AC106" s="141"/>
+      <c r="AD106" s="141"/>
+      <c r="AE106" s="142"/>
       <c r="AF106" s="60" t="s">
         <v>50</v>
       </c>
@@ -5879,21 +5862,21 @@
       <c r="AK107" s="8"/>
     </row>
     <row r="108" spans="1:37" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="141" t="s">
+      <c r="A108" s="105" t="s">
         <v>91</v>
       </c>
-      <c r="B108" s="142"/>
-      <c r="C108" s="142"/>
-      <c r="D108" s="142"/>
-      <c r="E108" s="142"/>
-      <c r="F108" s="142"/>
-      <c r="G108" s="142"/>
-      <c r="H108" s="142"/>
-      <c r="I108" s="142"/>
-      <c r="J108" s="142"/>
-      <c r="K108" s="142"/>
-      <c r="L108" s="142"/>
-      <c r="M108" s="142"/>
+      <c r="B108" s="106"/>
+      <c r="C108" s="106"/>
+      <c r="D108" s="106"/>
+      <c r="E108" s="106"/>
+      <c r="F108" s="106"/>
+      <c r="G108" s="106"/>
+      <c r="H108" s="106"/>
+      <c r="I108" s="106"/>
+      <c r="J108" s="106"/>
+      <c r="K108" s="106"/>
+      <c r="L108" s="106"/>
+      <c r="M108" s="106"/>
       <c r="N108" s="38" t="s">
         <v>50</v>
       </c>
@@ -5903,21 +5886,21 @@
         <v>63</v>
       </c>
       <c r="R108" s="83"/>
-      <c r="S108" s="147" t="s">
+      <c r="S108" s="140" t="s">
         <v>92</v>
       </c>
-      <c r="T108" s="128"/>
-      <c r="U108" s="128"/>
-      <c r="V108" s="128"/>
-      <c r="W108" s="128"/>
-      <c r="X108" s="128"/>
-      <c r="Y108" s="128"/>
-      <c r="Z108" s="128"/>
-      <c r="AA108" s="128"/>
-      <c r="AB108" s="128"/>
-      <c r="AC108" s="128"/>
-      <c r="AD108" s="128"/>
-      <c r="AE108" s="175"/>
+      <c r="T108" s="141"/>
+      <c r="U108" s="141"/>
+      <c r="V108" s="141"/>
+      <c r="W108" s="141"/>
+      <c r="X108" s="141"/>
+      <c r="Y108" s="141"/>
+      <c r="Z108" s="141"/>
+      <c r="AA108" s="141"/>
+      <c r="AB108" s="141"/>
+      <c r="AC108" s="141"/>
+      <c r="AD108" s="141"/>
+      <c r="AE108" s="142"/>
       <c r="AF108" s="60" t="s">
         <v>50</v>
       </c>
@@ -5966,45 +5949,45 @@
       <c r="AK109" s="8"/>
     </row>
     <row r="110" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="141" t="s">
+      <c r="A110" s="105" t="s">
         <v>93</v>
       </c>
-      <c r="B110" s="142"/>
-      <c r="C110" s="142"/>
-      <c r="D110" s="142"/>
-      <c r="E110" s="142"/>
-      <c r="F110" s="142"/>
-      <c r="G110" s="142"/>
-      <c r="H110" s="142"/>
-      <c r="I110" s="142"/>
-      <c r="J110" s="142"/>
-      <c r="K110" s="142"/>
-      <c r="L110" s="142"/>
-      <c r="M110" s="142"/>
-      <c r="N110" s="157" t="s">
+      <c r="B110" s="106"/>
+      <c r="C110" s="106"/>
+      <c r="D110" s="106"/>
+      <c r="E110" s="106"/>
+      <c r="F110" s="106"/>
+      <c r="G110" s="106"/>
+      <c r="H110" s="106"/>
+      <c r="I110" s="106"/>
+      <c r="J110" s="106"/>
+      <c r="K110" s="106"/>
+      <c r="L110" s="106"/>
+      <c r="M110" s="106"/>
+      <c r="N110" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="O110" s="159"/>
+      <c r="O110" s="121"/>
       <c r="P110" s="58"/>
-      <c r="Q110" s="161" t="s">
+      <c r="Q110" s="123" t="s">
         <v>63</v>
       </c>
-      <c r="R110" s="163"/>
-      <c r="S110" s="165" t="s">
+      <c r="R110" s="125"/>
+      <c r="S110" s="127" t="s">
         <v>94</v>
       </c>
-      <c r="T110" s="166"/>
-      <c r="U110" s="166"/>
-      <c r="V110" s="166"/>
-      <c r="W110" s="166"/>
-      <c r="X110" s="166"/>
-      <c r="Y110" s="166"/>
-      <c r="Z110" s="166"/>
-      <c r="AA110" s="166"/>
-      <c r="AB110" s="166"/>
-      <c r="AC110" s="166"/>
-      <c r="AD110" s="166"/>
-      <c r="AE110" s="167"/>
+      <c r="T110" s="128"/>
+      <c r="U110" s="128"/>
+      <c r="V110" s="128"/>
+      <c r="W110" s="128"/>
+      <c r="X110" s="128"/>
+      <c r="Y110" s="128"/>
+      <c r="Z110" s="128"/>
+      <c r="AA110" s="128"/>
+      <c r="AB110" s="128"/>
+      <c r="AC110" s="128"/>
+      <c r="AD110" s="128"/>
+      <c r="AE110" s="129"/>
       <c r="AF110" s="60" t="s">
         <v>50</v>
       </c>
@@ -6017,154 +6000,154 @@
       <c r="AK110" s="8"/>
     </row>
     <row r="111" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="155"/>
-      <c r="B111" s="156"/>
-      <c r="C111" s="156"/>
-      <c r="D111" s="156"/>
-      <c r="E111" s="156"/>
-      <c r="F111" s="156"/>
-      <c r="G111" s="156"/>
-      <c r="H111" s="156"/>
-      <c r="I111" s="156"/>
-      <c r="J111" s="156"/>
-      <c r="K111" s="156"/>
-      <c r="L111" s="156"/>
-      <c r="M111" s="156"/>
-      <c r="N111" s="158"/>
-      <c r="O111" s="160"/>
+      <c r="A111" s="117"/>
+      <c r="B111" s="118"/>
+      <c r="C111" s="118"/>
+      <c r="D111" s="118"/>
+      <c r="E111" s="118"/>
+      <c r="F111" s="118"/>
+      <c r="G111" s="118"/>
+      <c r="H111" s="118"/>
+      <c r="I111" s="118"/>
+      <c r="J111" s="118"/>
+      <c r="K111" s="118"/>
+      <c r="L111" s="118"/>
+      <c r="M111" s="118"/>
+      <c r="N111" s="120"/>
+      <c r="O111" s="122"/>
       <c r="P111" s="27"/>
-      <c r="Q111" s="162"/>
-      <c r="R111" s="164"/>
-      <c r="S111" s="168" t="s">
+      <c r="Q111" s="124"/>
+      <c r="R111" s="126"/>
+      <c r="S111" s="143" t="s">
         <v>95</v>
       </c>
-      <c r="T111" s="169"/>
-      <c r="U111" s="170"/>
-      <c r="V111" s="170"/>
-      <c r="W111" s="170"/>
-      <c r="X111" s="170"/>
-      <c r="Y111" s="170"/>
-      <c r="Z111" s="170"/>
-      <c r="AA111" s="170"/>
-      <c r="AB111" s="170"/>
-      <c r="AC111" s="170"/>
-      <c r="AD111" s="170"/>
-      <c r="AE111" s="170"/>
-      <c r="AF111" s="170"/>
-      <c r="AG111" s="170"/>
-      <c r="AH111" s="170"/>
-      <c r="AI111" s="170"/>
-      <c r="AJ111" s="170"/>
-      <c r="AK111" s="171"/>
+      <c r="T111" s="144"/>
+      <c r="U111" s="145"/>
+      <c r="V111" s="145"/>
+      <c r="W111" s="145"/>
+      <c r="X111" s="145"/>
+      <c r="Y111" s="145"/>
+      <c r="Z111" s="145"/>
+      <c r="AA111" s="145"/>
+      <c r="AB111" s="145"/>
+      <c r="AC111" s="145"/>
+      <c r="AD111" s="145"/>
+      <c r="AE111" s="145"/>
+      <c r="AF111" s="145"/>
+      <c r="AG111" s="145"/>
+      <c r="AH111" s="145"/>
+      <c r="AI111" s="145"/>
+      <c r="AJ111" s="145"/>
+      <c r="AK111" s="146"/>
     </row>
     <row r="112" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="94" t="s">
+      <c r="A112" s="92" t="s">
         <v>96</v>
       </c>
-      <c r="B112" s="95"/>
-      <c r="C112" s="95"/>
-      <c r="D112" s="95"/>
-      <c r="E112" s="95"/>
-      <c r="F112" s="95"/>
-      <c r="G112" s="95"/>
-      <c r="H112" s="95"/>
-      <c r="I112" s="95"/>
-      <c r="J112" s="95"/>
-      <c r="K112" s="95"/>
-      <c r="L112" s="95"/>
-      <c r="M112" s="95"/>
-      <c r="N112" s="95"/>
-      <c r="O112" s="95"/>
-      <c r="P112" s="95"/>
-      <c r="Q112" s="95"/>
-      <c r="R112" s="95"/>
-      <c r="S112" s="94" t="s">
+      <c r="B112" s="93"/>
+      <c r="C112" s="93"/>
+      <c r="D112" s="93"/>
+      <c r="E112" s="93"/>
+      <c r="F112" s="93"/>
+      <c r="G112" s="93"/>
+      <c r="H112" s="93"/>
+      <c r="I112" s="93"/>
+      <c r="J112" s="93"/>
+      <c r="K112" s="93"/>
+      <c r="L112" s="93"/>
+      <c r="M112" s="93"/>
+      <c r="N112" s="93"/>
+      <c r="O112" s="93"/>
+      <c r="P112" s="93"/>
+      <c r="Q112" s="93"/>
+      <c r="R112" s="93"/>
+      <c r="S112" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="T112" s="95"/>
-      <c r="U112" s="95"/>
-      <c r="V112" s="95"/>
-      <c r="W112" s="95"/>
-      <c r="X112" s="95"/>
-      <c r="Y112" s="95"/>
-      <c r="Z112" s="95"/>
-      <c r="AA112" s="95"/>
-      <c r="AB112" s="95"/>
-      <c r="AC112" s="95"/>
-      <c r="AD112" s="95"/>
-      <c r="AE112" s="95"/>
-      <c r="AF112" s="95"/>
-      <c r="AG112" s="95"/>
-      <c r="AH112" s="95"/>
-      <c r="AI112" s="95"/>
-      <c r="AJ112" s="95"/>
-      <c r="AK112" s="96"/>
+      <c r="T112" s="93"/>
+      <c r="U112" s="93"/>
+      <c r="V112" s="93"/>
+      <c r="W112" s="93"/>
+      <c r="X112" s="93"/>
+      <c r="Y112" s="93"/>
+      <c r="Z112" s="93"/>
+      <c r="AA112" s="93"/>
+      <c r="AB112" s="93"/>
+      <c r="AC112" s="93"/>
+      <c r="AD112" s="93"/>
+      <c r="AE112" s="93"/>
+      <c r="AF112" s="93"/>
+      <c r="AG112" s="93"/>
+      <c r="AH112" s="93"/>
+      <c r="AI112" s="93"/>
+      <c r="AJ112" s="93"/>
+      <c r="AK112" s="94"/>
     </row>
     <row r="113" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="149" t="s">
+      <c r="A113" s="111" t="s">
         <v>80</v>
       </c>
-      <c r="B113" s="150"/>
-      <c r="C113" s="150"/>
-      <c r="D113" s="150"/>
-      <c r="E113" s="150"/>
-      <c r="F113" s="150"/>
-      <c r="G113" s="150"/>
-      <c r="H113" s="150"/>
-      <c r="I113" s="150"/>
-      <c r="J113" s="150"/>
-      <c r="K113" s="150"/>
-      <c r="L113" s="150"/>
-      <c r="M113" s="151"/>
-      <c r="N113" s="152" t="s">
+      <c r="B113" s="112"/>
+      <c r="C113" s="112"/>
+      <c r="D113" s="112"/>
+      <c r="E113" s="112"/>
+      <c r="F113" s="112"/>
+      <c r="G113" s="112"/>
+      <c r="H113" s="112"/>
+      <c r="I113" s="112"/>
+      <c r="J113" s="112"/>
+      <c r="K113" s="112"/>
+      <c r="L113" s="112"/>
+      <c r="M113" s="113"/>
+      <c r="N113" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="O113" s="153"/>
-      <c r="P113" s="153"/>
-      <c r="Q113" s="153"/>
-      <c r="R113" s="154"/>
-      <c r="S113" s="149" t="s">
+      <c r="O113" s="115"/>
+      <c r="P113" s="115"/>
+      <c r="Q113" s="115"/>
+      <c r="R113" s="116"/>
+      <c r="S113" s="111" t="s">
         <v>98</v>
       </c>
-      <c r="T113" s="150"/>
-      <c r="U113" s="150"/>
-      <c r="V113" s="150"/>
-      <c r="W113" s="150"/>
-      <c r="X113" s="150"/>
-      <c r="Y113" s="150"/>
-      <c r="Z113" s="150"/>
-      <c r="AA113" s="150"/>
-      <c r="AB113" s="150"/>
-      <c r="AC113" s="150"/>
-      <c r="AD113" s="150"/>
-      <c r="AE113" s="151"/>
-      <c r="AF113" s="172" t="s">
+      <c r="T113" s="112"/>
+      <c r="U113" s="112"/>
+      <c r="V113" s="112"/>
+      <c r="W113" s="112"/>
+      <c r="X113" s="112"/>
+      <c r="Y113" s="112"/>
+      <c r="Z113" s="112"/>
+      <c r="AA113" s="112"/>
+      <c r="AB113" s="112"/>
+      <c r="AC113" s="112"/>
+      <c r="AD113" s="112"/>
+      <c r="AE113" s="113"/>
+      <c r="AF113" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="AG113" s="173"/>
-      <c r="AH113" s="173"/>
-      <c r="AI113" s="173"/>
-      <c r="AJ113" s="173"/>
-      <c r="AK113" s="174"/>
+      <c r="AG113" s="109"/>
+      <c r="AH113" s="109"/>
+      <c r="AI113" s="109"/>
+      <c r="AJ113" s="109"/>
+      <c r="AK113" s="110"/>
     </row>
     <row r="114" spans="1:37" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="193" t="s">
+      <c r="A114" s="138" t="s">
         <v>99</v>
       </c>
-      <c r="B114" s="194" t="s">
+      <c r="B114" s="139" t="s">
         <v>100</v>
       </c>
-      <c r="C114" s="194"/>
-      <c r="D114" s="194"/>
-      <c r="E114" s="194"/>
-      <c r="F114" s="194"/>
-      <c r="G114" s="194"/>
-      <c r="H114" s="194"/>
-      <c r="I114" s="194"/>
-      <c r="J114" s="194"/>
-      <c r="K114" s="194"/>
-      <c r="L114" s="194"/>
-      <c r="M114" s="194"/>
+      <c r="C114" s="139"/>
+      <c r="D114" s="139"/>
+      <c r="E114" s="139"/>
+      <c r="F114" s="139"/>
+      <c r="G114" s="139"/>
+      <c r="H114" s="139"/>
+      <c r="I114" s="139"/>
+      <c r="J114" s="139"/>
+      <c r="K114" s="139"/>
+      <c r="L114" s="139"/>
+      <c r="M114" s="139"/>
       <c r="N114" s="28" t="s">
         <v>50</v>
       </c>
@@ -6174,21 +6157,21 @@
         <v>63</v>
       </c>
       <c r="R114" s="82"/>
-      <c r="S114" s="193" t="s">
+      <c r="S114" s="138" t="s">
         <v>101</v>
       </c>
-      <c r="T114" s="194"/>
-      <c r="U114" s="194"/>
-      <c r="V114" s="194"/>
-      <c r="W114" s="194"/>
-      <c r="X114" s="194"/>
-      <c r="Y114" s="194"/>
-      <c r="Z114" s="194"/>
-      <c r="AA114" s="194"/>
-      <c r="AB114" s="194"/>
-      <c r="AC114" s="194"/>
-      <c r="AD114" s="194"/>
-      <c r="AE114" s="194"/>
+      <c r="T114" s="139"/>
+      <c r="U114" s="139"/>
+      <c r="V114" s="139"/>
+      <c r="W114" s="139"/>
+      <c r="X114" s="139"/>
+      <c r="Y114" s="139"/>
+      <c r="Z114" s="139"/>
+      <c r="AA114" s="139"/>
+      <c r="AB114" s="139"/>
+      <c r="AC114" s="139"/>
+      <c r="AD114" s="139"/>
+      <c r="AE114" s="139"/>
       <c r="AF114" s="38" t="s">
         <v>50</v>
       </c>
@@ -6236,23 +6219,23 @@
       <c r="AK115" s="8"/>
     </row>
     <row r="116" spans="1:37" s="2" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="155" t="s">
+      <c r="A116" s="117" t="s">
         <v>102</v>
       </c>
-      <c r="B116" s="156" t="s">
+      <c r="B116" s="118" t="s">
         <v>100</v>
       </c>
-      <c r="C116" s="156"/>
-      <c r="D116" s="156"/>
-      <c r="E116" s="156"/>
-      <c r="F116" s="156"/>
-      <c r="G116" s="156"/>
-      <c r="H116" s="156"/>
-      <c r="I116" s="156"/>
-      <c r="J116" s="156"/>
-      <c r="K116" s="156"/>
-      <c r="L116" s="156"/>
-      <c r="M116" s="156"/>
+      <c r="C116" s="118"/>
+      <c r="D116" s="118"/>
+      <c r="E116" s="118"/>
+      <c r="F116" s="118"/>
+      <c r="G116" s="118"/>
+      <c r="H116" s="118"/>
+      <c r="I116" s="118"/>
+      <c r="J116" s="118"/>
+      <c r="K116" s="118"/>
+      <c r="L116" s="118"/>
+      <c r="M116" s="118"/>
       <c r="N116" s="31" t="s">
         <v>50</v>
       </c>
@@ -6262,21 +6245,21 @@
         <v>63</v>
       </c>
       <c r="R116" s="84"/>
-      <c r="S116" s="155" t="s">
+      <c r="S116" s="117" t="s">
         <v>103</v>
       </c>
-      <c r="T116" s="156"/>
-      <c r="U116" s="156"/>
-      <c r="V116" s="156"/>
-      <c r="W116" s="156"/>
-      <c r="X116" s="156"/>
-      <c r="Y116" s="156"/>
-      <c r="Z116" s="156"/>
-      <c r="AA116" s="156"/>
-      <c r="AB116" s="156"/>
-      <c r="AC116" s="156"/>
-      <c r="AD116" s="156"/>
-      <c r="AE116" s="156"/>
+      <c r="T116" s="118"/>
+      <c r="U116" s="118"/>
+      <c r="V116" s="118"/>
+      <c r="W116" s="118"/>
+      <c r="X116" s="118"/>
+      <c r="Y116" s="118"/>
+      <c r="Z116" s="118"/>
+      <c r="AA116" s="118"/>
+      <c r="AB116" s="118"/>
+      <c r="AC116" s="118"/>
+      <c r="AD116" s="118"/>
+      <c r="AE116" s="118"/>
       <c r="AF116" s="31" t="s">
         <v>50</v>
       </c>
@@ -6289,80 +6272,80 @@
       <c r="AK116" s="10"/>
     </row>
     <row r="117" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="94" t="s">
+      <c r="A117" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="B117" s="95"/>
-      <c r="C117" s="95"/>
-      <c r="D117" s="95"/>
-      <c r="E117" s="95"/>
-      <c r="F117" s="95"/>
-      <c r="G117" s="95"/>
-      <c r="H117" s="95"/>
-      <c r="I117" s="95"/>
-      <c r="J117" s="95"/>
-      <c r="K117" s="95"/>
-      <c r="L117" s="95"/>
-      <c r="M117" s="95"/>
-      <c r="N117" s="95"/>
-      <c r="O117" s="95"/>
-      <c r="P117" s="95"/>
-      <c r="Q117" s="95"/>
-      <c r="R117" s="95"/>
-      <c r="S117" s="95"/>
-      <c r="T117" s="95"/>
-      <c r="U117" s="95"/>
-      <c r="V117" s="95"/>
-      <c r="W117" s="95"/>
-      <c r="X117" s="95"/>
-      <c r="Y117" s="95"/>
-      <c r="Z117" s="95"/>
-      <c r="AA117" s="95"/>
-      <c r="AB117" s="95"/>
-      <c r="AC117" s="95"/>
-      <c r="AD117" s="95"/>
-      <c r="AE117" s="95"/>
-      <c r="AF117" s="95"/>
-      <c r="AG117" s="95"/>
-      <c r="AH117" s="95"/>
-      <c r="AI117" s="95"/>
-      <c r="AJ117" s="95"/>
-      <c r="AK117" s="96"/>
+      <c r="B117" s="93"/>
+      <c r="C117" s="93"/>
+      <c r="D117" s="93"/>
+      <c r="E117" s="93"/>
+      <c r="F117" s="93"/>
+      <c r="G117" s="93"/>
+      <c r="H117" s="93"/>
+      <c r="I117" s="93"/>
+      <c r="J117" s="93"/>
+      <c r="K117" s="93"/>
+      <c r="L117" s="93"/>
+      <c r="M117" s="93"/>
+      <c r="N117" s="93"/>
+      <c r="O117" s="93"/>
+      <c r="P117" s="93"/>
+      <c r="Q117" s="93"/>
+      <c r="R117" s="93"/>
+      <c r="S117" s="93"/>
+      <c r="T117" s="93"/>
+      <c r="U117" s="93"/>
+      <c r="V117" s="93"/>
+      <c r="W117" s="93"/>
+      <c r="X117" s="93"/>
+      <c r="Y117" s="93"/>
+      <c r="Z117" s="93"/>
+      <c r="AA117" s="93"/>
+      <c r="AB117" s="93"/>
+      <c r="AC117" s="93"/>
+      <c r="AD117" s="93"/>
+      <c r="AE117" s="93"/>
+      <c r="AF117" s="93"/>
+      <c r="AG117" s="93"/>
+      <c r="AH117" s="93"/>
+      <c r="AI117" s="93"/>
+      <c r="AJ117" s="93"/>
+      <c r="AK117" s="94"/>
     </row>
     <row r="118" spans="1:37" s="2" customFormat="1" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="179" t="s">
+      <c r="A118" s="136" t="s">
         <v>107</v>
       </c>
-      <c r="B118" s="180"/>
-      <c r="C118" s="180"/>
-      <c r="D118" s="180"/>
-      <c r="E118" s="180"/>
-      <c r="F118" s="180"/>
-      <c r="G118" s="180"/>
-      <c r="H118" s="180"/>
-      <c r="I118" s="180"/>
-      <c r="J118" s="180"/>
-      <c r="K118" s="180"/>
-      <c r="L118" s="180"/>
-      <c r="M118" s="180"/>
-      <c r="N118" s="180"/>
-      <c r="O118" s="180"/>
-      <c r="P118" s="180"/>
-      <c r="Q118" s="180"/>
-      <c r="R118" s="180"/>
-      <c r="S118" s="180"/>
-      <c r="T118" s="180"/>
-      <c r="U118" s="180"/>
-      <c r="V118" s="180"/>
-      <c r="W118" s="180"/>
-      <c r="X118" s="180"/>
-      <c r="Y118" s="180"/>
-      <c r="Z118" s="180"/>
-      <c r="AA118" s="180"/>
-      <c r="AB118" s="180"/>
-      <c r="AC118" s="180"/>
-      <c r="AD118" s="180"/>
-      <c r="AE118" s="180"/>
+      <c r="B118" s="137"/>
+      <c r="C118" s="137"/>
+      <c r="D118" s="137"/>
+      <c r="E118" s="137"/>
+      <c r="F118" s="137"/>
+      <c r="G118" s="137"/>
+      <c r="H118" s="137"/>
+      <c r="I118" s="137"/>
+      <c r="J118" s="137"/>
+      <c r="K118" s="137"/>
+      <c r="L118" s="137"/>
+      <c r="M118" s="137"/>
+      <c r="N118" s="137"/>
+      <c r="O118" s="137"/>
+      <c r="P118" s="137"/>
+      <c r="Q118" s="137"/>
+      <c r="R118" s="137"/>
+      <c r="S118" s="137"/>
+      <c r="T118" s="137"/>
+      <c r="U118" s="137"/>
+      <c r="V118" s="137"/>
+      <c r="W118" s="137"/>
+      <c r="X118" s="137"/>
+      <c r="Y118" s="137"/>
+      <c r="Z118" s="137"/>
+      <c r="AA118" s="137"/>
+      <c r="AB118" s="137"/>
+      <c r="AC118" s="137"/>
+      <c r="AD118" s="137"/>
+      <c r="AE118" s="137"/>
       <c r="AF118" s="31" t="s">
         <v>50</v>
       </c>
@@ -6374,33 +6357,33 @@
       <c r="AJ118" s="78"/>
       <c r="AK118" s="8"/>
     </row>
-    <row r="119" spans="1:37" s="183" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="181" t="s">
+    <row r="119" spans="1:37" s="91" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="B119" s="182"/>
-      <c r="C119" s="182"/>
-      <c r="D119" s="182"/>
-      <c r="E119" s="182"/>
-      <c r="F119" s="182"/>
-      <c r="G119" s="182"/>
-      <c r="H119" s="182"/>
-      <c r="I119" s="182"/>
-      <c r="J119" s="182"/>
-      <c r="K119" s="182"/>
-      <c r="L119" s="182"/>
-      <c r="M119" s="182"/>
-      <c r="N119" s="182"/>
-      <c r="O119" s="182"/>
-      <c r="P119" s="182"/>
-      <c r="Q119" s="182"/>
-      <c r="R119" s="182"/>
-      <c r="S119" s="182"/>
-      <c r="T119" s="182"/>
-      <c r="U119" s="182"/>
-      <c r="V119" s="182"/>
-      <c r="W119" s="182"/>
-      <c r="X119" s="182"/>
+      <c r="B119" s="90"/>
+      <c r="C119" s="90"/>
+      <c r="D119" s="90"/>
+      <c r="E119" s="90"/>
+      <c r="F119" s="90"/>
+      <c r="G119" s="90"/>
+      <c r="H119" s="90"/>
+      <c r="I119" s="90"/>
+      <c r="J119" s="90"/>
+      <c r="K119" s="90"/>
+      <c r="L119" s="90"/>
+      <c r="M119" s="90"/>
+      <c r="N119" s="90"/>
+      <c r="O119" s="90"/>
+      <c r="P119" s="90"/>
+      <c r="Q119" s="90"/>
+      <c r="R119" s="90"/>
+      <c r="S119" s="90"/>
+      <c r="T119" s="90"/>
+      <c r="U119" s="90"/>
+      <c r="V119" s="90"/>
+      <c r="W119" s="90"/>
+      <c r="X119" s="90"/>
     </row>
     <row r="120" spans="1:37" s="2" customFormat="1" ht="3" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="47"/>
@@ -6438,349 +6421,347 @@
       <c r="AK120" s="8"/>
     </row>
     <row r="121" spans="1:37" s="2" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="94" t="s">
+      <c r="A121" s="92" t="s">
         <v>106</v>
       </c>
-      <c r="B121" s="95"/>
-      <c r="C121" s="95"/>
-      <c r="D121" s="95"/>
-      <c r="E121" s="95"/>
-      <c r="F121" s="95"/>
-      <c r="G121" s="95"/>
-      <c r="H121" s="95"/>
-      <c r="I121" s="95"/>
-      <c r="J121" s="95"/>
-      <c r="K121" s="95"/>
-      <c r="L121" s="95"/>
-      <c r="M121" s="95"/>
-      <c r="N121" s="95"/>
-      <c r="O121" s="95"/>
-      <c r="P121" s="95"/>
-      <c r="Q121" s="95"/>
-      <c r="R121" s="95"/>
-      <c r="S121" s="95"/>
-      <c r="T121" s="95"/>
-      <c r="U121" s="95"/>
-      <c r="V121" s="95"/>
-      <c r="W121" s="95"/>
-      <c r="X121" s="95"/>
-      <c r="Y121" s="95"/>
-      <c r="Z121" s="95"/>
-      <c r="AA121" s="95"/>
-      <c r="AB121" s="95"/>
-      <c r="AC121" s="95"/>
-      <c r="AD121" s="95"/>
-      <c r="AE121" s="95"/>
-      <c r="AF121" s="95"/>
-      <c r="AG121" s="95"/>
-      <c r="AH121" s="95"/>
-      <c r="AI121" s="95"/>
-      <c r="AJ121" s="95"/>
-      <c r="AK121" s="96"/>
+      <c r="B121" s="93"/>
+      <c r="C121" s="93"/>
+      <c r="D121" s="93"/>
+      <c r="E121" s="93"/>
+      <c r="F121" s="93"/>
+      <c r="G121" s="93"/>
+      <c r="H121" s="93"/>
+      <c r="I121" s="93"/>
+      <c r="J121" s="93"/>
+      <c r="K121" s="93"/>
+      <c r="L121" s="93"/>
+      <c r="M121" s="93"/>
+      <c r="N121" s="93"/>
+      <c r="O121" s="93"/>
+      <c r="P121" s="93"/>
+      <c r="Q121" s="93"/>
+      <c r="R121" s="93"/>
+      <c r="S121" s="93"/>
+      <c r="T121" s="93"/>
+      <c r="U121" s="93"/>
+      <c r="V121" s="93"/>
+      <c r="W121" s="93"/>
+      <c r="X121" s="93"/>
+      <c r="Y121" s="93"/>
+      <c r="Z121" s="93"/>
+      <c r="AA121" s="93"/>
+      <c r="AB121" s="93"/>
+      <c r="AC121" s="93"/>
+      <c r="AD121" s="93"/>
+      <c r="AE121" s="93"/>
+      <c r="AF121" s="93"/>
+      <c r="AG121" s="93"/>
+      <c r="AH121" s="93"/>
+      <c r="AI121" s="93"/>
+      <c r="AJ121" s="93"/>
+      <c r="AK121" s="94"/>
     </row>
     <row r="122" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="184"/>
-      <c r="B122" s="185"/>
-      <c r="C122" s="185"/>
-      <c r="D122" s="185"/>
-      <c r="E122" s="185"/>
-      <c r="F122" s="185"/>
-      <c r="G122" s="185"/>
-      <c r="H122" s="185"/>
-      <c r="I122" s="185"/>
-      <c r="J122" s="185"/>
-      <c r="K122" s="185"/>
-      <c r="L122" s="185"/>
-      <c r="M122" s="185"/>
-      <c r="N122" s="185"/>
-      <c r="O122" s="185"/>
-      <c r="P122" s="185"/>
-      <c r="Q122" s="185"/>
-      <c r="R122" s="185"/>
-      <c r="S122" s="185"/>
-      <c r="T122" s="185"/>
-      <c r="U122" s="185"/>
-      <c r="V122" s="185"/>
-      <c r="W122" s="185"/>
-      <c r="X122" s="185"/>
-      <c r="Y122" s="185"/>
-      <c r="Z122" s="185"/>
-      <c r="AA122" s="185"/>
-      <c r="AB122" s="185"/>
-      <c r="AC122" s="185"/>
-      <c r="AD122" s="185"/>
-      <c r="AE122" s="185"/>
-      <c r="AF122" s="185"/>
-      <c r="AG122" s="185"/>
-      <c r="AH122" s="185"/>
-      <c r="AI122" s="185"/>
-      <c r="AJ122" s="185"/>
-      <c r="AK122" s="186"/>
+      <c r="A122" s="95"/>
+      <c r="B122" s="96"/>
+      <c r="C122" s="96"/>
+      <c r="D122" s="96"/>
+      <c r="E122" s="96"/>
+      <c r="F122" s="96"/>
+      <c r="G122" s="96"/>
+      <c r="H122" s="96"/>
+      <c r="I122" s="96"/>
+      <c r="J122" s="96"/>
+      <c r="K122" s="96"/>
+      <c r="L122" s="96"/>
+      <c r="M122" s="96"/>
+      <c r="N122" s="96"/>
+      <c r="O122" s="96"/>
+      <c r="P122" s="96"/>
+      <c r="Q122" s="96"/>
+      <c r="R122" s="96"/>
+      <c r="S122" s="96"/>
+      <c r="T122" s="96"/>
+      <c r="U122" s="96"/>
+      <c r="V122" s="96"/>
+      <c r="W122" s="96"/>
+      <c r="X122" s="96"/>
+      <c r="Y122" s="96"/>
+      <c r="Z122" s="96"/>
+      <c r="AA122" s="96"/>
+      <c r="AB122" s="96"/>
+      <c r="AC122" s="96"/>
+      <c r="AD122" s="96"/>
+      <c r="AE122" s="96"/>
+      <c r="AF122" s="96"/>
+      <c r="AG122" s="96"/>
+      <c r="AH122" s="96"/>
+      <c r="AI122" s="96"/>
+      <c r="AJ122" s="96"/>
+      <c r="AK122" s="97"/>
     </row>
     <row r="123" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="187"/>
-      <c r="B123" s="188"/>
-      <c r="C123" s="188"/>
-      <c r="D123" s="188"/>
-      <c r="E123" s="188"/>
-      <c r="F123" s="188"/>
-      <c r="G123" s="188"/>
-      <c r="H123" s="188"/>
-      <c r="I123" s="188"/>
-      <c r="J123" s="188"/>
-      <c r="K123" s="188"/>
-      <c r="L123" s="188"/>
-      <c r="M123" s="188"/>
-      <c r="N123" s="188"/>
-      <c r="O123" s="188"/>
-      <c r="P123" s="188"/>
-      <c r="Q123" s="188"/>
-      <c r="R123" s="188"/>
-      <c r="S123" s="188"/>
-      <c r="T123" s="188"/>
-      <c r="U123" s="188"/>
-      <c r="V123" s="188"/>
-      <c r="W123" s="188"/>
-      <c r="X123" s="188"/>
-      <c r="Y123" s="188"/>
-      <c r="Z123" s="188"/>
-      <c r="AA123" s="188"/>
-      <c r="AB123" s="188"/>
-      <c r="AC123" s="188"/>
-      <c r="AD123" s="188"/>
-      <c r="AE123" s="188"/>
-      <c r="AF123" s="188"/>
-      <c r="AG123" s="188"/>
-      <c r="AH123" s="188"/>
-      <c r="AI123" s="188"/>
-      <c r="AJ123" s="188"/>
-      <c r="AK123" s="189"/>
+      <c r="A123" s="98"/>
+      <c r="B123" s="99"/>
+      <c r="C123" s="99"/>
+      <c r="D123" s="99"/>
+      <c r="E123" s="99"/>
+      <c r="F123" s="99"/>
+      <c r="G123" s="99"/>
+      <c r="H123" s="99"/>
+      <c r="I123" s="99"/>
+      <c r="J123" s="99"/>
+      <c r="K123" s="99"/>
+      <c r="L123" s="99"/>
+      <c r="M123" s="99"/>
+      <c r="N123" s="99"/>
+      <c r="O123" s="99"/>
+      <c r="P123" s="99"/>
+      <c r="Q123" s="99"/>
+      <c r="R123" s="99"/>
+      <c r="S123" s="99"/>
+      <c r="T123" s="99"/>
+      <c r="U123" s="99"/>
+      <c r="V123" s="99"/>
+      <c r="W123" s="99"/>
+      <c r="X123" s="99"/>
+      <c r="Y123" s="99"/>
+      <c r="Z123" s="99"/>
+      <c r="AA123" s="99"/>
+      <c r="AB123" s="99"/>
+      <c r="AC123" s="99"/>
+      <c r="AD123" s="99"/>
+      <c r="AE123" s="99"/>
+      <c r="AF123" s="99"/>
+      <c r="AG123" s="99"/>
+      <c r="AH123" s="99"/>
+      <c r="AI123" s="99"/>
+      <c r="AJ123" s="99"/>
+      <c r="AK123" s="100"/>
     </row>
     <row r="124" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="187"/>
-      <c r="B124" s="188"/>
-      <c r="C124" s="188"/>
-      <c r="D124" s="188"/>
-      <c r="E124" s="188"/>
-      <c r="F124" s="188"/>
-      <c r="G124" s="188"/>
-      <c r="H124" s="188"/>
-      <c r="I124" s="188"/>
-      <c r="J124" s="188"/>
-      <c r="K124" s="188"/>
-      <c r="L124" s="188"/>
-      <c r="M124" s="188"/>
-      <c r="N124" s="188"/>
-      <c r="O124" s="188"/>
-      <c r="P124" s="188"/>
-      <c r="Q124" s="188"/>
-      <c r="R124" s="188"/>
-      <c r="S124" s="188"/>
-      <c r="T124" s="188"/>
-      <c r="U124" s="188"/>
-      <c r="V124" s="188"/>
-      <c r="W124" s="188"/>
-      <c r="X124" s="188"/>
-      <c r="Y124" s="188"/>
-      <c r="Z124" s="188"/>
-      <c r="AA124" s="188"/>
-      <c r="AB124" s="188"/>
-      <c r="AC124" s="188"/>
-      <c r="AD124" s="188"/>
-      <c r="AE124" s="188"/>
-      <c r="AF124" s="188"/>
-      <c r="AG124" s="188"/>
-      <c r="AH124" s="188"/>
-      <c r="AI124" s="188"/>
-      <c r="AJ124" s="188"/>
-      <c r="AK124" s="189"/>
+      <c r="A124" s="98"/>
+      <c r="B124" s="99"/>
+      <c r="C124" s="99"/>
+      <c r="D124" s="99"/>
+      <c r="E124" s="99"/>
+      <c r="F124" s="99"/>
+      <c r="G124" s="99"/>
+      <c r="H124" s="99"/>
+      <c r="I124" s="99"/>
+      <c r="J124" s="99"/>
+      <c r="K124" s="99"/>
+      <c r="L124" s="99"/>
+      <c r="M124" s="99"/>
+      <c r="N124" s="99"/>
+      <c r="O124" s="99"/>
+      <c r="P124" s="99"/>
+      <c r="Q124" s="99"/>
+      <c r="R124" s="99"/>
+      <c r="S124" s="99"/>
+      <c r="T124" s="99"/>
+      <c r="U124" s="99"/>
+      <c r="V124" s="99"/>
+      <c r="W124" s="99"/>
+      <c r="X124" s="99"/>
+      <c r="Y124" s="99"/>
+      <c r="Z124" s="99"/>
+      <c r="AA124" s="99"/>
+      <c r="AB124" s="99"/>
+      <c r="AC124" s="99"/>
+      <c r="AD124" s="99"/>
+      <c r="AE124" s="99"/>
+      <c r="AF124" s="99"/>
+      <c r="AG124" s="99"/>
+      <c r="AH124" s="99"/>
+      <c r="AI124" s="99"/>
+      <c r="AJ124" s="99"/>
+      <c r="AK124" s="100"/>
     </row>
     <row r="125" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="187"/>
-      <c r="B125" s="188"/>
-      <c r="C125" s="188"/>
-      <c r="D125" s="188"/>
-      <c r="E125" s="188"/>
-      <c r="F125" s="188"/>
-      <c r="G125" s="188"/>
-      <c r="H125" s="188"/>
-      <c r="I125" s="188"/>
-      <c r="J125" s="188"/>
-      <c r="K125" s="188"/>
-      <c r="L125" s="188"/>
-      <c r="M125" s="188"/>
-      <c r="N125" s="188"/>
-      <c r="O125" s="188"/>
-      <c r="P125" s="188"/>
-      <c r="Q125" s="188"/>
-      <c r="R125" s="188"/>
-      <c r="S125" s="188"/>
-      <c r="T125" s="188"/>
-      <c r="U125" s="188"/>
-      <c r="V125" s="188"/>
-      <c r="W125" s="188"/>
-      <c r="X125" s="188"/>
-      <c r="Y125" s="188"/>
-      <c r="Z125" s="188"/>
-      <c r="AA125" s="188"/>
-      <c r="AB125" s="188"/>
-      <c r="AC125" s="188"/>
-      <c r="AD125" s="188"/>
-      <c r="AE125" s="188"/>
-      <c r="AF125" s="188"/>
-      <c r="AG125" s="188"/>
-      <c r="AH125" s="188"/>
-      <c r="AI125" s="188"/>
-      <c r="AJ125" s="188"/>
-      <c r="AK125" s="189"/>
+      <c r="A125" s="98"/>
+      <c r="B125" s="99"/>
+      <c r="C125" s="99"/>
+      <c r="D125" s="99"/>
+      <c r="E125" s="99"/>
+      <c r="F125" s="99"/>
+      <c r="G125" s="99"/>
+      <c r="H125" s="99"/>
+      <c r="I125" s="99"/>
+      <c r="J125" s="99"/>
+      <c r="K125" s="99"/>
+      <c r="L125" s="99"/>
+      <c r="M125" s="99"/>
+      <c r="N125" s="99"/>
+      <c r="O125" s="99"/>
+      <c r="P125" s="99"/>
+      <c r="Q125" s="99"/>
+      <c r="R125" s="99"/>
+      <c r="S125" s="99"/>
+      <c r="T125" s="99"/>
+      <c r="U125" s="99"/>
+      <c r="V125" s="99"/>
+      <c r="W125" s="99"/>
+      <c r="X125" s="99"/>
+      <c r="Y125" s="99"/>
+      <c r="Z125" s="99"/>
+      <c r="AA125" s="99"/>
+      <c r="AB125" s="99"/>
+      <c r="AC125" s="99"/>
+      <c r="AD125" s="99"/>
+      <c r="AE125" s="99"/>
+      <c r="AF125" s="99"/>
+      <c r="AG125" s="99"/>
+      <c r="AH125" s="99"/>
+      <c r="AI125" s="99"/>
+      <c r="AJ125" s="99"/>
+      <c r="AK125" s="100"/>
     </row>
     <row r="126" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="187"/>
-      <c r="B126" s="188"/>
-      <c r="C126" s="188"/>
-      <c r="D126" s="188"/>
-      <c r="E126" s="188"/>
-      <c r="F126" s="188"/>
-      <c r="G126" s="188"/>
-      <c r="H126" s="188"/>
-      <c r="I126" s="188"/>
-      <c r="J126" s="188"/>
-      <c r="K126" s="188"/>
-      <c r="L126" s="188"/>
-      <c r="M126" s="188"/>
-      <c r="N126" s="188"/>
-      <c r="O126" s="188"/>
-      <c r="P126" s="188"/>
-      <c r="Q126" s="188"/>
-      <c r="R126" s="188"/>
-      <c r="S126" s="188"/>
-      <c r="T126" s="188"/>
-      <c r="U126" s="188"/>
-      <c r="V126" s="188"/>
-      <c r="W126" s="188"/>
-      <c r="X126" s="188"/>
-      <c r="Y126" s="188"/>
-      <c r="Z126" s="188"/>
-      <c r="AA126" s="188"/>
-      <c r="AB126" s="188"/>
-      <c r="AC126" s="188"/>
-      <c r="AD126" s="188"/>
-      <c r="AE126" s="188"/>
-      <c r="AF126" s="188"/>
-      <c r="AG126" s="188"/>
-      <c r="AH126" s="188"/>
-      <c r="AI126" s="188"/>
-      <c r="AJ126" s="188"/>
-      <c r="AK126" s="189"/>
+      <c r="A126" s="98"/>
+      <c r="B126" s="99"/>
+      <c r="C126" s="99"/>
+      <c r="D126" s="99"/>
+      <c r="E126" s="99"/>
+      <c r="F126" s="99"/>
+      <c r="G126" s="99"/>
+      <c r="H126" s="99"/>
+      <c r="I126" s="99"/>
+      <c r="J126" s="99"/>
+      <c r="K126" s="99"/>
+      <c r="L126" s="99"/>
+      <c r="M126" s="99"/>
+      <c r="N126" s="99"/>
+      <c r="O126" s="99"/>
+      <c r="P126" s="99"/>
+      <c r="Q126" s="99"/>
+      <c r="R126" s="99"/>
+      <c r="S126" s="99"/>
+      <c r="T126" s="99"/>
+      <c r="U126" s="99"/>
+      <c r="V126" s="99"/>
+      <c r="W126" s="99"/>
+      <c r="X126" s="99"/>
+      <c r="Y126" s="99"/>
+      <c r="Z126" s="99"/>
+      <c r="AA126" s="99"/>
+      <c r="AB126" s="99"/>
+      <c r="AC126" s="99"/>
+      <c r="AD126" s="99"/>
+      <c r="AE126" s="99"/>
+      <c r="AF126" s="99"/>
+      <c r="AG126" s="99"/>
+      <c r="AH126" s="99"/>
+      <c r="AI126" s="99"/>
+      <c r="AJ126" s="99"/>
+      <c r="AK126" s="100"/>
     </row>
     <row r="127" spans="1:37" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="190"/>
-      <c r="B127" s="191"/>
-      <c r="C127" s="191"/>
-      <c r="D127" s="191"/>
-      <c r="E127" s="191"/>
-      <c r="F127" s="191"/>
-      <c r="G127" s="191"/>
-      <c r="H127" s="191"/>
-      <c r="I127" s="191"/>
-      <c r="J127" s="191"/>
-      <c r="K127" s="191"/>
-      <c r="L127" s="191"/>
-      <c r="M127" s="191"/>
-      <c r="N127" s="191"/>
-      <c r="O127" s="191"/>
-      <c r="P127" s="191"/>
-      <c r="Q127" s="191"/>
-      <c r="R127" s="191"/>
-      <c r="S127" s="191"/>
-      <c r="T127" s="191"/>
-      <c r="U127" s="191"/>
-      <c r="V127" s="191"/>
-      <c r="W127" s="191"/>
-      <c r="X127" s="191"/>
-      <c r="Y127" s="191"/>
-      <c r="Z127" s="191"/>
-      <c r="AA127" s="191"/>
-      <c r="AB127" s="191"/>
-      <c r="AC127" s="191"/>
-      <c r="AD127" s="191"/>
-      <c r="AE127" s="191"/>
-      <c r="AF127" s="191"/>
-      <c r="AG127" s="191"/>
-      <c r="AH127" s="191"/>
-      <c r="AI127" s="191"/>
-      <c r="AJ127" s="191"/>
-      <c r="AK127" s="192"/>
+      <c r="A127" s="101"/>
+      <c r="B127" s="102"/>
+      <c r="C127" s="102"/>
+      <c r="D127" s="102"/>
+      <c r="E127" s="102"/>
+      <c r="F127" s="102"/>
+      <c r="G127" s="102"/>
+      <c r="H127" s="102"/>
+      <c r="I127" s="102"/>
+      <c r="J127" s="102"/>
+      <c r="K127" s="102"/>
+      <c r="L127" s="102"/>
+      <c r="M127" s="102"/>
+      <c r="N127" s="102"/>
+      <c r="O127" s="102"/>
+      <c r="P127" s="102"/>
+      <c r="Q127" s="102"/>
+      <c r="R127" s="102"/>
+      <c r="S127" s="102"/>
+      <c r="T127" s="102"/>
+      <c r="U127" s="102"/>
+      <c r="V127" s="102"/>
+      <c r="W127" s="102"/>
+      <c r="X127" s="102"/>
+      <c r="Y127" s="102"/>
+      <c r="Z127" s="102"/>
+      <c r="AA127" s="102"/>
+      <c r="AB127" s="102"/>
+      <c r="AC127" s="102"/>
+      <c r="AD127" s="102"/>
+      <c r="AE127" s="102"/>
+      <c r="AF127" s="102"/>
+      <c r="AG127" s="102"/>
+      <c r="AH127" s="102"/>
+      <c r="AI127" s="102"/>
+      <c r="AJ127" s="102"/>
+      <c r="AK127" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="157">
-    <mergeCell ref="E33:M33"/>
-    <mergeCell ref="R59:W59"/>
-    <mergeCell ref="A117:AK117"/>
-    <mergeCell ref="A118:AE118"/>
-    <mergeCell ref="A119:X119"/>
-    <mergeCell ref="Y119:XFD119"/>
-    <mergeCell ref="A121:AK121"/>
-    <mergeCell ref="A122:AK127"/>
-    <mergeCell ref="G18:R18"/>
+    <mergeCell ref="AC53:AI53"/>
+    <mergeCell ref="AC55:AI55"/>
+    <mergeCell ref="P33:AH33"/>
+    <mergeCell ref="B2:M3"/>
+    <mergeCell ref="P1:AJ2"/>
+    <mergeCell ref="P3:AJ4"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="A6:AK6"/>
+    <mergeCell ref="A47:AK47"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D35:L35"/>
+    <mergeCell ref="N35:R35"/>
+    <mergeCell ref="T35:X35"/>
+    <mergeCell ref="AA35:AC35"/>
+    <mergeCell ref="AD35:AE35"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="AB41:AF41"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="V45:Z45"/>
+    <mergeCell ref="P10:AI10"/>
+    <mergeCell ref="Q12:AD12"/>
+    <mergeCell ref="F8:O8"/>
+    <mergeCell ref="G23:AI23"/>
+    <mergeCell ref="B25:AI25"/>
     <mergeCell ref="H16:Y16"/>
-    <mergeCell ref="A114:M114"/>
-    <mergeCell ref="S114:AE114"/>
-    <mergeCell ref="A116:M116"/>
-    <mergeCell ref="S116:AE116"/>
-    <mergeCell ref="A104:M104"/>
-    <mergeCell ref="S104:AE104"/>
-    <mergeCell ref="A106:M106"/>
-    <mergeCell ref="S106:AE106"/>
-    <mergeCell ref="A108:M108"/>
-    <mergeCell ref="S108:AE108"/>
-    <mergeCell ref="A98:M98"/>
-    <mergeCell ref="S98:AE98"/>
-    <mergeCell ref="A100:M100"/>
-    <mergeCell ref="S100:AE100"/>
-    <mergeCell ref="S101:T101"/>
-    <mergeCell ref="A102:M102"/>
-    <mergeCell ref="S102:AE102"/>
-    <mergeCell ref="A92:M92"/>
-    <mergeCell ref="A96:R96"/>
-    <mergeCell ref="A97:M97"/>
-    <mergeCell ref="N97:R97"/>
-    <mergeCell ref="S97:AE97"/>
-    <mergeCell ref="A86:M86"/>
-    <mergeCell ref="A88:M88"/>
-    <mergeCell ref="A90:M90"/>
-    <mergeCell ref="S96:AK96"/>
-    <mergeCell ref="AF97:AK97"/>
-    <mergeCell ref="A94:AK94"/>
-    <mergeCell ref="A112:R112"/>
-    <mergeCell ref="A113:M113"/>
-    <mergeCell ref="N113:R113"/>
-    <mergeCell ref="S113:AE113"/>
-    <mergeCell ref="A110:M111"/>
-    <mergeCell ref="N110:N111"/>
-    <mergeCell ref="O110:O111"/>
-    <mergeCell ref="Q110:Q111"/>
-    <mergeCell ref="R110:R111"/>
-    <mergeCell ref="S110:AE110"/>
-    <mergeCell ref="S111:T111"/>
-    <mergeCell ref="U111:AK111"/>
-    <mergeCell ref="S112:AK112"/>
-    <mergeCell ref="AF113:AK113"/>
-    <mergeCell ref="A80:M80"/>
-    <mergeCell ref="S80:AE80"/>
-    <mergeCell ref="A82:M82"/>
-    <mergeCell ref="A84:M84"/>
-    <mergeCell ref="A74:M74"/>
-    <mergeCell ref="S74:AE74"/>
-    <mergeCell ref="A76:M76"/>
-    <mergeCell ref="S76:AE76"/>
-    <mergeCell ref="A78:M78"/>
-    <mergeCell ref="S78:AE78"/>
-    <mergeCell ref="A71:R71"/>
-    <mergeCell ref="S71:AJ71"/>
-    <mergeCell ref="A72:M72"/>
-    <mergeCell ref="N72:R72"/>
-    <mergeCell ref="S72:AE72"/>
+    <mergeCell ref="B27:AI27"/>
+    <mergeCell ref="Q29:AI29"/>
+    <mergeCell ref="A21:AK21"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="H49:T49"/>
+    <mergeCell ref="V49:AB49"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="H51:T51"/>
+    <mergeCell ref="V51:AB51"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="M14:AI14"/>
+    <mergeCell ref="AG12:AI12"/>
+    <mergeCell ref="X18:AI18"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="T37:Y37"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="B31:AI31"/>
+    <mergeCell ref="O39:AI39"/>
+    <mergeCell ref="G43:AI43"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="AA45:AI45"/>
+    <mergeCell ref="AC49:AI49"/>
+    <mergeCell ref="AC51:AI51"/>
+    <mergeCell ref="Q62:U62"/>
+    <mergeCell ref="V62:AB62"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="H57:T57"/>
+    <mergeCell ref="V57:AB57"/>
+    <mergeCell ref="A59:N59"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="H53:T53"/>
+    <mergeCell ref="V53:AB53"/>
+    <mergeCell ref="Y59:AB59"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="H55:T55"/>
+    <mergeCell ref="V55:AB55"/>
     <mergeCell ref="A67:G67"/>
     <mergeCell ref="N67:P67"/>
     <mergeCell ref="Q67:U67"/>
@@ -6788,6 +6769,7 @@
     <mergeCell ref="H67:L67"/>
     <mergeCell ref="AC67:AI67"/>
     <mergeCell ref="A69:AK69"/>
+    <mergeCell ref="AF72:AK72"/>
     <mergeCell ref="AC57:AI57"/>
     <mergeCell ref="AC59:AI59"/>
     <mergeCell ref="AC62:AI62"/>
@@ -6804,73 +6786,74 @@
     <mergeCell ref="AC65:AI65"/>
     <mergeCell ref="A62:G62"/>
     <mergeCell ref="N62:P62"/>
-    <mergeCell ref="Q62:U62"/>
-    <mergeCell ref="V62:AB62"/>
-    <mergeCell ref="A57:G57"/>
-    <mergeCell ref="H57:T57"/>
-    <mergeCell ref="V57:AB57"/>
-    <mergeCell ref="A59:N59"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="A53:G53"/>
-    <mergeCell ref="H53:T53"/>
-    <mergeCell ref="V53:AB53"/>
-    <mergeCell ref="Y59:AB59"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="H55:T55"/>
-    <mergeCell ref="V55:AB55"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="H49:T49"/>
-    <mergeCell ref="V49:AB49"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="H51:T51"/>
-    <mergeCell ref="V51:AB51"/>
+    <mergeCell ref="A100:M100"/>
+    <mergeCell ref="S100:AE100"/>
+    <mergeCell ref="S101:T101"/>
+    <mergeCell ref="A102:M102"/>
+    <mergeCell ref="S102:AE102"/>
+    <mergeCell ref="A92:M92"/>
+    <mergeCell ref="A71:R71"/>
+    <mergeCell ref="S71:AJ71"/>
+    <mergeCell ref="A72:M72"/>
+    <mergeCell ref="N72:R72"/>
+    <mergeCell ref="S72:AE72"/>
+    <mergeCell ref="S74:AE74"/>
+    <mergeCell ref="A76:M76"/>
+    <mergeCell ref="S76:AE76"/>
+    <mergeCell ref="A78:M78"/>
+    <mergeCell ref="S78:AE78"/>
     <mergeCell ref="S84:AK92"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="M14:AI14"/>
-    <mergeCell ref="AG12:AI12"/>
-    <mergeCell ref="X18:AI18"/>
-    <mergeCell ref="P10:AI10"/>
-    <mergeCell ref="Q12:AD12"/>
-    <mergeCell ref="F8:O8"/>
-    <mergeCell ref="G23:AI23"/>
-    <mergeCell ref="B25:AI25"/>
-    <mergeCell ref="B27:AI27"/>
-    <mergeCell ref="Q29:AI29"/>
-    <mergeCell ref="A21:AK21"/>
-    <mergeCell ref="O37:Q37"/>
-    <mergeCell ref="T37:Y37"/>
-    <mergeCell ref="A39:N39"/>
-    <mergeCell ref="B31:AI31"/>
-    <mergeCell ref="O39:AI39"/>
-    <mergeCell ref="G43:AI43"/>
-    <mergeCell ref="AA45:AI45"/>
-    <mergeCell ref="AC49:AI49"/>
-    <mergeCell ref="AC51:AI51"/>
-    <mergeCell ref="AC53:AI53"/>
-    <mergeCell ref="AC55:AI55"/>
-    <mergeCell ref="P33:AH33"/>
-    <mergeCell ref="B2:M3"/>
-    <mergeCell ref="P1:AJ2"/>
-    <mergeCell ref="P3:AJ4"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="A6:AK6"/>
     <mergeCell ref="S82:AK82"/>
-    <mergeCell ref="AF72:AK72"/>
-    <mergeCell ref="A47:AK47"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="D35:L35"/>
-    <mergeCell ref="N35:R35"/>
-    <mergeCell ref="T35:X35"/>
-    <mergeCell ref="AA35:AC35"/>
-    <mergeCell ref="AD35:AE35"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="AB41:AF41"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="V45:Z45"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="A98:M98"/>
+    <mergeCell ref="S98:AE98"/>
+    <mergeCell ref="A86:M86"/>
+    <mergeCell ref="E33:M33"/>
+    <mergeCell ref="R59:W59"/>
+    <mergeCell ref="A117:AK117"/>
+    <mergeCell ref="A118:AE118"/>
+    <mergeCell ref="A114:M114"/>
+    <mergeCell ref="S114:AE114"/>
+    <mergeCell ref="A116:M116"/>
+    <mergeCell ref="S116:AE116"/>
+    <mergeCell ref="A104:M104"/>
+    <mergeCell ref="S104:AE104"/>
+    <mergeCell ref="A106:M106"/>
+    <mergeCell ref="S106:AE106"/>
+    <mergeCell ref="A108:M108"/>
+    <mergeCell ref="S108:AE108"/>
+    <mergeCell ref="S111:T111"/>
+    <mergeCell ref="U111:AK111"/>
+    <mergeCell ref="S112:AK112"/>
+    <mergeCell ref="AF113:AK113"/>
+    <mergeCell ref="A80:M80"/>
+    <mergeCell ref="S80:AE80"/>
+    <mergeCell ref="A82:M82"/>
+    <mergeCell ref="A84:M84"/>
+    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="A119:X119"/>
+    <mergeCell ref="Y119:XFD119"/>
+    <mergeCell ref="A121:AK121"/>
+    <mergeCell ref="A122:AK127"/>
+    <mergeCell ref="G18:R18"/>
+    <mergeCell ref="A88:M88"/>
+    <mergeCell ref="A90:M90"/>
+    <mergeCell ref="S96:AK96"/>
+    <mergeCell ref="AF97:AK97"/>
+    <mergeCell ref="A94:AK94"/>
+    <mergeCell ref="A112:R112"/>
+    <mergeCell ref="A113:M113"/>
+    <mergeCell ref="N113:R113"/>
+    <mergeCell ref="S113:AE113"/>
+    <mergeCell ref="A110:M111"/>
+    <mergeCell ref="N110:N111"/>
+    <mergeCell ref="O110:O111"/>
+    <mergeCell ref="Q110:Q111"/>
+    <mergeCell ref="R110:R111"/>
+    <mergeCell ref="S110:AE110"/>
+    <mergeCell ref="A96:R96"/>
+    <mergeCell ref="A97:M97"/>
+    <mergeCell ref="N97:R97"/>
+    <mergeCell ref="S97:AE97"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
